--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9201937-15A1-425D-9C0E-3E5F09926F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5C4E8F-69C1-4657-A2F1-BB1DBDD5C20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="26">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,6 +79,9 @@
     <t>B</t>
   </si>
   <si>
+    <t>15/7/2025</t>
+  </si>
+  <si>
     <t>14/7/2025</t>
   </si>
   <si>
@@ -88,7 +91,22 @@
     <t>10/3/2023</t>
   </si>
   <si>
-    <t>16/7/2025</t>
+    <t>17/7/2025</t>
+  </si>
+  <si>
+    <t>16/07/2025</t>
+  </si>
+  <si>
+    <t>17/07/2025</t>
+  </si>
+  <si>
+    <t>15/07/2025</t>
+  </si>
+  <si>
+    <t>13/06/2025</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
   </si>
 </sst>
 </file>
@@ -506,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O118"/>
+  <dimension ref="A1:O222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -576,7 +594,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>133350787</v>
+        <v>132693991</v>
       </c>
       <c r="E2" s="5">
         <v>601</v>
@@ -591,7 +609,7 @@
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -607,7 +625,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>133406023</v>
+        <v>132699553</v>
       </c>
       <c r="E3" s="5">
         <v>601</v>
@@ -638,22 +656,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>133407539</v>
+        <v>133406721</v>
       </c>
       <c r="E4" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -669,22 +687,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>133407543</v>
+        <v>133422077</v>
       </c>
       <c r="E5" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -700,22 +718,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>133407957</v>
+        <v>123058958</v>
       </c>
       <c r="E6" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -731,22 +749,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>133408938</v>
+        <v>129851803</v>
       </c>
       <c r="E7" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -762,22 +780,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>133408943</v>
+        <v>132070807</v>
       </c>
       <c r="E8" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -793,22 +811,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>133409738</v>
+        <v>132958526</v>
       </c>
       <c r="E9" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -824,22 +842,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>133409979</v>
+        <v>133386528</v>
       </c>
       <c r="E10" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -855,22 +873,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>133410781</v>
+        <v>129851803</v>
       </c>
       <c r="E11" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -886,22 +904,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133412251</v>
+        <v>132958526</v>
       </c>
       <c r="E12" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -917,22 +935,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>133417874</v>
+        <v>133386528</v>
       </c>
       <c r="E13" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -948,22 +966,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>133418333</v>
+        <v>133478780</v>
       </c>
       <c r="E14" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -979,22 +997,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>133419532</v>
+        <v>133479015</v>
       </c>
       <c r="E15" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1010,22 +1028,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>133419985</v>
+        <v>133480611</v>
       </c>
       <c r="E16" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>1117</v>
+        <v>718</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1041,22 +1059,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>133420440</v>
+        <v>133483501</v>
       </c>
       <c r="E17" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>1118</v>
+        <v>718</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1072,22 +1090,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>133420501</v>
+        <v>133483548</v>
       </c>
       <c r="E18" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1103,22 +1121,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>133420741</v>
+        <v>133483809</v>
       </c>
       <c r="E19" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1134,22 +1152,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>133420947</v>
+        <v>133484318</v>
       </c>
       <c r="E20" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>1117</v>
+        <v>718</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1165,22 +1183,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>133421459</v>
+        <v>133489992</v>
       </c>
       <c r="E21" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1196,22 +1214,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>133422550</v>
+        <v>133490948</v>
       </c>
       <c r="E22" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>1118</v>
+        <v>718</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1227,22 +1245,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>133422562</v>
+        <v>133491182</v>
       </c>
       <c r="E23" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1258,22 +1276,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>133423597</v>
+        <v>133491478</v>
       </c>
       <c r="E24" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>1118</v>
+        <v>718</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1289,22 +1307,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>133424284</v>
+        <v>133491660</v>
       </c>
       <c r="E25" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
       </c>
       <c r="J25" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -1320,22 +1338,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>133424526</v>
+        <v>128926213</v>
       </c>
       <c r="E26" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>1118</v>
+        <v>715</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1351,22 +1369,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>133424728</v>
+        <v>129137503</v>
       </c>
       <c r="E27" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>8013</v>
+        <v>715</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1382,22 +1400,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>133425158</v>
+        <v>129388090</v>
       </c>
       <c r="E28" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>8013</v>
+        <v>715</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1413,22 +1431,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>133425313</v>
+        <v>129642982</v>
       </c>
       <c r="E29" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
       </c>
       <c r="J29" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -1444,22 +1462,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>133425314</v>
+        <v>129855372</v>
       </c>
       <c r="E30" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
       </c>
       <c r="J30" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -1475,22 +1493,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>133406152</v>
+        <v>129867704</v>
       </c>
       <c r="E31" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
       </c>
       <c r="J31" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K31" s="5">
         <v>0</v>
@@ -1506,22 +1524,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>133406448</v>
+        <v>129933617</v>
       </c>
       <c r="E32" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
       </c>
       <c r="J32" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -1537,22 +1555,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>133407007</v>
+        <v>130138058</v>
       </c>
       <c r="E33" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
       </c>
       <c r="J33" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -1568,22 +1586,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>133407478</v>
+        <v>130210711</v>
       </c>
       <c r="E34" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
       </c>
       <c r="J34" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -1599,22 +1617,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>133407768</v>
+        <v>130259017</v>
       </c>
       <c r="E35" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
       </c>
       <c r="J35" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -1630,22 +1648,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>133407812</v>
+        <v>130262276</v>
       </c>
       <c r="E36" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
       </c>
       <c r="J36" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -1661,22 +1679,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>133408271</v>
+        <v>130303680</v>
       </c>
       <c r="E37" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
       </c>
       <c r="J37" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -1692,22 +1710,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>133408347</v>
+        <v>130493774</v>
       </c>
       <c r="E38" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
       </c>
       <c r="J38" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
@@ -1723,22 +1741,22 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>133408591</v>
+        <v>130535618</v>
       </c>
       <c r="E39" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
       </c>
       <c r="J39" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K39" s="5">
         <v>0</v>
@@ -1754,22 +1772,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>133408779</v>
+        <v>130560793</v>
       </c>
       <c r="E40" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
       </c>
       <c r="J40" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -1785,22 +1803,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>133408810</v>
+        <v>130889631</v>
       </c>
       <c r="E41" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
       </c>
       <c r="J41" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -1816,22 +1834,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>133409360</v>
+        <v>131068444</v>
       </c>
       <c r="E42" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -1847,22 +1865,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>133409447</v>
+        <v>131310228</v>
       </c>
       <c r="E43" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I43" s="5">
         <v>42</v>
       </c>
       <c r="J43" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -1878,22 +1896,22 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>133409460</v>
+        <v>131751281</v>
       </c>
       <c r="E44" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
       </c>
       <c r="J44" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -1909,22 +1927,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>133409827</v>
+        <v>132319727</v>
       </c>
       <c r="E45" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
       </c>
       <c r="J45" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -1940,22 +1958,22 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>133410036</v>
+        <v>132468692</v>
       </c>
       <c r="E46" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I46" s="5">
         <v>42</v>
       </c>
       <c r="J46" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
@@ -1971,22 +1989,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>133411259</v>
+        <v>132545489</v>
       </c>
       <c r="E47" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
       </c>
       <c r="J47" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -2002,22 +2020,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>133411279</v>
+        <v>132676857</v>
       </c>
       <c r="E48" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2033,22 +2051,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>133411360</v>
+        <v>133047284</v>
       </c>
       <c r="E49" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2064,22 +2082,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>133411385</v>
+        <v>133429144</v>
       </c>
       <c r="E50" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2095,22 +2113,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>133412004</v>
+        <v>133432292</v>
       </c>
       <c r="E51" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
       </c>
       <c r="J51" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -2126,22 +2144,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>133412231</v>
+        <v>133432893</v>
       </c>
       <c r="E52" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -2157,22 +2175,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>133412467</v>
+        <v>133439115</v>
       </c>
       <c r="E53" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2188,22 +2206,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>133412527</v>
+        <v>133443980</v>
       </c>
       <c r="E54" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2219,22 +2237,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>133412835</v>
+        <v>133453604</v>
       </c>
       <c r="E55" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -2250,22 +2268,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>133413083</v>
+        <v>133454388</v>
       </c>
       <c r="E56" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
       </c>
       <c r="J56" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -2281,22 +2299,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>133413748</v>
+        <v>133454652</v>
       </c>
       <c r="E57" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -2312,22 +2330,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>133414407</v>
+        <v>133455313</v>
       </c>
       <c r="E58" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
       </c>
       <c r="J58" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -2343,22 +2361,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>133414922</v>
+        <v>133455765</v>
       </c>
       <c r="E59" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2374,22 +2392,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>133414932</v>
+        <v>133458457</v>
       </c>
       <c r="E60" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
       </c>
       <c r="J60" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K60" s="5">
         <v>0</v>
@@ -2405,22 +2423,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>133415134</v>
+        <v>133459219</v>
       </c>
       <c r="E61" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
       </c>
       <c r="J61" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K61" s="5">
         <v>0</v>
@@ -2436,22 +2454,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>133415718</v>
+        <v>133459855</v>
       </c>
       <c r="E62" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I62" s="5">
         <v>42</v>
       </c>
       <c r="J62" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K62" s="5">
         <v>0</v>
@@ -2467,22 +2485,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>133415897</v>
+        <v>133460201</v>
       </c>
       <c r="E63" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
       </c>
       <c r="J63" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K63" s="5">
         <v>0</v>
@@ -2498,22 +2516,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>133416192</v>
+        <v>133460584</v>
       </c>
       <c r="E64" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
       </c>
       <c r="J64" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K64" s="5">
         <v>0</v>
@@ -2529,22 +2547,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>133416325</v>
+        <v>133464097</v>
       </c>
       <c r="E65" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
       </c>
       <c r="J65" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K65" s="5">
         <v>0</v>
@@ -2560,22 +2578,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>133416844</v>
+        <v>133464205</v>
       </c>
       <c r="E66" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
       </c>
       <c r="J66" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -2591,22 +2609,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>133416888</v>
+        <v>133464864</v>
       </c>
       <c r="E67" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
       </c>
       <c r="J67" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K67" s="5">
         <v>0</v>
@@ -2622,22 +2640,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>133417287</v>
+        <v>133464989</v>
       </c>
       <c r="E68" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
       </c>
       <c r="J68" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K68" s="5">
         <v>0</v>
@@ -2653,22 +2671,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>133417818</v>
+        <v>133465369</v>
       </c>
       <c r="E69" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
       </c>
       <c r="J69" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
@@ -2684,22 +2702,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>133418553</v>
+        <v>133465826</v>
       </c>
       <c r="E70" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
       </c>
       <c r="J70" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
@@ -2715,22 +2733,22 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>133418845</v>
+        <v>133466841</v>
       </c>
       <c r="E71" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
       </c>
       <c r="J71" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K71" s="5">
         <v>0</v>
@@ -2746,22 +2764,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>133419728</v>
+        <v>133467187</v>
       </c>
       <c r="E72" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I72" s="5">
         <v>42</v>
       </c>
       <c r="J72" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K72" s="5">
         <v>0</v>
@@ -2777,22 +2795,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>133420044</v>
+        <v>133467667</v>
       </c>
       <c r="E73" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
       </c>
       <c r="J73" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K73" s="5">
         <v>0</v>
@@ -2808,22 +2826,22 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>133420140</v>
+        <v>133468317</v>
       </c>
       <c r="E74" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
       </c>
       <c r="J74" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K74" s="5">
         <v>0</v>
@@ -2839,22 +2857,22 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>133420576</v>
+        <v>133468578</v>
       </c>
       <c r="E75" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
       </c>
       <c r="J75" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K75" s="5">
         <v>0</v>
@@ -2870,22 +2888,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>133420598</v>
+        <v>133470418</v>
       </c>
       <c r="E76" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
       </c>
       <c r="J76" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K76" s="5">
         <v>0</v>
@@ -2901,22 +2919,22 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>133421387</v>
+        <v>133470565</v>
       </c>
       <c r="E77" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
       </c>
       <c r="J77" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K77" s="5">
         <v>0</v>
@@ -2932,22 +2950,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>133421409</v>
+        <v>133470642</v>
       </c>
       <c r="E78" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I78" s="5">
         <v>42</v>
       </c>
       <c r="J78" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K78" s="5">
         <v>0</v>
@@ -2963,22 +2981,22 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>133421583</v>
+        <v>133470811</v>
       </c>
       <c r="E79" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I79" s="5">
         <v>42</v>
       </c>
       <c r="J79" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K79" s="5">
         <v>0</v>
@@ -2994,22 +3012,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>133422178</v>
+        <v>133470999</v>
       </c>
       <c r="E80" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I80" s="5">
         <v>42</v>
       </c>
       <c r="J80" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K80" s="5">
         <v>0</v>
@@ -3025,22 +3043,22 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>133423025</v>
+        <v>133471469</v>
       </c>
       <c r="E81" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I81" s="5">
         <v>42</v>
       </c>
       <c r="J81" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K81" s="5">
         <v>0</v>
@@ -3056,22 +3074,22 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>133423026</v>
+        <v>133472407</v>
       </c>
       <c r="E82" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I82" s="5">
         <v>42</v>
       </c>
       <c r="J82" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K82" s="5">
         <v>0</v>
@@ -3087,22 +3105,22 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>133423356</v>
+        <v>133473337</v>
       </c>
       <c r="E83" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I83" s="5">
         <v>42</v>
       </c>
       <c r="J83" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K83" s="5">
         <v>0</v>
@@ -3118,22 +3136,22 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>133424032</v>
+        <v>133474063</v>
       </c>
       <c r="E84" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I84" s="5">
         <v>42</v>
       </c>
       <c r="J84" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K84" s="5">
         <v>0</v>
@@ -3149,22 +3167,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>133424299</v>
+        <v>133474492</v>
       </c>
       <c r="E85" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I85" s="5">
         <v>42</v>
       </c>
       <c r="J85" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K85" s="5">
         <v>0</v>
@@ -3180,22 +3198,22 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>133424374</v>
+        <v>133475767</v>
       </c>
       <c r="E86" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I86" s="5">
         <v>42</v>
       </c>
       <c r="J86" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K86" s="5">
         <v>0</v>
@@ -3211,22 +3229,22 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>133424509</v>
+        <v>133476336</v>
       </c>
       <c r="E87" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I87" s="5">
         <v>42</v>
       </c>
       <c r="J87" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K87" s="5">
         <v>0</v>
@@ -3242,22 +3260,22 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
-        <v>133424563</v>
+        <v>133477033</v>
       </c>
       <c r="E88" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I88" s="5">
         <v>42</v>
       </c>
       <c r="J88" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K88" s="5">
         <v>0</v>
@@ -3273,22 +3291,22 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>133424915</v>
+        <v>133477595</v>
       </c>
       <c r="E89" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I89" s="5">
         <v>42</v>
       </c>
       <c r="J89" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K89" s="5">
         <v>0</v>
@@ -3304,22 +3322,22 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>133393461</v>
+        <v>133479257</v>
       </c>
       <c r="E90" s="5">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I90" s="5">
         <v>42</v>
       </c>
       <c r="J90" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K90" s="5">
         <v>0</v>
@@ -3335,22 +3353,22 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>133415994</v>
+        <v>133480400</v>
       </c>
       <c r="E91" s="5">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I91" s="5">
         <v>42</v>
       </c>
       <c r="J91" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K91" s="5">
         <v>0</v>
@@ -3366,22 +3384,22 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>133419013</v>
+        <v>133481502</v>
       </c>
       <c r="E92" s="5">
-        <v>609</v>
+        <v>1213</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I92" s="5">
         <v>42</v>
       </c>
       <c r="J92" s="5">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="K92" s="5">
         <v>0</v>
@@ -3397,22 +3415,22 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>123058958</v>
+        <v>133482046</v>
       </c>
       <c r="E93" s="5">
         <v>1211</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I93" s="5">
         <v>42</v>
       </c>
       <c r="J93" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K93" s="5">
         <v>0</v>
@@ -3428,22 +3446,22 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>128886730</v>
+        <v>133482217</v>
       </c>
       <c r="E94" s="5">
         <v>1211</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I94" s="5">
         <v>42</v>
       </c>
       <c r="J94" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K94" s="5">
         <v>0</v>
@@ -3459,22 +3477,22 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>129881944</v>
+        <v>133483569</v>
       </c>
       <c r="E95" s="5">
         <v>1211</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I95" s="5">
         <v>42</v>
       </c>
       <c r="J95" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K95" s="5">
         <v>0</v>
@@ -3490,22 +3508,22 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>130379805</v>
+        <v>133485583</v>
       </c>
       <c r="E96" s="5">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I96" s="5">
         <v>42</v>
       </c>
       <c r="J96" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K96" s="5">
         <v>0</v>
@@ -3521,22 +3539,22 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>132640854</v>
+        <v>133485939</v>
       </c>
       <c r="E97" s="5">
         <v>1211</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I97" s="5">
         <v>42</v>
       </c>
       <c r="J97" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K97" s="5">
         <v>0</v>
@@ -3552,22 +3570,22 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <v>133076385</v>
+        <v>133486109</v>
       </c>
       <c r="E98" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I98" s="5">
         <v>42</v>
       </c>
       <c r="J98" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K98" s="5">
         <v>0</v>
@@ -3583,22 +3601,22 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <v>128886730</v>
+        <v>133486761</v>
       </c>
       <c r="E99" s="5">
         <v>1211</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I99" s="5">
         <v>42</v>
       </c>
       <c r="J99" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K99" s="5">
         <v>0</v>
@@ -3614,22 +3632,22 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <v>129881944</v>
+        <v>133487912</v>
       </c>
       <c r="E100" s="5">
         <v>1211</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I100" s="5">
         <v>42</v>
       </c>
       <c r="J100" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K100" s="5">
         <v>0</v>
@@ -3645,22 +3663,22 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <v>130379805</v>
+        <v>133488262</v>
       </c>
       <c r="E101" s="5">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I101" s="5">
         <v>42</v>
       </c>
       <c r="J101" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K101" s="5">
         <v>0</v>
@@ -3676,22 +3694,22 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <v>132640854</v>
+        <v>133489077</v>
       </c>
       <c r="E102" s="5">
         <v>1211</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I102" s="5">
         <v>42</v>
       </c>
       <c r="J102" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K102" s="5">
         <v>0</v>
@@ -3707,22 +3725,22 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <v>133076385</v>
+        <v>133489341</v>
       </c>
       <c r="E103" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I103" s="5">
         <v>42</v>
       </c>
       <c r="J103" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K103" s="5">
         <v>0</v>
@@ -3738,22 +3756,22 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <v>133452749</v>
+        <v>133489580</v>
       </c>
       <c r="E104" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I104" s="5">
         <v>42</v>
       </c>
       <c r="J104" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K104" s="5">
         <v>0</v>
@@ -3769,22 +3787,22 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
-        <v>133453003</v>
+        <v>133490191</v>
       </c>
       <c r="E105" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I105" s="5">
         <v>42</v>
       </c>
       <c r="J105" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K105" s="5">
         <v>0</v>
@@ -3800,22 +3818,22 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <v>133455403</v>
+        <v>133490251</v>
       </c>
       <c r="E106" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I106" s="5">
         <v>42</v>
       </c>
       <c r="J106" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
@@ -3831,22 +3849,22 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <v>133456199</v>
+        <v>133491336</v>
       </c>
       <c r="E107" s="5">
-        <v>2013</v>
+        <v>1213</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I107" s="5">
         <v>42</v>
       </c>
       <c r="J107" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K107" s="5">
         <v>0</v>
@@ -3862,22 +3880,22 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <v>133457968</v>
+        <v>133491900</v>
       </c>
       <c r="E108" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I108" s="5">
         <v>42</v>
       </c>
       <c r="J108" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K108" s="5">
         <v>0</v>
@@ -3893,22 +3911,22 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <v>133458433</v>
+        <v>133492171</v>
       </c>
       <c r="E109" s="5">
-        <v>2013</v>
+        <v>1213</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I109" s="5">
         <v>42</v>
       </c>
       <c r="J109" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
@@ -3924,22 +3942,22 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <v>133458657</v>
+        <v>133493082</v>
       </c>
       <c r="E110" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I110" s="5">
         <v>42</v>
       </c>
       <c r="J110" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K110" s="5">
         <v>0</v>
@@ -3955,22 +3973,22 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <v>133460226</v>
+        <v>133493271</v>
       </c>
       <c r="E111" s="5">
-        <v>2013</v>
+        <v>1213</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I111" s="5">
         <v>42</v>
       </c>
       <c r="J111" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K111" s="5">
         <v>0</v>
@@ -3986,22 +4004,22 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <v>133460695</v>
+        <v>132914455</v>
       </c>
       <c r="E112" s="5">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I112" s="5">
         <v>42</v>
       </c>
       <c r="J112" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K112" s="5">
         <v>0</v>
@@ -4017,22 +4035,22 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
-        <v>133462946</v>
+        <v>133430708</v>
       </c>
       <c r="E113" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I113" s="5">
         <v>42</v>
       </c>
       <c r="J113" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
@@ -4048,22 +4066,22 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
-        <v>133464446</v>
+        <v>133474238</v>
       </c>
       <c r="E114" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I114" s="5">
         <v>42</v>
       </c>
       <c r="J114" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K114" s="5">
         <v>0</v>
@@ -4079,22 +4097,22 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <v>133465045</v>
+        <v>133474488</v>
       </c>
       <c r="E115" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I115" s="5">
         <v>42</v>
       </c>
       <c r="J115" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K115" s="5">
         <v>0</v>
@@ -4110,22 +4128,22 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <v>133466318</v>
+        <v>133474520</v>
       </c>
       <c r="E116" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I116" s="5">
         <v>42</v>
       </c>
       <c r="J116" s="5">
-        <v>718</v>
+        <v>1117</v>
       </c>
       <c r="K116" s="5">
         <v>0</v>
@@ -4141,22 +4159,22 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <v>133467715</v>
+        <v>133474756</v>
       </c>
       <c r="E117" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I117" s="5">
         <v>42</v>
       </c>
       <c r="J117" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K117" s="5">
         <v>0</v>
@@ -4172,22 +4190,22 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <v>133468300</v>
+        <v>133474882</v>
       </c>
       <c r="E118" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I118" s="5">
         <v>42</v>
       </c>
       <c r="J118" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K118" s="5">
         <v>0</v>
@@ -4198,6 +4216,3230 @@
       <c r="M118" s="5"/>
       <c r="N118" s="5"/>
       <c r="O118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="5">
+        <v>133474885</v>
+      </c>
+      <c r="E119" s="5">
+        <v>601</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" s="5">
+        <v>42</v>
+      </c>
+      <c r="J119" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5">
+        <v>61</v>
+      </c>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="5">
+        <v>133475101</v>
+      </c>
+      <c r="E120" s="5">
+        <v>601</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I120" s="5">
+        <v>42</v>
+      </c>
+      <c r="J120" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5">
+        <v>61</v>
+      </c>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="5">
+        <v>133475144</v>
+      </c>
+      <c r="E121" s="5">
+        <v>601</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I121" s="5">
+        <v>42</v>
+      </c>
+      <c r="J121" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5">
+        <v>61</v>
+      </c>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="5">
+        <v>133475278</v>
+      </c>
+      <c r="E122" s="5">
+        <v>601</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="5">
+        <v>133475418</v>
+      </c>
+      <c r="E123" s="5">
+        <v>601</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="5">
+        <v>133476036</v>
+      </c>
+      <c r="E124" s="5">
+        <v>601</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="5">
+        <v>133476463</v>
+      </c>
+      <c r="E125" s="5">
+        <v>601</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="5">
+        <v>133476543</v>
+      </c>
+      <c r="E126" s="5">
+        <v>601</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="5">
+        <v>133476635</v>
+      </c>
+      <c r="E127" s="5">
+        <v>601</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="5">
+        <v>133476996</v>
+      </c>
+      <c r="E128" s="5">
+        <v>601</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="5">
+        <v>133477206</v>
+      </c>
+      <c r="E129" s="5">
+        <v>601</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="5">
+        <v>133477217</v>
+      </c>
+      <c r="E130" s="5">
+        <v>601</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="5">
+        <v>133477239</v>
+      </c>
+      <c r="E131" s="5">
+        <v>601</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="5">
+        <v>133477362</v>
+      </c>
+      <c r="E132" s="5">
+        <v>601</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="5">
+        <v>133477464</v>
+      </c>
+      <c r="E133" s="5">
+        <v>601</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="M133" s="5"/>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="5">
+        <v>133477512</v>
+      </c>
+      <c r="E134" s="5">
+        <v>601</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="M134" s="5"/>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="5">
+        <v>133477644</v>
+      </c>
+      <c r="E135" s="5">
+        <v>601</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="5">
+        <v>133478254</v>
+      </c>
+      <c r="E136" s="5">
+        <v>601</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="M136" s="5"/>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
+        <v>133478453</v>
+      </c>
+      <c r="E137" s="5">
+        <v>601</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="M137" s="5"/>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="5">
+        <v>133479115</v>
+      </c>
+      <c r="E138" s="5">
+        <v>601</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="M138" s="5"/>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="5">
+        <v>133479270</v>
+      </c>
+      <c r="E139" s="5">
+        <v>601</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+      <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="5">
+        <v>133479312</v>
+      </c>
+      <c r="E140" s="5">
+        <v>601</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="5">
+        <v>133479432</v>
+      </c>
+      <c r="E141" s="5">
+        <v>601</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="5">
+        <v>133479764</v>
+      </c>
+      <c r="E142" s="5">
+        <v>601</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="M142" s="5"/>
+      <c r="N142" s="5"/>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="5">
+        <v>133479875</v>
+      </c>
+      <c r="E143" s="5">
+        <v>601</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="M143" s="5"/>
+      <c r="N143" s="5"/>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="5">
+        <v>133480009</v>
+      </c>
+      <c r="E144" s="5">
+        <v>601</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="M144" s="5"/>
+      <c r="N144" s="5"/>
+      <c r="O144" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="5">
+        <v>133480038</v>
+      </c>
+      <c r="E145" s="5">
+        <v>601</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I145" s="5">
+        <v>42</v>
+      </c>
+      <c r="J145" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="L145" s="5">
+        <v>61</v>
+      </c>
+      <c r="M145" s="5"/>
+      <c r="N145" s="5"/>
+      <c r="O145" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="5">
+        <v>133480079</v>
+      </c>
+      <c r="E146" s="5">
+        <v>601</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I146" s="5">
+        <v>42</v>
+      </c>
+      <c r="J146" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5">
+        <v>61</v>
+      </c>
+      <c r="M146" s="5"/>
+      <c r="N146" s="5"/>
+      <c r="O146" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="5">
+        <v>133480368</v>
+      </c>
+      <c r="E147" s="5">
+        <v>601</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I147" s="5">
+        <v>42</v>
+      </c>
+      <c r="J147" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5">
+        <v>61</v>
+      </c>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="5">
+        <v>133480674</v>
+      </c>
+      <c r="E148" s="5">
+        <v>601</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I148" s="5">
+        <v>42</v>
+      </c>
+      <c r="J148" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5">
+        <v>61</v>
+      </c>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="5">
+        <v>133480850</v>
+      </c>
+      <c r="E149" s="5">
+        <v>601</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I149" s="5">
+        <v>42</v>
+      </c>
+      <c r="J149" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5">
+        <v>61</v>
+      </c>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
+      <c r="O149" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="5">
+        <v>133481475</v>
+      </c>
+      <c r="E150" s="5">
+        <v>601</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I150" s="5">
+        <v>42</v>
+      </c>
+      <c r="J150" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5">
+        <v>61</v>
+      </c>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="5">
+        <v>133482207</v>
+      </c>
+      <c r="E151" s="5">
+        <v>601</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I151" s="5">
+        <v>42</v>
+      </c>
+      <c r="J151" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5">
+        <v>61</v>
+      </c>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="5">
+        <v>133483174</v>
+      </c>
+      <c r="E152" s="5">
+        <v>601</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I152" s="5">
+        <v>42</v>
+      </c>
+      <c r="J152" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="L152" s="5">
+        <v>61</v>
+      </c>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="5">
+        <v>133483316</v>
+      </c>
+      <c r="E153" s="5">
+        <v>601</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I153" s="5">
+        <v>42</v>
+      </c>
+      <c r="J153" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K153" s="5">
+        <v>0</v>
+      </c>
+      <c r="L153" s="5">
+        <v>61</v>
+      </c>
+      <c r="M153" s="5"/>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="5">
+        <v>133483883</v>
+      </c>
+      <c r="E154" s="5">
+        <v>601</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I154" s="5">
+        <v>42</v>
+      </c>
+      <c r="J154" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K154" s="5">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5">
+        <v>61</v>
+      </c>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="5">
+        <v>133483917</v>
+      </c>
+      <c r="E155" s="5">
+        <v>601</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I155" s="5">
+        <v>42</v>
+      </c>
+      <c r="J155" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K155" s="5">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5">
+        <v>61</v>
+      </c>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="5">
+        <v>133483982</v>
+      </c>
+      <c r="E156" s="5">
+        <v>601</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I156" s="5">
+        <v>42</v>
+      </c>
+      <c r="J156" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K156" s="5">
+        <v>0</v>
+      </c>
+      <c r="L156" s="5">
+        <v>61</v>
+      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="5">
+        <v>133484150</v>
+      </c>
+      <c r="E157" s="5">
+        <v>601</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I157" s="5">
+        <v>42</v>
+      </c>
+      <c r="J157" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K157" s="5">
+        <v>0</v>
+      </c>
+      <c r="L157" s="5">
+        <v>61</v>
+      </c>
+      <c r="M157" s="5"/>
+      <c r="N157" s="5"/>
+      <c r="O157" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="5">
+        <v>133484170</v>
+      </c>
+      <c r="E158" s="5">
+        <v>601</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I158" s="5">
+        <v>42</v>
+      </c>
+      <c r="J158" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K158" s="5">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5">
+        <v>61</v>
+      </c>
+      <c r="M158" s="5"/>
+      <c r="N158" s="5"/>
+      <c r="O158" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="5">
+        <v>133484172</v>
+      </c>
+      <c r="E159" s="5">
+        <v>601</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I159" s="5">
+        <v>42</v>
+      </c>
+      <c r="J159" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K159" s="5">
+        <v>0</v>
+      </c>
+      <c r="L159" s="5">
+        <v>61</v>
+      </c>
+      <c r="M159" s="5"/>
+      <c r="N159" s="5"/>
+      <c r="O159" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="5">
+        <v>133484176</v>
+      </c>
+      <c r="E160" s="5">
+        <v>609</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I160" s="5">
+        <v>42</v>
+      </c>
+      <c r="J160" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K160" s="5">
+        <v>0</v>
+      </c>
+      <c r="L160" s="5">
+        <v>61</v>
+      </c>
+      <c r="M160" s="5"/>
+      <c r="N160" s="5"/>
+      <c r="O160" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="5">
+        <v>133484636</v>
+      </c>
+      <c r="E161" s="5">
+        <v>601</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I161" s="5">
+        <v>42</v>
+      </c>
+      <c r="J161" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K161" s="5">
+        <v>0</v>
+      </c>
+      <c r="L161" s="5">
+        <v>61</v>
+      </c>
+      <c r="M161" s="5"/>
+      <c r="N161" s="5"/>
+      <c r="O161" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="5">
+        <v>133484946</v>
+      </c>
+      <c r="E162" s="5">
+        <v>601</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I162" s="5">
+        <v>42</v>
+      </c>
+      <c r="J162" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K162" s="5">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5">
+        <v>61</v>
+      </c>
+      <c r="M162" s="5"/>
+      <c r="N162" s="5"/>
+      <c r="O162" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="5">
+        <v>133485059</v>
+      </c>
+      <c r="E163" s="5">
+        <v>601</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I163" s="5">
+        <v>42</v>
+      </c>
+      <c r="J163" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K163" s="5">
+        <v>0</v>
+      </c>
+      <c r="L163" s="5">
+        <v>61</v>
+      </c>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
+      <c r="O163" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164" s="5">
+        <v>133485138</v>
+      </c>
+      <c r="E164" s="5">
+        <v>601</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I164" s="5">
+        <v>42</v>
+      </c>
+      <c r="J164" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K164" s="5">
+        <v>0</v>
+      </c>
+      <c r="L164" s="5">
+        <v>61</v>
+      </c>
+      <c r="M164" s="5"/>
+      <c r="N164" s="5"/>
+      <c r="O164" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165" s="5">
+        <v>133485186</v>
+      </c>
+      <c r="E165" s="5">
+        <v>601</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I165" s="5">
+        <v>42</v>
+      </c>
+      <c r="J165" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K165" s="5">
+        <v>0</v>
+      </c>
+      <c r="L165" s="5">
+        <v>61</v>
+      </c>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+      <c r="O165" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166" s="5">
+        <v>133485408</v>
+      </c>
+      <c r="E166" s="5">
+        <v>601</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I166" s="5">
+        <v>42</v>
+      </c>
+      <c r="J166" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K166" s="5">
+        <v>0</v>
+      </c>
+      <c r="L166" s="5">
+        <v>61</v>
+      </c>
+      <c r="M166" s="5"/>
+      <c r="N166" s="5"/>
+      <c r="O166" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="5">
+        <v>133486382</v>
+      </c>
+      <c r="E167" s="5">
+        <v>601</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I167" s="5">
+        <v>42</v>
+      </c>
+      <c r="J167" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K167" s="5">
+        <v>0</v>
+      </c>
+      <c r="L167" s="5">
+        <v>61</v>
+      </c>
+      <c r="M167" s="5"/>
+      <c r="N167" s="5"/>
+      <c r="O167" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168" s="5">
+        <v>133486431</v>
+      </c>
+      <c r="E168" s="5">
+        <v>601</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" s="5">
+        <v>42</v>
+      </c>
+      <c r="J168" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K168" s="5">
+        <v>0</v>
+      </c>
+      <c r="L168" s="5">
+        <v>61</v>
+      </c>
+      <c r="M168" s="5"/>
+      <c r="N168" s="5"/>
+      <c r="O168" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169" s="5">
+        <v>133486443</v>
+      </c>
+      <c r="E169" s="5">
+        <v>601</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" s="5">
+        <v>42</v>
+      </c>
+      <c r="J169" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K169" s="5">
+        <v>0</v>
+      </c>
+      <c r="L169" s="5">
+        <v>61</v>
+      </c>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="5">
+        <v>133486448</v>
+      </c>
+      <c r="E170" s="5">
+        <v>601</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" s="5">
+        <v>42</v>
+      </c>
+      <c r="J170" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K170" s="5">
+        <v>0</v>
+      </c>
+      <c r="L170" s="5">
+        <v>61</v>
+      </c>
+      <c r="M170" s="5"/>
+      <c r="N170" s="5"/>
+      <c r="O170" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171" s="5">
+        <v>133486525</v>
+      </c>
+      <c r="E171" s="5">
+        <v>601</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" s="5">
+        <v>42</v>
+      </c>
+      <c r="J171" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K171" s="5">
+        <v>0</v>
+      </c>
+      <c r="L171" s="5">
+        <v>61</v>
+      </c>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="5">
+        <v>133486768</v>
+      </c>
+      <c r="E172" s="5">
+        <v>601</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I172" s="5">
+        <v>42</v>
+      </c>
+      <c r="J172" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K172" s="5">
+        <v>0</v>
+      </c>
+      <c r="L172" s="5">
+        <v>61</v>
+      </c>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+      <c r="O172" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="5">
+        <v>133487100</v>
+      </c>
+      <c r="E173" s="5">
+        <v>601</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I173" s="5">
+        <v>42</v>
+      </c>
+      <c r="J173" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K173" s="5">
+        <v>0</v>
+      </c>
+      <c r="L173" s="5">
+        <v>61</v>
+      </c>
+      <c r="M173" s="5"/>
+      <c r="N173" s="5"/>
+      <c r="O173" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="5">
+        <v>133487432</v>
+      </c>
+      <c r="E174" s="5">
+        <v>601</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I174" s="5">
+        <v>42</v>
+      </c>
+      <c r="J174" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K174" s="5">
+        <v>0</v>
+      </c>
+      <c r="L174" s="5">
+        <v>61</v>
+      </c>
+      <c r="M174" s="5"/>
+      <c r="N174" s="5"/>
+      <c r="O174" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" s="5">
+        <v>133487589</v>
+      </c>
+      <c r="E175" s="5">
+        <v>601</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I175" s="5">
+        <v>42</v>
+      </c>
+      <c r="J175" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K175" s="5">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5">
+        <v>61</v>
+      </c>
+      <c r="M175" s="5"/>
+      <c r="N175" s="5"/>
+      <c r="O175" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" s="5">
+        <v>133487593</v>
+      </c>
+      <c r="E176" s="5">
+        <v>601</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I176" s="5">
+        <v>42</v>
+      </c>
+      <c r="J176" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K176" s="5">
+        <v>0</v>
+      </c>
+      <c r="L176" s="5">
+        <v>61</v>
+      </c>
+      <c r="M176" s="5"/>
+      <c r="N176" s="5"/>
+      <c r="O176" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" s="5">
+        <v>133487671</v>
+      </c>
+      <c r="E177" s="5">
+        <v>601</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I177" s="5">
+        <v>42</v>
+      </c>
+      <c r="J177" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K177" s="5">
+        <v>0</v>
+      </c>
+      <c r="L177" s="5">
+        <v>61</v>
+      </c>
+      <c r="M177" s="5"/>
+      <c r="N177" s="5"/>
+      <c r="O177" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" s="5">
+        <v>133487825</v>
+      </c>
+      <c r="E178" s="5">
+        <v>601</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I178" s="5">
+        <v>42</v>
+      </c>
+      <c r="J178" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K178" s="5">
+        <v>0</v>
+      </c>
+      <c r="L178" s="5">
+        <v>61</v>
+      </c>
+      <c r="M178" s="5"/>
+      <c r="N178" s="5"/>
+      <c r="O178" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="5">
+        <v>133487842</v>
+      </c>
+      <c r="E179" s="5">
+        <v>601</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I179" s="5">
+        <v>42</v>
+      </c>
+      <c r="J179" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K179" s="5">
+        <v>0</v>
+      </c>
+      <c r="L179" s="5">
+        <v>61</v>
+      </c>
+      <c r="M179" s="5"/>
+      <c r="N179" s="5"/>
+      <c r="O179" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" s="5">
+        <v>133487939</v>
+      </c>
+      <c r="E180" s="5">
+        <v>601</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I180" s="5">
+        <v>42</v>
+      </c>
+      <c r="J180" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K180" s="5">
+        <v>0</v>
+      </c>
+      <c r="L180" s="5">
+        <v>61</v>
+      </c>
+      <c r="M180" s="5"/>
+      <c r="N180" s="5"/>
+      <c r="O180" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" s="5">
+        <v>133487973</v>
+      </c>
+      <c r="E181" s="5">
+        <v>601</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I181" s="5">
+        <v>42</v>
+      </c>
+      <c r="J181" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K181" s="5">
+        <v>0</v>
+      </c>
+      <c r="L181" s="5">
+        <v>61</v>
+      </c>
+      <c r="M181" s="5"/>
+      <c r="N181" s="5"/>
+      <c r="O181" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" s="5">
+        <v>133488216</v>
+      </c>
+      <c r="E182" s="5">
+        <v>601</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I182" s="5">
+        <v>42</v>
+      </c>
+      <c r="J182" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K182" s="5">
+        <v>0</v>
+      </c>
+      <c r="L182" s="5">
+        <v>61</v>
+      </c>
+      <c r="M182" s="5"/>
+      <c r="N182" s="5"/>
+      <c r="O182" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183" s="5">
+        <v>133488324</v>
+      </c>
+      <c r="E183" s="5">
+        <v>601</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I183" s="5">
+        <v>42</v>
+      </c>
+      <c r="J183" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K183" s="5">
+        <v>0</v>
+      </c>
+      <c r="L183" s="5">
+        <v>61</v>
+      </c>
+      <c r="M183" s="5"/>
+      <c r="N183" s="5"/>
+      <c r="O183" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184" s="5">
+        <v>133488733</v>
+      </c>
+      <c r="E184" s="5">
+        <v>601</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I184" s="5">
+        <v>42</v>
+      </c>
+      <c r="J184" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K184" s="5">
+        <v>0</v>
+      </c>
+      <c r="L184" s="5">
+        <v>61</v>
+      </c>
+      <c r="M184" s="5"/>
+      <c r="N184" s="5"/>
+      <c r="O184" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" s="5">
+        <v>133488773</v>
+      </c>
+      <c r="E185" s="5">
+        <v>601</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I185" s="5">
+        <v>42</v>
+      </c>
+      <c r="J185" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K185" s="5">
+        <v>0</v>
+      </c>
+      <c r="L185" s="5">
+        <v>61</v>
+      </c>
+      <c r="M185" s="5"/>
+      <c r="N185" s="5"/>
+      <c r="O185" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186" s="5">
+        <v>133489773</v>
+      </c>
+      <c r="E186" s="5">
+        <v>601</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I186" s="5">
+        <v>42</v>
+      </c>
+      <c r="J186" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K186" s="5">
+        <v>0</v>
+      </c>
+      <c r="L186" s="5">
+        <v>61</v>
+      </c>
+      <c r="M186" s="5"/>
+      <c r="N186" s="5"/>
+      <c r="O186" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187" s="5">
+        <v>133489897</v>
+      </c>
+      <c r="E187" s="5">
+        <v>601</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I187" s="5">
+        <v>42</v>
+      </c>
+      <c r="J187" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K187" s="5">
+        <v>0</v>
+      </c>
+      <c r="L187" s="5">
+        <v>61</v>
+      </c>
+      <c r="M187" s="5"/>
+      <c r="N187" s="5"/>
+      <c r="O187" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" s="5">
+        <v>133490042</v>
+      </c>
+      <c r="E188" s="5">
+        <v>601</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I188" s="5">
+        <v>42</v>
+      </c>
+      <c r="J188" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K188" s="5">
+        <v>0</v>
+      </c>
+      <c r="L188" s="5">
+        <v>61</v>
+      </c>
+      <c r="M188" s="5"/>
+      <c r="N188" s="5"/>
+      <c r="O188" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189" s="5">
+        <v>133490070</v>
+      </c>
+      <c r="E189" s="5">
+        <v>601</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I189" s="5">
+        <v>42</v>
+      </c>
+      <c r="J189" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K189" s="5">
+        <v>0</v>
+      </c>
+      <c r="L189" s="5">
+        <v>61</v>
+      </c>
+      <c r="M189" s="5"/>
+      <c r="N189" s="5"/>
+      <c r="O189" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190" s="5">
+        <v>133490294</v>
+      </c>
+      <c r="E190" s="5">
+        <v>601</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I190" s="5">
+        <v>42</v>
+      </c>
+      <c r="J190" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K190" s="5">
+        <v>0</v>
+      </c>
+      <c r="L190" s="5">
+        <v>61</v>
+      </c>
+      <c r="M190" s="5"/>
+      <c r="N190" s="5"/>
+      <c r="O190" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191" s="5">
+        <v>133490755</v>
+      </c>
+      <c r="E191" s="5">
+        <v>601</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I191" s="5">
+        <v>42</v>
+      </c>
+      <c r="J191" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K191" s="5">
+        <v>0</v>
+      </c>
+      <c r="L191" s="5">
+        <v>61</v>
+      </c>
+      <c r="M191" s="5"/>
+      <c r="N191" s="5"/>
+      <c r="O191" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192" s="5">
+        <v>133490894</v>
+      </c>
+      <c r="E192" s="5">
+        <v>601</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I192" s="5">
+        <v>42</v>
+      </c>
+      <c r="J192" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K192" s="5">
+        <v>0</v>
+      </c>
+      <c r="L192" s="5">
+        <v>61</v>
+      </c>
+      <c r="M192" s="5"/>
+      <c r="N192" s="5"/>
+      <c r="O192" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A193" s="5">
+        <v>133491203</v>
+      </c>
+      <c r="E193" s="5">
+        <v>601</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I193" s="5">
+        <v>42</v>
+      </c>
+      <c r="J193" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K193" s="5">
+        <v>0</v>
+      </c>
+      <c r="L193" s="5">
+        <v>61</v>
+      </c>
+      <c r="M193" s="5"/>
+      <c r="N193" s="5"/>
+      <c r="O193" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A194" s="5">
+        <v>133491289</v>
+      </c>
+      <c r="E194" s="5">
+        <v>601</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I194" s="5">
+        <v>42</v>
+      </c>
+      <c r="J194" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K194" s="5">
+        <v>0</v>
+      </c>
+      <c r="L194" s="5">
+        <v>61</v>
+      </c>
+      <c r="M194" s="5"/>
+      <c r="N194" s="5"/>
+      <c r="O194" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A195" s="5">
+        <v>133491654</v>
+      </c>
+      <c r="E195" s="5">
+        <v>601</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I195" s="5">
+        <v>42</v>
+      </c>
+      <c r="J195" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K195" s="5">
+        <v>0</v>
+      </c>
+      <c r="L195" s="5">
+        <v>61</v>
+      </c>
+      <c r="M195" s="5"/>
+      <c r="N195" s="5"/>
+      <c r="O195" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A196" s="5">
+        <v>133491658</v>
+      </c>
+      <c r="E196" s="5">
+        <v>601</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I196" s="5">
+        <v>42</v>
+      </c>
+      <c r="J196" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K196" s="5">
+        <v>0</v>
+      </c>
+      <c r="L196" s="5">
+        <v>61</v>
+      </c>
+      <c r="M196" s="5"/>
+      <c r="N196" s="5"/>
+      <c r="O196" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197" s="5">
+        <v>133491666</v>
+      </c>
+      <c r="E197" s="5">
+        <v>601</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I197" s="5">
+        <v>42</v>
+      </c>
+      <c r="J197" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K197" s="5">
+        <v>0</v>
+      </c>
+      <c r="L197" s="5">
+        <v>61</v>
+      </c>
+      <c r="M197" s="5"/>
+      <c r="N197" s="5"/>
+      <c r="O197" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198" s="5">
+        <v>133491682</v>
+      </c>
+      <c r="E198" s="5">
+        <v>601</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I198" s="5">
+        <v>42</v>
+      </c>
+      <c r="J198" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K198" s="5">
+        <v>0</v>
+      </c>
+      <c r="L198" s="5">
+        <v>61</v>
+      </c>
+      <c r="M198" s="5"/>
+      <c r="N198" s="5"/>
+      <c r="O198" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A199" s="5">
+        <v>133491685</v>
+      </c>
+      <c r="E199" s="5">
+        <v>601</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I199" s="5">
+        <v>42</v>
+      </c>
+      <c r="J199" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K199" s="5">
+        <v>0</v>
+      </c>
+      <c r="L199" s="5">
+        <v>61</v>
+      </c>
+      <c r="M199" s="5"/>
+      <c r="N199" s="5"/>
+      <c r="O199" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A200" s="5">
+        <v>133491688</v>
+      </c>
+      <c r="E200" s="5">
+        <v>601</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I200" s="5">
+        <v>42</v>
+      </c>
+      <c r="J200" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K200" s="5">
+        <v>0</v>
+      </c>
+      <c r="L200" s="5">
+        <v>61</v>
+      </c>
+      <c r="M200" s="5"/>
+      <c r="N200" s="5"/>
+      <c r="O200" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A201" s="5">
+        <v>133491693</v>
+      </c>
+      <c r="E201" s="5">
+        <v>601</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I201" s="5">
+        <v>42</v>
+      </c>
+      <c r="J201" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K201" s="5">
+        <v>0</v>
+      </c>
+      <c r="L201" s="5">
+        <v>61</v>
+      </c>
+      <c r="M201" s="5"/>
+      <c r="N201" s="5"/>
+      <c r="O201" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A202" s="5">
+        <v>133491716</v>
+      </c>
+      <c r="E202" s="5">
+        <v>601</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I202" s="5">
+        <v>42</v>
+      </c>
+      <c r="J202" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K202" s="5">
+        <v>0</v>
+      </c>
+      <c r="L202" s="5">
+        <v>61</v>
+      </c>
+      <c r="M202" s="5"/>
+      <c r="N202" s="5"/>
+      <c r="O202" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203" s="5">
+        <v>133491730</v>
+      </c>
+      <c r="E203" s="5">
+        <v>601</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I203" s="5">
+        <v>42</v>
+      </c>
+      <c r="J203" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K203" s="5">
+        <v>0</v>
+      </c>
+      <c r="L203" s="5">
+        <v>61</v>
+      </c>
+      <c r="M203" s="5"/>
+      <c r="N203" s="5"/>
+      <c r="O203" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204" s="5">
+        <v>133491853</v>
+      </c>
+      <c r="E204" s="5">
+        <v>601</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I204" s="5">
+        <v>42</v>
+      </c>
+      <c r="J204" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K204" s="5">
+        <v>0</v>
+      </c>
+      <c r="L204" s="5">
+        <v>61</v>
+      </c>
+      <c r="M204" s="5"/>
+      <c r="N204" s="5"/>
+      <c r="O204" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A205" s="5">
+        <v>133491869</v>
+      </c>
+      <c r="E205" s="5">
+        <v>601</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I205" s="5">
+        <v>42</v>
+      </c>
+      <c r="J205" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K205" s="5">
+        <v>0</v>
+      </c>
+      <c r="L205" s="5">
+        <v>61</v>
+      </c>
+      <c r="M205" s="5"/>
+      <c r="N205" s="5"/>
+      <c r="O205" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206" s="5">
+        <v>133491913</v>
+      </c>
+      <c r="E206" s="5">
+        <v>601</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I206" s="5">
+        <v>42</v>
+      </c>
+      <c r="J206" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K206" s="5">
+        <v>0</v>
+      </c>
+      <c r="L206" s="5">
+        <v>61</v>
+      </c>
+      <c r="M206" s="5"/>
+      <c r="N206" s="5"/>
+      <c r="O206" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207" s="5">
+        <v>133492028</v>
+      </c>
+      <c r="E207" s="5">
+        <v>601</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I207" s="5">
+        <v>42</v>
+      </c>
+      <c r="J207" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K207" s="5">
+        <v>0</v>
+      </c>
+      <c r="L207" s="5">
+        <v>61</v>
+      </c>
+      <c r="M207" s="5"/>
+      <c r="N207" s="5"/>
+      <c r="O207" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208" s="5">
+        <v>133492052</v>
+      </c>
+      <c r="E208" s="5">
+        <v>601</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I208" s="5">
+        <v>42</v>
+      </c>
+      <c r="J208" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K208" s="5">
+        <v>0</v>
+      </c>
+      <c r="L208" s="5">
+        <v>61</v>
+      </c>
+      <c r="M208" s="5"/>
+      <c r="N208" s="5"/>
+      <c r="O208" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209" s="5">
+        <v>133492061</v>
+      </c>
+      <c r="E209" s="5">
+        <v>601</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I209" s="5">
+        <v>42</v>
+      </c>
+      <c r="J209" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K209" s="5">
+        <v>0</v>
+      </c>
+      <c r="L209" s="5">
+        <v>61</v>
+      </c>
+      <c r="M209" s="5"/>
+      <c r="N209" s="5"/>
+      <c r="O209" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210" s="5">
+        <v>133492067</v>
+      </c>
+      <c r="E210" s="5">
+        <v>601</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I210" s="5">
+        <v>42</v>
+      </c>
+      <c r="J210" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K210" s="5">
+        <v>0</v>
+      </c>
+      <c r="L210" s="5">
+        <v>61</v>
+      </c>
+      <c r="M210" s="5"/>
+      <c r="N210" s="5"/>
+      <c r="O210" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A211" s="5">
+        <v>133492080</v>
+      </c>
+      <c r="E211" s="5">
+        <v>601</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I211" s="5">
+        <v>42</v>
+      </c>
+      <c r="J211" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K211" s="5">
+        <v>0</v>
+      </c>
+      <c r="L211" s="5">
+        <v>61</v>
+      </c>
+      <c r="M211" s="5"/>
+      <c r="N211" s="5"/>
+      <c r="O211" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A212" s="5">
+        <v>133492349</v>
+      </c>
+      <c r="E212" s="5">
+        <v>601</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I212" s="5">
+        <v>42</v>
+      </c>
+      <c r="J212" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K212" s="5">
+        <v>0</v>
+      </c>
+      <c r="L212" s="5">
+        <v>61</v>
+      </c>
+      <c r="M212" s="5"/>
+      <c r="N212" s="5"/>
+      <c r="O212" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A213" s="5">
+        <v>133492377</v>
+      </c>
+      <c r="E213" s="5">
+        <v>601</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I213" s="5">
+        <v>42</v>
+      </c>
+      <c r="J213" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K213" s="5">
+        <v>0</v>
+      </c>
+      <c r="L213" s="5">
+        <v>61</v>
+      </c>
+      <c r="M213" s="5"/>
+      <c r="N213" s="5"/>
+      <c r="O213" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A214" s="5">
+        <v>133492486</v>
+      </c>
+      <c r="E214" s="5">
+        <v>601</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I214" s="5">
+        <v>42</v>
+      </c>
+      <c r="J214" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K214" s="5">
+        <v>0</v>
+      </c>
+      <c r="L214" s="5">
+        <v>61</v>
+      </c>
+      <c r="M214" s="5"/>
+      <c r="N214" s="5"/>
+      <c r="O214" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215" s="5">
+        <v>133492598</v>
+      </c>
+      <c r="E215" s="5">
+        <v>601</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I215" s="5">
+        <v>42</v>
+      </c>
+      <c r="J215" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K215" s="5">
+        <v>0</v>
+      </c>
+      <c r="L215" s="5">
+        <v>61</v>
+      </c>
+      <c r="M215" s="5"/>
+      <c r="N215" s="5"/>
+      <c r="O215" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A216" s="5">
+        <v>133492706</v>
+      </c>
+      <c r="E216" s="5">
+        <v>601</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I216" s="5">
+        <v>42</v>
+      </c>
+      <c r="J216" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K216" s="5">
+        <v>0</v>
+      </c>
+      <c r="L216" s="5">
+        <v>61</v>
+      </c>
+      <c r="M216" s="5"/>
+      <c r="N216" s="5"/>
+      <c r="O216" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A217" s="5">
+        <v>133492710</v>
+      </c>
+      <c r="E217" s="5">
+        <v>601</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I217" s="5">
+        <v>42</v>
+      </c>
+      <c r="J217" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K217" s="5">
+        <v>0</v>
+      </c>
+      <c r="L217" s="5">
+        <v>61</v>
+      </c>
+      <c r="M217" s="5"/>
+      <c r="N217" s="5"/>
+      <c r="O217" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A218" s="5">
+        <v>133492863</v>
+      </c>
+      <c r="E218" s="5">
+        <v>601</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I218" s="5">
+        <v>42</v>
+      </c>
+      <c r="J218" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K218" s="5">
+        <v>0</v>
+      </c>
+      <c r="L218" s="5">
+        <v>61</v>
+      </c>
+      <c r="M218" s="5"/>
+      <c r="N218" s="5"/>
+      <c r="O218" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A219" s="5">
+        <v>133492953</v>
+      </c>
+      <c r="E219" s="5">
+        <v>601</v>
+      </c>
+      <c r="F219" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I219" s="5">
+        <v>42</v>
+      </c>
+      <c r="J219" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K219" s="5">
+        <v>0</v>
+      </c>
+      <c r="L219" s="5">
+        <v>61</v>
+      </c>
+      <c r="M219" s="5"/>
+      <c r="N219" s="5"/>
+      <c r="O219" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A220" s="5">
+        <v>133493156</v>
+      </c>
+      <c r="E220" s="5">
+        <v>601</v>
+      </c>
+      <c r="F220" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I220" s="5">
+        <v>42</v>
+      </c>
+      <c r="J220" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K220" s="5">
+        <v>0</v>
+      </c>
+      <c r="L220" s="5">
+        <v>61</v>
+      </c>
+      <c r="M220" s="5"/>
+      <c r="N220" s="5"/>
+      <c r="O220" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A221" s="5">
+        <v>133493208</v>
+      </c>
+      <c r="E221" s="5">
+        <v>601</v>
+      </c>
+      <c r="F221" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I221" s="5">
+        <v>42</v>
+      </c>
+      <c r="J221" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K221" s="5">
+        <v>0</v>
+      </c>
+      <c r="L221" s="5">
+        <v>61</v>
+      </c>
+      <c r="M221" s="5"/>
+      <c r="N221" s="5"/>
+      <c r="O221" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A222" s="5">
+        <v>133493446</v>
+      </c>
+      <c r="E222" s="5">
+        <v>601</v>
+      </c>
+      <c r="F222" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I222" s="5">
+        <v>42</v>
+      </c>
+      <c r="J222" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K222" s="5">
+        <v>0</v>
+      </c>
+      <c r="L222" s="5">
+        <v>61</v>
+      </c>
+      <c r="M222" s="5"/>
+      <c r="N222" s="5"/>
+      <c r="O222" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD70F7F-2EFC-4137-8D75-1CCE3844BCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A82009A-C761-4CF1-88CE-1DA40FA2BF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="27">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,16 +79,37 @@
     <t>B</t>
   </si>
   <si>
+    <t>21/7/2025</t>
+  </si>
+  <si>
     <t>8/3/2023</t>
   </si>
   <si>
     <t>10/3/2023</t>
   </si>
   <si>
+    <t>23/7/2025</t>
+  </si>
+  <si>
     <t>17/7/2025</t>
   </si>
   <si>
     <t>22/7/2025</t>
+  </si>
+  <si>
+    <t>13/06/2025</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
+    <t>22/07/2025</t>
+  </si>
+  <si>
+    <t>23/07/2025</t>
+  </si>
+  <si>
+    <t>17/07/2025</t>
   </si>
 </sst>
 </file>
@@ -506,7 +527,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O314"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -576,22 +597,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>123058958</v>
+        <v>133525273</v>
       </c>
       <c r="E2" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8003</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -607,22 +628,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>133479798</v>
+        <v>123058958</v>
       </c>
       <c r="E3" s="5">
         <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>19</v>
-      </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -638,13 +659,13 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>133547412</v>
+        <v>128828598</v>
       </c>
       <c r="E4" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>19</v>
@@ -653,7 +674,7 @@
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -669,13 +690,13 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>133547468</v>
+        <v>129464931</v>
       </c>
       <c r="E5" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>19</v>
@@ -684,7 +705,7 @@
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -700,13 +721,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>133547647</v>
+        <v>129896460</v>
       </c>
       <c r="E6" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>19</v>
@@ -715,7 +736,7 @@
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -731,13 +752,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>133548963</v>
+        <v>131508518</v>
       </c>
       <c r="E7" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>19</v>
@@ -746,7 +767,7 @@
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -762,13 +783,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>133549006</v>
+        <v>131526427</v>
       </c>
       <c r="E8" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>19</v>
@@ -777,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -793,13 +814,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>133549119</v>
+        <v>132674435</v>
       </c>
       <c r="E9" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>19</v>
@@ -808,7 +829,7 @@
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -824,13 +845,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>133550057</v>
+        <v>132942672</v>
       </c>
       <c r="E10" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>19</v>
@@ -839,7 +860,7 @@
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -855,13 +876,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>133550353</v>
+        <v>128828598</v>
       </c>
       <c r="E11" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>19</v>
@@ -870,7 +891,7 @@
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -886,13 +907,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133550798</v>
+        <v>129464931</v>
       </c>
       <c r="E12" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>19</v>
@@ -901,7 +922,7 @@
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -917,13 +938,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>133550912</v>
+        <v>129896460</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>19</v>
@@ -932,7 +953,7 @@
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -948,22 +969,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>133550977</v>
+        <v>133479798</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -979,7 +1000,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>133551057</v>
+        <v>133569190</v>
       </c>
       <c r="E15" s="5">
         <v>2013</v>
@@ -1010,7 +1031,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>133551237</v>
+        <v>133569218</v>
       </c>
       <c r="E16" s="5">
         <v>2013</v>
@@ -1041,7 +1062,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>133551370</v>
+        <v>133569271</v>
       </c>
       <c r="E17" s="5">
         <v>2013</v>
@@ -1072,7 +1093,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>133551586</v>
+        <v>133570099</v>
       </c>
       <c r="E18" s="5">
         <v>2013</v>
@@ -1103,7 +1124,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>133552187</v>
+        <v>133570288</v>
       </c>
       <c r="E19" s="5">
         <v>2013</v>
@@ -1134,7 +1155,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>133552298</v>
+        <v>133570331</v>
       </c>
       <c r="E20" s="5">
         <v>2013</v>
@@ -1165,7 +1186,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>133552356</v>
+        <v>133570728</v>
       </c>
       <c r="E21" s="5">
         <v>2013</v>
@@ -1196,7 +1217,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>133552398</v>
+        <v>133572749</v>
       </c>
       <c r="E22" s="5">
         <v>2013</v>
@@ -1227,7 +1248,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>133552415</v>
+        <v>133573312</v>
       </c>
       <c r="E23" s="5">
         <v>2013</v>
@@ -1258,7 +1279,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>133552518</v>
+        <v>133573938</v>
       </c>
       <c r="E24" s="5">
         <v>2013</v>
@@ -1289,7 +1310,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>133552758</v>
+        <v>133574731</v>
       </c>
       <c r="E25" s="5">
         <v>2013</v>
@@ -1320,7 +1341,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>133553551</v>
+        <v>133575012</v>
       </c>
       <c r="E26" s="5">
         <v>2013</v>
@@ -1351,7 +1372,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>133554101</v>
+        <v>133575305</v>
       </c>
       <c r="E27" s="5">
         <v>2013</v>
@@ -1382,7 +1403,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>133554119</v>
+        <v>133575439</v>
       </c>
       <c r="E28" s="5">
         <v>2013</v>
@@ -1413,7 +1434,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>133554277</v>
+        <v>133575509</v>
       </c>
       <c r="E29" s="5">
         <v>2013</v>
@@ -1444,7 +1465,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>133555194</v>
+        <v>133576280</v>
       </c>
       <c r="E30" s="5">
         <v>2013</v>
@@ -1475,7 +1496,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>133555603</v>
+        <v>133576329</v>
       </c>
       <c r="E31" s="5">
         <v>2013</v>
@@ -1506,7 +1527,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>133555730</v>
+        <v>133576352</v>
       </c>
       <c r="E32" s="5">
         <v>2013</v>
@@ -1537,7 +1558,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>133557214</v>
+        <v>133576404</v>
       </c>
       <c r="E33" s="5">
         <v>2013</v>
@@ -1568,7 +1589,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>133557886</v>
+        <v>133576437</v>
       </c>
       <c r="E34" s="5">
         <v>2013</v>
@@ -1599,7 +1620,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>133558658</v>
+        <v>133576568</v>
       </c>
       <c r="E35" s="5">
         <v>2013</v>
@@ -1630,7 +1651,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>133558771</v>
+        <v>133576597</v>
       </c>
       <c r="E36" s="5">
         <v>2013</v>
@@ -1661,7 +1682,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>133559044</v>
+        <v>133576844</v>
       </c>
       <c r="E37" s="5">
         <v>2013</v>
@@ -1692,7 +1713,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>133559569</v>
+        <v>133576921</v>
       </c>
       <c r="E38" s="5">
         <v>2013</v>
@@ -1723,7 +1744,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>133559642</v>
+        <v>133577456</v>
       </c>
       <c r="E39" s="5">
         <v>2013</v>
@@ -1754,7 +1775,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>133560997</v>
+        <v>133577611</v>
       </c>
       <c r="E40" s="5">
         <v>2013</v>
@@ -1785,7 +1806,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>133561408</v>
+        <v>133577626</v>
       </c>
       <c r="E41" s="5">
         <v>2013</v>
@@ -1816,7 +1837,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>133561598</v>
+        <v>133577648</v>
       </c>
       <c r="E42" s="5">
         <v>2013</v>
@@ -1847,7 +1868,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>133561718</v>
+        <v>133577754</v>
       </c>
       <c r="E43" s="5">
         <v>2013</v>
@@ -1878,7 +1899,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>133561957</v>
+        <v>133577757</v>
       </c>
       <c r="E44" s="5">
         <v>2013</v>
@@ -1909,7 +1930,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>133562042</v>
+        <v>133577771</v>
       </c>
       <c r="E45" s="5">
         <v>2013</v>
@@ -1940,7 +1961,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>133563229</v>
+        <v>133577796</v>
       </c>
       <c r="E46" s="5">
         <v>2013</v>
@@ -1971,7 +1992,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>133564953</v>
+        <v>133577960</v>
       </c>
       <c r="E47" s="5">
         <v>2013</v>
@@ -2002,7 +2023,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>133564978</v>
+        <v>133578073</v>
       </c>
       <c r="E48" s="5">
         <v>2013</v>
@@ -2028,6 +2049,8252 @@
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
       <c r="O48" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>133578088</v>
+      </c>
+      <c r="E49" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="5">
+        <v>42</v>
+      </c>
+      <c r="J49" s="5">
+        <v>718</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>61</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>133578147</v>
+      </c>
+      <c r="E50" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="5">
+        <v>42</v>
+      </c>
+      <c r="J50" s="5">
+        <v>718</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>61</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>133578219</v>
+      </c>
+      <c r="E51" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="5">
+        <v>42</v>
+      </c>
+      <c r="J51" s="5">
+        <v>718</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>61</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>133578315</v>
+      </c>
+      <c r="E52" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="5">
+        <v>42</v>
+      </c>
+      <c r="J52" s="5">
+        <v>718</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>61</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>133578432</v>
+      </c>
+      <c r="E53" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="5">
+        <v>42</v>
+      </c>
+      <c r="J53" s="5">
+        <v>718</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <v>61</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>133578442</v>
+      </c>
+      <c r="E54" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="5">
+        <v>42</v>
+      </c>
+      <c r="J54" s="5">
+        <v>718</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>61</v>
+      </c>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>133578451</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="5">
+        <v>42</v>
+      </c>
+      <c r="J55" s="5">
+        <v>718</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>61</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>133578622</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="5">
+        <v>42</v>
+      </c>
+      <c r="J56" s="5">
+        <v>718</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>61</v>
+      </c>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>133578654</v>
+      </c>
+      <c r="E57" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="5">
+        <v>42</v>
+      </c>
+      <c r="J57" s="5">
+        <v>718</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>61</v>
+      </c>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>133578845</v>
+      </c>
+      <c r="E58" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="5">
+        <v>42</v>
+      </c>
+      <c r="J58" s="5">
+        <v>718</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>61</v>
+      </c>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>133579027</v>
+      </c>
+      <c r="E59" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="5">
+        <v>42</v>
+      </c>
+      <c r="J59" s="5">
+        <v>718</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5">
+        <v>61</v>
+      </c>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>133579398</v>
+      </c>
+      <c r="E60" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>718</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>133579959</v>
+      </c>
+      <c r="E61" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>718</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>133580234</v>
+      </c>
+      <c r="E62" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>718</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>133580262</v>
+      </c>
+      <c r="E63" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>718</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>133580424</v>
+      </c>
+      <c r="E64" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>718</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>133580481</v>
+      </c>
+      <c r="E65" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>718</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>133580557</v>
+      </c>
+      <c r="E66" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>718</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>133580614</v>
+      </c>
+      <c r="E67" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>718</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>133580815</v>
+      </c>
+      <c r="E68" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>718</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>133580869</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>718</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>133580990</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>718</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>133581029</v>
+      </c>
+      <c r="E71" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>718</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>133581162</v>
+      </c>
+      <c r="E72" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>718</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>133581326</v>
+      </c>
+      <c r="E73" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>718</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>133581397</v>
+      </c>
+      <c r="E74" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>718</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>133581480</v>
+      </c>
+      <c r="E75" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
+        <v>718</v>
+      </c>
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>133581532</v>
+      </c>
+      <c r="E76" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>718</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>133581616</v>
+      </c>
+      <c r="E77" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>718</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>133581645</v>
+      </c>
+      <c r="E78" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>718</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>133581713</v>
+      </c>
+      <c r="E79" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I79" s="5">
+        <v>42</v>
+      </c>
+      <c r="J79" s="5">
+        <v>718</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5">
+        <v>61</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>133581878</v>
+      </c>
+      <c r="E80" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" s="5">
+        <v>42</v>
+      </c>
+      <c r="J80" s="5">
+        <v>718</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>61</v>
+      </c>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>133581941</v>
+      </c>
+      <c r="E81" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" s="5">
+        <v>42</v>
+      </c>
+      <c r="J81" s="5">
+        <v>718</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>61</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>133582745</v>
+      </c>
+      <c r="E82" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I82" s="5">
+        <v>42</v>
+      </c>
+      <c r="J82" s="5">
+        <v>718</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5">
+        <v>61</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>133582988</v>
+      </c>
+      <c r="E83" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" s="5">
+        <v>42</v>
+      </c>
+      <c r="J83" s="5">
+        <v>718</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5">
+        <v>61</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>133583056</v>
+      </c>
+      <c r="E84" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" s="5">
+        <v>42</v>
+      </c>
+      <c r="J84" s="5">
+        <v>718</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5">
+        <v>61</v>
+      </c>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>133583093</v>
+      </c>
+      <c r="E85" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I85" s="5">
+        <v>42</v>
+      </c>
+      <c r="J85" s="5">
+        <v>718</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5">
+        <v>61</v>
+      </c>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>133583737</v>
+      </c>
+      <c r="E86" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" s="5">
+        <v>42</v>
+      </c>
+      <c r="J86" s="5">
+        <v>718</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5">
+        <v>61</v>
+      </c>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>133584132</v>
+      </c>
+      <c r="E87" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" s="5">
+        <v>42</v>
+      </c>
+      <c r="J87" s="5">
+        <v>718</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5">
+        <v>61</v>
+      </c>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>133584283</v>
+      </c>
+      <c r="E88" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>718</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>133584322</v>
+      </c>
+      <c r="E89" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      </c>
+      <c r="J89" s="5">
+        <v>718</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5">
+        <v>61</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
+        <v>133584608</v>
+      </c>
+      <c r="E90" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I90" s="5">
+        <v>42</v>
+      </c>
+      <c r="J90" s="5">
+        <v>718</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5">
+        <v>61</v>
+      </c>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>133584780</v>
+      </c>
+      <c r="E91" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" s="5">
+        <v>42</v>
+      </c>
+      <c r="J91" s="5">
+        <v>718</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5">
+        <v>61</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
+        <v>133585066</v>
+      </c>
+      <c r="E92" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" s="5">
+        <v>42</v>
+      </c>
+      <c r="J92" s="5">
+        <v>718</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5">
+        <v>61</v>
+      </c>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>133585219</v>
+      </c>
+      <c r="E93" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I93" s="5">
+        <v>42</v>
+      </c>
+      <c r="J93" s="5">
+        <v>718</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5">
+        <v>61</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
+        <v>133585277</v>
+      </c>
+      <c r="E94" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" s="5">
+        <v>42</v>
+      </c>
+      <c r="J94" s="5">
+        <v>718</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5">
+        <v>61</v>
+      </c>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>133585310</v>
+      </c>
+      <c r="E95" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I95" s="5">
+        <v>42</v>
+      </c>
+      <c r="J95" s="5">
+        <v>718</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>61</v>
+      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="5">
+        <v>132914455</v>
+      </c>
+      <c r="E96" s="5">
+        <v>609</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I96" s="5">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5">
+        <v>61</v>
+      </c>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
+        <v>133244678</v>
+      </c>
+      <c r="E97" s="5">
+        <v>601</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I97" s="5">
+        <v>42</v>
+      </c>
+      <c r="J97" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5">
+        <v>61</v>
+      </c>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="5">
+        <v>133391941</v>
+      </c>
+      <c r="E98" s="5">
+        <v>609</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98" s="5">
+        <v>42</v>
+      </c>
+      <c r="J98" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5">
+        <v>61</v>
+      </c>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
+        <v>133396115</v>
+      </c>
+      <c r="E99" s="5">
+        <v>609</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99" s="5">
+        <v>42</v>
+      </c>
+      <c r="J99" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
+        <v>61</v>
+      </c>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="5">
+        <v>133397731</v>
+      </c>
+      <c r="E100" s="5">
+        <v>609</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I100" s="5">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>61</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>133398313</v>
+      </c>
+      <c r="E101" s="5">
+        <v>609</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="5">
+        <v>42</v>
+      </c>
+      <c r="J101" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>61</v>
+      </c>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="5">
+        <v>133467886</v>
+      </c>
+      <c r="E102" s="5">
+        <v>601</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I102" s="5">
+        <v>42</v>
+      </c>
+      <c r="J102" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>61</v>
+      </c>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
+        <v>133470616</v>
+      </c>
+      <c r="E103" s="5">
+        <v>601</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I103" s="5">
+        <v>42</v>
+      </c>
+      <c r="J103" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>61</v>
+      </c>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="5">
+        <v>133471434</v>
+      </c>
+      <c r="E104" s="5">
+        <v>601</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I104" s="5">
+        <v>42</v>
+      </c>
+      <c r="J104" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5">
+        <v>61</v>
+      </c>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
+        <v>133484718</v>
+      </c>
+      <c r="E105" s="5">
+        <v>601</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I105" s="5">
+        <v>42</v>
+      </c>
+      <c r="J105" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5">
+        <v>61</v>
+      </c>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="5">
+        <v>133497475</v>
+      </c>
+      <c r="E106" s="5">
+        <v>601</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I106" s="5">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5">
+        <v>61</v>
+      </c>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="5">
+        <v>133534897</v>
+      </c>
+      <c r="E107" s="5">
+        <v>601</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107" s="5">
+        <v>42</v>
+      </c>
+      <c r="J107" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5">
+        <v>61</v>
+      </c>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="5">
+        <v>133547063</v>
+      </c>
+      <c r="E108" s="5">
+        <v>609</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108" s="5">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5">
+        <v>61</v>
+      </c>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="5">
+        <v>133547361</v>
+      </c>
+      <c r="E109" s="5">
+        <v>601</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I109" s="5">
+        <v>42</v>
+      </c>
+      <c r="J109" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5">
+        <v>61</v>
+      </c>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="5">
+        <v>133547825</v>
+      </c>
+      <c r="E110" s="5">
+        <v>601</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I110" s="5">
+        <v>42</v>
+      </c>
+      <c r="J110" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5">
+        <v>61</v>
+      </c>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="5">
+        <v>133547928</v>
+      </c>
+      <c r="E111" s="5">
+        <v>601</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I111" s="5">
+        <v>42</v>
+      </c>
+      <c r="J111" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5">
+        <v>61</v>
+      </c>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="5">
+        <v>133547980</v>
+      </c>
+      <c r="E112" s="5">
+        <v>601</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I112" s="5">
+        <v>42</v>
+      </c>
+      <c r="J112" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5">
+        <v>61</v>
+      </c>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="5">
+        <v>133548557</v>
+      </c>
+      <c r="E113" s="5">
+        <v>601</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I113" s="5">
+        <v>42</v>
+      </c>
+      <c r="J113" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5">
+        <v>61</v>
+      </c>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="5">
+        <v>133548663</v>
+      </c>
+      <c r="E114" s="5">
+        <v>601</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I114" s="5">
+        <v>42</v>
+      </c>
+      <c r="J114" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5">
+        <v>61</v>
+      </c>
+      <c r="M114" s="5"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="5">
+        <v>133549070</v>
+      </c>
+      <c r="E115" s="5">
+        <v>601</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I115" s="5">
+        <v>42</v>
+      </c>
+      <c r="J115" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5">
+        <v>61</v>
+      </c>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="5">
+        <v>133549177</v>
+      </c>
+      <c r="E116" s="5">
+        <v>601</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I116" s="5">
+        <v>42</v>
+      </c>
+      <c r="J116" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" s="5">
+        <v>61</v>
+      </c>
+      <c r="M116" s="5"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="5">
+        <v>133549189</v>
+      </c>
+      <c r="E117" s="5">
+        <v>601</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I117" s="5">
+        <v>42</v>
+      </c>
+      <c r="J117" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" s="5">
+        <v>61</v>
+      </c>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="5">
+        <v>133549298</v>
+      </c>
+      <c r="E118" s="5">
+        <v>609</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118" s="5">
+        <v>42</v>
+      </c>
+      <c r="J118" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5">
+        <v>61</v>
+      </c>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5"/>
+      <c r="O118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="5">
+        <v>133549382</v>
+      </c>
+      <c r="E119" s="5">
+        <v>601</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I119" s="5">
+        <v>42</v>
+      </c>
+      <c r="J119" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5">
+        <v>61</v>
+      </c>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="5">
+        <v>133549491</v>
+      </c>
+      <c r="E120" s="5">
+        <v>601</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I120" s="5">
+        <v>42</v>
+      </c>
+      <c r="J120" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5">
+        <v>61</v>
+      </c>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="5">
+        <v>133549794</v>
+      </c>
+      <c r="E121" s="5">
+        <v>601</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121" s="5">
+        <v>42</v>
+      </c>
+      <c r="J121" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5">
+        <v>61</v>
+      </c>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="5">
+        <v>133549841</v>
+      </c>
+      <c r="E122" s="5">
+        <v>601</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="5">
+        <v>133549871</v>
+      </c>
+      <c r="E123" s="5">
+        <v>601</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="5">
+        <v>133550025</v>
+      </c>
+      <c r="E124" s="5">
+        <v>601</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="5">
+        <v>133550337</v>
+      </c>
+      <c r="E125" s="5">
+        <v>601</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="5">
+        <v>133550442</v>
+      </c>
+      <c r="E126" s="5">
+        <v>601</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="5">
+        <v>133550761</v>
+      </c>
+      <c r="E127" s="5">
+        <v>601</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="5">
+        <v>133551115</v>
+      </c>
+      <c r="E128" s="5">
+        <v>601</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="5">
+        <v>133551172</v>
+      </c>
+      <c r="E129" s="5">
+        <v>601</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="5">
+        <v>133551277</v>
+      </c>
+      <c r="E130" s="5">
+        <v>601</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="5">
+        <v>133551798</v>
+      </c>
+      <c r="E131" s="5">
+        <v>601</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="5">
+        <v>133552039</v>
+      </c>
+      <c r="E132" s="5">
+        <v>601</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="5">
+        <v>133552329</v>
+      </c>
+      <c r="E133" s="5">
+        <v>601</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="M133" s="5"/>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="5">
+        <v>133552331</v>
+      </c>
+      <c r="E134" s="5">
+        <v>601</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="M134" s="5"/>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="5">
+        <v>133552354</v>
+      </c>
+      <c r="E135" s="5">
+        <v>601</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="5">
+        <v>133552911</v>
+      </c>
+      <c r="E136" s="5">
+        <v>601</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="M136" s="5"/>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
+        <v>133552988</v>
+      </c>
+      <c r="E137" s="5">
+        <v>601</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="M137" s="5"/>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="5">
+        <v>133553050</v>
+      </c>
+      <c r="E138" s="5">
+        <v>601</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="M138" s="5"/>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="5">
+        <v>133553290</v>
+      </c>
+      <c r="E139" s="5">
+        <v>601</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+      <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="5">
+        <v>133553386</v>
+      </c>
+      <c r="E140" s="5">
+        <v>601</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="5">
+        <v>133553778</v>
+      </c>
+      <c r="E141" s="5">
+        <v>601</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="5">
+        <v>133553911</v>
+      </c>
+      <c r="E142" s="5">
+        <v>601</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="M142" s="5"/>
+      <c r="N142" s="5"/>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="5">
+        <v>133554217</v>
+      </c>
+      <c r="E143" s="5">
+        <v>601</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="M143" s="5"/>
+      <c r="N143" s="5"/>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="5">
+        <v>133554904</v>
+      </c>
+      <c r="E144" s="5">
+        <v>601</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="M144" s="5"/>
+      <c r="N144" s="5"/>
+      <c r="O144" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="5">
+        <v>133555081</v>
+      </c>
+      <c r="E145" s="5">
+        <v>601</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I145" s="5">
+        <v>42</v>
+      </c>
+      <c r="J145" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="L145" s="5">
+        <v>61</v>
+      </c>
+      <c r="M145" s="5"/>
+      <c r="N145" s="5"/>
+      <c r="O145" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="5">
+        <v>133555515</v>
+      </c>
+      <c r="E146" s="5">
+        <v>601</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I146" s="5">
+        <v>42</v>
+      </c>
+      <c r="J146" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5">
+        <v>61</v>
+      </c>
+      <c r="M146" s="5"/>
+      <c r="N146" s="5"/>
+      <c r="O146" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="5">
+        <v>133556098</v>
+      </c>
+      <c r="E147" s="5">
+        <v>601</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I147" s="5">
+        <v>42</v>
+      </c>
+      <c r="J147" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5">
+        <v>61</v>
+      </c>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="5">
+        <v>133556113</v>
+      </c>
+      <c r="E148" s="5">
+        <v>601</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I148" s="5">
+        <v>42</v>
+      </c>
+      <c r="J148" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5">
+        <v>61</v>
+      </c>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="5">
+        <v>133556660</v>
+      </c>
+      <c r="E149" s="5">
+        <v>601</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I149" s="5">
+        <v>42</v>
+      </c>
+      <c r="J149" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5">
+        <v>61</v>
+      </c>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
+      <c r="O149" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="5">
+        <v>133556927</v>
+      </c>
+      <c r="E150" s="5">
+        <v>601</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I150" s="5">
+        <v>42</v>
+      </c>
+      <c r="J150" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5">
+        <v>61</v>
+      </c>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="5">
+        <v>133557670</v>
+      </c>
+      <c r="E151" s="5">
+        <v>601</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I151" s="5">
+        <v>42</v>
+      </c>
+      <c r="J151" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5">
+        <v>61</v>
+      </c>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="5">
+        <v>133558040</v>
+      </c>
+      <c r="E152" s="5">
+        <v>601</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I152" s="5">
+        <v>42</v>
+      </c>
+      <c r="J152" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="L152" s="5">
+        <v>61</v>
+      </c>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="5">
+        <v>133558089</v>
+      </c>
+      <c r="E153" s="5">
+        <v>609</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I153" s="5">
+        <v>42</v>
+      </c>
+      <c r="J153" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K153" s="5">
+        <v>0</v>
+      </c>
+      <c r="L153" s="5">
+        <v>61</v>
+      </c>
+      <c r="M153" s="5"/>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="5">
+        <v>133558490</v>
+      </c>
+      <c r="E154" s="5">
+        <v>601</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I154" s="5">
+        <v>42</v>
+      </c>
+      <c r="J154" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K154" s="5">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5">
+        <v>61</v>
+      </c>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="5">
+        <v>133558592</v>
+      </c>
+      <c r="E155" s="5">
+        <v>601</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I155" s="5">
+        <v>42</v>
+      </c>
+      <c r="J155" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K155" s="5">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5">
+        <v>61</v>
+      </c>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="5">
+        <v>133558659</v>
+      </c>
+      <c r="E156" s="5">
+        <v>601</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I156" s="5">
+        <v>42</v>
+      </c>
+      <c r="J156" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K156" s="5">
+        <v>0</v>
+      </c>
+      <c r="L156" s="5">
+        <v>61</v>
+      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="5">
+        <v>133558709</v>
+      </c>
+      <c r="E157" s="5">
+        <v>601</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I157" s="5">
+        <v>42</v>
+      </c>
+      <c r="J157" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K157" s="5">
+        <v>0</v>
+      </c>
+      <c r="L157" s="5">
+        <v>61</v>
+      </c>
+      <c r="M157" s="5"/>
+      <c r="N157" s="5"/>
+      <c r="O157" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="5">
+        <v>133558939</v>
+      </c>
+      <c r="E158" s="5">
+        <v>601</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I158" s="5">
+        <v>42</v>
+      </c>
+      <c r="J158" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K158" s="5">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5">
+        <v>61</v>
+      </c>
+      <c r="M158" s="5"/>
+      <c r="N158" s="5"/>
+      <c r="O158" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="5">
+        <v>133558986</v>
+      </c>
+      <c r="E159" s="5">
+        <v>601</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I159" s="5">
+        <v>42</v>
+      </c>
+      <c r="J159" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K159" s="5">
+        <v>0</v>
+      </c>
+      <c r="L159" s="5">
+        <v>61</v>
+      </c>
+      <c r="M159" s="5"/>
+      <c r="N159" s="5"/>
+      <c r="O159" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="5">
+        <v>133558992</v>
+      </c>
+      <c r="E160" s="5">
+        <v>601</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I160" s="5">
+        <v>42</v>
+      </c>
+      <c r="J160" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K160" s="5">
+        <v>0</v>
+      </c>
+      <c r="L160" s="5">
+        <v>61</v>
+      </c>
+      <c r="M160" s="5"/>
+      <c r="N160" s="5"/>
+      <c r="O160" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="5">
+        <v>133559406</v>
+      </c>
+      <c r="E161" s="5">
+        <v>601</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I161" s="5">
+        <v>42</v>
+      </c>
+      <c r="J161" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K161" s="5">
+        <v>0</v>
+      </c>
+      <c r="L161" s="5">
+        <v>61</v>
+      </c>
+      <c r="M161" s="5"/>
+      <c r="N161" s="5"/>
+      <c r="O161" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="5">
+        <v>133559580</v>
+      </c>
+      <c r="E162" s="5">
+        <v>601</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I162" s="5">
+        <v>42</v>
+      </c>
+      <c r="J162" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K162" s="5">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5">
+        <v>61</v>
+      </c>
+      <c r="M162" s="5"/>
+      <c r="N162" s="5"/>
+      <c r="O162" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="5">
+        <v>133559681</v>
+      </c>
+      <c r="E163" s="5">
+        <v>601</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I163" s="5">
+        <v>42</v>
+      </c>
+      <c r="J163" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K163" s="5">
+        <v>0</v>
+      </c>
+      <c r="L163" s="5">
+        <v>61</v>
+      </c>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
+      <c r="O163" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164" s="5">
+        <v>133559894</v>
+      </c>
+      <c r="E164" s="5">
+        <v>601</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I164" s="5">
+        <v>42</v>
+      </c>
+      <c r="J164" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K164" s="5">
+        <v>0</v>
+      </c>
+      <c r="L164" s="5">
+        <v>61</v>
+      </c>
+      <c r="M164" s="5"/>
+      <c r="N164" s="5"/>
+      <c r="O164" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165" s="5">
+        <v>133560971</v>
+      </c>
+      <c r="E165" s="5">
+        <v>601</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I165" s="5">
+        <v>42</v>
+      </c>
+      <c r="J165" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K165" s="5">
+        <v>0</v>
+      </c>
+      <c r="L165" s="5">
+        <v>61</v>
+      </c>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+      <c r="O165" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166" s="5">
+        <v>133561053</v>
+      </c>
+      <c r="E166" s="5">
+        <v>601</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I166" s="5">
+        <v>42</v>
+      </c>
+      <c r="J166" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K166" s="5">
+        <v>0</v>
+      </c>
+      <c r="L166" s="5">
+        <v>61</v>
+      </c>
+      <c r="M166" s="5"/>
+      <c r="N166" s="5"/>
+      <c r="O166" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="5">
+        <v>133561235</v>
+      </c>
+      <c r="E167" s="5">
+        <v>601</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I167" s="5">
+        <v>42</v>
+      </c>
+      <c r="J167" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K167" s="5">
+        <v>0</v>
+      </c>
+      <c r="L167" s="5">
+        <v>61</v>
+      </c>
+      <c r="M167" s="5"/>
+      <c r="N167" s="5"/>
+      <c r="O167" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168" s="5">
+        <v>133561450</v>
+      </c>
+      <c r="E168" s="5">
+        <v>601</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I168" s="5">
+        <v>42</v>
+      </c>
+      <c r="J168" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K168" s="5">
+        <v>0</v>
+      </c>
+      <c r="L168" s="5">
+        <v>61</v>
+      </c>
+      <c r="M168" s="5"/>
+      <c r="N168" s="5"/>
+      <c r="O168" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169" s="5">
+        <v>133561472</v>
+      </c>
+      <c r="E169" s="5">
+        <v>601</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I169" s="5">
+        <v>42</v>
+      </c>
+      <c r="J169" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K169" s="5">
+        <v>0</v>
+      </c>
+      <c r="L169" s="5">
+        <v>61</v>
+      </c>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="5">
+        <v>133561507</v>
+      </c>
+      <c r="E170" s="5">
+        <v>601</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I170" s="5">
+        <v>42</v>
+      </c>
+      <c r="J170" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K170" s="5">
+        <v>0</v>
+      </c>
+      <c r="L170" s="5">
+        <v>61</v>
+      </c>
+      <c r="M170" s="5"/>
+      <c r="N170" s="5"/>
+      <c r="O170" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171" s="5">
+        <v>133561634</v>
+      </c>
+      <c r="E171" s="5">
+        <v>601</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I171" s="5">
+        <v>42</v>
+      </c>
+      <c r="J171" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K171" s="5">
+        <v>0</v>
+      </c>
+      <c r="L171" s="5">
+        <v>61</v>
+      </c>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="5">
+        <v>133562408</v>
+      </c>
+      <c r="E172" s="5">
+        <v>601</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I172" s="5">
+        <v>42</v>
+      </c>
+      <c r="J172" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K172" s="5">
+        <v>0</v>
+      </c>
+      <c r="L172" s="5">
+        <v>61</v>
+      </c>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+      <c r="O172" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="5">
+        <v>133562481</v>
+      </c>
+      <c r="E173" s="5">
+        <v>601</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I173" s="5">
+        <v>42</v>
+      </c>
+      <c r="J173" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K173" s="5">
+        <v>0</v>
+      </c>
+      <c r="L173" s="5">
+        <v>61</v>
+      </c>
+      <c r="M173" s="5"/>
+      <c r="N173" s="5"/>
+      <c r="O173" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="5">
+        <v>133562703</v>
+      </c>
+      <c r="E174" s="5">
+        <v>601</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I174" s="5">
+        <v>42</v>
+      </c>
+      <c r="J174" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K174" s="5">
+        <v>0</v>
+      </c>
+      <c r="L174" s="5">
+        <v>61</v>
+      </c>
+      <c r="M174" s="5"/>
+      <c r="N174" s="5"/>
+      <c r="O174" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" s="5">
+        <v>133562728</v>
+      </c>
+      <c r="E175" s="5">
+        <v>601</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I175" s="5">
+        <v>42</v>
+      </c>
+      <c r="J175" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K175" s="5">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5">
+        <v>61</v>
+      </c>
+      <c r="M175" s="5"/>
+      <c r="N175" s="5"/>
+      <c r="O175" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" s="5">
+        <v>133562829</v>
+      </c>
+      <c r="E176" s="5">
+        <v>601</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I176" s="5">
+        <v>42</v>
+      </c>
+      <c r="J176" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K176" s="5">
+        <v>0</v>
+      </c>
+      <c r="L176" s="5">
+        <v>61</v>
+      </c>
+      <c r="M176" s="5"/>
+      <c r="N176" s="5"/>
+      <c r="O176" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" s="5">
+        <v>133562875</v>
+      </c>
+      <c r="E177" s="5">
+        <v>601</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I177" s="5">
+        <v>42</v>
+      </c>
+      <c r="J177" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K177" s="5">
+        <v>0</v>
+      </c>
+      <c r="L177" s="5">
+        <v>61</v>
+      </c>
+      <c r="M177" s="5"/>
+      <c r="N177" s="5"/>
+      <c r="O177" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" s="5">
+        <v>133562922</v>
+      </c>
+      <c r="E178" s="5">
+        <v>601</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I178" s="5">
+        <v>42</v>
+      </c>
+      <c r="J178" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K178" s="5">
+        <v>0</v>
+      </c>
+      <c r="L178" s="5">
+        <v>61</v>
+      </c>
+      <c r="M178" s="5"/>
+      <c r="N178" s="5"/>
+      <c r="O178" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="5">
+        <v>133563088</v>
+      </c>
+      <c r="E179" s="5">
+        <v>601</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I179" s="5">
+        <v>42</v>
+      </c>
+      <c r="J179" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K179" s="5">
+        <v>0</v>
+      </c>
+      <c r="L179" s="5">
+        <v>61</v>
+      </c>
+      <c r="M179" s="5"/>
+      <c r="N179" s="5"/>
+      <c r="O179" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" s="5">
+        <v>133563158</v>
+      </c>
+      <c r="E180" s="5">
+        <v>601</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I180" s="5">
+        <v>42</v>
+      </c>
+      <c r="J180" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K180" s="5">
+        <v>0</v>
+      </c>
+      <c r="L180" s="5">
+        <v>61</v>
+      </c>
+      <c r="M180" s="5"/>
+      <c r="N180" s="5"/>
+      <c r="O180" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" s="5">
+        <v>133563245</v>
+      </c>
+      <c r="E181" s="5">
+        <v>601</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I181" s="5">
+        <v>42</v>
+      </c>
+      <c r="J181" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K181" s="5">
+        <v>0</v>
+      </c>
+      <c r="L181" s="5">
+        <v>61</v>
+      </c>
+      <c r="M181" s="5"/>
+      <c r="N181" s="5"/>
+      <c r="O181" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" s="5">
+        <v>133563606</v>
+      </c>
+      <c r="E182" s="5">
+        <v>601</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I182" s="5">
+        <v>42</v>
+      </c>
+      <c r="J182" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K182" s="5">
+        <v>0</v>
+      </c>
+      <c r="L182" s="5">
+        <v>61</v>
+      </c>
+      <c r="M182" s="5"/>
+      <c r="N182" s="5"/>
+      <c r="O182" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183" s="5">
+        <v>133563730</v>
+      </c>
+      <c r="E183" s="5">
+        <v>601</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I183" s="5">
+        <v>42</v>
+      </c>
+      <c r="J183" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K183" s="5">
+        <v>0</v>
+      </c>
+      <c r="L183" s="5">
+        <v>61</v>
+      </c>
+      <c r="M183" s="5"/>
+      <c r="N183" s="5"/>
+      <c r="O183" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184" s="5">
+        <v>133563884</v>
+      </c>
+      <c r="E184" s="5">
+        <v>601</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I184" s="5">
+        <v>42</v>
+      </c>
+      <c r="J184" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K184" s="5">
+        <v>0</v>
+      </c>
+      <c r="L184" s="5">
+        <v>61</v>
+      </c>
+      <c r="M184" s="5"/>
+      <c r="N184" s="5"/>
+      <c r="O184" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" s="5">
+        <v>133564001</v>
+      </c>
+      <c r="E185" s="5">
+        <v>609</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I185" s="5">
+        <v>42</v>
+      </c>
+      <c r="J185" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K185" s="5">
+        <v>0</v>
+      </c>
+      <c r="L185" s="5">
+        <v>61</v>
+      </c>
+      <c r="M185" s="5"/>
+      <c r="N185" s="5"/>
+      <c r="O185" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186" s="5">
+        <v>133564246</v>
+      </c>
+      <c r="E186" s="5">
+        <v>601</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I186" s="5">
+        <v>42</v>
+      </c>
+      <c r="J186" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K186" s="5">
+        <v>0</v>
+      </c>
+      <c r="L186" s="5">
+        <v>61</v>
+      </c>
+      <c r="M186" s="5"/>
+      <c r="N186" s="5"/>
+      <c r="O186" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187" s="5">
+        <v>133564403</v>
+      </c>
+      <c r="E187" s="5">
+        <v>601</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I187" s="5">
+        <v>42</v>
+      </c>
+      <c r="J187" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K187" s="5">
+        <v>0</v>
+      </c>
+      <c r="L187" s="5">
+        <v>61</v>
+      </c>
+      <c r="M187" s="5"/>
+      <c r="N187" s="5"/>
+      <c r="O187" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" s="5">
+        <v>133565335</v>
+      </c>
+      <c r="E188" s="5">
+        <v>601</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I188" s="5">
+        <v>42</v>
+      </c>
+      <c r="J188" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K188" s="5">
+        <v>0</v>
+      </c>
+      <c r="L188" s="5">
+        <v>61</v>
+      </c>
+      <c r="M188" s="5"/>
+      <c r="N188" s="5"/>
+      <c r="O188" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189" s="5">
+        <v>133565678</v>
+      </c>
+      <c r="E189" s="5">
+        <v>601</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I189" s="5">
+        <v>42</v>
+      </c>
+      <c r="J189" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K189" s="5">
+        <v>0</v>
+      </c>
+      <c r="L189" s="5">
+        <v>61</v>
+      </c>
+      <c r="M189" s="5"/>
+      <c r="N189" s="5"/>
+      <c r="O189" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190" s="5">
+        <v>133565755</v>
+      </c>
+      <c r="E190" s="5">
+        <v>601</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I190" s="5">
+        <v>42</v>
+      </c>
+      <c r="J190" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K190" s="5">
+        <v>0</v>
+      </c>
+      <c r="L190" s="5">
+        <v>61</v>
+      </c>
+      <c r="M190" s="5"/>
+      <c r="N190" s="5"/>
+      <c r="O190" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191" s="5">
+        <v>133565949</v>
+      </c>
+      <c r="E191" s="5">
+        <v>601</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I191" s="5">
+        <v>42</v>
+      </c>
+      <c r="J191" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K191" s="5">
+        <v>0</v>
+      </c>
+      <c r="L191" s="5">
+        <v>61</v>
+      </c>
+      <c r="M191" s="5"/>
+      <c r="N191" s="5"/>
+      <c r="O191" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192" s="5">
+        <v>133565968</v>
+      </c>
+      <c r="E192" s="5">
+        <v>601</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I192" s="5">
+        <v>42</v>
+      </c>
+      <c r="J192" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K192" s="5">
+        <v>0</v>
+      </c>
+      <c r="L192" s="5">
+        <v>61</v>
+      </c>
+      <c r="M192" s="5"/>
+      <c r="N192" s="5"/>
+      <c r="O192" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A193" s="5">
+        <v>133566144</v>
+      </c>
+      <c r="E193" s="5">
+        <v>601</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I193" s="5">
+        <v>42</v>
+      </c>
+      <c r="J193" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K193" s="5">
+        <v>0</v>
+      </c>
+      <c r="L193" s="5">
+        <v>61</v>
+      </c>
+      <c r="M193" s="5"/>
+      <c r="N193" s="5"/>
+      <c r="O193" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A194" s="5">
+        <v>133566305</v>
+      </c>
+      <c r="E194" s="5">
+        <v>601</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I194" s="5">
+        <v>42</v>
+      </c>
+      <c r="J194" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K194" s="5">
+        <v>0</v>
+      </c>
+      <c r="L194" s="5">
+        <v>61</v>
+      </c>
+      <c r="M194" s="5"/>
+      <c r="N194" s="5"/>
+      <c r="O194" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A195" s="5">
+        <v>133567871</v>
+      </c>
+      <c r="E195" s="5">
+        <v>609</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I195" s="5">
+        <v>42</v>
+      </c>
+      <c r="J195" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K195" s="5">
+        <v>0</v>
+      </c>
+      <c r="L195" s="5">
+        <v>61</v>
+      </c>
+      <c r="M195" s="5"/>
+      <c r="N195" s="5"/>
+      <c r="O195" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A196" s="5">
+        <v>133569109</v>
+      </c>
+      <c r="E196" s="5">
+        <v>601</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I196" s="5">
+        <v>42</v>
+      </c>
+      <c r="J196" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K196" s="5">
+        <v>0</v>
+      </c>
+      <c r="L196" s="5">
+        <v>61</v>
+      </c>
+      <c r="M196" s="5"/>
+      <c r="N196" s="5"/>
+      <c r="O196" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197" s="5">
+        <v>133569153</v>
+      </c>
+      <c r="E197" s="5">
+        <v>601</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I197" s="5">
+        <v>42</v>
+      </c>
+      <c r="J197" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K197" s="5">
+        <v>0</v>
+      </c>
+      <c r="L197" s="5">
+        <v>61</v>
+      </c>
+      <c r="M197" s="5"/>
+      <c r="N197" s="5"/>
+      <c r="O197" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198" s="5">
+        <v>133569175</v>
+      </c>
+      <c r="E198" s="5">
+        <v>601</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I198" s="5">
+        <v>42</v>
+      </c>
+      <c r="J198" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K198" s="5">
+        <v>0</v>
+      </c>
+      <c r="L198" s="5">
+        <v>61</v>
+      </c>
+      <c r="M198" s="5"/>
+      <c r="N198" s="5"/>
+      <c r="O198" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A199" s="5">
+        <v>133569259</v>
+      </c>
+      <c r="E199" s="5">
+        <v>601</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I199" s="5">
+        <v>42</v>
+      </c>
+      <c r="J199" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K199" s="5">
+        <v>0</v>
+      </c>
+      <c r="L199" s="5">
+        <v>61</v>
+      </c>
+      <c r="M199" s="5"/>
+      <c r="N199" s="5"/>
+      <c r="O199" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A200" s="5">
+        <v>133569281</v>
+      </c>
+      <c r="E200" s="5">
+        <v>601</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I200" s="5">
+        <v>42</v>
+      </c>
+      <c r="J200" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K200" s="5">
+        <v>0</v>
+      </c>
+      <c r="L200" s="5">
+        <v>61</v>
+      </c>
+      <c r="M200" s="5"/>
+      <c r="N200" s="5"/>
+      <c r="O200" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A201" s="5">
+        <v>133569308</v>
+      </c>
+      <c r="E201" s="5">
+        <v>601</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I201" s="5">
+        <v>42</v>
+      </c>
+      <c r="J201" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K201" s="5">
+        <v>0</v>
+      </c>
+      <c r="L201" s="5">
+        <v>61</v>
+      </c>
+      <c r="M201" s="5"/>
+      <c r="N201" s="5"/>
+      <c r="O201" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A202" s="5">
+        <v>133569388</v>
+      </c>
+      <c r="E202" s="5">
+        <v>601</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I202" s="5">
+        <v>42</v>
+      </c>
+      <c r="J202" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K202" s="5">
+        <v>0</v>
+      </c>
+      <c r="L202" s="5">
+        <v>61</v>
+      </c>
+      <c r="M202" s="5"/>
+      <c r="N202" s="5"/>
+      <c r="O202" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203" s="5">
+        <v>133569540</v>
+      </c>
+      <c r="E203" s="5">
+        <v>601</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I203" s="5">
+        <v>42</v>
+      </c>
+      <c r="J203" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K203" s="5">
+        <v>0</v>
+      </c>
+      <c r="L203" s="5">
+        <v>61</v>
+      </c>
+      <c r="M203" s="5"/>
+      <c r="N203" s="5"/>
+      <c r="O203" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204" s="5">
+        <v>133569587</v>
+      </c>
+      <c r="E204" s="5">
+        <v>601</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I204" s="5">
+        <v>42</v>
+      </c>
+      <c r="J204" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K204" s="5">
+        <v>0</v>
+      </c>
+      <c r="L204" s="5">
+        <v>61</v>
+      </c>
+      <c r="M204" s="5"/>
+      <c r="N204" s="5"/>
+      <c r="O204" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A205" s="5">
+        <v>133569656</v>
+      </c>
+      <c r="E205" s="5">
+        <v>601</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I205" s="5">
+        <v>42</v>
+      </c>
+      <c r="J205" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K205" s="5">
+        <v>0</v>
+      </c>
+      <c r="L205" s="5">
+        <v>61</v>
+      </c>
+      <c r="M205" s="5"/>
+      <c r="N205" s="5"/>
+      <c r="O205" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206" s="5">
+        <v>133569723</v>
+      </c>
+      <c r="E206" s="5">
+        <v>601</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I206" s="5">
+        <v>42</v>
+      </c>
+      <c r="J206" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K206" s="5">
+        <v>0</v>
+      </c>
+      <c r="L206" s="5">
+        <v>61</v>
+      </c>
+      <c r="M206" s="5"/>
+      <c r="N206" s="5"/>
+      <c r="O206" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207" s="5">
+        <v>133569770</v>
+      </c>
+      <c r="E207" s="5">
+        <v>601</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I207" s="5">
+        <v>42</v>
+      </c>
+      <c r="J207" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K207" s="5">
+        <v>0</v>
+      </c>
+      <c r="L207" s="5">
+        <v>61</v>
+      </c>
+      <c r="M207" s="5"/>
+      <c r="N207" s="5"/>
+      <c r="O207" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208" s="5">
+        <v>133569773</v>
+      </c>
+      <c r="E208" s="5">
+        <v>601</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I208" s="5">
+        <v>42</v>
+      </c>
+      <c r="J208" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K208" s="5">
+        <v>0</v>
+      </c>
+      <c r="L208" s="5">
+        <v>61</v>
+      </c>
+      <c r="M208" s="5"/>
+      <c r="N208" s="5"/>
+      <c r="O208" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209" s="5">
+        <v>133569776</v>
+      </c>
+      <c r="E209" s="5">
+        <v>601</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I209" s="5">
+        <v>42</v>
+      </c>
+      <c r="J209" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K209" s="5">
+        <v>0</v>
+      </c>
+      <c r="L209" s="5">
+        <v>61</v>
+      </c>
+      <c r="M209" s="5"/>
+      <c r="N209" s="5"/>
+      <c r="O209" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210" s="5">
+        <v>133569777</v>
+      </c>
+      <c r="E210" s="5">
+        <v>601</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I210" s="5">
+        <v>42</v>
+      </c>
+      <c r="J210" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K210" s="5">
+        <v>0</v>
+      </c>
+      <c r="L210" s="5">
+        <v>61</v>
+      </c>
+      <c r="M210" s="5"/>
+      <c r="N210" s="5"/>
+      <c r="O210" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A211" s="5">
+        <v>133569781</v>
+      </c>
+      <c r="E211" s="5">
+        <v>601</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I211" s="5">
+        <v>42</v>
+      </c>
+      <c r="J211" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K211" s="5">
+        <v>0</v>
+      </c>
+      <c r="L211" s="5">
+        <v>61</v>
+      </c>
+      <c r="M211" s="5"/>
+      <c r="N211" s="5"/>
+      <c r="O211" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A212" s="5">
+        <v>133569908</v>
+      </c>
+      <c r="E212" s="5">
+        <v>601</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I212" s="5">
+        <v>42</v>
+      </c>
+      <c r="J212" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K212" s="5">
+        <v>0</v>
+      </c>
+      <c r="L212" s="5">
+        <v>61</v>
+      </c>
+      <c r="M212" s="5"/>
+      <c r="N212" s="5"/>
+      <c r="O212" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A213" s="5">
+        <v>133569911</v>
+      </c>
+      <c r="E213" s="5">
+        <v>601</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I213" s="5">
+        <v>42</v>
+      </c>
+      <c r="J213" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K213" s="5">
+        <v>0</v>
+      </c>
+      <c r="L213" s="5">
+        <v>61</v>
+      </c>
+      <c r="M213" s="5"/>
+      <c r="N213" s="5"/>
+      <c r="O213" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A214" s="5">
+        <v>133570276</v>
+      </c>
+      <c r="E214" s="5">
+        <v>601</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I214" s="5">
+        <v>42</v>
+      </c>
+      <c r="J214" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K214" s="5">
+        <v>0</v>
+      </c>
+      <c r="L214" s="5">
+        <v>61</v>
+      </c>
+      <c r="M214" s="5"/>
+      <c r="N214" s="5"/>
+      <c r="O214" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215" s="5">
+        <v>133570421</v>
+      </c>
+      <c r="E215" s="5">
+        <v>601</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I215" s="5">
+        <v>42</v>
+      </c>
+      <c r="J215" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K215" s="5">
+        <v>0</v>
+      </c>
+      <c r="L215" s="5">
+        <v>61</v>
+      </c>
+      <c r="M215" s="5"/>
+      <c r="N215" s="5"/>
+      <c r="O215" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A216" s="5">
+        <v>133570508</v>
+      </c>
+      <c r="E216" s="5">
+        <v>601</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I216" s="5">
+        <v>42</v>
+      </c>
+      <c r="J216" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K216" s="5">
+        <v>0</v>
+      </c>
+      <c r="L216" s="5">
+        <v>61</v>
+      </c>
+      <c r="M216" s="5"/>
+      <c r="N216" s="5"/>
+      <c r="O216" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A217" s="5">
+        <v>133570547</v>
+      </c>
+      <c r="E217" s="5">
+        <v>601</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I217" s="5">
+        <v>42</v>
+      </c>
+      <c r="J217" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K217" s="5">
+        <v>0</v>
+      </c>
+      <c r="L217" s="5">
+        <v>61</v>
+      </c>
+      <c r="M217" s="5"/>
+      <c r="N217" s="5"/>
+      <c r="O217" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A218" s="5">
+        <v>133570629</v>
+      </c>
+      <c r="E218" s="5">
+        <v>601</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I218" s="5">
+        <v>42</v>
+      </c>
+      <c r="J218" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K218" s="5">
+        <v>0</v>
+      </c>
+      <c r="L218" s="5">
+        <v>61</v>
+      </c>
+      <c r="M218" s="5"/>
+      <c r="N218" s="5"/>
+      <c r="O218" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A219" s="5">
+        <v>133571136</v>
+      </c>
+      <c r="E219" s="5">
+        <v>601</v>
+      </c>
+      <c r="F219" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I219" s="5">
+        <v>42</v>
+      </c>
+      <c r="J219" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K219" s="5">
+        <v>0</v>
+      </c>
+      <c r="L219" s="5">
+        <v>61</v>
+      </c>
+      <c r="M219" s="5"/>
+      <c r="N219" s="5"/>
+      <c r="O219" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A220" s="5">
+        <v>133571312</v>
+      </c>
+      <c r="E220" s="5">
+        <v>601</v>
+      </c>
+      <c r="F220" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I220" s="5">
+        <v>42</v>
+      </c>
+      <c r="J220" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K220" s="5">
+        <v>0</v>
+      </c>
+      <c r="L220" s="5">
+        <v>61</v>
+      </c>
+      <c r="M220" s="5"/>
+      <c r="N220" s="5"/>
+      <c r="O220" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A221" s="5">
+        <v>133571452</v>
+      </c>
+      <c r="E221" s="5">
+        <v>601</v>
+      </c>
+      <c r="F221" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I221" s="5">
+        <v>42</v>
+      </c>
+      <c r="J221" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K221" s="5">
+        <v>0</v>
+      </c>
+      <c r="L221" s="5">
+        <v>61</v>
+      </c>
+      <c r="M221" s="5"/>
+      <c r="N221" s="5"/>
+      <c r="O221" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A222" s="5">
+        <v>133571484</v>
+      </c>
+      <c r="E222" s="5">
+        <v>601</v>
+      </c>
+      <c r="F222" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I222" s="5">
+        <v>42</v>
+      </c>
+      <c r="J222" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K222" s="5">
+        <v>0</v>
+      </c>
+      <c r="L222" s="5">
+        <v>61</v>
+      </c>
+      <c r="M222" s="5"/>
+      <c r="N222" s="5"/>
+      <c r="O222" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A223" s="5">
+        <v>133571703</v>
+      </c>
+      <c r="E223" s="5">
+        <v>601</v>
+      </c>
+      <c r="F223" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I223" s="5">
+        <v>42</v>
+      </c>
+      <c r="J223" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K223" s="5">
+        <v>0</v>
+      </c>
+      <c r="L223" s="5">
+        <v>61</v>
+      </c>
+      <c r="M223" s="5"/>
+      <c r="N223" s="5"/>
+      <c r="O223" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A224" s="5">
+        <v>133571935</v>
+      </c>
+      <c r="E224" s="5">
+        <v>601</v>
+      </c>
+      <c r="F224" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G224" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I224" s="5">
+        <v>42</v>
+      </c>
+      <c r="J224" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K224" s="5">
+        <v>0</v>
+      </c>
+      <c r="L224" s="5">
+        <v>61</v>
+      </c>
+      <c r="M224" s="5"/>
+      <c r="N224" s="5"/>
+      <c r="O224" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A225" s="5">
+        <v>133572040</v>
+      </c>
+      <c r="E225" s="5">
+        <v>601</v>
+      </c>
+      <c r="F225" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I225" s="5">
+        <v>42</v>
+      </c>
+      <c r="J225" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K225" s="5">
+        <v>0</v>
+      </c>
+      <c r="L225" s="5">
+        <v>61</v>
+      </c>
+      <c r="M225" s="5"/>
+      <c r="N225" s="5"/>
+      <c r="O225" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A226" s="5">
+        <v>133572212</v>
+      </c>
+      <c r="E226" s="5">
+        <v>601</v>
+      </c>
+      <c r="F226" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I226" s="5">
+        <v>42</v>
+      </c>
+      <c r="J226" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K226" s="5">
+        <v>0</v>
+      </c>
+      <c r="L226" s="5">
+        <v>61</v>
+      </c>
+      <c r="M226" s="5"/>
+      <c r="N226" s="5"/>
+      <c r="O226" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A227" s="5">
+        <v>133572234</v>
+      </c>
+      <c r="E227" s="5">
+        <v>601</v>
+      </c>
+      <c r="F227" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I227" s="5">
+        <v>42</v>
+      </c>
+      <c r="J227" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K227" s="5">
+        <v>0</v>
+      </c>
+      <c r="L227" s="5">
+        <v>61</v>
+      </c>
+      <c r="M227" s="5"/>
+      <c r="N227" s="5"/>
+      <c r="O227" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A228" s="5">
+        <v>133572271</v>
+      </c>
+      <c r="E228" s="5">
+        <v>601</v>
+      </c>
+      <c r="F228" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I228" s="5">
+        <v>42</v>
+      </c>
+      <c r="J228" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K228" s="5">
+        <v>0</v>
+      </c>
+      <c r="L228" s="5">
+        <v>61</v>
+      </c>
+      <c r="M228" s="5"/>
+      <c r="N228" s="5"/>
+      <c r="O228" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A229" s="5">
+        <v>133572369</v>
+      </c>
+      <c r="E229" s="5">
+        <v>601</v>
+      </c>
+      <c r="F229" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I229" s="5">
+        <v>42</v>
+      </c>
+      <c r="J229" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K229" s="5">
+        <v>0</v>
+      </c>
+      <c r="L229" s="5">
+        <v>61</v>
+      </c>
+      <c r="M229" s="5"/>
+      <c r="N229" s="5"/>
+      <c r="O229" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A230" s="5">
+        <v>133572530</v>
+      </c>
+      <c r="E230" s="5">
+        <v>601</v>
+      </c>
+      <c r="F230" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I230" s="5">
+        <v>42</v>
+      </c>
+      <c r="J230" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K230" s="5">
+        <v>0</v>
+      </c>
+      <c r="L230" s="5">
+        <v>61</v>
+      </c>
+      <c r="M230" s="5"/>
+      <c r="N230" s="5"/>
+      <c r="O230" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A231" s="5">
+        <v>133572562</v>
+      </c>
+      <c r="E231" s="5">
+        <v>601</v>
+      </c>
+      <c r="F231" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I231" s="5">
+        <v>42</v>
+      </c>
+      <c r="J231" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K231" s="5">
+        <v>0</v>
+      </c>
+      <c r="L231" s="5">
+        <v>61</v>
+      </c>
+      <c r="M231" s="5"/>
+      <c r="N231" s="5"/>
+      <c r="O231" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A232" s="5">
+        <v>133572579</v>
+      </c>
+      <c r="E232" s="5">
+        <v>601</v>
+      </c>
+      <c r="F232" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I232" s="5">
+        <v>42</v>
+      </c>
+      <c r="J232" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K232" s="5">
+        <v>0</v>
+      </c>
+      <c r="L232" s="5">
+        <v>61</v>
+      </c>
+      <c r="M232" s="5"/>
+      <c r="N232" s="5"/>
+      <c r="O232" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A233" s="5">
+        <v>133572663</v>
+      </c>
+      <c r="E233" s="5">
+        <v>601</v>
+      </c>
+      <c r="F233" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I233" s="5">
+        <v>42</v>
+      </c>
+      <c r="J233" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K233" s="5">
+        <v>0</v>
+      </c>
+      <c r="L233" s="5">
+        <v>61</v>
+      </c>
+      <c r="M233" s="5"/>
+      <c r="N233" s="5"/>
+      <c r="O233" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A234" s="5">
+        <v>133573122</v>
+      </c>
+      <c r="E234" s="5">
+        <v>601</v>
+      </c>
+      <c r="F234" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I234" s="5">
+        <v>42</v>
+      </c>
+      <c r="J234" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K234" s="5">
+        <v>0</v>
+      </c>
+      <c r="L234" s="5">
+        <v>61</v>
+      </c>
+      <c r="M234" s="5"/>
+      <c r="N234" s="5"/>
+      <c r="O234" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A235" s="5">
+        <v>133573229</v>
+      </c>
+      <c r="E235" s="5">
+        <v>601</v>
+      </c>
+      <c r="F235" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G235" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I235" s="5">
+        <v>42</v>
+      </c>
+      <c r="J235" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K235" s="5">
+        <v>0</v>
+      </c>
+      <c r="L235" s="5">
+        <v>61</v>
+      </c>
+      <c r="M235" s="5"/>
+      <c r="N235" s="5"/>
+      <c r="O235" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A236" s="5">
+        <v>133573334</v>
+      </c>
+      <c r="E236" s="5">
+        <v>601</v>
+      </c>
+      <c r="F236" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I236" s="5">
+        <v>42</v>
+      </c>
+      <c r="J236" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K236" s="5">
+        <v>0</v>
+      </c>
+      <c r="L236" s="5">
+        <v>61</v>
+      </c>
+      <c r="M236" s="5"/>
+      <c r="N236" s="5"/>
+      <c r="O236" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A237" s="5">
+        <v>133573348</v>
+      </c>
+      <c r="E237" s="5">
+        <v>601</v>
+      </c>
+      <c r="F237" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I237" s="5">
+        <v>42</v>
+      </c>
+      <c r="J237" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K237" s="5">
+        <v>0</v>
+      </c>
+      <c r="L237" s="5">
+        <v>61</v>
+      </c>
+      <c r="M237" s="5"/>
+      <c r="N237" s="5"/>
+      <c r="O237" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A238" s="5">
+        <v>133573397</v>
+      </c>
+      <c r="E238" s="5">
+        <v>601</v>
+      </c>
+      <c r="F238" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G238" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I238" s="5">
+        <v>42</v>
+      </c>
+      <c r="J238" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K238" s="5">
+        <v>0</v>
+      </c>
+      <c r="L238" s="5">
+        <v>61</v>
+      </c>
+      <c r="M238" s="5"/>
+      <c r="N238" s="5"/>
+      <c r="O238" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A239" s="5">
+        <v>133573494</v>
+      </c>
+      <c r="E239" s="5">
+        <v>601</v>
+      </c>
+      <c r="F239" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G239" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I239" s="5">
+        <v>42</v>
+      </c>
+      <c r="J239" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K239" s="5">
+        <v>0</v>
+      </c>
+      <c r="L239" s="5">
+        <v>61</v>
+      </c>
+      <c r="M239" s="5"/>
+      <c r="N239" s="5"/>
+      <c r="O239" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A240" s="5">
+        <v>133573714</v>
+      </c>
+      <c r="E240" s="5">
+        <v>601</v>
+      </c>
+      <c r="F240" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I240" s="5">
+        <v>42</v>
+      </c>
+      <c r="J240" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K240" s="5">
+        <v>0</v>
+      </c>
+      <c r="L240" s="5">
+        <v>61</v>
+      </c>
+      <c r="M240" s="5"/>
+      <c r="N240" s="5"/>
+      <c r="O240" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A241" s="5">
+        <v>133573910</v>
+      </c>
+      <c r="E241" s="5">
+        <v>601</v>
+      </c>
+      <c r="F241" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I241" s="5">
+        <v>42</v>
+      </c>
+      <c r="J241" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K241" s="5">
+        <v>0</v>
+      </c>
+      <c r="L241" s="5">
+        <v>61</v>
+      </c>
+      <c r="M241" s="5"/>
+      <c r="N241" s="5"/>
+      <c r="O241" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A242" s="5">
+        <v>133574017</v>
+      </c>
+      <c r="E242" s="5">
+        <v>601</v>
+      </c>
+      <c r="F242" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I242" s="5">
+        <v>42</v>
+      </c>
+      <c r="J242" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K242" s="5">
+        <v>0</v>
+      </c>
+      <c r="L242" s="5">
+        <v>61</v>
+      </c>
+      <c r="M242" s="5"/>
+      <c r="N242" s="5"/>
+      <c r="O242" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A243" s="5">
+        <v>133574043</v>
+      </c>
+      <c r="E243" s="5">
+        <v>601</v>
+      </c>
+      <c r="F243" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G243" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I243" s="5">
+        <v>42</v>
+      </c>
+      <c r="J243" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K243" s="5">
+        <v>0</v>
+      </c>
+      <c r="L243" s="5">
+        <v>61</v>
+      </c>
+      <c r="M243" s="5"/>
+      <c r="N243" s="5"/>
+      <c r="O243" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A244" s="5">
+        <v>133574285</v>
+      </c>
+      <c r="E244" s="5">
+        <v>601</v>
+      </c>
+      <c r="F244" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G244" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I244" s="5">
+        <v>42</v>
+      </c>
+      <c r="J244" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K244" s="5">
+        <v>0</v>
+      </c>
+      <c r="L244" s="5">
+        <v>61</v>
+      </c>
+      <c r="M244" s="5"/>
+      <c r="N244" s="5"/>
+      <c r="O244" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A245" s="5">
+        <v>133574388</v>
+      </c>
+      <c r="E245" s="5">
+        <v>601</v>
+      </c>
+      <c r="F245" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I245" s="5">
+        <v>42</v>
+      </c>
+      <c r="J245" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K245" s="5">
+        <v>0</v>
+      </c>
+      <c r="L245" s="5">
+        <v>61</v>
+      </c>
+      <c r="M245" s="5"/>
+      <c r="N245" s="5"/>
+      <c r="O245" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A246" s="5">
+        <v>133574572</v>
+      </c>
+      <c r="E246" s="5">
+        <v>601</v>
+      </c>
+      <c r="F246" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I246" s="5">
+        <v>42</v>
+      </c>
+      <c r="J246" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K246" s="5">
+        <v>0</v>
+      </c>
+      <c r="L246" s="5">
+        <v>61</v>
+      </c>
+      <c r="M246" s="5"/>
+      <c r="N246" s="5"/>
+      <c r="O246" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A247" s="5">
+        <v>133574838</v>
+      </c>
+      <c r="E247" s="5">
+        <v>601</v>
+      </c>
+      <c r="F247" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I247" s="5">
+        <v>42</v>
+      </c>
+      <c r="J247" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K247" s="5">
+        <v>0</v>
+      </c>
+      <c r="L247" s="5">
+        <v>61</v>
+      </c>
+      <c r="M247" s="5"/>
+      <c r="N247" s="5"/>
+      <c r="O247" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A248" s="5">
+        <v>133574968</v>
+      </c>
+      <c r="E248" s="5">
+        <v>601</v>
+      </c>
+      <c r="F248" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I248" s="5">
+        <v>42</v>
+      </c>
+      <c r="J248" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K248" s="5">
+        <v>0</v>
+      </c>
+      <c r="L248" s="5">
+        <v>61</v>
+      </c>
+      <c r="M248" s="5"/>
+      <c r="N248" s="5"/>
+      <c r="O248" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A249" s="5">
+        <v>133575207</v>
+      </c>
+      <c r="E249" s="5">
+        <v>601</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I249" s="5">
+        <v>42</v>
+      </c>
+      <c r="J249" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K249" s="5">
+        <v>0</v>
+      </c>
+      <c r="L249" s="5">
+        <v>61</v>
+      </c>
+      <c r="M249" s="5"/>
+      <c r="N249" s="5"/>
+      <c r="O249" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A250" s="5">
+        <v>133575349</v>
+      </c>
+      <c r="E250" s="5">
+        <v>601</v>
+      </c>
+      <c r="F250" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I250" s="5">
+        <v>42</v>
+      </c>
+      <c r="J250" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K250" s="5">
+        <v>0</v>
+      </c>
+      <c r="L250" s="5">
+        <v>61</v>
+      </c>
+      <c r="M250" s="5"/>
+      <c r="N250" s="5"/>
+      <c r="O250" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A251" s="5">
+        <v>133575391</v>
+      </c>
+      <c r="E251" s="5">
+        <v>601</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I251" s="5">
+        <v>42</v>
+      </c>
+      <c r="J251" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K251" s="5">
+        <v>0</v>
+      </c>
+      <c r="L251" s="5">
+        <v>61</v>
+      </c>
+      <c r="M251" s="5"/>
+      <c r="N251" s="5"/>
+      <c r="O251" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A252" s="5">
+        <v>133575441</v>
+      </c>
+      <c r="E252" s="5">
+        <v>601</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I252" s="5">
+        <v>42</v>
+      </c>
+      <c r="J252" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K252" s="5">
+        <v>0</v>
+      </c>
+      <c r="L252" s="5">
+        <v>61</v>
+      </c>
+      <c r="M252" s="5"/>
+      <c r="N252" s="5"/>
+      <c r="O252" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A253" s="5">
+        <v>133576238</v>
+      </c>
+      <c r="E253" s="5">
+        <v>601</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I253" s="5">
+        <v>42</v>
+      </c>
+      <c r="J253" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K253" s="5">
+        <v>0</v>
+      </c>
+      <c r="L253" s="5">
+        <v>61</v>
+      </c>
+      <c r="M253" s="5"/>
+      <c r="N253" s="5"/>
+      <c r="O253" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A254" s="5">
+        <v>133576492</v>
+      </c>
+      <c r="E254" s="5">
+        <v>601</v>
+      </c>
+      <c r="F254" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I254" s="5">
+        <v>42</v>
+      </c>
+      <c r="J254" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K254" s="5">
+        <v>0</v>
+      </c>
+      <c r="L254" s="5">
+        <v>61</v>
+      </c>
+      <c r="M254" s="5"/>
+      <c r="N254" s="5"/>
+      <c r="O254" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A255" s="5">
+        <v>133576504</v>
+      </c>
+      <c r="E255" s="5">
+        <v>601</v>
+      </c>
+      <c r="F255" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I255" s="5">
+        <v>42</v>
+      </c>
+      <c r="J255" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K255" s="5">
+        <v>0</v>
+      </c>
+      <c r="L255" s="5">
+        <v>61</v>
+      </c>
+      <c r="M255" s="5"/>
+      <c r="N255" s="5"/>
+      <c r="O255" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A256" s="5">
+        <v>133576694</v>
+      </c>
+      <c r="E256" s="5">
+        <v>601</v>
+      </c>
+      <c r="F256" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I256" s="5">
+        <v>42</v>
+      </c>
+      <c r="J256" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K256" s="5">
+        <v>0</v>
+      </c>
+      <c r="L256" s="5">
+        <v>61</v>
+      </c>
+      <c r="M256" s="5"/>
+      <c r="N256" s="5"/>
+      <c r="O256" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A257" s="5">
+        <v>133577083</v>
+      </c>
+      <c r="E257" s="5">
+        <v>601</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I257" s="5">
+        <v>42</v>
+      </c>
+      <c r="J257" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K257" s="5">
+        <v>0</v>
+      </c>
+      <c r="L257" s="5">
+        <v>61</v>
+      </c>
+      <c r="M257" s="5"/>
+      <c r="N257" s="5"/>
+      <c r="O257" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A258" s="5">
+        <v>133577457</v>
+      </c>
+      <c r="E258" s="5">
+        <v>601</v>
+      </c>
+      <c r="F258" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I258" s="5">
+        <v>42</v>
+      </c>
+      <c r="J258" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K258" s="5">
+        <v>0</v>
+      </c>
+      <c r="L258" s="5">
+        <v>61</v>
+      </c>
+      <c r="M258" s="5"/>
+      <c r="N258" s="5"/>
+      <c r="O258" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A259" s="5">
+        <v>133578268</v>
+      </c>
+      <c r="E259" s="5">
+        <v>601</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I259" s="5">
+        <v>42</v>
+      </c>
+      <c r="J259" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K259" s="5">
+        <v>0</v>
+      </c>
+      <c r="L259" s="5">
+        <v>61</v>
+      </c>
+      <c r="M259" s="5"/>
+      <c r="N259" s="5"/>
+      <c r="O259" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A260" s="5">
+        <v>133578282</v>
+      </c>
+      <c r="E260" s="5">
+        <v>601</v>
+      </c>
+      <c r="F260" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I260" s="5">
+        <v>42</v>
+      </c>
+      <c r="J260" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K260" s="5">
+        <v>0</v>
+      </c>
+      <c r="L260" s="5">
+        <v>61</v>
+      </c>
+      <c r="M260" s="5"/>
+      <c r="N260" s="5"/>
+      <c r="O260" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A261" s="5">
+        <v>133578574</v>
+      </c>
+      <c r="E261" s="5">
+        <v>601</v>
+      </c>
+      <c r="F261" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I261" s="5">
+        <v>42</v>
+      </c>
+      <c r="J261" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K261" s="5">
+        <v>0</v>
+      </c>
+      <c r="L261" s="5">
+        <v>61</v>
+      </c>
+      <c r="M261" s="5"/>
+      <c r="N261" s="5"/>
+      <c r="O261" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A262" s="5">
+        <v>133578636</v>
+      </c>
+      <c r="E262" s="5">
+        <v>601</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I262" s="5">
+        <v>42</v>
+      </c>
+      <c r="J262" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K262" s="5">
+        <v>0</v>
+      </c>
+      <c r="L262" s="5">
+        <v>61</v>
+      </c>
+      <c r="M262" s="5"/>
+      <c r="N262" s="5"/>
+      <c r="O262" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A263" s="5">
+        <v>133578663</v>
+      </c>
+      <c r="E263" s="5">
+        <v>601</v>
+      </c>
+      <c r="F263" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I263" s="5">
+        <v>42</v>
+      </c>
+      <c r="J263" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K263" s="5">
+        <v>0</v>
+      </c>
+      <c r="L263" s="5">
+        <v>61</v>
+      </c>
+      <c r="M263" s="5"/>
+      <c r="N263" s="5"/>
+      <c r="O263" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A264" s="5">
+        <v>133578830</v>
+      </c>
+      <c r="E264" s="5">
+        <v>601</v>
+      </c>
+      <c r="F264" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I264" s="5">
+        <v>42</v>
+      </c>
+      <c r="J264" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K264" s="5">
+        <v>0</v>
+      </c>
+      <c r="L264" s="5">
+        <v>61</v>
+      </c>
+      <c r="M264" s="5"/>
+      <c r="N264" s="5"/>
+      <c r="O264" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A265" s="5">
+        <v>133579010</v>
+      </c>
+      <c r="E265" s="5">
+        <v>601</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I265" s="5">
+        <v>42</v>
+      </c>
+      <c r="J265" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K265" s="5">
+        <v>0</v>
+      </c>
+      <c r="L265" s="5">
+        <v>61</v>
+      </c>
+      <c r="M265" s="5"/>
+      <c r="N265" s="5"/>
+      <c r="O265" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A266" s="5">
+        <v>133579303</v>
+      </c>
+      <c r="E266" s="5">
+        <v>601</v>
+      </c>
+      <c r="F266" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I266" s="5">
+        <v>42</v>
+      </c>
+      <c r="J266" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K266" s="5">
+        <v>0</v>
+      </c>
+      <c r="L266" s="5">
+        <v>61</v>
+      </c>
+      <c r="M266" s="5"/>
+      <c r="N266" s="5"/>
+      <c r="O266" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A267" s="5">
+        <v>133579351</v>
+      </c>
+      <c r="E267" s="5">
+        <v>601</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I267" s="5">
+        <v>42</v>
+      </c>
+      <c r="J267" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K267" s="5">
+        <v>0</v>
+      </c>
+      <c r="L267" s="5">
+        <v>61</v>
+      </c>
+      <c r="M267" s="5"/>
+      <c r="N267" s="5"/>
+      <c r="O267" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A268" s="5">
+        <v>133579514</v>
+      </c>
+      <c r="E268" s="5">
+        <v>601</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I268" s="5">
+        <v>42</v>
+      </c>
+      <c r="J268" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K268" s="5">
+        <v>0</v>
+      </c>
+      <c r="L268" s="5">
+        <v>61</v>
+      </c>
+      <c r="M268" s="5"/>
+      <c r="N268" s="5"/>
+      <c r="O268" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A269" s="5">
+        <v>133579535</v>
+      </c>
+      <c r="E269" s="5">
+        <v>601</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I269" s="5">
+        <v>42</v>
+      </c>
+      <c r="J269" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K269" s="5">
+        <v>0</v>
+      </c>
+      <c r="L269" s="5">
+        <v>61</v>
+      </c>
+      <c r="M269" s="5"/>
+      <c r="N269" s="5"/>
+      <c r="O269" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A270" s="5">
+        <v>133579764</v>
+      </c>
+      <c r="E270" s="5">
+        <v>601</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I270" s="5">
+        <v>42</v>
+      </c>
+      <c r="J270" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K270" s="5">
+        <v>0</v>
+      </c>
+      <c r="L270" s="5">
+        <v>61</v>
+      </c>
+      <c r="M270" s="5"/>
+      <c r="N270" s="5"/>
+      <c r="O270" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A271" s="5">
+        <v>133580031</v>
+      </c>
+      <c r="E271" s="5">
+        <v>601</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I271" s="5">
+        <v>42</v>
+      </c>
+      <c r="J271" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K271" s="5">
+        <v>0</v>
+      </c>
+      <c r="L271" s="5">
+        <v>61</v>
+      </c>
+      <c r="M271" s="5"/>
+      <c r="N271" s="5"/>
+      <c r="O271" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A272" s="5">
+        <v>133580054</v>
+      </c>
+      <c r="E272" s="5">
+        <v>601</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I272" s="5">
+        <v>42</v>
+      </c>
+      <c r="J272" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K272" s="5">
+        <v>0</v>
+      </c>
+      <c r="L272" s="5">
+        <v>61</v>
+      </c>
+      <c r="M272" s="5"/>
+      <c r="N272" s="5"/>
+      <c r="O272" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A273" s="5">
+        <v>133580316</v>
+      </c>
+      <c r="E273" s="5">
+        <v>601</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I273" s="5">
+        <v>42</v>
+      </c>
+      <c r="J273" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K273" s="5">
+        <v>0</v>
+      </c>
+      <c r="L273" s="5">
+        <v>61</v>
+      </c>
+      <c r="M273" s="5"/>
+      <c r="N273" s="5"/>
+      <c r="O273" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A274" s="5">
+        <v>133580421</v>
+      </c>
+      <c r="E274" s="5">
+        <v>601</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I274" s="5">
+        <v>42</v>
+      </c>
+      <c r="J274" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K274" s="5">
+        <v>0</v>
+      </c>
+      <c r="L274" s="5">
+        <v>61</v>
+      </c>
+      <c r="M274" s="5"/>
+      <c r="N274" s="5"/>
+      <c r="O274" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A275" s="5">
+        <v>133580445</v>
+      </c>
+      <c r="E275" s="5">
+        <v>601</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I275" s="5">
+        <v>42</v>
+      </c>
+      <c r="J275" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K275" s="5">
+        <v>0</v>
+      </c>
+      <c r="L275" s="5">
+        <v>61</v>
+      </c>
+      <c r="M275" s="5"/>
+      <c r="N275" s="5"/>
+      <c r="O275" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A276" s="5">
+        <v>133580491</v>
+      </c>
+      <c r="E276" s="5">
+        <v>601</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I276" s="5">
+        <v>42</v>
+      </c>
+      <c r="J276" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K276" s="5">
+        <v>0</v>
+      </c>
+      <c r="L276" s="5">
+        <v>61</v>
+      </c>
+      <c r="M276" s="5"/>
+      <c r="N276" s="5"/>
+      <c r="O276" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A277" s="5">
+        <v>133580816</v>
+      </c>
+      <c r="E277" s="5">
+        <v>601</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I277" s="5">
+        <v>42</v>
+      </c>
+      <c r="J277" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K277" s="5">
+        <v>0</v>
+      </c>
+      <c r="L277" s="5">
+        <v>61</v>
+      </c>
+      <c r="M277" s="5"/>
+      <c r="N277" s="5"/>
+      <c r="O277" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A278" s="5">
+        <v>133581099</v>
+      </c>
+      <c r="E278" s="5">
+        <v>601</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I278" s="5">
+        <v>42</v>
+      </c>
+      <c r="J278" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K278" s="5">
+        <v>0</v>
+      </c>
+      <c r="L278" s="5">
+        <v>61</v>
+      </c>
+      <c r="M278" s="5"/>
+      <c r="N278" s="5"/>
+      <c r="O278" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A279" s="5">
+        <v>133581414</v>
+      </c>
+      <c r="E279" s="5">
+        <v>601</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I279" s="5">
+        <v>42</v>
+      </c>
+      <c r="J279" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K279" s="5">
+        <v>0</v>
+      </c>
+      <c r="L279" s="5">
+        <v>61</v>
+      </c>
+      <c r="M279" s="5"/>
+      <c r="N279" s="5"/>
+      <c r="O279" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A280" s="5">
+        <v>133581636</v>
+      </c>
+      <c r="E280" s="5">
+        <v>601</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I280" s="5">
+        <v>42</v>
+      </c>
+      <c r="J280" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K280" s="5">
+        <v>0</v>
+      </c>
+      <c r="L280" s="5">
+        <v>61</v>
+      </c>
+      <c r="M280" s="5"/>
+      <c r="N280" s="5"/>
+      <c r="O280" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A281" s="5">
+        <v>133581768</v>
+      </c>
+      <c r="E281" s="5">
+        <v>601</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I281" s="5">
+        <v>42</v>
+      </c>
+      <c r="J281" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K281" s="5">
+        <v>0</v>
+      </c>
+      <c r="L281" s="5">
+        <v>61</v>
+      </c>
+      <c r="M281" s="5"/>
+      <c r="N281" s="5"/>
+      <c r="O281" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A282" s="5">
+        <v>133581854</v>
+      </c>
+      <c r="E282" s="5">
+        <v>601</v>
+      </c>
+      <c r="F282" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I282" s="5">
+        <v>42</v>
+      </c>
+      <c r="J282" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K282" s="5">
+        <v>0</v>
+      </c>
+      <c r="L282" s="5">
+        <v>61</v>
+      </c>
+      <c r="M282" s="5"/>
+      <c r="N282" s="5"/>
+      <c r="O282" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A283" s="5">
+        <v>133581887</v>
+      </c>
+      <c r="E283" s="5">
+        <v>609</v>
+      </c>
+      <c r="F283" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I283" s="5">
+        <v>42</v>
+      </c>
+      <c r="J283" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K283" s="5">
+        <v>0</v>
+      </c>
+      <c r="L283" s="5">
+        <v>61</v>
+      </c>
+      <c r="M283" s="5"/>
+      <c r="N283" s="5"/>
+      <c r="O283" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A284" s="5">
+        <v>133581891</v>
+      </c>
+      <c r="E284" s="5">
+        <v>601</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I284" s="5">
+        <v>42</v>
+      </c>
+      <c r="J284" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K284" s="5">
+        <v>0</v>
+      </c>
+      <c r="L284" s="5">
+        <v>61</v>
+      </c>
+      <c r="M284" s="5"/>
+      <c r="N284" s="5"/>
+      <c r="O284" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A285" s="5">
+        <v>133582255</v>
+      </c>
+      <c r="E285" s="5">
+        <v>601</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I285" s="5">
+        <v>42</v>
+      </c>
+      <c r="J285" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K285" s="5">
+        <v>0</v>
+      </c>
+      <c r="L285" s="5">
+        <v>61</v>
+      </c>
+      <c r="M285" s="5"/>
+      <c r="N285" s="5"/>
+      <c r="O285" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A286" s="5">
+        <v>133582438</v>
+      </c>
+      <c r="E286" s="5">
+        <v>601</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I286" s="5">
+        <v>42</v>
+      </c>
+      <c r="J286" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K286" s="5">
+        <v>0</v>
+      </c>
+      <c r="L286" s="5">
+        <v>61</v>
+      </c>
+      <c r="M286" s="5"/>
+      <c r="N286" s="5"/>
+      <c r="O286" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A287" s="5">
+        <v>133582561</v>
+      </c>
+      <c r="E287" s="5">
+        <v>601</v>
+      </c>
+      <c r="F287" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I287" s="5">
+        <v>42</v>
+      </c>
+      <c r="J287" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K287" s="5">
+        <v>0</v>
+      </c>
+      <c r="L287" s="5">
+        <v>61</v>
+      </c>
+      <c r="M287" s="5"/>
+      <c r="N287" s="5"/>
+      <c r="O287" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A288" s="5">
+        <v>133582727</v>
+      </c>
+      <c r="E288" s="5">
+        <v>601</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I288" s="5">
+        <v>42</v>
+      </c>
+      <c r="J288" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K288" s="5">
+        <v>0</v>
+      </c>
+      <c r="L288" s="5">
+        <v>61</v>
+      </c>
+      <c r="M288" s="5"/>
+      <c r="N288" s="5"/>
+      <c r="O288" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A289" s="5">
+        <v>133582753</v>
+      </c>
+      <c r="E289" s="5">
+        <v>601</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I289" s="5">
+        <v>42</v>
+      </c>
+      <c r="J289" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K289" s="5">
+        <v>0</v>
+      </c>
+      <c r="L289" s="5">
+        <v>61</v>
+      </c>
+      <c r="M289" s="5"/>
+      <c r="N289" s="5"/>
+      <c r="O289" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A290" s="5">
+        <v>133582910</v>
+      </c>
+      <c r="E290" s="5">
+        <v>601</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I290" s="5">
+        <v>42</v>
+      </c>
+      <c r="J290" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K290" s="5">
+        <v>0</v>
+      </c>
+      <c r="L290" s="5">
+        <v>61</v>
+      </c>
+      <c r="M290" s="5"/>
+      <c r="N290" s="5"/>
+      <c r="O290" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A291" s="5">
+        <v>133583096</v>
+      </c>
+      <c r="E291" s="5">
+        <v>601</v>
+      </c>
+      <c r="F291" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I291" s="5">
+        <v>42</v>
+      </c>
+      <c r="J291" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K291" s="5">
+        <v>0</v>
+      </c>
+      <c r="L291" s="5">
+        <v>61</v>
+      </c>
+      <c r="M291" s="5"/>
+      <c r="N291" s="5"/>
+      <c r="O291" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A292" s="5">
+        <v>133583137</v>
+      </c>
+      <c r="E292" s="5">
+        <v>601</v>
+      </c>
+      <c r="F292" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I292" s="5">
+        <v>42</v>
+      </c>
+      <c r="J292" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K292" s="5">
+        <v>0</v>
+      </c>
+      <c r="L292" s="5">
+        <v>61</v>
+      </c>
+      <c r="M292" s="5"/>
+      <c r="N292" s="5"/>
+      <c r="O292" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A293" s="5">
+        <v>133583604</v>
+      </c>
+      <c r="E293" s="5">
+        <v>601</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I293" s="5">
+        <v>42</v>
+      </c>
+      <c r="J293" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K293" s="5">
+        <v>0</v>
+      </c>
+      <c r="L293" s="5">
+        <v>61</v>
+      </c>
+      <c r="M293" s="5"/>
+      <c r="N293" s="5"/>
+      <c r="O293" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A294" s="5">
+        <v>133583892</v>
+      </c>
+      <c r="E294" s="5">
+        <v>601</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I294" s="5">
+        <v>42</v>
+      </c>
+      <c r="J294" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K294" s="5">
+        <v>0</v>
+      </c>
+      <c r="L294" s="5">
+        <v>61</v>
+      </c>
+      <c r="M294" s="5"/>
+      <c r="N294" s="5"/>
+      <c r="O294" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A295" s="5">
+        <v>133584261</v>
+      </c>
+      <c r="E295" s="5">
+        <v>601</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I295" s="5">
+        <v>42</v>
+      </c>
+      <c r="J295" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K295" s="5">
+        <v>0</v>
+      </c>
+      <c r="L295" s="5">
+        <v>61</v>
+      </c>
+      <c r="M295" s="5"/>
+      <c r="N295" s="5"/>
+      <c r="O295" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A296" s="5">
+        <v>133584282</v>
+      </c>
+      <c r="E296" s="5">
+        <v>601</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I296" s="5">
+        <v>42</v>
+      </c>
+      <c r="J296" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K296" s="5">
+        <v>0</v>
+      </c>
+      <c r="L296" s="5">
+        <v>61</v>
+      </c>
+      <c r="M296" s="5"/>
+      <c r="N296" s="5"/>
+      <c r="O296" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A297" s="5">
+        <v>133584616</v>
+      </c>
+      <c r="E297" s="5">
+        <v>601</v>
+      </c>
+      <c r="F297" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I297" s="5">
+        <v>42</v>
+      </c>
+      <c r="J297" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K297" s="5">
+        <v>0</v>
+      </c>
+      <c r="L297" s="5">
+        <v>61</v>
+      </c>
+      <c r="M297" s="5"/>
+      <c r="N297" s="5"/>
+      <c r="O297" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A298" s="5">
+        <v>133585549</v>
+      </c>
+      <c r="E298" s="5">
+        <v>601</v>
+      </c>
+      <c r="F298" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I298" s="5">
+        <v>42</v>
+      </c>
+      <c r="J298" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K298" s="5">
+        <v>0</v>
+      </c>
+      <c r="L298" s="5">
+        <v>61</v>
+      </c>
+      <c r="M298" s="5"/>
+      <c r="N298" s="5"/>
+      <c r="O298" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A299" s="5">
+        <v>133585556</v>
+      </c>
+      <c r="E299" s="5">
+        <v>601</v>
+      </c>
+      <c r="F299" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I299" s="5">
+        <v>42</v>
+      </c>
+      <c r="J299" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K299" s="5">
+        <v>0</v>
+      </c>
+      <c r="L299" s="5">
+        <v>61</v>
+      </c>
+      <c r="M299" s="5"/>
+      <c r="N299" s="5"/>
+      <c r="O299" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A300" s="5">
+        <v>133585606</v>
+      </c>
+      <c r="E300" s="5">
+        <v>601</v>
+      </c>
+      <c r="F300" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I300" s="5">
+        <v>42</v>
+      </c>
+      <c r="J300" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K300" s="5">
+        <v>0</v>
+      </c>
+      <c r="L300" s="5">
+        <v>61</v>
+      </c>
+      <c r="M300" s="5"/>
+      <c r="N300" s="5"/>
+      <c r="O300" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A301" s="5">
+        <v>133585713</v>
+      </c>
+      <c r="E301" s="5">
+        <v>601</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I301" s="5">
+        <v>42</v>
+      </c>
+      <c r="J301" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K301" s="5">
+        <v>0</v>
+      </c>
+      <c r="L301" s="5">
+        <v>61</v>
+      </c>
+      <c r="M301" s="5"/>
+      <c r="N301" s="5"/>
+      <c r="O301" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A302" s="5">
+        <v>133585960</v>
+      </c>
+      <c r="E302" s="5">
+        <v>601</v>
+      </c>
+      <c r="F302" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I302" s="5">
+        <v>42</v>
+      </c>
+      <c r="J302" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K302" s="5">
+        <v>0</v>
+      </c>
+      <c r="L302" s="5">
+        <v>61</v>
+      </c>
+      <c r="M302" s="5"/>
+      <c r="N302" s="5"/>
+      <c r="O302" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A303" s="5">
+        <v>133586145</v>
+      </c>
+      <c r="E303" s="5">
+        <v>601</v>
+      </c>
+      <c r="F303" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I303" s="5">
+        <v>42</v>
+      </c>
+      <c r="J303" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K303" s="5">
+        <v>0</v>
+      </c>
+      <c r="L303" s="5">
+        <v>61</v>
+      </c>
+      <c r="M303" s="5"/>
+      <c r="N303" s="5"/>
+      <c r="O303" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A304" s="5">
+        <v>133586207</v>
+      </c>
+      <c r="E304" s="5">
+        <v>601</v>
+      </c>
+      <c r="F304" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I304" s="5">
+        <v>42</v>
+      </c>
+      <c r="J304" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K304" s="5">
+        <v>0</v>
+      </c>
+      <c r="L304" s="5">
+        <v>61</v>
+      </c>
+      <c r="M304" s="5"/>
+      <c r="N304" s="5"/>
+      <c r="O304" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A305" s="5">
+        <v>133586218</v>
+      </c>
+      <c r="E305" s="5">
+        <v>601</v>
+      </c>
+      <c r="F305" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I305" s="5">
+        <v>42</v>
+      </c>
+      <c r="J305" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K305" s="5">
+        <v>0</v>
+      </c>
+      <c r="L305" s="5">
+        <v>61</v>
+      </c>
+      <c r="M305" s="5"/>
+      <c r="N305" s="5"/>
+      <c r="O305" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A306" s="5">
+        <v>133586373</v>
+      </c>
+      <c r="E306" s="5">
+        <v>601</v>
+      </c>
+      <c r="F306" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I306" s="5">
+        <v>42</v>
+      </c>
+      <c r="J306" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K306" s="5">
+        <v>0</v>
+      </c>
+      <c r="L306" s="5">
+        <v>61</v>
+      </c>
+      <c r="M306" s="5"/>
+      <c r="N306" s="5"/>
+      <c r="O306" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A307" s="5">
+        <v>133586512</v>
+      </c>
+      <c r="E307" s="5">
+        <v>601</v>
+      </c>
+      <c r="F307" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I307" s="5">
+        <v>42</v>
+      </c>
+      <c r="J307" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K307" s="5">
+        <v>0</v>
+      </c>
+      <c r="L307" s="5">
+        <v>61</v>
+      </c>
+      <c r="M307" s="5"/>
+      <c r="N307" s="5"/>
+      <c r="O307" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A308" s="5">
+        <v>133586860</v>
+      </c>
+      <c r="E308" s="5">
+        <v>601</v>
+      </c>
+      <c r="F308" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I308" s="5">
+        <v>42</v>
+      </c>
+      <c r="J308" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K308" s="5">
+        <v>0</v>
+      </c>
+      <c r="L308" s="5">
+        <v>61</v>
+      </c>
+      <c r="M308" s="5"/>
+      <c r="N308" s="5"/>
+      <c r="O308" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A309" s="5">
+        <v>133587224</v>
+      </c>
+      <c r="E309" s="5">
+        <v>601</v>
+      </c>
+      <c r="F309" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I309" s="5">
+        <v>42</v>
+      </c>
+      <c r="J309" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K309" s="5">
+        <v>0</v>
+      </c>
+      <c r="L309" s="5">
+        <v>61</v>
+      </c>
+      <c r="M309" s="5"/>
+      <c r="N309" s="5"/>
+      <c r="O309" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A310" s="5">
+        <v>133587562</v>
+      </c>
+      <c r="E310" s="5">
+        <v>601</v>
+      </c>
+      <c r="F310" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G310" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I310" s="5">
+        <v>42</v>
+      </c>
+      <c r="J310" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K310" s="5">
+        <v>0</v>
+      </c>
+      <c r="L310" s="5">
+        <v>61</v>
+      </c>
+      <c r="M310" s="5"/>
+      <c r="N310" s="5"/>
+      <c r="O310" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A311" s="5">
+        <v>133588138</v>
+      </c>
+      <c r="E311" s="5">
+        <v>601</v>
+      </c>
+      <c r="F311" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I311" s="5">
+        <v>42</v>
+      </c>
+      <c r="J311" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K311" s="5">
+        <v>0</v>
+      </c>
+      <c r="L311" s="5">
+        <v>61</v>
+      </c>
+      <c r="M311" s="5"/>
+      <c r="N311" s="5"/>
+      <c r="O311" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A312" s="5">
+        <v>133589045</v>
+      </c>
+      <c r="E312" s="5">
+        <v>601</v>
+      </c>
+      <c r="F312" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G312" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I312" s="5">
+        <v>42</v>
+      </c>
+      <c r="J312" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K312" s="5">
+        <v>0</v>
+      </c>
+      <c r="L312" s="5">
+        <v>61</v>
+      </c>
+      <c r="M312" s="5"/>
+      <c r="N312" s="5"/>
+      <c r="O312" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A313" s="5">
+        <v>133589825</v>
+      </c>
+      <c r="E313" s="5">
+        <v>609</v>
+      </c>
+      <c r="F313" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I313" s="5">
+        <v>42</v>
+      </c>
+      <c r="J313" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K313" s="5">
+        <v>0</v>
+      </c>
+      <c r="L313" s="5">
+        <v>61</v>
+      </c>
+      <c r="M313" s="5"/>
+      <c r="N313" s="5"/>
+      <c r="O313" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A314" s="5">
+        <v>133589847</v>
+      </c>
+      <c r="E314" s="5">
+        <v>609</v>
+      </c>
+      <c r="F314" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I314" s="5">
+        <v>42</v>
+      </c>
+      <c r="J314" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K314" s="5">
+        <v>0</v>
+      </c>
+      <c r="L314" s="5">
+        <v>61</v>
+      </c>
+      <c r="M314" s="5"/>
+      <c r="N314" s="5"/>
+      <c r="O314" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0543CC-487D-41E7-A67A-9C07CACB9D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304638ED-DD02-49D6-8E96-06C5F4D46102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="36">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,10 +79,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>22/7/2025</t>
-  </si>
-  <si>
-    <t>21/7/2025</t>
+    <t>25/7/2025</t>
   </si>
   <si>
     <t>8/3/2023</t>
@@ -91,7 +88,55 @@
     <t>10/3/2023</t>
   </si>
   <si>
-    <t>24/7/2025</t>
+    <t>26/7/2025</t>
+  </si>
+  <si>
+    <t>28/7/2025</t>
+  </si>
+  <si>
+    <t>23/7/2025</t>
+  </si>
+  <si>
+    <t>29/7/2025</t>
+  </si>
+  <si>
+    <t>10/07/2025</t>
+  </si>
+  <si>
+    <t>07/07/2025</t>
+  </si>
+  <si>
+    <t>13/06/2025</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
+    <t>04/07/2025</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>16/07/2025</t>
+  </si>
+  <si>
+    <t>29/07/2025</t>
+  </si>
+  <si>
+    <t>21/07/2025</t>
+  </si>
+  <si>
+    <t>22/07/2025</t>
+  </si>
+  <si>
+    <t>23/07/2025</t>
+  </si>
+  <si>
+    <t>24/07/2025</t>
+  </si>
+  <si>
+    <t>26/07/2025</t>
   </si>
 </sst>
 </file>
@@ -509,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -579,10 +624,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>133547591</v>
+        <v>133622778</v>
       </c>
       <c r="E2" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
@@ -594,7 +639,7 @@
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8003</v>
+        <v>1735</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -610,16 +655,16 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>133539235</v>
+        <v>133629666</v>
       </c>
       <c r="E3" s="5">
         <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
@@ -641,7 +686,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>133540517</v>
+        <v>123058958</v>
       </c>
       <c r="E4" s="5">
         <v>1211</v>
@@ -650,13 +695,13 @@
         <v>17</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -672,22 +717,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>133540543</v>
+        <v>130789903</v>
       </c>
       <c r="E5" s="5">
         <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -703,22 +748,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>133542393</v>
+        <v>130789903</v>
       </c>
       <c r="E6" s="5">
         <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -734,22 +779,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>123058958</v>
+        <v>133577242</v>
       </c>
       <c r="E7" s="5">
         <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -765,13 +810,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>130132602</v>
+        <v>133637216</v>
       </c>
       <c r="E8" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>20</v>
@@ -780,7 +825,7 @@
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -796,22 +841,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>131968288</v>
+        <v>133638652</v>
       </c>
       <c r="E9" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -827,13 +872,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>132148463</v>
+        <v>133638687</v>
       </c>
       <c r="E10" s="5">
-        <v>1212</v>
+        <v>2013</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>20</v>
@@ -842,7 +887,7 @@
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -858,13 +903,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>132148463</v>
+        <v>133639461</v>
       </c>
       <c r="E11" s="5">
-        <v>1212</v>
+        <v>2013</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>20</v>
@@ -873,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -889,7 +934,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133592443</v>
+        <v>133640088</v>
       </c>
       <c r="E12" s="5">
         <v>2013</v>
@@ -920,7 +965,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>133593062</v>
+        <v>133640125</v>
       </c>
       <c r="E13" s="5">
         <v>2013</v>
@@ -951,7 +996,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>133595328</v>
+        <v>133640963</v>
       </c>
       <c r="E14" s="5">
         <v>2013</v>
@@ -982,7 +1027,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>133595364</v>
+        <v>133641155</v>
       </c>
       <c r="E15" s="5">
         <v>2013</v>
@@ -991,7 +1036,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
@@ -1013,7 +1058,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>133595422</v>
+        <v>133642685</v>
       </c>
       <c r="E16" s="5">
         <v>2013</v>
@@ -1044,7 +1089,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>133595520</v>
+        <v>133645192</v>
       </c>
       <c r="E17" s="5">
         <v>2013</v>
@@ -1053,7 +1098,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1075,7 +1120,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>133595876</v>
+        <v>133647300</v>
       </c>
       <c r="E18" s="5">
         <v>2013</v>
@@ -1084,7 +1129,7 @@
         <v>20</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1106,7 +1151,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>133595904</v>
+        <v>133648152</v>
       </c>
       <c r="E19" s="5">
         <v>2013</v>
@@ -1115,7 +1160,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1137,7 +1182,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>133595972</v>
+        <v>133648780</v>
       </c>
       <c r="E20" s="5">
         <v>2013</v>
@@ -1146,7 +1191,7 @@
         <v>20</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1168,7 +1213,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>133596024</v>
+        <v>133648878</v>
       </c>
       <c r="E21" s="5">
         <v>2013</v>
@@ -1177,7 +1222,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1199,7 +1244,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>133597246</v>
+        <v>133649078</v>
       </c>
       <c r="E22" s="5">
         <v>2013</v>
@@ -1230,7 +1275,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>133597301</v>
+        <v>133649227</v>
       </c>
       <c r="E23" s="5">
         <v>2013</v>
@@ -1261,7 +1306,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>133597997</v>
+        <v>133649916</v>
       </c>
       <c r="E24" s="5">
         <v>2013</v>
@@ -1270,7 +1315,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1292,7 +1337,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>133598023</v>
+        <v>133650182</v>
       </c>
       <c r="E25" s="5">
         <v>2013</v>
@@ -1323,7 +1368,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>133599589</v>
+        <v>133650268</v>
       </c>
       <c r="E26" s="5">
         <v>2013</v>
@@ -1354,7 +1399,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>133601059</v>
+        <v>133650323</v>
       </c>
       <c r="E27" s="5">
         <v>2013</v>
@@ -1363,7 +1408,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
@@ -1385,7 +1430,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>133601750</v>
+        <v>133650534</v>
       </c>
       <c r="E28" s="5">
         <v>2013</v>
@@ -1416,7 +1461,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>133602242</v>
+        <v>133651035</v>
       </c>
       <c r="E29" s="5">
         <v>2013</v>
@@ -1447,7 +1492,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>133606762</v>
+        <v>133651554</v>
       </c>
       <c r="E30" s="5">
         <v>2013</v>
@@ -1456,7 +1501,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
@@ -1478,7 +1523,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>133607286</v>
+        <v>133651715</v>
       </c>
       <c r="E31" s="5">
         <v>2013</v>
@@ -1509,22 +1554,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>133607552</v>
+        <v>132677248</v>
       </c>
       <c r="E32" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
       </c>
       <c r="J32" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -1535,6 +1580,3323 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>132914455</v>
+      </c>
+      <c r="E33" s="5">
+        <v>609</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" s="5">
+        <v>42</v>
+      </c>
+      <c r="J33" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>61</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>133273225</v>
+      </c>
+      <c r="E34" s="5">
+        <v>601</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="5">
+        <v>42</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>61</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>133283865</v>
+      </c>
+      <c r="E35" s="5">
+        <v>601</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="5">
+        <v>42</v>
+      </c>
+      <c r="J35" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>61</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>133365654</v>
+      </c>
+      <c r="E36" s="5">
+        <v>601</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="5">
+        <v>42</v>
+      </c>
+      <c r="J36" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>61</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>133453383</v>
+      </c>
+      <c r="E37" s="5">
+        <v>601</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="5">
+        <v>42</v>
+      </c>
+      <c r="J37" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>61</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>133455571</v>
+      </c>
+      <c r="E38" s="5">
+        <v>601</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="5">
+        <v>42</v>
+      </c>
+      <c r="J38" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>61</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>133456928</v>
+      </c>
+      <c r="E39" s="5">
+        <v>609</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="5">
+        <v>42</v>
+      </c>
+      <c r="J39" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>61</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>133529510</v>
+      </c>
+      <c r="E40" s="5">
+        <v>601</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="5">
+        <v>42</v>
+      </c>
+      <c r="J40" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>61</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>133546576</v>
+      </c>
+      <c r="E41" s="5">
+        <v>601</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="5">
+        <v>42</v>
+      </c>
+      <c r="J41" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>61</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>133562394</v>
+      </c>
+      <c r="E42" s="5">
+        <v>601</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="5">
+        <v>42</v>
+      </c>
+      <c r="J42" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>61</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>133577255</v>
+      </c>
+      <c r="E43" s="5">
+        <v>601</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" s="5">
+        <v>42</v>
+      </c>
+      <c r="J43" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>61</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>133581885</v>
+      </c>
+      <c r="E44" s="5">
+        <v>601</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" s="5">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>61</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>133583834</v>
+      </c>
+      <c r="E45" s="5">
+        <v>601</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="5">
+        <v>42</v>
+      </c>
+      <c r="J45" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5">
+        <v>61</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>133590458</v>
+      </c>
+      <c r="E46" s="5">
+        <v>601</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" s="5">
+        <v>42</v>
+      </c>
+      <c r="J46" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>61</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>133591265</v>
+      </c>
+      <c r="E47" s="5">
+        <v>601</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="5">
+        <v>42</v>
+      </c>
+      <c r="J47" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>61</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>133592079</v>
+      </c>
+      <c r="E48" s="5">
+        <v>601</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I48" s="5">
+        <v>42</v>
+      </c>
+      <c r="J48" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <v>61</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>133592248</v>
+      </c>
+      <c r="E49" s="5">
+        <v>601</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="5">
+        <v>42</v>
+      </c>
+      <c r="J49" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>61</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>133592934</v>
+      </c>
+      <c r="E50" s="5">
+        <v>601</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I50" s="5">
+        <v>42</v>
+      </c>
+      <c r="J50" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>61</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>133594093</v>
+      </c>
+      <c r="E51" s="5">
+        <v>601</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I51" s="5">
+        <v>42</v>
+      </c>
+      <c r="J51" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>61</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>133599657</v>
+      </c>
+      <c r="E52" s="5">
+        <v>601</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I52" s="5">
+        <v>42</v>
+      </c>
+      <c r="J52" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>61</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>133603556</v>
+      </c>
+      <c r="E53" s="5">
+        <v>601</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I53" s="5">
+        <v>42</v>
+      </c>
+      <c r="J53" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <v>61</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>133636954</v>
+      </c>
+      <c r="E54" s="5">
+        <v>601</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="5">
+        <v>42</v>
+      </c>
+      <c r="J54" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>61</v>
+      </c>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>133637172</v>
+      </c>
+      <c r="E55" s="5">
+        <v>601</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" s="5">
+        <v>42</v>
+      </c>
+      <c r="J55" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>61</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>133637393</v>
+      </c>
+      <c r="E56" s="5">
+        <v>601</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="5">
+        <v>42</v>
+      </c>
+      <c r="J56" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>61</v>
+      </c>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>133637629</v>
+      </c>
+      <c r="E57" s="5">
+        <v>601</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I57" s="5">
+        <v>42</v>
+      </c>
+      <c r="J57" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>61</v>
+      </c>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>133637859</v>
+      </c>
+      <c r="E58" s="5">
+        <v>601</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" s="5">
+        <v>42</v>
+      </c>
+      <c r="J58" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>61</v>
+      </c>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>133637861</v>
+      </c>
+      <c r="E59" s="5">
+        <v>601</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I59" s="5">
+        <v>42</v>
+      </c>
+      <c r="J59" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5">
+        <v>61</v>
+      </c>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>133637898</v>
+      </c>
+      <c r="E60" s="5">
+        <v>601</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>133638190</v>
+      </c>
+      <c r="E61" s="5">
+        <v>601</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>133638623</v>
+      </c>
+      <c r="E62" s="5">
+        <v>601</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>133638776</v>
+      </c>
+      <c r="E63" s="5">
+        <v>601</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>133639523</v>
+      </c>
+      <c r="E64" s="5">
+        <v>601</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>133639644</v>
+      </c>
+      <c r="E65" s="5">
+        <v>601</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>133639689</v>
+      </c>
+      <c r="E66" s="5">
+        <v>601</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>133639738</v>
+      </c>
+      <c r="E67" s="5">
+        <v>601</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>133639906</v>
+      </c>
+      <c r="E68" s="5">
+        <v>601</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>133640205</v>
+      </c>
+      <c r="E69" s="5">
+        <v>601</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>133640462</v>
+      </c>
+      <c r="E70" s="5">
+        <v>601</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>133640876</v>
+      </c>
+      <c r="E71" s="5">
+        <v>601</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>133640968</v>
+      </c>
+      <c r="E72" s="5">
+        <v>601</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>133641016</v>
+      </c>
+      <c r="E73" s="5">
+        <v>601</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>133641042</v>
+      </c>
+      <c r="E74" s="5">
+        <v>601</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>133641634</v>
+      </c>
+      <c r="E75" s="5">
+        <v>601</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>133641882</v>
+      </c>
+      <c r="E76" s="5">
+        <v>601</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>133641959</v>
+      </c>
+      <c r="E77" s="5">
+        <v>601</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>133641997</v>
+      </c>
+      <c r="E78" s="5">
+        <v>601</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>133642316</v>
+      </c>
+      <c r="E79" s="5">
+        <v>601</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I79" s="5">
+        <v>42</v>
+      </c>
+      <c r="J79" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5">
+        <v>61</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>133642570</v>
+      </c>
+      <c r="E80" s="5">
+        <v>601</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I80" s="5">
+        <v>42</v>
+      </c>
+      <c r="J80" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>61</v>
+      </c>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>133643821</v>
+      </c>
+      <c r="E81" s="5">
+        <v>601</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81" s="5">
+        <v>42</v>
+      </c>
+      <c r="J81" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>61</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>133644176</v>
+      </c>
+      <c r="E82" s="5">
+        <v>601</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82" s="5">
+        <v>42</v>
+      </c>
+      <c r="J82" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5">
+        <v>61</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>133644350</v>
+      </c>
+      <c r="E83" s="5">
+        <v>601</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I83" s="5">
+        <v>42</v>
+      </c>
+      <c r="J83" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5">
+        <v>61</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>133644625</v>
+      </c>
+      <c r="E84" s="5">
+        <v>601</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" s="5">
+        <v>42</v>
+      </c>
+      <c r="J84" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5">
+        <v>61</v>
+      </c>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>133644688</v>
+      </c>
+      <c r="E85" s="5">
+        <v>601</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" s="5">
+        <v>42</v>
+      </c>
+      <c r="J85" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5">
+        <v>61</v>
+      </c>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>133644987</v>
+      </c>
+      <c r="E86" s="5">
+        <v>601</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86" s="5">
+        <v>42</v>
+      </c>
+      <c r="J86" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5">
+        <v>61</v>
+      </c>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>133645001</v>
+      </c>
+      <c r="E87" s="5">
+        <v>601</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" s="5">
+        <v>42</v>
+      </c>
+      <c r="J87" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5">
+        <v>61</v>
+      </c>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>133645083</v>
+      </c>
+      <c r="E88" s="5">
+        <v>601</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>133645509</v>
+      </c>
+      <c r="E89" s="5">
+        <v>601</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      </c>
+      <c r="J89" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5">
+        <v>61</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
+        <v>133645553</v>
+      </c>
+      <c r="E90" s="5">
+        <v>601</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="5">
+        <v>42</v>
+      </c>
+      <c r="J90" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5">
+        <v>61</v>
+      </c>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>133645860</v>
+      </c>
+      <c r="E91" s="5">
+        <v>601</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" s="5">
+        <v>42</v>
+      </c>
+      <c r="J91" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5">
+        <v>61</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
+        <v>133645949</v>
+      </c>
+      <c r="E92" s="5">
+        <v>601</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I92" s="5">
+        <v>42</v>
+      </c>
+      <c r="J92" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5">
+        <v>61</v>
+      </c>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>133646043</v>
+      </c>
+      <c r="E93" s="5">
+        <v>601</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I93" s="5">
+        <v>42</v>
+      </c>
+      <c r="J93" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5">
+        <v>61</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
+        <v>133646101</v>
+      </c>
+      <c r="E94" s="5">
+        <v>601</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" s="5">
+        <v>42</v>
+      </c>
+      <c r="J94" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5">
+        <v>61</v>
+      </c>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>133646122</v>
+      </c>
+      <c r="E95" s="5">
+        <v>601</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="5">
+        <v>42</v>
+      </c>
+      <c r="J95" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>61</v>
+      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="5">
+        <v>133646854</v>
+      </c>
+      <c r="E96" s="5">
+        <v>601</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96" s="5">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5">
+        <v>61</v>
+      </c>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
+        <v>133646885</v>
+      </c>
+      <c r="E97" s="5">
+        <v>601</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I97" s="5">
+        <v>42</v>
+      </c>
+      <c r="J97" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5">
+        <v>61</v>
+      </c>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="5">
+        <v>133646958</v>
+      </c>
+      <c r="E98" s="5">
+        <v>601</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I98" s="5">
+        <v>42</v>
+      </c>
+      <c r="J98" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5">
+        <v>61</v>
+      </c>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
+        <v>133647441</v>
+      </c>
+      <c r="E99" s="5">
+        <v>601</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="5">
+        <v>42</v>
+      </c>
+      <c r="J99" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
+        <v>61</v>
+      </c>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="5">
+        <v>133647530</v>
+      </c>
+      <c r="E100" s="5">
+        <v>609</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="5">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>61</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>133647692</v>
+      </c>
+      <c r="E101" s="5">
+        <v>601</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I101" s="5">
+        <v>42</v>
+      </c>
+      <c r="J101" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>61</v>
+      </c>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="5">
+        <v>133647702</v>
+      </c>
+      <c r="E102" s="5">
+        <v>601</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I102" s="5">
+        <v>42</v>
+      </c>
+      <c r="J102" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>61</v>
+      </c>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
+        <v>133647888</v>
+      </c>
+      <c r="E103" s="5">
+        <v>601</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I103" s="5">
+        <v>42</v>
+      </c>
+      <c r="J103" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>61</v>
+      </c>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="5">
+        <v>133647999</v>
+      </c>
+      <c r="E104" s="5">
+        <v>601</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I104" s="5">
+        <v>42</v>
+      </c>
+      <c r="J104" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5">
+        <v>61</v>
+      </c>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
+        <v>133648017</v>
+      </c>
+      <c r="E105" s="5">
+        <v>601</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I105" s="5">
+        <v>42</v>
+      </c>
+      <c r="J105" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5">
+        <v>61</v>
+      </c>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="5">
+        <v>133648085</v>
+      </c>
+      <c r="E106" s="5">
+        <v>609</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I106" s="5">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5">
+        <v>61</v>
+      </c>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="5">
+        <v>133648357</v>
+      </c>
+      <c r="E107" s="5">
+        <v>601</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I107" s="5">
+        <v>42</v>
+      </c>
+      <c r="J107" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5">
+        <v>61</v>
+      </c>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="5">
+        <v>133648585</v>
+      </c>
+      <c r="E108" s="5">
+        <v>601</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I108" s="5">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5">
+        <v>61</v>
+      </c>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="5">
+        <v>133648740</v>
+      </c>
+      <c r="E109" s="5">
+        <v>601</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I109" s="5">
+        <v>42</v>
+      </c>
+      <c r="J109" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5">
+        <v>61</v>
+      </c>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="5">
+        <v>133648742</v>
+      </c>
+      <c r="E110" s="5">
+        <v>601</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I110" s="5">
+        <v>42</v>
+      </c>
+      <c r="J110" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5">
+        <v>61</v>
+      </c>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="5">
+        <v>133648823</v>
+      </c>
+      <c r="E111" s="5">
+        <v>609</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I111" s="5">
+        <v>42</v>
+      </c>
+      <c r="J111" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5">
+        <v>61</v>
+      </c>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="5">
+        <v>133648986</v>
+      </c>
+      <c r="E112" s="5">
+        <v>601</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I112" s="5">
+        <v>42</v>
+      </c>
+      <c r="J112" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5">
+        <v>61</v>
+      </c>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="5">
+        <v>133649082</v>
+      </c>
+      <c r="E113" s="5">
+        <v>601</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I113" s="5">
+        <v>42</v>
+      </c>
+      <c r="J113" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5">
+        <v>61</v>
+      </c>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="5">
+        <v>133649239</v>
+      </c>
+      <c r="E114" s="5">
+        <v>609</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I114" s="5">
+        <v>42</v>
+      </c>
+      <c r="J114" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5">
+        <v>61</v>
+      </c>
+      <c r="M114" s="5"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="5">
+        <v>133649275</v>
+      </c>
+      <c r="E115" s="5">
+        <v>601</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I115" s="5">
+        <v>42</v>
+      </c>
+      <c r="J115" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5">
+        <v>61</v>
+      </c>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="5">
+        <v>133649401</v>
+      </c>
+      <c r="E116" s="5">
+        <v>609</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I116" s="5">
+        <v>42</v>
+      </c>
+      <c r="J116" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" s="5">
+        <v>61</v>
+      </c>
+      <c r="M116" s="5"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="5">
+        <v>133649482</v>
+      </c>
+      <c r="E117" s="5">
+        <v>601</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I117" s="5">
+        <v>42</v>
+      </c>
+      <c r="J117" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" s="5">
+        <v>61</v>
+      </c>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="5">
+        <v>133649506</v>
+      </c>
+      <c r="E118" s="5">
+        <v>609</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I118" s="5">
+        <v>42</v>
+      </c>
+      <c r="J118" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5">
+        <v>61</v>
+      </c>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5"/>
+      <c r="O118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="5">
+        <v>133649660</v>
+      </c>
+      <c r="E119" s="5">
+        <v>609</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I119" s="5">
+        <v>42</v>
+      </c>
+      <c r="J119" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5">
+        <v>61</v>
+      </c>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="5">
+        <v>133649703</v>
+      </c>
+      <c r="E120" s="5">
+        <v>601</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I120" s="5">
+        <v>42</v>
+      </c>
+      <c r="J120" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5">
+        <v>61</v>
+      </c>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="5">
+        <v>133649718</v>
+      </c>
+      <c r="E121" s="5">
+        <v>601</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I121" s="5">
+        <v>42</v>
+      </c>
+      <c r="J121" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5">
+        <v>61</v>
+      </c>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="5">
+        <v>133649867</v>
+      </c>
+      <c r="E122" s="5">
+        <v>609</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="5">
+        <v>133650032</v>
+      </c>
+      <c r="E123" s="5">
+        <v>609</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="5">
+        <v>133650034</v>
+      </c>
+      <c r="E124" s="5">
+        <v>601</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="5">
+        <v>133650427</v>
+      </c>
+      <c r="E125" s="5">
+        <v>601</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="5">
+        <v>133650659</v>
+      </c>
+      <c r="E126" s="5">
+        <v>601</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="5">
+        <v>133650790</v>
+      </c>
+      <c r="E127" s="5">
+        <v>601</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="5">
+        <v>133650828</v>
+      </c>
+      <c r="E128" s="5">
+        <v>601</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="5">
+        <v>133650896</v>
+      </c>
+      <c r="E129" s="5">
+        <v>601</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="5">
+        <v>133650982</v>
+      </c>
+      <c r="E130" s="5">
+        <v>601</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="5">
+        <v>133651086</v>
+      </c>
+      <c r="E131" s="5">
+        <v>601</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="5">
+        <v>133651392</v>
+      </c>
+      <c r="E132" s="5">
+        <v>601</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="5">
+        <v>133651665</v>
+      </c>
+      <c r="E133" s="5">
+        <v>601</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="M133" s="5"/>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="5">
+        <v>133651991</v>
+      </c>
+      <c r="E134" s="5">
+        <v>601</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="M134" s="5"/>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="5">
+        <v>133652182</v>
+      </c>
+      <c r="E135" s="5">
+        <v>601</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="5">
+        <v>133653050</v>
+      </c>
+      <c r="E136" s="5">
+        <v>601</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="M136" s="5"/>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
+        <v>133653144</v>
+      </c>
+      <c r="E137" s="5">
+        <v>601</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="M137" s="5"/>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="5">
+        <v>133653182</v>
+      </c>
+      <c r="E138" s="5">
+        <v>601</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="M138" s="5"/>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="5">
+        <v>133653329</v>
+      </c>
+      <c r="E139" s="5">
+        <v>601</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+      <c r="O139" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304638ED-DD02-49D6-8E96-06C5F4D46102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D4BD31-E0BD-45E5-9A16-2524A329DFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="37">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,22 +79,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>25/7/2025</t>
-  </si>
-  <si>
     <t>8/3/2023</t>
   </si>
   <si>
     <t>10/3/2023</t>
   </si>
   <si>
-    <t>26/7/2025</t>
+    <t>23/7/2025</t>
   </si>
   <si>
     <t>28/7/2025</t>
-  </si>
-  <si>
-    <t>23/7/2025</t>
   </si>
   <si>
     <t>29/7/2025</t>
@@ -112,19 +106,25 @@
     <t>10/06/2025</t>
   </si>
   <si>
+    <t>03/07/2025</t>
+  </si>
+  <si>
     <t>04/07/2025</t>
   </si>
   <si>
     <t>28/07/2025</t>
   </si>
   <si>
+    <t>09/07/2025</t>
+  </si>
+  <si>
     <t>16/07/2025</t>
   </si>
   <si>
-    <t>29/07/2025</t>
+    <t>17/07/2025</t>
   </si>
   <si>
-    <t>21/07/2025</t>
+    <t>18/07/2025</t>
   </si>
   <si>
     <t>22/07/2025</t>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>26/07/2025</t>
+  </si>
+  <si>
+    <t>29/07/2025</t>
   </si>
 </sst>
 </file>
@@ -554,7 +557,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -624,7 +627,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>133622778</v>
+        <v>123058958</v>
       </c>
       <c r="E2" s="5">
         <v>1211</v>
@@ -633,13 +636,13 @@
         <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -655,22 +658,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>133629666</v>
+        <v>133577242</v>
       </c>
       <c r="E3" s="5">
         <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>1735</v>
+        <v>715</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -686,22 +689,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>123058958</v>
+        <v>133656486</v>
       </c>
       <c r="E4" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -717,13 +720,13 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>130789903</v>
+        <v>133660124</v>
       </c>
       <c r="E5" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>20</v>
@@ -732,7 +735,7 @@
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -748,13 +751,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>130789903</v>
+        <v>133660658</v>
       </c>
       <c r="E6" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>20</v>
@@ -763,7 +766,7 @@
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -779,13 +782,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>133577242</v>
+        <v>133661191</v>
       </c>
       <c r="E7" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>20</v>
@@ -794,7 +797,7 @@
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -810,7 +813,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>133637216</v>
+        <v>133662866</v>
       </c>
       <c r="E8" s="5">
         <v>2013</v>
@@ -841,7 +844,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>133638652</v>
+        <v>133665837</v>
       </c>
       <c r="E9" s="5">
         <v>2013</v>
@@ -850,7 +853,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
@@ -872,7 +875,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>133638687</v>
+        <v>133667347</v>
       </c>
       <c r="E10" s="5">
         <v>2013</v>
@@ -903,7 +906,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>133639461</v>
+        <v>133668529</v>
       </c>
       <c r="E11" s="5">
         <v>2013</v>
@@ -934,7 +937,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133640088</v>
+        <v>133669535</v>
       </c>
       <c r="E12" s="5">
         <v>2013</v>
@@ -965,7 +968,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>133640125</v>
+        <v>133669645</v>
       </c>
       <c r="E13" s="5">
         <v>2013</v>
@@ -996,7 +999,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>133640963</v>
+        <v>133669802</v>
       </c>
       <c r="E14" s="5">
         <v>2013</v>
@@ -1027,7 +1030,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>133641155</v>
+        <v>133671017</v>
       </c>
       <c r="E15" s="5">
         <v>2013</v>
@@ -1036,7 +1039,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
@@ -1058,7 +1061,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>133642685</v>
+        <v>133671458</v>
       </c>
       <c r="E16" s="5">
         <v>2013</v>
@@ -1089,7 +1092,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>133645192</v>
+        <v>133671547</v>
       </c>
       <c r="E17" s="5">
         <v>2013</v>
@@ -1098,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1120,13 +1123,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>133647300</v>
+        <v>132677248</v>
       </c>
       <c r="E18" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>22</v>
@@ -1135,7 +1138,7 @@
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1151,22 +1154,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>133648152</v>
+        <v>132914455</v>
       </c>
       <c r="E19" s="5">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1182,22 +1185,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>133648780</v>
+        <v>133247225</v>
       </c>
       <c r="E20" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1213,22 +1216,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>133648878</v>
+        <v>133256147</v>
       </c>
       <c r="E21" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1244,22 +1247,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>133649078</v>
+        <v>133267278</v>
       </c>
       <c r="E22" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1275,22 +1278,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>133649227</v>
+        <v>133268793</v>
       </c>
       <c r="E23" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1306,22 +1309,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>133649916</v>
+        <v>133273225</v>
       </c>
       <c r="E24" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1337,22 +1340,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>133650182</v>
+        <v>133279998</v>
       </c>
       <c r="E25" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
       </c>
       <c r="J25" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -1368,22 +1371,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>133650268</v>
+        <v>133283865</v>
       </c>
       <c r="E26" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1399,13 +1402,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>133650323</v>
+        <v>133309477</v>
       </c>
       <c r="E27" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>22</v>
@@ -1414,7 +1417,7 @@
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1430,22 +1433,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>133650534</v>
+        <v>133340046</v>
       </c>
       <c r="E28" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1461,22 +1464,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>133651035</v>
+        <v>133357532</v>
       </c>
       <c r="E29" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
       </c>
       <c r="J29" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -1492,22 +1495,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>133651554</v>
+        <v>133365654</v>
       </c>
       <c r="E30" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
       </c>
       <c r="J30" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -1523,22 +1526,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>133651715</v>
+        <v>133453383</v>
       </c>
       <c r="E31" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
       </c>
       <c r="J31" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K31" s="5">
         <v>0</v>
@@ -1554,22 +1557,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>132677248</v>
+        <v>133456928</v>
       </c>
       <c r="E32" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
       </c>
       <c r="J32" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -1585,22 +1588,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>132914455</v>
+        <v>133486026</v>
       </c>
       <c r="E33" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
       </c>
       <c r="J33" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -1616,16 +1619,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>133273225</v>
+        <v>133499371</v>
       </c>
       <c r="E34" s="5">
         <v>601</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1647,16 +1650,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>133283865</v>
+        <v>133508346</v>
       </c>
       <c r="E35" s="5">
         <v>601</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
@@ -1678,16 +1681,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>133365654</v>
+        <v>133562394</v>
       </c>
       <c r="E36" s="5">
         <v>601</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
@@ -1709,16 +1712,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>133453383</v>
+        <v>133577255</v>
       </c>
       <c r="E37" s="5">
         <v>601</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
@@ -1740,22 +1743,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>133455571</v>
+        <v>133581885</v>
       </c>
       <c r="E38" s="5">
         <v>601</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
       </c>
       <c r="J38" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
@@ -1771,16 +1774,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>133456928</v>
+        <v>133583834</v>
       </c>
       <c r="E39" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
@@ -1802,16 +1805,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>133529510</v>
+        <v>133590458</v>
       </c>
       <c r="E40" s="5">
         <v>601</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
@@ -1833,16 +1836,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>133546576</v>
+        <v>133591265</v>
       </c>
       <c r="E41" s="5">
         <v>601</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
@@ -1864,16 +1867,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>133562394</v>
+        <v>133592079</v>
       </c>
       <c r="E42" s="5">
         <v>601</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
@@ -1895,22 +1898,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>133577255</v>
+        <v>133592248</v>
       </c>
       <c r="E43" s="5">
         <v>601</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I43" s="5">
         <v>42</v>
       </c>
       <c r="J43" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -1926,16 +1929,16 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>133581885</v>
+        <v>133594093</v>
       </c>
       <c r="E44" s="5">
         <v>601</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
@@ -1957,16 +1960,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>133583834</v>
+        <v>133599657</v>
       </c>
       <c r="E45" s="5">
         <v>601</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
@@ -1988,7 +1991,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>133590458</v>
+        <v>133602164</v>
       </c>
       <c r="E46" s="5">
         <v>601</v>
@@ -2019,13 +2022,13 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>133591265</v>
+        <v>133603556</v>
       </c>
       <c r="E47" s="5">
         <v>601</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>34</v>
@@ -2034,7 +2037,7 @@
         <v>42</v>
       </c>
       <c r="J47" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -2050,22 +2053,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>133592079</v>
+        <v>133636954</v>
       </c>
       <c r="E48" s="5">
         <v>601</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2081,22 +2084,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>133592248</v>
+        <v>133637172</v>
       </c>
       <c r="E49" s="5">
         <v>601</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2112,22 +2115,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>133592934</v>
+        <v>133637393</v>
       </c>
       <c r="E50" s="5">
         <v>601</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2143,16 +2146,16 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>133594093</v>
+        <v>133637629</v>
       </c>
       <c r="E51" s="5">
         <v>601</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
@@ -2174,16 +2177,16 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>133599657</v>
+        <v>133637859</v>
       </c>
       <c r="E52" s="5">
         <v>601</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
@@ -2205,22 +2208,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>133603556</v>
+        <v>133637861</v>
       </c>
       <c r="E53" s="5">
         <v>601</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2236,22 +2239,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>133636954</v>
+        <v>133637898</v>
       </c>
       <c r="E54" s="5">
         <v>601</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2267,16 +2270,16 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>133637172</v>
+        <v>133638190</v>
       </c>
       <c r="E55" s="5">
         <v>601</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
@@ -2298,16 +2301,16 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>133637393</v>
+        <v>133638623</v>
       </c>
       <c r="E56" s="5">
         <v>601</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
@@ -2329,16 +2332,16 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>133637629</v>
+        <v>133638776</v>
       </c>
       <c r="E57" s="5">
         <v>601</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
@@ -2360,16 +2363,16 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>133637859</v>
+        <v>133639523</v>
       </c>
       <c r="E58" s="5">
         <v>601</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
@@ -2391,22 +2394,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>133637861</v>
+        <v>133639689</v>
       </c>
       <c r="E59" s="5">
         <v>601</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2422,16 +2425,16 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>133637898</v>
+        <v>133639738</v>
       </c>
       <c r="E60" s="5">
         <v>601</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
@@ -2453,16 +2456,16 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>133638190</v>
+        <v>133639906</v>
       </c>
       <c r="E61" s="5">
         <v>601</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
@@ -2484,16 +2487,16 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>133638623</v>
+        <v>133640205</v>
       </c>
       <c r="E62" s="5">
         <v>601</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I62" s="5">
         <v>42</v>
@@ -2515,16 +2518,16 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>133638776</v>
+        <v>133640462</v>
       </c>
       <c r="E63" s="5">
         <v>601</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
@@ -2546,16 +2549,16 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>133639523</v>
+        <v>133640876</v>
       </c>
       <c r="E64" s="5">
         <v>601</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
@@ -2577,16 +2580,16 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>133639644</v>
+        <v>133640968</v>
       </c>
       <c r="E65" s="5">
         <v>601</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
@@ -2608,22 +2611,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>133639689</v>
+        <v>133641016</v>
       </c>
       <c r="E66" s="5">
         <v>601</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
       </c>
       <c r="J66" s="5">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -2639,16 +2642,16 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>133639738</v>
+        <v>133641042</v>
       </c>
       <c r="E67" s="5">
         <v>601</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
@@ -2670,16 +2673,16 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>133639906</v>
+        <v>133641634</v>
       </c>
       <c r="E68" s="5">
         <v>601</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
@@ -2701,16 +2704,16 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>133640205</v>
+        <v>133641882</v>
       </c>
       <c r="E69" s="5">
         <v>601</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
@@ -2732,16 +2735,16 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>133640462</v>
+        <v>133641959</v>
       </c>
       <c r="E70" s="5">
         <v>601</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
@@ -2763,16 +2766,16 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>133640876</v>
+        <v>133641997</v>
       </c>
       <c r="E71" s="5">
         <v>601</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
@@ -2794,16 +2797,16 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>133640968</v>
+        <v>133642316</v>
       </c>
       <c r="E72" s="5">
         <v>601</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I72" s="5">
         <v>42</v>
@@ -2825,16 +2828,16 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>133641016</v>
+        <v>133642570</v>
       </c>
       <c r="E73" s="5">
         <v>601</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
@@ -2856,16 +2859,16 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>133641042</v>
+        <v>133643821</v>
       </c>
       <c r="E74" s="5">
         <v>601</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
@@ -2887,16 +2890,16 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>133641634</v>
+        <v>133644176</v>
       </c>
       <c r="E75" s="5">
         <v>601</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
@@ -2918,16 +2921,16 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>133641882</v>
+        <v>133644350</v>
       </c>
       <c r="E76" s="5">
         <v>601</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
@@ -2949,16 +2952,16 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>133641959</v>
+        <v>133644688</v>
       </c>
       <c r="E77" s="5">
         <v>601</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
@@ -2980,16 +2983,16 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>133641997</v>
+        <v>133644987</v>
       </c>
       <c r="E78" s="5">
         <v>601</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I78" s="5">
         <v>42</v>
@@ -3011,16 +3014,16 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>133642316</v>
+        <v>133645001</v>
       </c>
       <c r="E79" s="5">
         <v>601</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I79" s="5">
         <v>42</v>
@@ -3042,16 +3045,16 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>133642570</v>
+        <v>133645083</v>
       </c>
       <c r="E80" s="5">
         <v>601</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I80" s="5">
         <v>42</v>
@@ -3073,16 +3076,16 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>133643821</v>
+        <v>133645509</v>
       </c>
       <c r="E81" s="5">
         <v>601</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I81" s="5">
         <v>42</v>
@@ -3104,16 +3107,16 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>133644176</v>
+        <v>133645553</v>
       </c>
       <c r="E82" s="5">
         <v>601</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I82" s="5">
         <v>42</v>
@@ -3135,16 +3138,16 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>133644350</v>
+        <v>133646043</v>
       </c>
       <c r="E83" s="5">
         <v>601</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I83" s="5">
         <v>42</v>
@@ -3166,22 +3169,22 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>133644625</v>
+        <v>133646101</v>
       </c>
       <c r="E84" s="5">
         <v>601</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I84" s="5">
         <v>42</v>
       </c>
       <c r="J84" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K84" s="5">
         <v>0</v>
@@ -3197,22 +3200,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>133644688</v>
+        <v>133646122</v>
       </c>
       <c r="E85" s="5">
         <v>601</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I85" s="5">
         <v>42</v>
       </c>
       <c r="J85" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K85" s="5">
         <v>0</v>
@@ -3228,16 +3231,16 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>133644987</v>
+        <v>133646854</v>
       </c>
       <c r="E86" s="5">
         <v>601</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I86" s="5">
         <v>42</v>
@@ -3259,16 +3262,16 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>133645001</v>
+        <v>133646885</v>
       </c>
       <c r="E87" s="5">
         <v>601</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I87" s="5">
         <v>42</v>
@@ -3290,16 +3293,16 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
-        <v>133645083</v>
+        <v>133647441</v>
       </c>
       <c r="E88" s="5">
         <v>601</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I88" s="5">
         <v>42</v>
@@ -3321,16 +3324,16 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>133645509</v>
+        <v>133647530</v>
       </c>
       <c r="E89" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I89" s="5">
         <v>42</v>
@@ -3352,16 +3355,16 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>133645553</v>
+        <v>133647692</v>
       </c>
       <c r="E90" s="5">
         <v>601</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I90" s="5">
         <v>42</v>
@@ -3383,16 +3386,16 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>133645860</v>
+        <v>133647702</v>
       </c>
       <c r="E91" s="5">
         <v>601</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I91" s="5">
         <v>42</v>
@@ -3414,16 +3417,16 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>133645949</v>
+        <v>133647888</v>
       </c>
       <c r="E92" s="5">
         <v>601</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I92" s="5">
         <v>42</v>
@@ -3445,16 +3448,16 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>133646043</v>
+        <v>133647999</v>
       </c>
       <c r="E93" s="5">
         <v>601</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I93" s="5">
         <v>42</v>
@@ -3476,22 +3479,22 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>133646101</v>
+        <v>133648017</v>
       </c>
       <c r="E94" s="5">
         <v>601</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I94" s="5">
         <v>42</v>
       </c>
       <c r="J94" s="5">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="K94" s="5">
         <v>0</v>
@@ -3507,22 +3510,22 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>133646122</v>
+        <v>133648085</v>
       </c>
       <c r="E95" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I95" s="5">
         <v>42</v>
       </c>
       <c r="J95" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K95" s="5">
         <v>0</v>
@@ -3538,16 +3541,16 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>133646854</v>
+        <v>133648357</v>
       </c>
       <c r="E96" s="5">
         <v>601</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I96" s="5">
         <v>42</v>
@@ -3569,16 +3572,16 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>133646885</v>
+        <v>133648585</v>
       </c>
       <c r="E97" s="5">
         <v>601</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I97" s="5">
         <v>42</v>
@@ -3600,22 +3603,22 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <v>133646958</v>
+        <v>133648740</v>
       </c>
       <c r="E98" s="5">
         <v>601</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I98" s="5">
         <v>42</v>
       </c>
       <c r="J98" s="5">
-        <v>8004</v>
+        <v>1118</v>
       </c>
       <c r="K98" s="5">
         <v>0</v>
@@ -3631,16 +3634,16 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <v>133647441</v>
+        <v>133648742</v>
       </c>
       <c r="E99" s="5">
         <v>601</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I99" s="5">
         <v>42</v>
@@ -3662,16 +3665,16 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <v>133647530</v>
+        <v>133648823</v>
       </c>
       <c r="E100" s="5">
         <v>609</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I100" s="5">
         <v>42</v>
@@ -3693,16 +3696,16 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <v>133647692</v>
+        <v>133648986</v>
       </c>
       <c r="E101" s="5">
         <v>601</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I101" s="5">
         <v>42</v>
@@ -3724,22 +3727,22 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <v>133647702</v>
+        <v>133649082</v>
       </c>
       <c r="E102" s="5">
         <v>601</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I102" s="5">
         <v>42</v>
       </c>
       <c r="J102" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K102" s="5">
         <v>0</v>
@@ -3755,16 +3758,16 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <v>133647888</v>
+        <v>133649239</v>
       </c>
       <c r="E103" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I103" s="5">
         <v>42</v>
@@ -3786,16 +3789,16 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <v>133647999</v>
+        <v>133649275</v>
       </c>
       <c r="E104" s="5">
         <v>601</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I104" s="5">
         <v>42</v>
@@ -3817,16 +3820,16 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
-        <v>133648017</v>
+        <v>133649401</v>
       </c>
       <c r="E105" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I105" s="5">
         <v>42</v>
@@ -3848,22 +3851,22 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <v>133648085</v>
+        <v>133649482</v>
       </c>
       <c r="E106" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I106" s="5">
         <v>42</v>
       </c>
       <c r="J106" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
@@ -3879,16 +3882,16 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <v>133648357</v>
+        <v>133649506</v>
       </c>
       <c r="E107" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I107" s="5">
         <v>42</v>
@@ -3910,16 +3913,16 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <v>133648585</v>
+        <v>133649660</v>
       </c>
       <c r="E108" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I108" s="5">
         <v>42</v>
@@ -3941,22 +3944,22 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <v>133648740</v>
+        <v>133649703</v>
       </c>
       <c r="E109" s="5">
         <v>601</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I109" s="5">
         <v>42</v>
       </c>
       <c r="J109" s="5">
-        <v>1118</v>
+        <v>8004</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
@@ -3972,16 +3975,16 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <v>133648742</v>
+        <v>133649718</v>
       </c>
       <c r="E110" s="5">
         <v>601</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I110" s="5">
         <v>42</v>
@@ -4003,16 +4006,16 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <v>133648823</v>
+        <v>133649867</v>
       </c>
       <c r="E111" s="5">
         <v>609</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I111" s="5">
         <v>42</v>
@@ -4034,16 +4037,16 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <v>133648986</v>
+        <v>133650032</v>
       </c>
       <c r="E112" s="5">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I112" s="5">
         <v>42</v>
@@ -4065,22 +4068,22 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
-        <v>133649082</v>
+        <v>133650034</v>
       </c>
       <c r="E113" s="5">
         <v>601</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I113" s="5">
         <v>42</v>
       </c>
       <c r="J113" s="5">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
@@ -4096,16 +4099,16 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
-        <v>133649239</v>
+        <v>133650427</v>
       </c>
       <c r="E114" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I114" s="5">
         <v>42</v>
@@ -4127,16 +4130,16 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <v>133649275</v>
+        <v>133650659</v>
       </c>
       <c r="E115" s="5">
         <v>601</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I115" s="5">
         <v>42</v>
@@ -4158,16 +4161,16 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <v>133649401</v>
+        <v>133650790</v>
       </c>
       <c r="E116" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I116" s="5">
         <v>42</v>
@@ -4189,22 +4192,22 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <v>133649482</v>
+        <v>133650828</v>
       </c>
       <c r="E117" s="5">
         <v>601</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I117" s="5">
         <v>42</v>
       </c>
       <c r="J117" s="5">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="K117" s="5">
         <v>0</v>
@@ -4220,16 +4223,16 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <v>133649506</v>
+        <v>133650982</v>
       </c>
       <c r="E118" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I118" s="5">
         <v>42</v>
@@ -4251,22 +4254,22 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
-        <v>133649660</v>
+        <v>133651086</v>
       </c>
       <c r="E119" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I119" s="5">
         <v>42</v>
       </c>
       <c r="J119" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K119" s="5">
         <v>0</v>
@@ -4282,16 +4285,16 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
-        <v>133649703</v>
+        <v>133651392</v>
       </c>
       <c r="E120" s="5">
         <v>601</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I120" s="5">
         <v>42</v>
@@ -4313,22 +4316,22 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
-        <v>133649718</v>
+        <v>133651665</v>
       </c>
       <c r="E121" s="5">
         <v>601</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I121" s="5">
         <v>42</v>
       </c>
       <c r="J121" s="5">
-        <v>8004</v>
+        <v>1118</v>
       </c>
       <c r="K121" s="5">
         <v>0</v>
@@ -4344,16 +4347,16 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
-        <v>133649867</v>
+        <v>133651991</v>
       </c>
       <c r="E122" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I122" s="5">
         <v>42</v>
@@ -4375,16 +4378,16 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
-        <v>133650032</v>
+        <v>133652182</v>
       </c>
       <c r="E123" s="5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I123" s="5">
         <v>42</v>
@@ -4406,16 +4409,16 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
-        <v>133650034</v>
+        <v>133652357</v>
       </c>
       <c r="E124" s="5">
         <v>601</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I124" s="5">
         <v>42</v>
@@ -4437,22 +4440,22 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
-        <v>133650427</v>
+        <v>133653050</v>
       </c>
       <c r="E125" s="5">
         <v>601</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I125" s="5">
         <v>42</v>
       </c>
       <c r="J125" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K125" s="5">
         <v>0</v>
@@ -4468,16 +4471,16 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
-        <v>133650659</v>
+        <v>133653144</v>
       </c>
       <c r="E126" s="5">
         <v>601</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I126" s="5">
         <v>42</v>
@@ -4499,16 +4502,16 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
-        <v>133650790</v>
+        <v>133653182</v>
       </c>
       <c r="E127" s="5">
         <v>601</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I127" s="5">
         <v>42</v>
@@ -4530,16 +4533,16 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
-        <v>133650828</v>
+        <v>133656288</v>
       </c>
       <c r="E128" s="5">
         <v>601</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I128" s="5">
         <v>42</v>
@@ -4561,16 +4564,16 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
-        <v>133650896</v>
+        <v>133656466</v>
       </c>
       <c r="E129" s="5">
         <v>601</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I129" s="5">
         <v>42</v>
@@ -4592,16 +4595,16 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
-        <v>133650982</v>
+        <v>133656534</v>
       </c>
       <c r="E130" s="5">
         <v>601</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I130" s="5">
         <v>42</v>
@@ -4623,22 +4626,22 @@
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
-        <v>133651086</v>
+        <v>133656540</v>
       </c>
       <c r="E131" s="5">
         <v>601</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I131" s="5">
         <v>42</v>
       </c>
       <c r="J131" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K131" s="5">
         <v>0</v>
@@ -4654,16 +4657,16 @@
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
-        <v>133651392</v>
+        <v>133656658</v>
       </c>
       <c r="E132" s="5">
         <v>601</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I132" s="5">
         <v>42</v>
@@ -4685,22 +4688,22 @@
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
-        <v>133651665</v>
+        <v>133656731</v>
       </c>
       <c r="E133" s="5">
         <v>601</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I133" s="5">
         <v>42</v>
       </c>
       <c r="J133" s="5">
-        <v>1118</v>
+        <v>8004</v>
       </c>
       <c r="K133" s="5">
         <v>0</v>
@@ -4716,16 +4719,16 @@
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
-        <v>133651991</v>
+        <v>133656838</v>
       </c>
       <c r="E134" s="5">
         <v>601</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I134" s="5">
         <v>42</v>
@@ -4747,16 +4750,16 @@
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
-        <v>133652182</v>
+        <v>133656846</v>
       </c>
       <c r="E135" s="5">
         <v>601</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I135" s="5">
         <v>42</v>
@@ -4778,22 +4781,22 @@
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
-        <v>133653050</v>
+        <v>133656908</v>
       </c>
       <c r="E136" s="5">
         <v>601</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I136" s="5">
         <v>42</v>
       </c>
       <c r="J136" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K136" s="5">
         <v>0</v>
@@ -4809,16 +4812,16 @@
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
-        <v>133653144</v>
+        <v>133657120</v>
       </c>
       <c r="E137" s="5">
         <v>601</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I137" s="5">
         <v>42</v>
@@ -4840,16 +4843,16 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
-        <v>133653182</v>
+        <v>133657453</v>
       </c>
       <c r="E138" s="5">
         <v>601</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I138" s="5">
         <v>42</v>
@@ -4871,16 +4874,16 @@
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
-        <v>133653329</v>
+        <v>133657464</v>
       </c>
       <c r="E139" s="5">
         <v>601</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I139" s="5">
         <v>42</v>
@@ -4897,6 +4900,3478 @@
       <c r="M139" s="5"/>
       <c r="N139" s="5"/>
       <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="5">
+        <v>133657761</v>
+      </c>
+      <c r="E140" s="5">
+        <v>601</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="5">
+        <v>133657879</v>
+      </c>
+      <c r="E141" s="5">
+        <v>601</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="5">
+        <v>133658362</v>
+      </c>
+      <c r="E142" s="5">
+        <v>601</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="M142" s="5"/>
+      <c r="N142" s="5"/>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="5">
+        <v>133658474</v>
+      </c>
+      <c r="E143" s="5">
+        <v>601</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="M143" s="5"/>
+      <c r="N143" s="5"/>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="5">
+        <v>133658515</v>
+      </c>
+      <c r="E144" s="5">
+        <v>601</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="M144" s="5"/>
+      <c r="N144" s="5"/>
+      <c r="O144" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="5">
+        <v>133658833</v>
+      </c>
+      <c r="E145" s="5">
+        <v>601</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I145" s="5">
+        <v>42</v>
+      </c>
+      <c r="J145" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="L145" s="5">
+        <v>61</v>
+      </c>
+      <c r="M145" s="5"/>
+      <c r="N145" s="5"/>
+      <c r="O145" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="5">
+        <v>133659634</v>
+      </c>
+      <c r="E146" s="5">
+        <v>601</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I146" s="5">
+        <v>42</v>
+      </c>
+      <c r="J146" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5">
+        <v>61</v>
+      </c>
+      <c r="M146" s="5"/>
+      <c r="N146" s="5"/>
+      <c r="O146" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="5">
+        <v>133659765</v>
+      </c>
+      <c r="E147" s="5">
+        <v>601</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I147" s="5">
+        <v>42</v>
+      </c>
+      <c r="J147" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5">
+        <v>61</v>
+      </c>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="5">
+        <v>133659838</v>
+      </c>
+      <c r="E148" s="5">
+        <v>601</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I148" s="5">
+        <v>42</v>
+      </c>
+      <c r="J148" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5">
+        <v>61</v>
+      </c>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="5">
+        <v>133659884</v>
+      </c>
+      <c r="E149" s="5">
+        <v>601</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I149" s="5">
+        <v>42</v>
+      </c>
+      <c r="J149" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5">
+        <v>61</v>
+      </c>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
+      <c r="O149" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="5">
+        <v>133659899</v>
+      </c>
+      <c r="E150" s="5">
+        <v>601</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I150" s="5">
+        <v>42</v>
+      </c>
+      <c r="J150" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5">
+        <v>61</v>
+      </c>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="5">
+        <v>133659983</v>
+      </c>
+      <c r="E151" s="5">
+        <v>601</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I151" s="5">
+        <v>42</v>
+      </c>
+      <c r="J151" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5">
+        <v>61</v>
+      </c>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="5">
+        <v>133660164</v>
+      </c>
+      <c r="E152" s="5">
+        <v>601</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I152" s="5">
+        <v>42</v>
+      </c>
+      <c r="J152" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="L152" s="5">
+        <v>61</v>
+      </c>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="5">
+        <v>133660186</v>
+      </c>
+      <c r="E153" s="5">
+        <v>601</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I153" s="5">
+        <v>42</v>
+      </c>
+      <c r="J153" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K153" s="5">
+        <v>0</v>
+      </c>
+      <c r="L153" s="5">
+        <v>61</v>
+      </c>
+      <c r="M153" s="5"/>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="5">
+        <v>133660316</v>
+      </c>
+      <c r="E154" s="5">
+        <v>601</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I154" s="5">
+        <v>42</v>
+      </c>
+      <c r="J154" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K154" s="5">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5">
+        <v>61</v>
+      </c>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="5">
+        <v>133660447</v>
+      </c>
+      <c r="E155" s="5">
+        <v>601</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I155" s="5">
+        <v>42</v>
+      </c>
+      <c r="J155" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K155" s="5">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5">
+        <v>61</v>
+      </c>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="5">
+        <v>133660632</v>
+      </c>
+      <c r="E156" s="5">
+        <v>601</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I156" s="5">
+        <v>42</v>
+      </c>
+      <c r="J156" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K156" s="5">
+        <v>0</v>
+      </c>
+      <c r="L156" s="5">
+        <v>61</v>
+      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="5">
+        <v>133660769</v>
+      </c>
+      <c r="E157" s="5">
+        <v>601</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I157" s="5">
+        <v>42</v>
+      </c>
+      <c r="J157" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K157" s="5">
+        <v>0</v>
+      </c>
+      <c r="L157" s="5">
+        <v>61</v>
+      </c>
+      <c r="M157" s="5"/>
+      <c r="N157" s="5"/>
+      <c r="O157" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="5">
+        <v>133660843</v>
+      </c>
+      <c r="E158" s="5">
+        <v>601</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I158" s="5">
+        <v>42</v>
+      </c>
+      <c r="J158" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K158" s="5">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5">
+        <v>61</v>
+      </c>
+      <c r="M158" s="5"/>
+      <c r="N158" s="5"/>
+      <c r="O158" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="5">
+        <v>133660954</v>
+      </c>
+      <c r="E159" s="5">
+        <v>601</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I159" s="5">
+        <v>42</v>
+      </c>
+      <c r="J159" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K159" s="5">
+        <v>0</v>
+      </c>
+      <c r="L159" s="5">
+        <v>61</v>
+      </c>
+      <c r="M159" s="5"/>
+      <c r="N159" s="5"/>
+      <c r="O159" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="5">
+        <v>133661010</v>
+      </c>
+      <c r="E160" s="5">
+        <v>601</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I160" s="5">
+        <v>42</v>
+      </c>
+      <c r="J160" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K160" s="5">
+        <v>0</v>
+      </c>
+      <c r="L160" s="5">
+        <v>61</v>
+      </c>
+      <c r="M160" s="5"/>
+      <c r="N160" s="5"/>
+      <c r="O160" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="5">
+        <v>133661052</v>
+      </c>
+      <c r="E161" s="5">
+        <v>601</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I161" s="5">
+        <v>42</v>
+      </c>
+      <c r="J161" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K161" s="5">
+        <v>0</v>
+      </c>
+      <c r="L161" s="5">
+        <v>61</v>
+      </c>
+      <c r="M161" s="5"/>
+      <c r="N161" s="5"/>
+      <c r="O161" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="5">
+        <v>133661110</v>
+      </c>
+      <c r="E162" s="5">
+        <v>601</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I162" s="5">
+        <v>42</v>
+      </c>
+      <c r="J162" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K162" s="5">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5">
+        <v>61</v>
+      </c>
+      <c r="M162" s="5"/>
+      <c r="N162" s="5"/>
+      <c r="O162" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="5">
+        <v>133661118</v>
+      </c>
+      <c r="E163" s="5">
+        <v>601</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I163" s="5">
+        <v>42</v>
+      </c>
+      <c r="J163" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K163" s="5">
+        <v>0</v>
+      </c>
+      <c r="L163" s="5">
+        <v>61</v>
+      </c>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
+      <c r="O163" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164" s="5">
+        <v>133661235</v>
+      </c>
+      <c r="E164" s="5">
+        <v>601</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I164" s="5">
+        <v>42</v>
+      </c>
+      <c r="J164" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K164" s="5">
+        <v>0</v>
+      </c>
+      <c r="L164" s="5">
+        <v>61</v>
+      </c>
+      <c r="M164" s="5"/>
+      <c r="N164" s="5"/>
+      <c r="O164" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165" s="5">
+        <v>133661265</v>
+      </c>
+      <c r="E165" s="5">
+        <v>601</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I165" s="5">
+        <v>42</v>
+      </c>
+      <c r="J165" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K165" s="5">
+        <v>0</v>
+      </c>
+      <c r="L165" s="5">
+        <v>61</v>
+      </c>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+      <c r="O165" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166" s="5">
+        <v>133661531</v>
+      </c>
+      <c r="E166" s="5">
+        <v>601</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I166" s="5">
+        <v>42</v>
+      </c>
+      <c r="J166" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K166" s="5">
+        <v>0</v>
+      </c>
+      <c r="L166" s="5">
+        <v>61</v>
+      </c>
+      <c r="M166" s="5"/>
+      <c r="N166" s="5"/>
+      <c r="O166" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="5">
+        <v>133661966</v>
+      </c>
+      <c r="E167" s="5">
+        <v>601</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I167" s="5">
+        <v>42</v>
+      </c>
+      <c r="J167" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K167" s="5">
+        <v>0</v>
+      </c>
+      <c r="L167" s="5">
+        <v>61</v>
+      </c>
+      <c r="M167" s="5"/>
+      <c r="N167" s="5"/>
+      <c r="O167" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168" s="5">
+        <v>133662236</v>
+      </c>
+      <c r="E168" s="5">
+        <v>601</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I168" s="5">
+        <v>42</v>
+      </c>
+      <c r="J168" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K168" s="5">
+        <v>0</v>
+      </c>
+      <c r="L168" s="5">
+        <v>61</v>
+      </c>
+      <c r="M168" s="5"/>
+      <c r="N168" s="5"/>
+      <c r="O168" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169" s="5">
+        <v>133662585</v>
+      </c>
+      <c r="E169" s="5">
+        <v>601</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I169" s="5">
+        <v>42</v>
+      </c>
+      <c r="J169" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K169" s="5">
+        <v>0</v>
+      </c>
+      <c r="L169" s="5">
+        <v>61</v>
+      </c>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="5">
+        <v>133662814</v>
+      </c>
+      <c r="E170" s="5">
+        <v>601</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I170" s="5">
+        <v>42</v>
+      </c>
+      <c r="J170" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K170" s="5">
+        <v>0</v>
+      </c>
+      <c r="L170" s="5">
+        <v>61</v>
+      </c>
+      <c r="M170" s="5"/>
+      <c r="N170" s="5"/>
+      <c r="O170" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171" s="5">
+        <v>133662964</v>
+      </c>
+      <c r="E171" s="5">
+        <v>601</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I171" s="5">
+        <v>42</v>
+      </c>
+      <c r="J171" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K171" s="5">
+        <v>0</v>
+      </c>
+      <c r="L171" s="5">
+        <v>61</v>
+      </c>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="5">
+        <v>133663526</v>
+      </c>
+      <c r="E172" s="5">
+        <v>601</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I172" s="5">
+        <v>42</v>
+      </c>
+      <c r="J172" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K172" s="5">
+        <v>0</v>
+      </c>
+      <c r="L172" s="5">
+        <v>61</v>
+      </c>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+      <c r="O172" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="5">
+        <v>133663597</v>
+      </c>
+      <c r="E173" s="5">
+        <v>601</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I173" s="5">
+        <v>42</v>
+      </c>
+      <c r="J173" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K173" s="5">
+        <v>0</v>
+      </c>
+      <c r="L173" s="5">
+        <v>61</v>
+      </c>
+      <c r="M173" s="5"/>
+      <c r="N173" s="5"/>
+      <c r="O173" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="5">
+        <v>133664191</v>
+      </c>
+      <c r="E174" s="5">
+        <v>601</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I174" s="5">
+        <v>42</v>
+      </c>
+      <c r="J174" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K174" s="5">
+        <v>0</v>
+      </c>
+      <c r="L174" s="5">
+        <v>61</v>
+      </c>
+      <c r="M174" s="5"/>
+      <c r="N174" s="5"/>
+      <c r="O174" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" s="5">
+        <v>133664768</v>
+      </c>
+      <c r="E175" s="5">
+        <v>601</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I175" s="5">
+        <v>42</v>
+      </c>
+      <c r="J175" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K175" s="5">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5">
+        <v>61</v>
+      </c>
+      <c r="M175" s="5"/>
+      <c r="N175" s="5"/>
+      <c r="O175" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" s="5">
+        <v>133664810</v>
+      </c>
+      <c r="E176" s="5">
+        <v>601</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I176" s="5">
+        <v>42</v>
+      </c>
+      <c r="J176" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K176" s="5">
+        <v>0</v>
+      </c>
+      <c r="L176" s="5">
+        <v>61</v>
+      </c>
+      <c r="M176" s="5"/>
+      <c r="N176" s="5"/>
+      <c r="O176" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" s="5">
+        <v>133664901</v>
+      </c>
+      <c r="E177" s="5">
+        <v>601</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I177" s="5">
+        <v>42</v>
+      </c>
+      <c r="J177" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K177" s="5">
+        <v>0</v>
+      </c>
+      <c r="L177" s="5">
+        <v>61</v>
+      </c>
+      <c r="M177" s="5"/>
+      <c r="N177" s="5"/>
+      <c r="O177" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" s="5">
+        <v>133665144</v>
+      </c>
+      <c r="E178" s="5">
+        <v>601</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I178" s="5">
+        <v>42</v>
+      </c>
+      <c r="J178" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K178" s="5">
+        <v>0</v>
+      </c>
+      <c r="L178" s="5">
+        <v>61</v>
+      </c>
+      <c r="M178" s="5"/>
+      <c r="N178" s="5"/>
+      <c r="O178" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="5">
+        <v>133665327</v>
+      </c>
+      <c r="E179" s="5">
+        <v>601</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I179" s="5">
+        <v>42</v>
+      </c>
+      <c r="J179" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K179" s="5">
+        <v>0</v>
+      </c>
+      <c r="L179" s="5">
+        <v>61</v>
+      </c>
+      <c r="M179" s="5"/>
+      <c r="N179" s="5"/>
+      <c r="O179" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" s="5">
+        <v>133665401</v>
+      </c>
+      <c r="E180" s="5">
+        <v>601</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I180" s="5">
+        <v>42</v>
+      </c>
+      <c r="J180" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K180" s="5">
+        <v>0</v>
+      </c>
+      <c r="L180" s="5">
+        <v>61</v>
+      </c>
+      <c r="M180" s="5"/>
+      <c r="N180" s="5"/>
+      <c r="O180" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" s="5">
+        <v>133665537</v>
+      </c>
+      <c r="E181" s="5">
+        <v>601</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I181" s="5">
+        <v>42</v>
+      </c>
+      <c r="J181" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K181" s="5">
+        <v>0</v>
+      </c>
+      <c r="L181" s="5">
+        <v>61</v>
+      </c>
+      <c r="M181" s="5"/>
+      <c r="N181" s="5"/>
+      <c r="O181" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" s="5">
+        <v>133665822</v>
+      </c>
+      <c r="E182" s="5">
+        <v>601</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I182" s="5">
+        <v>42</v>
+      </c>
+      <c r="J182" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K182" s="5">
+        <v>0</v>
+      </c>
+      <c r="L182" s="5">
+        <v>61</v>
+      </c>
+      <c r="M182" s="5"/>
+      <c r="N182" s="5"/>
+      <c r="O182" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183" s="5">
+        <v>133666018</v>
+      </c>
+      <c r="E183" s="5">
+        <v>601</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I183" s="5">
+        <v>42</v>
+      </c>
+      <c r="J183" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K183" s="5">
+        <v>0</v>
+      </c>
+      <c r="L183" s="5">
+        <v>61</v>
+      </c>
+      <c r="M183" s="5"/>
+      <c r="N183" s="5"/>
+      <c r="O183" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184" s="5">
+        <v>133666066</v>
+      </c>
+      <c r="E184" s="5">
+        <v>601</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I184" s="5">
+        <v>42</v>
+      </c>
+      <c r="J184" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K184" s="5">
+        <v>0</v>
+      </c>
+      <c r="L184" s="5">
+        <v>61</v>
+      </c>
+      <c r="M184" s="5"/>
+      <c r="N184" s="5"/>
+      <c r="O184" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" s="5">
+        <v>133666293</v>
+      </c>
+      <c r="E185" s="5">
+        <v>601</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I185" s="5">
+        <v>42</v>
+      </c>
+      <c r="J185" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K185" s="5">
+        <v>0</v>
+      </c>
+      <c r="L185" s="5">
+        <v>61</v>
+      </c>
+      <c r="M185" s="5"/>
+      <c r="N185" s="5"/>
+      <c r="O185" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186" s="5">
+        <v>133666500</v>
+      </c>
+      <c r="E186" s="5">
+        <v>601</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I186" s="5">
+        <v>42</v>
+      </c>
+      <c r="J186" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K186" s="5">
+        <v>0</v>
+      </c>
+      <c r="L186" s="5">
+        <v>61</v>
+      </c>
+      <c r="M186" s="5"/>
+      <c r="N186" s="5"/>
+      <c r="O186" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187" s="5">
+        <v>133666559</v>
+      </c>
+      <c r="E187" s="5">
+        <v>601</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I187" s="5">
+        <v>42</v>
+      </c>
+      <c r="J187" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K187" s="5">
+        <v>0</v>
+      </c>
+      <c r="L187" s="5">
+        <v>61</v>
+      </c>
+      <c r="M187" s="5"/>
+      <c r="N187" s="5"/>
+      <c r="O187" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" s="5">
+        <v>133666661</v>
+      </c>
+      <c r="E188" s="5">
+        <v>601</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I188" s="5">
+        <v>42</v>
+      </c>
+      <c r="J188" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K188" s="5">
+        <v>0</v>
+      </c>
+      <c r="L188" s="5">
+        <v>61</v>
+      </c>
+      <c r="M188" s="5"/>
+      <c r="N188" s="5"/>
+      <c r="O188" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189" s="5">
+        <v>133667006</v>
+      </c>
+      <c r="E189" s="5">
+        <v>601</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I189" s="5">
+        <v>42</v>
+      </c>
+      <c r="J189" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K189" s="5">
+        <v>0</v>
+      </c>
+      <c r="L189" s="5">
+        <v>61</v>
+      </c>
+      <c r="M189" s="5"/>
+      <c r="N189" s="5"/>
+      <c r="O189" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190" s="5">
+        <v>133667044</v>
+      </c>
+      <c r="E190" s="5">
+        <v>601</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I190" s="5">
+        <v>42</v>
+      </c>
+      <c r="J190" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K190" s="5">
+        <v>0</v>
+      </c>
+      <c r="L190" s="5">
+        <v>61</v>
+      </c>
+      <c r="M190" s="5"/>
+      <c r="N190" s="5"/>
+      <c r="O190" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191" s="5">
+        <v>133667157</v>
+      </c>
+      <c r="E191" s="5">
+        <v>601</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I191" s="5">
+        <v>42</v>
+      </c>
+      <c r="J191" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K191" s="5">
+        <v>0</v>
+      </c>
+      <c r="L191" s="5">
+        <v>61</v>
+      </c>
+      <c r="M191" s="5"/>
+      <c r="N191" s="5"/>
+      <c r="O191" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192" s="5">
+        <v>133667932</v>
+      </c>
+      <c r="E192" s="5">
+        <v>601</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I192" s="5">
+        <v>42</v>
+      </c>
+      <c r="J192" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K192" s="5">
+        <v>0</v>
+      </c>
+      <c r="L192" s="5">
+        <v>61</v>
+      </c>
+      <c r="M192" s="5"/>
+      <c r="N192" s="5"/>
+      <c r="O192" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A193" s="5">
+        <v>133667994</v>
+      </c>
+      <c r="E193" s="5">
+        <v>601</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I193" s="5">
+        <v>42</v>
+      </c>
+      <c r="J193" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K193" s="5">
+        <v>0</v>
+      </c>
+      <c r="L193" s="5">
+        <v>61</v>
+      </c>
+      <c r="M193" s="5"/>
+      <c r="N193" s="5"/>
+      <c r="O193" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A194" s="5">
+        <v>133668203</v>
+      </c>
+      <c r="E194" s="5">
+        <v>601</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I194" s="5">
+        <v>42</v>
+      </c>
+      <c r="J194" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K194" s="5">
+        <v>0</v>
+      </c>
+      <c r="L194" s="5">
+        <v>61</v>
+      </c>
+      <c r="M194" s="5"/>
+      <c r="N194" s="5"/>
+      <c r="O194" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A195" s="5">
+        <v>133668256</v>
+      </c>
+      <c r="E195" s="5">
+        <v>601</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I195" s="5">
+        <v>42</v>
+      </c>
+      <c r="J195" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K195" s="5">
+        <v>0</v>
+      </c>
+      <c r="L195" s="5">
+        <v>61</v>
+      </c>
+      <c r="M195" s="5"/>
+      <c r="N195" s="5"/>
+      <c r="O195" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A196" s="5">
+        <v>133668398</v>
+      </c>
+      <c r="E196" s="5">
+        <v>601</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I196" s="5">
+        <v>42</v>
+      </c>
+      <c r="J196" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K196" s="5">
+        <v>0</v>
+      </c>
+      <c r="L196" s="5">
+        <v>61</v>
+      </c>
+      <c r="M196" s="5"/>
+      <c r="N196" s="5"/>
+      <c r="O196" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197" s="5">
+        <v>133668508</v>
+      </c>
+      <c r="E197" s="5">
+        <v>601</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I197" s="5">
+        <v>42</v>
+      </c>
+      <c r="J197" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K197" s="5">
+        <v>0</v>
+      </c>
+      <c r="L197" s="5">
+        <v>61</v>
+      </c>
+      <c r="M197" s="5"/>
+      <c r="N197" s="5"/>
+      <c r="O197" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198" s="5">
+        <v>133668516</v>
+      </c>
+      <c r="E198" s="5">
+        <v>601</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I198" s="5">
+        <v>42</v>
+      </c>
+      <c r="J198" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K198" s="5">
+        <v>0</v>
+      </c>
+      <c r="L198" s="5">
+        <v>61</v>
+      </c>
+      <c r="M198" s="5"/>
+      <c r="N198" s="5"/>
+      <c r="O198" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A199" s="5">
+        <v>133668664</v>
+      </c>
+      <c r="E199" s="5">
+        <v>601</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I199" s="5">
+        <v>42</v>
+      </c>
+      <c r="J199" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K199" s="5">
+        <v>0</v>
+      </c>
+      <c r="L199" s="5">
+        <v>61</v>
+      </c>
+      <c r="M199" s="5"/>
+      <c r="N199" s="5"/>
+      <c r="O199" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A200" s="5">
+        <v>133668803</v>
+      </c>
+      <c r="E200" s="5">
+        <v>601</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I200" s="5">
+        <v>42</v>
+      </c>
+      <c r="J200" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K200" s="5">
+        <v>0</v>
+      </c>
+      <c r="L200" s="5">
+        <v>61</v>
+      </c>
+      <c r="M200" s="5"/>
+      <c r="N200" s="5"/>
+      <c r="O200" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A201" s="5">
+        <v>133668957</v>
+      </c>
+      <c r="E201" s="5">
+        <v>601</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I201" s="5">
+        <v>42</v>
+      </c>
+      <c r="J201" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K201" s="5">
+        <v>0</v>
+      </c>
+      <c r="L201" s="5">
+        <v>61</v>
+      </c>
+      <c r="M201" s="5"/>
+      <c r="N201" s="5"/>
+      <c r="O201" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A202" s="5">
+        <v>133669173</v>
+      </c>
+      <c r="E202" s="5">
+        <v>601</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I202" s="5">
+        <v>42</v>
+      </c>
+      <c r="J202" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K202" s="5">
+        <v>0</v>
+      </c>
+      <c r="L202" s="5">
+        <v>61</v>
+      </c>
+      <c r="M202" s="5"/>
+      <c r="N202" s="5"/>
+      <c r="O202" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203" s="5">
+        <v>133669181</v>
+      </c>
+      <c r="E203" s="5">
+        <v>601</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I203" s="5">
+        <v>42</v>
+      </c>
+      <c r="J203" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K203" s="5">
+        <v>0</v>
+      </c>
+      <c r="L203" s="5">
+        <v>61</v>
+      </c>
+      <c r="M203" s="5"/>
+      <c r="N203" s="5"/>
+      <c r="O203" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204" s="5">
+        <v>133669318</v>
+      </c>
+      <c r="E204" s="5">
+        <v>601</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I204" s="5">
+        <v>42</v>
+      </c>
+      <c r="J204" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K204" s="5">
+        <v>0</v>
+      </c>
+      <c r="L204" s="5">
+        <v>61</v>
+      </c>
+      <c r="M204" s="5"/>
+      <c r="N204" s="5"/>
+      <c r="O204" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A205" s="5">
+        <v>133669434</v>
+      </c>
+      <c r="E205" s="5">
+        <v>601</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I205" s="5">
+        <v>42</v>
+      </c>
+      <c r="J205" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K205" s="5">
+        <v>0</v>
+      </c>
+      <c r="L205" s="5">
+        <v>61</v>
+      </c>
+      <c r="M205" s="5"/>
+      <c r="N205" s="5"/>
+      <c r="O205" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206" s="5">
+        <v>133669498</v>
+      </c>
+      <c r="E206" s="5">
+        <v>601</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I206" s="5">
+        <v>42</v>
+      </c>
+      <c r="J206" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K206" s="5">
+        <v>0</v>
+      </c>
+      <c r="L206" s="5">
+        <v>61</v>
+      </c>
+      <c r="M206" s="5"/>
+      <c r="N206" s="5"/>
+      <c r="O206" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207" s="5">
+        <v>133669595</v>
+      </c>
+      <c r="E207" s="5">
+        <v>601</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I207" s="5">
+        <v>42</v>
+      </c>
+      <c r="J207" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K207" s="5">
+        <v>0</v>
+      </c>
+      <c r="L207" s="5">
+        <v>61</v>
+      </c>
+      <c r="M207" s="5"/>
+      <c r="N207" s="5"/>
+      <c r="O207" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208" s="5">
+        <v>133669694</v>
+      </c>
+      <c r="E208" s="5">
+        <v>601</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I208" s="5">
+        <v>42</v>
+      </c>
+      <c r="J208" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K208" s="5">
+        <v>0</v>
+      </c>
+      <c r="L208" s="5">
+        <v>61</v>
+      </c>
+      <c r="M208" s="5"/>
+      <c r="N208" s="5"/>
+      <c r="O208" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209" s="5">
+        <v>133670396</v>
+      </c>
+      <c r="E209" s="5">
+        <v>601</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I209" s="5">
+        <v>42</v>
+      </c>
+      <c r="J209" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K209" s="5">
+        <v>0</v>
+      </c>
+      <c r="L209" s="5">
+        <v>61</v>
+      </c>
+      <c r="M209" s="5"/>
+      <c r="N209" s="5"/>
+      <c r="O209" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210" s="5">
+        <v>133670440</v>
+      </c>
+      <c r="E210" s="5">
+        <v>601</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I210" s="5">
+        <v>42</v>
+      </c>
+      <c r="J210" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K210" s="5">
+        <v>0</v>
+      </c>
+      <c r="L210" s="5">
+        <v>61</v>
+      </c>
+      <c r="M210" s="5"/>
+      <c r="N210" s="5"/>
+      <c r="O210" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A211" s="5">
+        <v>133670856</v>
+      </c>
+      <c r="E211" s="5">
+        <v>601</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I211" s="5">
+        <v>42</v>
+      </c>
+      <c r="J211" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K211" s="5">
+        <v>0</v>
+      </c>
+      <c r="L211" s="5">
+        <v>61</v>
+      </c>
+      <c r="M211" s="5"/>
+      <c r="N211" s="5"/>
+      <c r="O211" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A212" s="5">
+        <v>133670981</v>
+      </c>
+      <c r="E212" s="5">
+        <v>601</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I212" s="5">
+        <v>42</v>
+      </c>
+      <c r="J212" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K212" s="5">
+        <v>0</v>
+      </c>
+      <c r="L212" s="5">
+        <v>61</v>
+      </c>
+      <c r="M212" s="5"/>
+      <c r="N212" s="5"/>
+      <c r="O212" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A213" s="5">
+        <v>133671023</v>
+      </c>
+      <c r="E213" s="5">
+        <v>601</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I213" s="5">
+        <v>42</v>
+      </c>
+      <c r="J213" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K213" s="5">
+        <v>0</v>
+      </c>
+      <c r="L213" s="5">
+        <v>61</v>
+      </c>
+      <c r="M213" s="5"/>
+      <c r="N213" s="5"/>
+      <c r="O213" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A214" s="5">
+        <v>133671185</v>
+      </c>
+      <c r="E214" s="5">
+        <v>601</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I214" s="5">
+        <v>42</v>
+      </c>
+      <c r="J214" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K214" s="5">
+        <v>0</v>
+      </c>
+      <c r="L214" s="5">
+        <v>61</v>
+      </c>
+      <c r="M214" s="5"/>
+      <c r="N214" s="5"/>
+      <c r="O214" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215" s="5">
+        <v>133671203</v>
+      </c>
+      <c r="E215" s="5">
+        <v>601</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I215" s="5">
+        <v>42</v>
+      </c>
+      <c r="J215" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K215" s="5">
+        <v>0</v>
+      </c>
+      <c r="L215" s="5">
+        <v>61</v>
+      </c>
+      <c r="M215" s="5"/>
+      <c r="N215" s="5"/>
+      <c r="O215" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A216" s="5">
+        <v>133671260</v>
+      </c>
+      <c r="E216" s="5">
+        <v>601</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I216" s="5">
+        <v>42</v>
+      </c>
+      <c r="J216" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K216" s="5">
+        <v>0</v>
+      </c>
+      <c r="L216" s="5">
+        <v>61</v>
+      </c>
+      <c r="M216" s="5"/>
+      <c r="N216" s="5"/>
+      <c r="O216" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A217" s="5">
+        <v>133671310</v>
+      </c>
+      <c r="E217" s="5">
+        <v>601</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I217" s="5">
+        <v>42</v>
+      </c>
+      <c r="J217" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K217" s="5">
+        <v>0</v>
+      </c>
+      <c r="L217" s="5">
+        <v>61</v>
+      </c>
+      <c r="M217" s="5"/>
+      <c r="N217" s="5"/>
+      <c r="O217" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A218" s="5">
+        <v>133671798</v>
+      </c>
+      <c r="E218" s="5">
+        <v>601</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I218" s="5">
+        <v>42</v>
+      </c>
+      <c r="J218" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K218" s="5">
+        <v>0</v>
+      </c>
+      <c r="L218" s="5">
+        <v>61</v>
+      </c>
+      <c r="M218" s="5"/>
+      <c r="N218" s="5"/>
+      <c r="O218" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A219" s="5">
+        <v>133671837</v>
+      </c>
+      <c r="E219" s="5">
+        <v>601</v>
+      </c>
+      <c r="F219" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I219" s="5">
+        <v>42</v>
+      </c>
+      <c r="J219" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K219" s="5">
+        <v>0</v>
+      </c>
+      <c r="L219" s="5">
+        <v>61</v>
+      </c>
+      <c r="M219" s="5"/>
+      <c r="N219" s="5"/>
+      <c r="O219" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A220" s="5">
+        <v>133671920</v>
+      </c>
+      <c r="E220" s="5">
+        <v>601</v>
+      </c>
+      <c r="F220" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I220" s="5">
+        <v>42</v>
+      </c>
+      <c r="J220" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K220" s="5">
+        <v>0</v>
+      </c>
+      <c r="L220" s="5">
+        <v>61</v>
+      </c>
+      <c r="M220" s="5"/>
+      <c r="N220" s="5"/>
+      <c r="O220" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A221" s="5">
+        <v>133672168</v>
+      </c>
+      <c r="E221" s="5">
+        <v>601</v>
+      </c>
+      <c r="F221" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I221" s="5">
+        <v>42</v>
+      </c>
+      <c r="J221" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K221" s="5">
+        <v>0</v>
+      </c>
+      <c r="L221" s="5">
+        <v>61</v>
+      </c>
+      <c r="M221" s="5"/>
+      <c r="N221" s="5"/>
+      <c r="O221" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A222" s="5">
+        <v>133672677</v>
+      </c>
+      <c r="E222" s="5">
+        <v>601</v>
+      </c>
+      <c r="F222" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I222" s="5">
+        <v>42</v>
+      </c>
+      <c r="J222" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K222" s="5">
+        <v>0</v>
+      </c>
+      <c r="L222" s="5">
+        <v>61</v>
+      </c>
+      <c r="M222" s="5"/>
+      <c r="N222" s="5"/>
+      <c r="O222" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A223" s="5">
+        <v>133672777</v>
+      </c>
+      <c r="E223" s="5">
+        <v>601</v>
+      </c>
+      <c r="F223" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I223" s="5">
+        <v>42</v>
+      </c>
+      <c r="J223" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K223" s="5">
+        <v>0</v>
+      </c>
+      <c r="L223" s="5">
+        <v>61</v>
+      </c>
+      <c r="M223" s="5"/>
+      <c r="N223" s="5"/>
+      <c r="O223" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A224" s="5">
+        <v>133672784</v>
+      </c>
+      <c r="E224" s="5">
+        <v>601</v>
+      </c>
+      <c r="F224" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G224" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I224" s="5">
+        <v>42</v>
+      </c>
+      <c r="J224" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K224" s="5">
+        <v>0</v>
+      </c>
+      <c r="L224" s="5">
+        <v>61</v>
+      </c>
+      <c r="M224" s="5"/>
+      <c r="N224" s="5"/>
+      <c r="O224" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A225" s="5">
+        <v>133672786</v>
+      </c>
+      <c r="E225" s="5">
+        <v>601</v>
+      </c>
+      <c r="F225" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I225" s="5">
+        <v>42</v>
+      </c>
+      <c r="J225" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K225" s="5">
+        <v>0</v>
+      </c>
+      <c r="L225" s="5">
+        <v>61</v>
+      </c>
+      <c r="M225" s="5"/>
+      <c r="N225" s="5"/>
+      <c r="O225" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A226" s="5">
+        <v>133672790</v>
+      </c>
+      <c r="E226" s="5">
+        <v>601</v>
+      </c>
+      <c r="F226" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I226" s="5">
+        <v>42</v>
+      </c>
+      <c r="J226" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K226" s="5">
+        <v>0</v>
+      </c>
+      <c r="L226" s="5">
+        <v>61</v>
+      </c>
+      <c r="M226" s="5"/>
+      <c r="N226" s="5"/>
+      <c r="O226" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A227" s="5">
+        <v>133672814</v>
+      </c>
+      <c r="E227" s="5">
+        <v>601</v>
+      </c>
+      <c r="F227" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I227" s="5">
+        <v>42</v>
+      </c>
+      <c r="J227" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K227" s="5">
+        <v>0</v>
+      </c>
+      <c r="L227" s="5">
+        <v>61</v>
+      </c>
+      <c r="M227" s="5"/>
+      <c r="N227" s="5"/>
+      <c r="O227" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A228" s="5">
+        <v>133672817</v>
+      </c>
+      <c r="E228" s="5">
+        <v>601</v>
+      </c>
+      <c r="F228" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I228" s="5">
+        <v>42</v>
+      </c>
+      <c r="J228" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K228" s="5">
+        <v>0</v>
+      </c>
+      <c r="L228" s="5">
+        <v>61</v>
+      </c>
+      <c r="M228" s="5"/>
+      <c r="N228" s="5"/>
+      <c r="O228" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A229" s="5">
+        <v>133672900</v>
+      </c>
+      <c r="E229" s="5">
+        <v>601</v>
+      </c>
+      <c r="F229" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I229" s="5">
+        <v>42</v>
+      </c>
+      <c r="J229" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K229" s="5">
+        <v>0</v>
+      </c>
+      <c r="L229" s="5">
+        <v>61</v>
+      </c>
+      <c r="M229" s="5"/>
+      <c r="N229" s="5"/>
+      <c r="O229" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A230" s="5">
+        <v>133672904</v>
+      </c>
+      <c r="E230" s="5">
+        <v>601</v>
+      </c>
+      <c r="F230" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I230" s="5">
+        <v>42</v>
+      </c>
+      <c r="J230" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K230" s="5">
+        <v>0</v>
+      </c>
+      <c r="L230" s="5">
+        <v>61</v>
+      </c>
+      <c r="M230" s="5"/>
+      <c r="N230" s="5"/>
+      <c r="O230" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A231" s="5">
+        <v>133672908</v>
+      </c>
+      <c r="E231" s="5">
+        <v>601</v>
+      </c>
+      <c r="F231" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I231" s="5">
+        <v>42</v>
+      </c>
+      <c r="J231" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K231" s="5">
+        <v>0</v>
+      </c>
+      <c r="L231" s="5">
+        <v>61</v>
+      </c>
+      <c r="M231" s="5"/>
+      <c r="N231" s="5"/>
+      <c r="O231" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A232" s="5">
+        <v>133672993</v>
+      </c>
+      <c r="E232" s="5">
+        <v>601</v>
+      </c>
+      <c r="F232" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I232" s="5">
+        <v>42</v>
+      </c>
+      <c r="J232" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K232" s="5">
+        <v>0</v>
+      </c>
+      <c r="L232" s="5">
+        <v>61</v>
+      </c>
+      <c r="M232" s="5"/>
+      <c r="N232" s="5"/>
+      <c r="O232" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A233" s="5">
+        <v>133673015</v>
+      </c>
+      <c r="E233" s="5">
+        <v>601</v>
+      </c>
+      <c r="F233" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I233" s="5">
+        <v>42</v>
+      </c>
+      <c r="J233" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K233" s="5">
+        <v>0</v>
+      </c>
+      <c r="L233" s="5">
+        <v>61</v>
+      </c>
+      <c r="M233" s="5"/>
+      <c r="N233" s="5"/>
+      <c r="O233" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A234" s="5">
+        <v>133673255</v>
+      </c>
+      <c r="E234" s="5">
+        <v>601</v>
+      </c>
+      <c r="F234" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I234" s="5">
+        <v>42</v>
+      </c>
+      <c r="J234" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K234" s="5">
+        <v>0</v>
+      </c>
+      <c r="L234" s="5">
+        <v>61</v>
+      </c>
+      <c r="M234" s="5"/>
+      <c r="N234" s="5"/>
+      <c r="O234" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A235" s="5">
+        <v>133673492</v>
+      </c>
+      <c r="E235" s="5">
+        <v>601</v>
+      </c>
+      <c r="F235" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G235" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I235" s="5">
+        <v>42</v>
+      </c>
+      <c r="J235" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K235" s="5">
+        <v>0</v>
+      </c>
+      <c r="L235" s="5">
+        <v>61</v>
+      </c>
+      <c r="M235" s="5"/>
+      <c r="N235" s="5"/>
+      <c r="O235" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A236" s="5">
+        <v>133673666</v>
+      </c>
+      <c r="E236" s="5">
+        <v>601</v>
+      </c>
+      <c r="F236" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I236" s="5">
+        <v>42</v>
+      </c>
+      <c r="J236" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K236" s="5">
+        <v>0</v>
+      </c>
+      <c r="L236" s="5">
+        <v>61</v>
+      </c>
+      <c r="M236" s="5"/>
+      <c r="N236" s="5"/>
+      <c r="O236" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A237" s="5">
+        <v>133673950</v>
+      </c>
+      <c r="E237" s="5">
+        <v>601</v>
+      </c>
+      <c r="F237" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I237" s="5">
+        <v>42</v>
+      </c>
+      <c r="J237" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K237" s="5">
+        <v>0</v>
+      </c>
+      <c r="L237" s="5">
+        <v>61</v>
+      </c>
+      <c r="M237" s="5"/>
+      <c r="N237" s="5"/>
+      <c r="O237" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A238" s="5">
+        <v>133673978</v>
+      </c>
+      <c r="E238" s="5">
+        <v>601</v>
+      </c>
+      <c r="F238" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G238" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I238" s="5">
+        <v>42</v>
+      </c>
+      <c r="J238" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K238" s="5">
+        <v>0</v>
+      </c>
+      <c r="L238" s="5">
+        <v>61</v>
+      </c>
+      <c r="M238" s="5"/>
+      <c r="N238" s="5"/>
+      <c r="O238" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A239" s="5">
+        <v>133674276</v>
+      </c>
+      <c r="E239" s="5">
+        <v>601</v>
+      </c>
+      <c r="F239" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G239" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I239" s="5">
+        <v>42</v>
+      </c>
+      <c r="J239" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K239" s="5">
+        <v>0</v>
+      </c>
+      <c r="L239" s="5">
+        <v>61</v>
+      </c>
+      <c r="M239" s="5"/>
+      <c r="N239" s="5"/>
+      <c r="O239" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A240" s="5">
+        <v>133674332</v>
+      </c>
+      <c r="E240" s="5">
+        <v>601</v>
+      </c>
+      <c r="F240" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I240" s="5">
+        <v>42</v>
+      </c>
+      <c r="J240" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K240" s="5">
+        <v>0</v>
+      </c>
+      <c r="L240" s="5">
+        <v>61</v>
+      </c>
+      <c r="M240" s="5"/>
+      <c r="N240" s="5"/>
+      <c r="O240" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A241" s="5">
+        <v>133674370</v>
+      </c>
+      <c r="E241" s="5">
+        <v>601</v>
+      </c>
+      <c r="F241" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I241" s="5">
+        <v>42</v>
+      </c>
+      <c r="J241" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K241" s="5">
+        <v>0</v>
+      </c>
+      <c r="L241" s="5">
+        <v>61</v>
+      </c>
+      <c r="M241" s="5"/>
+      <c r="N241" s="5"/>
+      <c r="O241" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A242" s="5">
+        <v>133674661</v>
+      </c>
+      <c r="E242" s="5">
+        <v>601</v>
+      </c>
+      <c r="F242" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I242" s="5">
+        <v>42</v>
+      </c>
+      <c r="J242" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K242" s="5">
+        <v>0</v>
+      </c>
+      <c r="L242" s="5">
+        <v>61</v>
+      </c>
+      <c r="M242" s="5"/>
+      <c r="N242" s="5"/>
+      <c r="O242" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A243" s="5">
+        <v>133674662</v>
+      </c>
+      <c r="E243" s="5">
+        <v>601</v>
+      </c>
+      <c r="F243" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G243" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I243" s="5">
+        <v>42</v>
+      </c>
+      <c r="J243" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K243" s="5">
+        <v>0</v>
+      </c>
+      <c r="L243" s="5">
+        <v>61</v>
+      </c>
+      <c r="M243" s="5"/>
+      <c r="N243" s="5"/>
+      <c r="O243" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A244" s="5">
+        <v>133675151</v>
+      </c>
+      <c r="E244" s="5">
+        <v>601</v>
+      </c>
+      <c r="F244" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G244" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I244" s="5">
+        <v>42</v>
+      </c>
+      <c r="J244" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K244" s="5">
+        <v>0</v>
+      </c>
+      <c r="L244" s="5">
+        <v>61</v>
+      </c>
+      <c r="M244" s="5"/>
+      <c r="N244" s="5"/>
+      <c r="O244" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A245" s="5">
+        <v>133675803</v>
+      </c>
+      <c r="E245" s="5">
+        <v>601</v>
+      </c>
+      <c r="F245" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I245" s="5">
+        <v>42</v>
+      </c>
+      <c r="J245" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K245" s="5">
+        <v>0</v>
+      </c>
+      <c r="L245" s="5">
+        <v>61</v>
+      </c>
+      <c r="M245" s="5"/>
+      <c r="N245" s="5"/>
+      <c r="O245" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A246" s="5">
+        <v>133675871</v>
+      </c>
+      <c r="E246" s="5">
+        <v>601</v>
+      </c>
+      <c r="F246" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I246" s="5">
+        <v>42</v>
+      </c>
+      <c r="J246" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K246" s="5">
+        <v>0</v>
+      </c>
+      <c r="L246" s="5">
+        <v>61</v>
+      </c>
+      <c r="M246" s="5"/>
+      <c r="N246" s="5"/>
+      <c r="O246" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A247" s="5">
+        <v>133675938</v>
+      </c>
+      <c r="E247" s="5">
+        <v>601</v>
+      </c>
+      <c r="F247" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I247" s="5">
+        <v>42</v>
+      </c>
+      <c r="J247" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K247" s="5">
+        <v>0</v>
+      </c>
+      <c r="L247" s="5">
+        <v>61</v>
+      </c>
+      <c r="M247" s="5"/>
+      <c r="N247" s="5"/>
+      <c r="O247" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A248" s="5">
+        <v>133676020</v>
+      </c>
+      <c r="E248" s="5">
+        <v>601</v>
+      </c>
+      <c r="F248" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I248" s="5">
+        <v>42</v>
+      </c>
+      <c r="J248" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K248" s="5">
+        <v>0</v>
+      </c>
+      <c r="L248" s="5">
+        <v>61</v>
+      </c>
+      <c r="M248" s="5"/>
+      <c r="N248" s="5"/>
+      <c r="O248" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A249" s="5">
+        <v>133676093</v>
+      </c>
+      <c r="E249" s="5">
+        <v>601</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I249" s="5">
+        <v>42</v>
+      </c>
+      <c r="J249" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K249" s="5">
+        <v>0</v>
+      </c>
+      <c r="L249" s="5">
+        <v>61</v>
+      </c>
+      <c r="M249" s="5"/>
+      <c r="N249" s="5"/>
+      <c r="O249" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A250" s="5">
+        <v>133676201</v>
+      </c>
+      <c r="E250" s="5">
+        <v>601</v>
+      </c>
+      <c r="F250" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I250" s="5">
+        <v>42</v>
+      </c>
+      <c r="J250" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K250" s="5">
+        <v>0</v>
+      </c>
+      <c r="L250" s="5">
+        <v>61</v>
+      </c>
+      <c r="M250" s="5"/>
+      <c r="N250" s="5"/>
+      <c r="O250" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A251" s="5">
+        <v>133676621</v>
+      </c>
+      <c r="E251" s="5">
+        <v>601</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I251" s="5">
+        <v>42</v>
+      </c>
+      <c r="J251" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K251" s="5">
+        <v>0</v>
+      </c>
+      <c r="L251" s="5">
+        <v>61</v>
+      </c>
+      <c r="M251" s="5"/>
+      <c r="N251" s="5"/>
+      <c r="O251" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA70C4E-7F0A-431A-A67C-951D206CC680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095B251D-15EE-469D-A8D5-F48860E13389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIEL" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="21">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,22 +79,16 @@
     <t>B</t>
   </si>
   <si>
+    <t>8/3/2023</t>
+  </si>
+  <si>
+    <t>10/3/2023</t>
+  </si>
+  <si>
+    <t>31/7/2025</t>
+  </si>
+  <si>
     <t>2/8/2025</t>
-  </si>
-  <si>
-    <t>1/8/2025</t>
-  </si>
-  <si>
-    <t>8/3/2023</t>
-  </si>
-  <si>
-    <t>10/3/2023</t>
-  </si>
-  <si>
-    <t>31/7/2025</t>
-  </si>
-  <si>
-    <t>4/8/2025</t>
   </si>
   <si>
     <t>5/8/2025</t>
@@ -515,7 +509,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -585,22 +579,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>133743679</v>
+        <v>123058958</v>
       </c>
       <c r="E2" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -616,22 +610,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>133740975</v>
+        <v>133719774</v>
       </c>
       <c r="E3" s="5">
         <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -647,22 +641,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>123058958</v>
+        <v>133769515</v>
       </c>
       <c r="E4" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -678,22 +672,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>133719774</v>
+        <v>133769683</v>
       </c>
       <c r="E5" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8021</v>
+        <v>718</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -709,22 +703,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>133710433</v>
+        <v>133769751</v>
       </c>
       <c r="E6" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -740,16 +734,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>133722990</v>
+        <v>133769996</v>
       </c>
       <c r="E7" s="5">
         <v>2013</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
@@ -771,16 +765,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>133723108</v>
+        <v>133770097</v>
       </c>
       <c r="E8" s="5">
         <v>2013</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
@@ -802,16 +796,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>133723173</v>
+        <v>133770266</v>
       </c>
       <c r="E9" s="5">
         <v>2013</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
@@ -833,16 +827,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>133724508</v>
+        <v>133770291</v>
       </c>
       <c r="E10" s="5">
         <v>2013</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
@@ -864,16 +858,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>133724864</v>
+        <v>133770418</v>
       </c>
       <c r="E11" s="5">
         <v>2013</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
@@ -895,16 +889,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133724973</v>
+        <v>133770431</v>
       </c>
       <c r="E12" s="5">
         <v>2013</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
@@ -926,16 +920,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>133730245</v>
+        <v>133770897</v>
       </c>
       <c r="E13" s="5">
         <v>2013</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
@@ -957,16 +951,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>133731170</v>
+        <v>133772805</v>
       </c>
       <c r="E14" s="5">
         <v>2013</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
@@ -988,16 +982,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>133733789</v>
+        <v>133772846</v>
       </c>
       <c r="E15" s="5">
         <v>2013</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
@@ -1019,16 +1013,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>133734715</v>
+        <v>133773089</v>
       </c>
       <c r="E16" s="5">
         <v>2013</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
@@ -1050,16 +1044,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>133736631</v>
+        <v>133773497</v>
       </c>
       <c r="E17" s="5">
         <v>2013</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1081,16 +1075,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>133737112</v>
+        <v>133774834</v>
       </c>
       <c r="E18" s="5">
         <v>2013</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1112,16 +1106,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>133737779</v>
+        <v>133775975</v>
       </c>
       <c r="E19" s="5">
         <v>2013</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1143,16 +1137,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>133738136</v>
+        <v>133776259</v>
       </c>
       <c r="E20" s="5">
         <v>2013</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1174,16 +1168,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>133738367</v>
+        <v>133776323</v>
       </c>
       <c r="E21" s="5">
         <v>2013</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1205,16 +1199,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>133738490</v>
+        <v>133776364</v>
       </c>
       <c r="E22" s="5">
         <v>2013</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
@@ -1236,16 +1230,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>133738623</v>
+        <v>133776921</v>
       </c>
       <c r="E23" s="5">
         <v>2013</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1267,16 +1261,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>133738726</v>
+        <v>133776968</v>
       </c>
       <c r="E24" s="5">
         <v>2013</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1298,16 +1292,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>133738806</v>
+        <v>133777011</v>
       </c>
       <c r="E25" s="5">
         <v>2013</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1329,16 +1323,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>133738897</v>
+        <v>133777109</v>
       </c>
       <c r="E26" s="5">
         <v>2013</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1360,16 +1354,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>133739652</v>
+        <v>133777136</v>
       </c>
       <c r="E27" s="5">
         <v>2013</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
@@ -1391,16 +1385,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>133747255</v>
+        <v>133777412</v>
       </c>
       <c r="E28" s="5">
         <v>2013</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
@@ -1422,16 +1416,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>133747292</v>
+        <v>133777441</v>
       </c>
       <c r="E29" s="5">
         <v>2013</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
@@ -1453,16 +1447,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>133747414</v>
+        <v>133777466</v>
       </c>
       <c r="E30" s="5">
         <v>2013</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
@@ -1484,16 +1478,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>133747451</v>
+        <v>133782243</v>
       </c>
       <c r="E31" s="5">
         <v>2013</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
@@ -1515,16 +1509,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>133747565</v>
+        <v>133782817</v>
       </c>
       <c r="E32" s="5">
         <v>2013</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
@@ -1546,16 +1540,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>133747614</v>
+        <v>133783078</v>
       </c>
       <c r="E33" s="5">
         <v>2013</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
@@ -1577,16 +1571,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>133747831</v>
+        <v>133783608</v>
       </c>
       <c r="E34" s="5">
         <v>2013</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1608,16 +1602,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>133751842</v>
+        <v>133783743</v>
       </c>
       <c r="E35" s="5">
         <v>2013</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
@@ -1634,874 +1628,6 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
-        <v>133752754</v>
-      </c>
-      <c r="E36" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="5">
-        <v>42</v>
-      </c>
-      <c r="J36" s="5">
-        <v>718</v>
-      </c>
-      <c r="K36" s="5">
-        <v>0</v>
-      </c>
-      <c r="L36" s="5">
-        <v>61</v>
-      </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>133752803</v>
-      </c>
-      <c r="E37" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="5">
-        <v>42</v>
-      </c>
-      <c r="J37" s="5">
-        <v>718</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0</v>
-      </c>
-      <c r="L37" s="5">
-        <v>61</v>
-      </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
-        <v>133752834</v>
-      </c>
-      <c r="E38" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="5">
-        <v>42</v>
-      </c>
-      <c r="J38" s="5">
-        <v>718</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5">
-        <v>61</v>
-      </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
-        <v>133752889</v>
-      </c>
-      <c r="E39" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="5">
-        <v>42</v>
-      </c>
-      <c r="J39" s="5">
-        <v>718</v>
-      </c>
-      <c r="K39" s="5">
-        <v>0</v>
-      </c>
-      <c r="L39" s="5">
-        <v>61</v>
-      </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
-        <v>133753179</v>
-      </c>
-      <c r="E40" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="5">
-        <v>42</v>
-      </c>
-      <c r="J40" s="5">
-        <v>718</v>
-      </c>
-      <c r="K40" s="5">
-        <v>0</v>
-      </c>
-      <c r="L40" s="5">
-        <v>61</v>
-      </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
-        <v>133753317</v>
-      </c>
-      <c r="E41" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="5">
-        <v>42</v>
-      </c>
-      <c r="J41" s="5">
-        <v>718</v>
-      </c>
-      <c r="K41" s="5">
-        <v>0</v>
-      </c>
-      <c r="L41" s="5">
-        <v>61</v>
-      </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>133753367</v>
-      </c>
-      <c r="E42" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="5">
-        <v>42</v>
-      </c>
-      <c r="J42" s="5">
-        <v>718</v>
-      </c>
-      <c r="K42" s="5">
-        <v>0</v>
-      </c>
-      <c r="L42" s="5">
-        <v>61</v>
-      </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>133753436</v>
-      </c>
-      <c r="E43" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="5">
-        <v>42</v>
-      </c>
-      <c r="J43" s="5">
-        <v>718</v>
-      </c>
-      <c r="K43" s="5">
-        <v>0</v>
-      </c>
-      <c r="L43" s="5">
-        <v>61</v>
-      </c>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
-        <v>133753456</v>
-      </c>
-      <c r="E44" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44" s="5">
-        <v>42</v>
-      </c>
-      <c r="J44" s="5">
-        <v>718</v>
-      </c>
-      <c r="K44" s="5">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5">
-        <v>61</v>
-      </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>133753610</v>
-      </c>
-      <c r="E45" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45" s="5">
-        <v>42</v>
-      </c>
-      <c r="J45" s="5">
-        <v>718</v>
-      </c>
-      <c r="K45" s="5">
-        <v>0</v>
-      </c>
-      <c r="L45" s="5">
-        <v>61</v>
-      </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
-        <v>133755138</v>
-      </c>
-      <c r="E46" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="5">
-        <v>42</v>
-      </c>
-      <c r="J46" s="5">
-        <v>718</v>
-      </c>
-      <c r="K46" s="5">
-        <v>0</v>
-      </c>
-      <c r="L46" s="5">
-        <v>61</v>
-      </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
-        <v>133755290</v>
-      </c>
-      <c r="E47" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47" s="5">
-        <v>42</v>
-      </c>
-      <c r="J47" s="5">
-        <v>718</v>
-      </c>
-      <c r="K47" s="5">
-        <v>0</v>
-      </c>
-      <c r="L47" s="5">
-        <v>61</v>
-      </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="5">
-        <v>133755397</v>
-      </c>
-      <c r="E48" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I48" s="5">
-        <v>42</v>
-      </c>
-      <c r="J48" s="5">
-        <v>718</v>
-      </c>
-      <c r="K48" s="5">
-        <v>0</v>
-      </c>
-      <c r="L48" s="5">
-        <v>61</v>
-      </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="5">
-        <v>133755671</v>
-      </c>
-      <c r="E49" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49" s="5">
-        <v>42</v>
-      </c>
-      <c r="J49" s="5">
-        <v>718</v>
-      </c>
-      <c r="K49" s="5">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5">
-        <v>61</v>
-      </c>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="5">
-        <v>133756228</v>
-      </c>
-      <c r="E50" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" s="5">
-        <v>42</v>
-      </c>
-      <c r="J50" s="5">
-        <v>718</v>
-      </c>
-      <c r="K50" s="5">
-        <v>0</v>
-      </c>
-      <c r="L50" s="5">
-        <v>61</v>
-      </c>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="5">
-        <v>133756323</v>
-      </c>
-      <c r="E51" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51" s="5">
-        <v>42</v>
-      </c>
-      <c r="J51" s="5">
-        <v>718</v>
-      </c>
-      <c r="K51" s="5">
-        <v>0</v>
-      </c>
-      <c r="L51" s="5">
-        <v>61</v>
-      </c>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="5">
-        <v>133756463</v>
-      </c>
-      <c r="E52" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="5">
-        <v>42</v>
-      </c>
-      <c r="J52" s="5">
-        <v>718</v>
-      </c>
-      <c r="K52" s="5">
-        <v>0</v>
-      </c>
-      <c r="L52" s="5">
-        <v>61</v>
-      </c>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="5">
-        <v>133757075</v>
-      </c>
-      <c r="E53" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" s="5">
-        <v>42</v>
-      </c>
-      <c r="J53" s="5">
-        <v>718</v>
-      </c>
-      <c r="K53" s="5">
-        <v>0</v>
-      </c>
-      <c r="L53" s="5">
-        <v>61</v>
-      </c>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="5">
-        <v>133757438</v>
-      </c>
-      <c r="E54" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54" s="5">
-        <v>42</v>
-      </c>
-      <c r="J54" s="5">
-        <v>718</v>
-      </c>
-      <c r="K54" s="5">
-        <v>0</v>
-      </c>
-      <c r="L54" s="5">
-        <v>61</v>
-      </c>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
-        <v>133757757</v>
-      </c>
-      <c r="E55" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="5">
-        <v>42</v>
-      </c>
-      <c r="J55" s="5">
-        <v>718</v>
-      </c>
-      <c r="K55" s="5">
-        <v>0</v>
-      </c>
-      <c r="L55" s="5">
-        <v>61</v>
-      </c>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="5">
-        <v>133758154</v>
-      </c>
-      <c r="E56" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56" s="5">
-        <v>42</v>
-      </c>
-      <c r="J56" s="5">
-        <v>718</v>
-      </c>
-      <c r="K56" s="5">
-        <v>0</v>
-      </c>
-      <c r="L56" s="5">
-        <v>61</v>
-      </c>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
-        <v>133758288</v>
-      </c>
-      <c r="E57" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57" s="5">
-        <v>42</v>
-      </c>
-      <c r="J57" s="5">
-        <v>718</v>
-      </c>
-      <c r="K57" s="5">
-        <v>0</v>
-      </c>
-      <c r="L57" s="5">
-        <v>61</v>
-      </c>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="5">
-        <v>133759619</v>
-      </c>
-      <c r="E58" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I58" s="5">
-        <v>42</v>
-      </c>
-      <c r="J58" s="5">
-        <v>718</v>
-      </c>
-      <c r="K58" s="5">
-        <v>0</v>
-      </c>
-      <c r="L58" s="5">
-        <v>61</v>
-      </c>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5"/>
-      <c r="O58" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
-        <v>133760329</v>
-      </c>
-      <c r="E59" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59" s="5">
-        <v>42</v>
-      </c>
-      <c r="J59" s="5">
-        <v>718</v>
-      </c>
-      <c r="K59" s="5">
-        <v>0</v>
-      </c>
-      <c r="L59" s="5">
-        <v>61</v>
-      </c>
-      <c r="M59" s="5"/>
-      <c r="N59" s="5"/>
-      <c r="O59" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
-        <v>133760404</v>
-      </c>
-      <c r="E60" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I60" s="5">
-        <v>42</v>
-      </c>
-      <c r="J60" s="5">
-        <v>718</v>
-      </c>
-      <c r="K60" s="5">
-        <v>0</v>
-      </c>
-      <c r="L60" s="5">
-        <v>61</v>
-      </c>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
-        <v>133761589</v>
-      </c>
-      <c r="E61" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" s="5">
-        <v>42</v>
-      </c>
-      <c r="J61" s="5">
-        <v>718</v>
-      </c>
-      <c r="K61" s="5">
-        <v>0</v>
-      </c>
-      <c r="L61" s="5">
-        <v>61</v>
-      </c>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
-        <v>133762706</v>
-      </c>
-      <c r="E62" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I62" s="5">
-        <v>42</v>
-      </c>
-      <c r="J62" s="5">
-        <v>718</v>
-      </c>
-      <c r="K62" s="5">
-        <v>0</v>
-      </c>
-      <c r="L62" s="5">
-        <v>61</v>
-      </c>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
-        <v>133762783</v>
-      </c>
-      <c r="E63" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I63" s="5">
-        <v>42</v>
-      </c>
-      <c r="J63" s="5">
-        <v>718</v>
-      </c>
-      <c r="K63" s="5">
-        <v>0</v>
-      </c>
-      <c r="L63" s="5">
-        <v>61</v>
-      </c>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
-      <c r="O63" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AD40C2-EA5E-411A-A119-C9D5520777F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1C079D-4BE3-4628-9F6B-7371D25AFDAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="26">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -91,7 +91,22 @@
     <t>8/8/2025</t>
   </si>
   <si>
+    <t>19/8/2025</t>
+  </si>
+  <si>
     <t>20/8/2025</t>
+  </si>
+  <si>
+    <t>21/8/2025</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
   </si>
 </sst>
 </file>
@@ -509,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -579,10 +594,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>133982270</v>
+        <v>133981749</v>
       </c>
       <c r="E2" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
@@ -594,7 +609,7 @@
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -672,22 +687,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>130092105</v>
+        <v>133994784</v>
       </c>
       <c r="E5" s="5">
         <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -703,16 +718,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>130289244</v>
+        <v>133538921</v>
       </c>
       <c r="E6" s="5">
         <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
@@ -734,16 +749,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>131829363</v>
+        <v>133698804</v>
       </c>
       <c r="E7" s="5">
         <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
@@ -765,13 +780,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>131898226</v>
+        <v>133978356</v>
       </c>
       <c r="E8" s="5">
         <v>1211</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>20</v>
@@ -796,16 +811,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>132150052</v>
+        <v>133538921</v>
       </c>
       <c r="E9" s="5">
         <v>1211</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
@@ -827,16 +842,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>133298431</v>
+        <v>133698804</v>
       </c>
       <c r="E10" s="5">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
@@ -858,13 +873,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>130092105</v>
+        <v>133978356</v>
       </c>
       <c r="E11" s="5">
         <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>20</v>
@@ -889,7 +904,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>130289244</v>
+        <v>133977527</v>
       </c>
       <c r="E12" s="5">
         <v>1211</v>
@@ -904,7 +919,7 @@
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -920,7 +935,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>131829363</v>
+        <v>133986028</v>
       </c>
       <c r="E13" s="5">
         <v>1211</v>
@@ -929,13 +944,13 @@
         <v>16</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -951,22 +966,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>131898226</v>
+        <v>134020682</v>
       </c>
       <c r="E14" s="5">
         <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -982,16 +997,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134018467</v>
+        <v>134041470</v>
       </c>
       <c r="E15" s="5">
         <v>2013</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
@@ -1013,16 +1028,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>134018516</v>
+        <v>134041481</v>
       </c>
       <c r="E16" s="5">
         <v>2013</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
@@ -1044,16 +1059,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>134018530</v>
+        <v>134041796</v>
       </c>
       <c r="E17" s="5">
         <v>2013</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1075,16 +1090,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>134018535</v>
+        <v>134041851</v>
       </c>
       <c r="E18" s="5">
         <v>2013</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1106,16 +1121,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>134018543</v>
+        <v>134041951</v>
       </c>
       <c r="E19" s="5">
         <v>2013</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1137,16 +1152,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>134018545</v>
+        <v>134043105</v>
       </c>
       <c r="E20" s="5">
         <v>2013</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1168,16 +1183,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>134018555</v>
+        <v>134043231</v>
       </c>
       <c r="E21" s="5">
         <v>2013</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1199,16 +1214,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>134018559</v>
+        <v>134043349</v>
       </c>
       <c r="E22" s="5">
         <v>2013</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
@@ -1230,16 +1245,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>134018572</v>
+        <v>134043446</v>
       </c>
       <c r="E23" s="5">
         <v>2013</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1261,16 +1276,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>134018578</v>
+        <v>134043571</v>
       </c>
       <c r="E24" s="5">
         <v>2013</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1292,16 +1307,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>134018579</v>
+        <v>134043719</v>
       </c>
       <c r="E25" s="5">
         <v>2013</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1323,16 +1338,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>134018594</v>
+        <v>134043841</v>
       </c>
       <c r="E26" s="5">
         <v>2013</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1354,16 +1369,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>134018599</v>
+        <v>134043882</v>
       </c>
       <c r="E27" s="5">
         <v>2013</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
@@ -1385,16 +1400,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>134018617</v>
+        <v>134044368</v>
       </c>
       <c r="E28" s="5">
         <v>2013</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
@@ -1416,16 +1431,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>134018666</v>
+        <v>134044642</v>
       </c>
       <c r="E29" s="5">
         <v>2013</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
@@ -1447,16 +1462,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>134018700</v>
+        <v>134044821</v>
       </c>
       <c r="E30" s="5">
         <v>2013</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
@@ -1478,16 +1493,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>134018733</v>
+        <v>134044862</v>
       </c>
       <c r="E31" s="5">
         <v>2013</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
@@ -1509,16 +1524,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>134018920</v>
+        <v>134045271</v>
       </c>
       <c r="E32" s="5">
         <v>2013</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
@@ -1540,16 +1555,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>134018952</v>
+        <v>134046378</v>
       </c>
       <c r="E33" s="5">
         <v>2013</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
@@ -1571,16 +1586,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>134019017</v>
+        <v>134047342</v>
       </c>
       <c r="E34" s="5">
         <v>2013</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1602,16 +1617,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>134019083</v>
+        <v>134047469</v>
       </c>
       <c r="E35" s="5">
         <v>2013</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
@@ -1633,16 +1648,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>134019097</v>
+        <v>134048466</v>
       </c>
       <c r="E36" s="5">
         <v>2013</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
@@ -1664,16 +1679,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>134019115</v>
+        <v>134051083</v>
       </c>
       <c r="E37" s="5">
         <v>2013</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
@@ -1695,16 +1710,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>134019178</v>
+        <v>134051179</v>
       </c>
       <c r="E38" s="5">
         <v>2013</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
@@ -1726,16 +1741,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>134019305</v>
+        <v>134058661</v>
       </c>
       <c r="E39" s="5">
         <v>2013</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
@@ -1757,16 +1772,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>134019391</v>
+        <v>134058784</v>
       </c>
       <c r="E40" s="5">
         <v>2013</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
@@ -1788,22 +1803,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>134019481</v>
+        <v>133689570</v>
       </c>
       <c r="E41" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
       </c>
       <c r="J41" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -1819,22 +1834,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>134019615</v>
+        <v>134009333</v>
       </c>
       <c r="E42" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -1850,22 +1865,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>134019663</v>
+        <v>134010187</v>
       </c>
       <c r="E43" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I43" s="5">
         <v>42</v>
       </c>
       <c r="J43" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -1881,22 +1896,22 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>134019698</v>
+        <v>134010908</v>
       </c>
       <c r="E44" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
       </c>
       <c r="J44" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -1912,22 +1927,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>134019756</v>
+        <v>134018951</v>
       </c>
       <c r="E45" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
       </c>
       <c r="J45" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -1943,22 +1958,22 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>134019766</v>
+        <v>134019259</v>
       </c>
       <c r="E46" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I46" s="5">
         <v>42</v>
       </c>
       <c r="J46" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
@@ -1974,22 +1989,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>134019787</v>
+        <v>134019433</v>
       </c>
       <c r="E47" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
       </c>
       <c r="J47" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -2005,22 +2020,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>134019843</v>
+        <v>134020009</v>
       </c>
       <c r="E48" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2036,22 +2051,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>134019891</v>
+        <v>134020246</v>
       </c>
       <c r="E49" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2067,22 +2082,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>134019994</v>
+        <v>134020570</v>
       </c>
       <c r="E50" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2098,22 +2113,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>134020018</v>
+        <v>134021124</v>
       </c>
       <c r="E51" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
       </c>
       <c r="J51" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -2129,22 +2144,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>134020284</v>
+        <v>134021959</v>
       </c>
       <c r="E52" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -2160,22 +2175,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>134020448</v>
+        <v>134022233</v>
       </c>
       <c r="E53" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2191,22 +2206,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>134020474</v>
+        <v>134022738</v>
       </c>
       <c r="E54" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2222,22 +2237,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>134021486</v>
+        <v>134023846</v>
       </c>
       <c r="E55" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -2253,22 +2268,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>134022111</v>
+        <v>134024197</v>
       </c>
       <c r="E56" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
       </c>
       <c r="J56" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -2284,22 +2299,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>134022143</v>
+        <v>134024287</v>
       </c>
       <c r="E57" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -2315,22 +2330,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>134022157</v>
+        <v>134025148</v>
       </c>
       <c r="E58" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
       </c>
       <c r="J58" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -2346,22 +2361,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>134022180</v>
+        <v>134025980</v>
       </c>
       <c r="E59" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2377,22 +2392,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>134022245</v>
+        <v>134026297</v>
       </c>
       <c r="E60" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
       </c>
       <c r="J60" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K60" s="5">
         <v>0</v>
@@ -2408,22 +2423,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>134022262</v>
+        <v>134027977</v>
       </c>
       <c r="E61" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
       </c>
       <c r="J61" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K61" s="5">
         <v>0</v>
@@ -2439,22 +2454,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>134022292</v>
+        <v>134028272</v>
       </c>
       <c r="E62" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I62" s="5">
         <v>42</v>
       </c>
       <c r="J62" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K62" s="5">
         <v>0</v>
@@ -2470,22 +2485,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>134022628</v>
+        <v>134028717</v>
       </c>
       <c r="E63" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
       </c>
       <c r="J63" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K63" s="5">
         <v>0</v>
@@ -2501,22 +2516,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>134022730</v>
+        <v>134028854</v>
       </c>
       <c r="E64" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
       </c>
       <c r="J64" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K64" s="5">
         <v>0</v>
@@ -2532,22 +2547,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>134022862</v>
+        <v>134029016</v>
       </c>
       <c r="E65" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
       </c>
       <c r="J65" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K65" s="5">
         <v>0</v>
@@ -2563,22 +2578,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>134022962</v>
+        <v>134029233</v>
       </c>
       <c r="E66" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
       </c>
       <c r="J66" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -2594,22 +2609,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>134023270</v>
+        <v>134029311</v>
       </c>
       <c r="E67" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
       </c>
       <c r="J67" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K67" s="5">
         <v>0</v>
@@ -2625,22 +2640,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>134023438</v>
+        <v>134029819</v>
       </c>
       <c r="E68" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
       </c>
       <c r="J68" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K68" s="5">
         <v>0</v>
@@ -2656,22 +2671,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>134023662</v>
+        <v>134029923</v>
       </c>
       <c r="E69" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
       </c>
       <c r="J69" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
@@ -2687,22 +2702,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>134024054</v>
+        <v>134030516</v>
       </c>
       <c r="E70" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
       </c>
       <c r="J70" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
@@ -2718,22 +2733,22 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>134024105</v>
+        <v>134030902</v>
       </c>
       <c r="E71" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
       </c>
       <c r="J71" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K71" s="5">
         <v>0</v>
@@ -2749,22 +2764,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>134024252</v>
+        <v>134031161</v>
       </c>
       <c r="E72" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I72" s="5">
         <v>42</v>
       </c>
       <c r="J72" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K72" s="5">
         <v>0</v>
@@ -2780,22 +2795,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>134025098</v>
+        <v>134031227</v>
       </c>
       <c r="E73" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
       </c>
       <c r="J73" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K73" s="5">
         <v>0</v>
@@ -2811,22 +2826,22 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>134025185</v>
+        <v>134032184</v>
       </c>
       <c r="E74" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
       </c>
       <c r="J74" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K74" s="5">
         <v>0</v>
@@ -2842,22 +2857,22 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>134025279</v>
+        <v>134032517</v>
       </c>
       <c r="E75" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
       </c>
       <c r="J75" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K75" s="5">
         <v>0</v>
@@ -2873,22 +2888,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>134025389</v>
+        <v>134032750</v>
       </c>
       <c r="E76" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
       </c>
       <c r="J76" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K76" s="5">
         <v>0</v>
@@ -2904,22 +2919,22 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>134025535</v>
+        <v>134032869</v>
       </c>
       <c r="E77" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
       </c>
       <c r="J77" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K77" s="5">
         <v>0</v>
@@ -2935,22 +2950,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>134025597</v>
+        <v>134032934</v>
       </c>
       <c r="E78" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I78" s="5">
         <v>42</v>
       </c>
       <c r="J78" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K78" s="5">
         <v>0</v>
@@ -2966,22 +2981,22 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>134025655</v>
+        <v>134033083</v>
       </c>
       <c r="E79" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I79" s="5">
         <v>42</v>
       </c>
       <c r="J79" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K79" s="5">
         <v>0</v>
@@ -2997,22 +3012,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>134025701</v>
+        <v>134033621</v>
       </c>
       <c r="E80" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I80" s="5">
         <v>42</v>
       </c>
       <c r="J80" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K80" s="5">
         <v>0</v>
@@ -3028,22 +3043,22 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>134025934</v>
+        <v>134033880</v>
       </c>
       <c r="E81" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I81" s="5">
         <v>42</v>
       </c>
       <c r="J81" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K81" s="5">
         <v>0</v>
@@ -3059,22 +3074,22 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>134025991</v>
+        <v>134033987</v>
       </c>
       <c r="E82" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I82" s="5">
         <v>42</v>
       </c>
       <c r="J82" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K82" s="5">
         <v>0</v>
@@ -3090,22 +3105,22 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>134026082</v>
+        <v>134034146</v>
       </c>
       <c r="E83" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I83" s="5">
         <v>42</v>
       </c>
       <c r="J83" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K83" s="5">
         <v>0</v>
@@ -3121,22 +3136,22 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>134026153</v>
+        <v>134034627</v>
       </c>
       <c r="E84" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I84" s="5">
         <v>42</v>
       </c>
       <c r="J84" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K84" s="5">
         <v>0</v>
@@ -3152,22 +3167,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>134026234</v>
+        <v>134034867</v>
       </c>
       <c r="E85" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I85" s="5">
         <v>42</v>
       </c>
       <c r="J85" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K85" s="5">
         <v>0</v>
@@ -3183,22 +3198,22 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>134026500</v>
+        <v>134035188</v>
       </c>
       <c r="E86" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I86" s="5">
         <v>42</v>
       </c>
       <c r="J86" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K86" s="5">
         <v>0</v>
@@ -3214,22 +3229,22 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>134028012</v>
+        <v>134035201</v>
       </c>
       <c r="E87" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I87" s="5">
         <v>42</v>
       </c>
       <c r="J87" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K87" s="5">
         <v>0</v>
@@ -3245,22 +3260,22 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
-        <v>134028128</v>
+        <v>134035972</v>
       </c>
       <c r="E88" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I88" s="5">
         <v>42</v>
       </c>
       <c r="J88" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K88" s="5">
         <v>0</v>
@@ -3276,22 +3291,22 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>134028287</v>
+        <v>134036265</v>
       </c>
       <c r="E89" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I89" s="5">
         <v>42</v>
       </c>
       <c r="J89" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K89" s="5">
         <v>0</v>
@@ -3307,22 +3322,22 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>134028411</v>
+        <v>134036312</v>
       </c>
       <c r="E90" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I90" s="5">
         <v>42</v>
       </c>
       <c r="J90" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K90" s="5">
         <v>0</v>
@@ -3338,22 +3353,22 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>134028797</v>
+        <v>134036319</v>
       </c>
       <c r="E91" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I91" s="5">
         <v>42</v>
       </c>
       <c r="J91" s="5">
-        <v>718</v>
+        <v>1118</v>
       </c>
       <c r="K91" s="5">
         <v>0</v>
@@ -3369,22 +3384,22 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>134029639</v>
+        <v>134037631</v>
       </c>
       <c r="E92" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I92" s="5">
         <v>42</v>
       </c>
       <c r="J92" s="5">
-        <v>718</v>
+        <v>1117</v>
       </c>
       <c r="K92" s="5">
         <v>0</v>
@@ -3400,22 +3415,22 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>134029655</v>
+        <v>134037721</v>
       </c>
       <c r="E93" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I93" s="5">
         <v>42</v>
       </c>
       <c r="J93" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K93" s="5">
         <v>0</v>
@@ -3431,22 +3446,22 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>134030213</v>
+        <v>134038085</v>
       </c>
       <c r="E94" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I94" s="5">
         <v>42</v>
       </c>
       <c r="J94" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K94" s="5">
         <v>0</v>
@@ -3462,22 +3477,22 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>134031585</v>
+        <v>134038198</v>
       </c>
       <c r="E95" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I95" s="5">
         <v>42</v>
       </c>
       <c r="J95" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K95" s="5">
         <v>0</v>
@@ -3493,22 +3508,22 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>134031618</v>
+        <v>134038653</v>
       </c>
       <c r="E96" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I96" s="5">
         <v>42</v>
       </c>
       <c r="J96" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K96" s="5">
         <v>0</v>
@@ -3524,22 +3539,22 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>134031656</v>
+        <v>134040150</v>
       </c>
       <c r="E97" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I97" s="5">
         <v>42</v>
       </c>
       <c r="J97" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K97" s="5">
         <v>0</v>
@@ -3555,22 +3570,22 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <v>134032049</v>
+        <v>134040866</v>
       </c>
       <c r="E98" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I98" s="5">
         <v>42</v>
       </c>
       <c r="J98" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K98" s="5">
         <v>0</v>
@@ -3586,22 +3601,22 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <v>134032897</v>
+        <v>134041652</v>
       </c>
       <c r="E99" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I99" s="5">
         <v>42</v>
       </c>
       <c r="J99" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K99" s="5">
         <v>0</v>
@@ -3617,22 +3632,22 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <v>134033368</v>
+        <v>134042199</v>
       </c>
       <c r="E100" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I100" s="5">
         <v>42</v>
       </c>
       <c r="J100" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K100" s="5">
         <v>0</v>
@@ -3648,22 +3663,22 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <v>134034831</v>
+        <v>134042322</v>
       </c>
       <c r="E101" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I101" s="5">
         <v>42</v>
       </c>
       <c r="J101" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K101" s="5">
         <v>0</v>
@@ -3679,22 +3694,22 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <v>134034969</v>
+        <v>134043369</v>
       </c>
       <c r="E102" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I102" s="5">
         <v>42</v>
       </c>
       <c r="J102" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K102" s="5">
         <v>0</v>
@@ -3710,22 +3725,22 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <v>134035736</v>
+        <v>134043494</v>
       </c>
       <c r="E103" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I103" s="5">
         <v>42</v>
       </c>
       <c r="J103" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K103" s="5">
         <v>0</v>
@@ -3741,22 +3756,22 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <v>134035737</v>
+        <v>134043771</v>
       </c>
       <c r="E104" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I104" s="5">
         <v>42</v>
       </c>
       <c r="J104" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K104" s="5">
         <v>0</v>
@@ -3772,22 +3787,22 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
-        <v>134035911</v>
+        <v>134043918</v>
       </c>
       <c r="E105" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I105" s="5">
         <v>42</v>
       </c>
       <c r="J105" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K105" s="5">
         <v>0</v>
@@ -3803,22 +3818,22 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <v>134036182</v>
+        <v>134044054</v>
       </c>
       <c r="E106" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I106" s="5">
         <v>42</v>
       </c>
       <c r="J106" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
@@ -3834,22 +3849,22 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <v>134037261</v>
+        <v>134044208</v>
       </c>
       <c r="E107" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I107" s="5">
         <v>42</v>
       </c>
       <c r="J107" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K107" s="5">
         <v>0</v>
@@ -3865,22 +3880,22 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <v>134037347</v>
+        <v>134044719</v>
       </c>
       <c r="E108" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I108" s="5">
         <v>42</v>
       </c>
       <c r="J108" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K108" s="5">
         <v>0</v>
@@ -3896,22 +3911,22 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <v>134037398</v>
+        <v>134045058</v>
       </c>
       <c r="E109" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I109" s="5">
         <v>42</v>
       </c>
       <c r="J109" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
@@ -3927,22 +3942,22 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <v>134037440</v>
+        <v>134046267</v>
       </c>
       <c r="E110" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I110" s="5">
         <v>42</v>
       </c>
       <c r="J110" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K110" s="5">
         <v>0</v>
@@ -3958,22 +3973,22 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <v>134037478</v>
+        <v>134046282</v>
       </c>
       <c r="E111" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I111" s="5">
         <v>42</v>
       </c>
       <c r="J111" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K111" s="5">
         <v>0</v>
@@ -3989,22 +4004,22 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <v>134037618</v>
+        <v>134046375</v>
       </c>
       <c r="E112" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I112" s="5">
         <v>42</v>
       </c>
       <c r="J112" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K112" s="5">
         <v>0</v>
@@ -4020,22 +4035,22 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
-        <v>134037640</v>
+        <v>134046722</v>
       </c>
       <c r="E113" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I113" s="5">
         <v>42</v>
       </c>
       <c r="J113" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
@@ -4051,22 +4066,22 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
-        <v>134037703</v>
+        <v>134047113</v>
       </c>
       <c r="E114" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I114" s="5">
         <v>42</v>
       </c>
       <c r="J114" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K114" s="5">
         <v>0</v>
@@ -4082,22 +4097,22 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <v>134037756</v>
+        <v>134047688</v>
       </c>
       <c r="E115" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I115" s="5">
         <v>42</v>
       </c>
       <c r="J115" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K115" s="5">
         <v>0</v>
@@ -4113,22 +4128,22 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <v>134038088</v>
+        <v>134048819</v>
       </c>
       <c r="E116" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I116" s="5">
         <v>42</v>
       </c>
       <c r="J116" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K116" s="5">
         <v>0</v>
@@ -4144,22 +4159,22 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <v>134038450</v>
+        <v>134049188</v>
       </c>
       <c r="E117" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I117" s="5">
         <v>42</v>
       </c>
       <c r="J117" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K117" s="5">
         <v>0</v>
@@ -4175,22 +4190,22 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <v>134038527</v>
+        <v>134049671</v>
       </c>
       <c r="E118" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I118" s="5">
         <v>42</v>
       </c>
       <c r="J118" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K118" s="5">
         <v>0</v>
@@ -4206,22 +4221,22 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
-        <v>134038570</v>
+        <v>134049759</v>
       </c>
       <c r="E119" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I119" s="5">
         <v>42</v>
       </c>
       <c r="J119" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K119" s="5">
         <v>0</v>
@@ -4237,22 +4252,22 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
-        <v>134038625</v>
+        <v>134050624</v>
       </c>
       <c r="E120" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I120" s="5">
         <v>42</v>
       </c>
       <c r="J120" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K120" s="5">
         <v>0</v>
@@ -4268,22 +4283,22 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
-        <v>134038799</v>
+        <v>134050948</v>
       </c>
       <c r="E121" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I121" s="5">
         <v>42</v>
       </c>
       <c r="J121" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K121" s="5">
         <v>0</v>
@@ -4294,6 +4309,719 @@
       <c r="M121" s="5"/>
       <c r="N121" s="5"/>
       <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="5">
+        <v>134051159</v>
+      </c>
+      <c r="E122" s="5">
+        <v>601</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="5">
+        <v>134051272</v>
+      </c>
+      <c r="E123" s="5">
+        <v>601</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="5">
+        <v>134051415</v>
+      </c>
+      <c r="E124" s="5">
+        <v>601</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="5">
+        <v>134051730</v>
+      </c>
+      <c r="E125" s="5">
+        <v>601</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="5">
+        <v>134052343</v>
+      </c>
+      <c r="E126" s="5">
+        <v>601</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="5">
+        <v>134052450</v>
+      </c>
+      <c r="E127" s="5">
+        <v>601</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="5">
+        <v>134052937</v>
+      </c>
+      <c r="E128" s="5">
+        <v>601</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="5">
+        <v>134053026</v>
+      </c>
+      <c r="E129" s="5">
+        <v>601</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="5">
+        <v>134053873</v>
+      </c>
+      <c r="E130" s="5">
+        <v>601</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="5">
+        <v>134054103</v>
+      </c>
+      <c r="E131" s="5">
+        <v>601</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="5">
+        <v>134054586</v>
+      </c>
+      <c r="E132" s="5">
+        <v>601</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="5">
+        <v>134055406</v>
+      </c>
+      <c r="E133" s="5">
+        <v>601</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="M133" s="5"/>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="5">
+        <v>134055683</v>
+      </c>
+      <c r="E134" s="5">
+        <v>601</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="M134" s="5"/>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="5">
+        <v>134055880</v>
+      </c>
+      <c r="E135" s="5">
+        <v>601</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="5">
+        <v>134056773</v>
+      </c>
+      <c r="E136" s="5">
+        <v>601</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="M136" s="5"/>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
+        <v>134057210</v>
+      </c>
+      <c r="E137" s="5">
+        <v>601</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="M137" s="5"/>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="5">
+        <v>134057883</v>
+      </c>
+      <c r="E138" s="5">
+        <v>601</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="M138" s="5"/>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="5">
+        <v>134059155</v>
+      </c>
+      <c r="E139" s="5">
+        <v>601</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+      <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="5">
+        <v>134059180</v>
+      </c>
+      <c r="E140" s="5">
+        <v>601</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="5">
+        <v>134059309</v>
+      </c>
+      <c r="E141" s="5">
+        <v>601</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="5">
+        <v>134059441</v>
+      </c>
+      <c r="E142" s="5">
+        <v>601</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="M142" s="5"/>
+      <c r="N142" s="5"/>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="5">
+        <v>134059592</v>
+      </c>
+      <c r="E143" s="5">
+        <v>601</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="M143" s="5"/>
+      <c r="N143" s="5"/>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="5">
+        <v>134060122</v>
+      </c>
+      <c r="E144" s="5">
+        <v>601</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="M144" s="5"/>
+      <c r="N144" s="5"/>
+      <c r="O144" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8860ED25-2D05-4DC8-B283-313E5F34B61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A983122D-8654-4D62-9B14-DE15E1444499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="27">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,22 +79,37 @@
     <t>B</t>
   </si>
   <si>
-    <t>8/3/2023</t>
+    <t>05/08/2025</t>
   </si>
   <si>
-    <t>10/3/2023</t>
+    <t>13/08/2025</t>
   </si>
   <si>
-    <t>19/8/2025</t>
+    <t>15/08/2025</t>
   </si>
   <si>
-    <t>20/8/2025</t>
+    <t>19/08/2025</t>
   </si>
   <si>
-    <t>25/8/2025</t>
+    <t>20/08/2025</t>
   </si>
   <si>
-    <t>27/8/2025</t>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
   </si>
 </sst>
 </file>
@@ -582,22 +597,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>123058958</v>
+        <v>133769226</v>
       </c>
       <c r="E2" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -613,22 +628,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>133994784</v>
+        <v>133916446</v>
       </c>
       <c r="E3" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -644,22 +659,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>131455658</v>
+        <v>133917972</v>
       </c>
       <c r="E4" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -675,22 +690,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>132430370</v>
+        <v>133967889</v>
       </c>
       <c r="E5" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -706,22 +721,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>132976194</v>
+        <v>134007999</v>
       </c>
       <c r="E6" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -737,22 +752,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>133001123</v>
+        <v>134008576</v>
       </c>
       <c r="E7" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8001</v>
+        <v>1117</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -768,22 +783,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>133541173</v>
+        <v>134029757</v>
       </c>
       <c r="E8" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -799,22 +814,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>133662994</v>
+        <v>134038110</v>
       </c>
       <c r="E9" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -830,13 +845,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134044424</v>
+        <v>134054484</v>
       </c>
       <c r="E10" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>21</v>
@@ -845,7 +860,7 @@
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -861,22 +876,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>131455658</v>
+        <v>134072666</v>
       </c>
       <c r="E11" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -892,22 +907,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133662994</v>
+        <v>134084576</v>
       </c>
       <c r="E12" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -923,22 +938,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134137620</v>
+        <v>134107254</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -954,22 +969,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134137707</v>
+        <v>134108385</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -985,22 +1000,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134137750</v>
+        <v>134127911</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1016,22 +1031,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>134137858</v>
+        <v>134137880</v>
       </c>
       <c r="E16" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1047,22 +1062,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>134137938</v>
+        <v>134137964</v>
       </c>
       <c r="E17" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1078,22 +1093,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>134138061</v>
+        <v>134138723</v>
       </c>
       <c r="E18" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1109,22 +1124,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>134138099</v>
+        <v>134138824</v>
       </c>
       <c r="E19" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1140,22 +1155,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>134138197</v>
+        <v>134138968</v>
       </c>
       <c r="E20" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1171,22 +1186,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>134138226</v>
+        <v>134139457</v>
       </c>
       <c r="E21" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1202,22 +1217,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>134138302</v>
+        <v>134139599</v>
       </c>
       <c r="E22" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1233,22 +1248,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>134138366</v>
+        <v>134140129</v>
       </c>
       <c r="E23" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1264,22 +1279,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>134138377</v>
+        <v>134140541</v>
       </c>
       <c r="E24" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1295,22 +1310,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>134138444</v>
+        <v>134140598</v>
       </c>
       <c r="E25" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
       </c>
       <c r="J25" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -1326,22 +1341,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>134138448</v>
+        <v>134140848</v>
       </c>
       <c r="E26" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1357,22 +1372,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>134138603</v>
+        <v>134140923</v>
       </c>
       <c r="E27" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1388,22 +1403,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>134138697</v>
+        <v>134140957</v>
       </c>
       <c r="E28" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1419,22 +1434,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>134138716</v>
+        <v>134141130</v>
       </c>
       <c r="E29" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
       </c>
       <c r="J29" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -1450,22 +1465,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>134138722</v>
+        <v>134141139</v>
       </c>
       <c r="E30" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
       </c>
       <c r="J30" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -1481,22 +1496,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>134138740</v>
+        <v>134141254</v>
       </c>
       <c r="E31" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
       </c>
       <c r="J31" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K31" s="5">
         <v>0</v>
@@ -1512,22 +1527,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>134139312</v>
+        <v>134142120</v>
       </c>
       <c r="E32" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
       </c>
       <c r="J32" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -1543,22 +1558,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>134139362</v>
+        <v>134142296</v>
       </c>
       <c r="E33" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
       </c>
       <c r="J33" s="5">
-        <v>718</v>
+        <v>1117</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -1574,22 +1589,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>134139386</v>
+        <v>134142486</v>
       </c>
       <c r="E34" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
       </c>
       <c r="J34" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -1605,22 +1620,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>134139446</v>
+        <v>134143072</v>
       </c>
       <c r="E35" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
       </c>
       <c r="J35" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -1636,22 +1651,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>134139496</v>
+        <v>134143297</v>
       </c>
       <c r="E36" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
       </c>
       <c r="J36" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -1667,22 +1682,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>134139633</v>
+        <v>134143344</v>
       </c>
       <c r="E37" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
       </c>
       <c r="J37" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -1698,22 +1713,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>134139710</v>
+        <v>134144378</v>
       </c>
       <c r="E38" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
       </c>
       <c r="J38" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
@@ -1729,22 +1744,22 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>134140040</v>
+        <v>134144554</v>
       </c>
       <c r="E39" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
       </c>
       <c r="J39" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K39" s="5">
         <v>0</v>
@@ -1760,22 +1775,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>134140102</v>
+        <v>134144724</v>
       </c>
       <c r="E40" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
       </c>
       <c r="J40" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -1791,22 +1806,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>134140125</v>
+        <v>134145395</v>
       </c>
       <c r="E41" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
       </c>
       <c r="J41" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -1822,22 +1837,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>134140449</v>
+        <v>134145490</v>
       </c>
       <c r="E42" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -1853,22 +1868,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>134140491</v>
+        <v>134146570</v>
       </c>
       <c r="E43" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I43" s="5">
         <v>42</v>
       </c>
       <c r="J43" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -1884,22 +1899,22 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>134140522</v>
+        <v>134147508</v>
       </c>
       <c r="E44" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
       </c>
       <c r="J44" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -1915,22 +1930,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>134140585</v>
+        <v>134147684</v>
       </c>
       <c r="E45" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
       </c>
       <c r="J45" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -1946,22 +1961,22 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>134140837</v>
+        <v>134148136</v>
       </c>
       <c r="E46" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I46" s="5">
         <v>42</v>
       </c>
       <c r="J46" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
@@ -1977,22 +1992,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>134140875</v>
+        <v>134148284</v>
       </c>
       <c r="E47" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
       </c>
       <c r="J47" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -2008,22 +2023,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>134140945</v>
+        <v>134148874</v>
       </c>
       <c r="E48" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2039,22 +2054,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>134140967</v>
+        <v>134149996</v>
       </c>
       <c r="E49" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2070,22 +2085,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>134141009</v>
+        <v>134151099</v>
       </c>
       <c r="E50" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2101,22 +2116,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>134141038</v>
+        <v>134151152</v>
       </c>
       <c r="E51" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
       </c>
       <c r="J51" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -2132,22 +2147,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>134141082</v>
+        <v>134151373</v>
       </c>
       <c r="E52" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -2163,22 +2178,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>134141140</v>
+        <v>134151590</v>
       </c>
       <c r="E53" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2194,22 +2209,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>134141148</v>
+        <v>134152016</v>
       </c>
       <c r="E54" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2225,22 +2240,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>134141273</v>
+        <v>134152207</v>
       </c>
       <c r="E55" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -2256,22 +2271,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>134141392</v>
+        <v>134152361</v>
       </c>
       <c r="E56" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
       </c>
       <c r="J56" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -2287,22 +2302,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>134141430</v>
+        <v>134152445</v>
       </c>
       <c r="E57" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -2318,22 +2333,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>134141474</v>
+        <v>134152480</v>
       </c>
       <c r="E58" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
       </c>
       <c r="J58" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -2349,22 +2364,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>134141518</v>
+        <v>134152512</v>
       </c>
       <c r="E59" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2380,22 +2395,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>134141549</v>
+        <v>134152683</v>
       </c>
       <c r="E60" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
       </c>
       <c r="J60" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K60" s="5">
         <v>0</v>
@@ -2411,22 +2426,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>134141593</v>
+        <v>134152829</v>
       </c>
       <c r="E61" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
       </c>
       <c r="J61" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K61" s="5">
         <v>0</v>
@@ -2442,22 +2457,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>134141629</v>
+        <v>134152928</v>
       </c>
       <c r="E62" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I62" s="5">
         <v>42</v>
       </c>
       <c r="J62" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K62" s="5">
         <v>0</v>
@@ -2473,22 +2488,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>134141647</v>
+        <v>134153832</v>
       </c>
       <c r="E63" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
       </c>
       <c r="J63" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K63" s="5">
         <v>0</v>
@@ -2504,22 +2519,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>134141649</v>
+        <v>134153856</v>
       </c>
       <c r="E64" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
       </c>
       <c r="J64" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K64" s="5">
         <v>0</v>
@@ -2535,22 +2550,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>134141690</v>
+        <v>134154349</v>
       </c>
       <c r="E65" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
       </c>
       <c r="J65" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K65" s="5">
         <v>0</v>
@@ -2566,22 +2581,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>134141776</v>
+        <v>134154357</v>
       </c>
       <c r="E66" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
       </c>
       <c r="J66" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -2597,22 +2612,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>134142036</v>
+        <v>134154564</v>
       </c>
       <c r="E67" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
       </c>
       <c r="J67" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K67" s="5">
         <v>0</v>
@@ -2628,22 +2643,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>134142062</v>
+        <v>134154981</v>
       </c>
       <c r="E68" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
       </c>
       <c r="J68" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K68" s="5">
         <v>0</v>
@@ -2659,22 +2674,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>134142117</v>
+        <v>134155252</v>
       </c>
       <c r="E69" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
       </c>
       <c r="J69" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
@@ -2690,22 +2705,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>134142154</v>
+        <v>134155260</v>
       </c>
       <c r="E70" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
       </c>
       <c r="J70" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
@@ -2721,22 +2736,22 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>134142187</v>
+        <v>134155645</v>
       </c>
       <c r="E71" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
       </c>
       <c r="J71" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K71" s="5">
         <v>0</v>
@@ -2752,22 +2767,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>134142570</v>
+        <v>134155811</v>
       </c>
       <c r="E72" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I72" s="5">
         <v>42</v>
       </c>
       <c r="J72" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K72" s="5">
         <v>0</v>
@@ -2783,22 +2798,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>134143232</v>
+        <v>134155849</v>
       </c>
       <c r="E73" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
       </c>
       <c r="J73" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K73" s="5">
         <v>0</v>
@@ -2814,22 +2829,22 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>134143340</v>
+        <v>134155922</v>
       </c>
       <c r="E74" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
       </c>
       <c r="J74" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K74" s="5">
         <v>0</v>
@@ -2845,22 +2860,22 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>134143597</v>
+        <v>134155982</v>
       </c>
       <c r="E75" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
       </c>
       <c r="J75" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K75" s="5">
         <v>0</v>
@@ -2876,22 +2891,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>134143653</v>
+        <v>134156437</v>
       </c>
       <c r="E76" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
       </c>
       <c r="J76" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K76" s="5">
         <v>0</v>
@@ -2907,22 +2922,22 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>134143807</v>
+        <v>134156609</v>
       </c>
       <c r="E77" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
       </c>
       <c r="J77" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K77" s="5">
         <v>0</v>
@@ -2937,1368 +2952,186 @@
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
-        <v>134143861</v>
-      </c>
-      <c r="E78" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I78" s="5">
-        <v>42</v>
-      </c>
-      <c r="J78" s="5">
-        <v>718</v>
-      </c>
-      <c r="K78" s="5">
-        <v>0</v>
-      </c>
-      <c r="L78" s="5">
-        <v>61</v>
-      </c>
+      <c r="A78" s="5"/>
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
-      <c r="O78" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O78" s="5"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="5">
-        <v>134143904</v>
-      </c>
-      <c r="E79" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79" s="5">
-        <v>42</v>
-      </c>
-      <c r="J79" s="5">
-        <v>718</v>
-      </c>
-      <c r="K79" s="5">
-        <v>0</v>
-      </c>
-      <c r="L79" s="5">
-        <v>61</v>
-      </c>
+      <c r="A79" s="5"/>
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
-      <c r="O79" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O79" s="5"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
-        <v>134143952</v>
-      </c>
-      <c r="E80" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I80" s="5">
-        <v>42</v>
-      </c>
-      <c r="J80" s="5">
-        <v>718</v>
-      </c>
-      <c r="K80" s="5">
-        <v>0</v>
-      </c>
-      <c r="L80" s="5">
-        <v>61</v>
-      </c>
+      <c r="A80" s="5"/>
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
-      <c r="O80" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" s="5">
-        <v>134144029</v>
-      </c>
-      <c r="E81" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I81" s="5">
-        <v>42</v>
-      </c>
-      <c r="J81" s="5">
-        <v>718</v>
-      </c>
-      <c r="K81" s="5">
-        <v>0</v>
-      </c>
-      <c r="L81" s="5">
-        <v>61</v>
-      </c>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="5">
-        <v>134144165</v>
-      </c>
-      <c r="E82" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I82" s="5">
-        <v>42</v>
-      </c>
-      <c r="J82" s="5">
-        <v>718</v>
-      </c>
-      <c r="K82" s="5">
-        <v>0</v>
-      </c>
-      <c r="L82" s="5">
-        <v>61</v>
-      </c>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
-      <c r="O82" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
-        <v>134145299</v>
-      </c>
-      <c r="E83" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I83" s="5">
-        <v>42</v>
-      </c>
-      <c r="J83" s="5">
-        <v>718</v>
-      </c>
-      <c r="K83" s="5">
-        <v>0</v>
-      </c>
-      <c r="L83" s="5">
-        <v>61</v>
-      </c>
-      <c r="M83" s="5"/>
-      <c r="N83" s="5"/>
-      <c r="O83" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
-        <v>134147480</v>
-      </c>
-      <c r="E84" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I84" s="5">
-        <v>42</v>
-      </c>
-      <c r="J84" s="5">
-        <v>718</v>
-      </c>
-      <c r="K84" s="5">
-        <v>0</v>
-      </c>
-      <c r="L84" s="5">
-        <v>61</v>
-      </c>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
-        <v>134147511</v>
-      </c>
-      <c r="E85" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I85" s="5">
-        <v>42</v>
-      </c>
-      <c r="J85" s="5">
-        <v>718</v>
-      </c>
-      <c r="K85" s="5">
-        <v>0</v>
-      </c>
-      <c r="L85" s="5">
-        <v>61</v>
-      </c>
-      <c r="M85" s="5"/>
-      <c r="N85" s="5"/>
-      <c r="O85" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="5">
-        <v>134147598</v>
-      </c>
-      <c r="E86" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I86" s="5">
-        <v>42</v>
-      </c>
-      <c r="J86" s="5">
-        <v>718</v>
-      </c>
-      <c r="K86" s="5">
-        <v>0</v>
-      </c>
-      <c r="L86" s="5">
-        <v>61</v>
-      </c>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
-      <c r="O86" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
-        <v>134147657</v>
-      </c>
-      <c r="E87" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87" s="5">
-        <v>42</v>
-      </c>
-      <c r="J87" s="5">
-        <v>718</v>
-      </c>
-      <c r="K87" s="5">
-        <v>0</v>
-      </c>
-      <c r="L87" s="5">
-        <v>61</v>
-      </c>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
-      <c r="O87" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" s="5">
-        <v>134147714</v>
-      </c>
-      <c r="E88" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" s="5">
-        <v>42</v>
-      </c>
-      <c r="J88" s="5">
-        <v>718</v>
-      </c>
-      <c r="K88" s="5">
-        <v>0</v>
-      </c>
-      <c r="L88" s="5">
-        <v>61</v>
-      </c>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
-      <c r="O88" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" s="5">
-        <v>134147743</v>
-      </c>
-      <c r="E89" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89" s="5">
-        <v>42</v>
-      </c>
-      <c r="J89" s="5">
-        <v>718</v>
-      </c>
-      <c r="K89" s="5">
-        <v>0</v>
-      </c>
-      <c r="L89" s="5">
-        <v>61</v>
-      </c>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
-      <c r="O89" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="5">
-        <v>134147782</v>
-      </c>
-      <c r="E90" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90" s="5">
-        <v>42</v>
-      </c>
-      <c r="J90" s="5">
-        <v>718</v>
-      </c>
-      <c r="K90" s="5">
-        <v>0</v>
-      </c>
-      <c r="L90" s="5">
-        <v>61</v>
-      </c>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
-      <c r="O90" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="5">
-        <v>134147819</v>
-      </c>
-      <c r="E91" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I91" s="5">
-        <v>42</v>
-      </c>
-      <c r="J91" s="5">
-        <v>718</v>
-      </c>
-      <c r="K91" s="5">
-        <v>0</v>
-      </c>
-      <c r="L91" s="5">
-        <v>61</v>
-      </c>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="5">
-        <v>134148021</v>
-      </c>
-      <c r="E92" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92" s="5">
-        <v>42</v>
-      </c>
-      <c r="J92" s="5">
-        <v>718</v>
-      </c>
-      <c r="K92" s="5">
-        <v>0</v>
-      </c>
-      <c r="L92" s="5">
-        <v>61</v>
-      </c>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-      <c r="O92" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" s="5">
-        <v>134148053</v>
-      </c>
-      <c r="E93" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93" s="5">
-        <v>42</v>
-      </c>
-      <c r="J93" s="5">
-        <v>718</v>
-      </c>
-      <c r="K93" s="5">
-        <v>0</v>
-      </c>
-      <c r="L93" s="5">
-        <v>61</v>
-      </c>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
-      <c r="O93" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="5">
-        <v>134148289</v>
-      </c>
-      <c r="E94" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I94" s="5">
-        <v>42</v>
-      </c>
-      <c r="J94" s="5">
-        <v>718</v>
-      </c>
-      <c r="K94" s="5">
-        <v>0</v>
-      </c>
-      <c r="L94" s="5">
-        <v>61</v>
-      </c>
-      <c r="M94" s="5"/>
-      <c r="N94" s="5"/>
-      <c r="O94" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="5">
-        <v>134148360</v>
-      </c>
-      <c r="E95" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95" s="5">
-        <v>42</v>
-      </c>
-      <c r="J95" s="5">
-        <v>718</v>
-      </c>
-      <c r="K95" s="5">
-        <v>0</v>
-      </c>
-      <c r="L95" s="5">
-        <v>61</v>
-      </c>
-      <c r="M95" s="5"/>
-      <c r="N95" s="5"/>
-      <c r="O95" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="5">
-        <v>134148996</v>
-      </c>
-      <c r="E96" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96" s="5">
-        <v>42</v>
-      </c>
-      <c r="J96" s="5">
-        <v>718</v>
-      </c>
-      <c r="K96" s="5">
-        <v>0</v>
-      </c>
-      <c r="L96" s="5">
-        <v>61</v>
-      </c>
-      <c r="M96" s="5"/>
-      <c r="N96" s="5"/>
-      <c r="O96" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" s="5">
-        <v>134149111</v>
-      </c>
-      <c r="E97" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97" s="5">
-        <v>42</v>
-      </c>
-      <c r="J97" s="5">
-        <v>718</v>
-      </c>
-      <c r="K97" s="5">
-        <v>0</v>
-      </c>
-      <c r="L97" s="5">
-        <v>61</v>
-      </c>
-      <c r="M97" s="5"/>
-      <c r="N97" s="5"/>
-      <c r="O97" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="5">
-        <v>134149134</v>
-      </c>
-      <c r="E98" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98" s="5">
-        <v>42</v>
-      </c>
-      <c r="J98" s="5">
-        <v>718</v>
-      </c>
-      <c r="K98" s="5">
-        <v>0</v>
-      </c>
-      <c r="L98" s="5">
-        <v>61</v>
-      </c>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" s="5">
-        <v>134149347</v>
-      </c>
-      <c r="E99" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I99" s="5">
-        <v>42</v>
-      </c>
-      <c r="J99" s="5">
-        <v>718</v>
-      </c>
-      <c r="K99" s="5">
-        <v>0</v>
-      </c>
-      <c r="L99" s="5">
-        <v>61</v>
-      </c>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
-      <c r="O99" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="5">
-        <v>134149908</v>
-      </c>
-      <c r="E100" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100" s="5">
-        <v>42</v>
-      </c>
-      <c r="J100" s="5">
-        <v>718</v>
-      </c>
-      <c r="K100" s="5">
-        <v>0</v>
-      </c>
-      <c r="L100" s="5">
-        <v>61</v>
-      </c>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
-      <c r="O100" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="5">
-        <v>134151116</v>
-      </c>
-      <c r="E101" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101" s="5">
-        <v>42</v>
-      </c>
-      <c r="J101" s="5">
-        <v>718</v>
-      </c>
-      <c r="K101" s="5">
-        <v>0</v>
-      </c>
-      <c r="L101" s="5">
-        <v>61</v>
-      </c>
-      <c r="M101" s="5"/>
-      <c r="N101" s="5"/>
-      <c r="O101" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A102" s="5">
-        <v>134151186</v>
-      </c>
-      <c r="E102" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102" s="5">
-        <v>42</v>
-      </c>
-      <c r="J102" s="5">
-        <v>718</v>
-      </c>
-      <c r="K102" s="5">
-        <v>0</v>
-      </c>
-      <c r="L102" s="5">
-        <v>61</v>
-      </c>
-      <c r="M102" s="5"/>
-      <c r="N102" s="5"/>
-      <c r="O102" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="5">
-        <v>134151501</v>
-      </c>
-      <c r="E103" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103" s="5">
-        <v>42</v>
-      </c>
-      <c r="J103" s="5">
-        <v>718</v>
-      </c>
-      <c r="K103" s="5">
-        <v>0</v>
-      </c>
-      <c r="L103" s="5">
-        <v>61</v>
-      </c>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5"/>
-      <c r="O103" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="5">
-        <v>134151654</v>
-      </c>
-      <c r="E104" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104" s="5">
-        <v>42</v>
-      </c>
-      <c r="J104" s="5">
-        <v>718</v>
-      </c>
-      <c r="K104" s="5">
-        <v>0</v>
-      </c>
-      <c r="L104" s="5">
-        <v>61</v>
-      </c>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
-      <c r="O104" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
-        <v>134152766</v>
-      </c>
-      <c r="E105" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105" s="5">
-        <v>42</v>
-      </c>
-      <c r="J105" s="5">
-        <v>718</v>
-      </c>
-      <c r="K105" s="5">
-        <v>0</v>
-      </c>
-      <c r="L105" s="5">
-        <v>61</v>
-      </c>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
-      <c r="O105" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A106" s="5">
-        <v>134152953</v>
-      </c>
-      <c r="E106" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I106" s="5">
-        <v>42</v>
-      </c>
-      <c r="J106" s="5">
-        <v>718</v>
-      </c>
-      <c r="K106" s="5">
-        <v>0</v>
-      </c>
-      <c r="L106" s="5">
-        <v>61</v>
-      </c>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
-      <c r="O106" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A107" s="5">
-        <v>134153452</v>
-      </c>
-      <c r="E107" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I107" s="5">
-        <v>42</v>
-      </c>
-      <c r="J107" s="5">
-        <v>718</v>
-      </c>
-      <c r="K107" s="5">
-        <v>0</v>
-      </c>
-      <c r="L107" s="5">
-        <v>61</v>
-      </c>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5"/>
-      <c r="O107" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A108" s="5">
-        <v>134153581</v>
-      </c>
-      <c r="E108" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G108" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I108" s="5">
-        <v>42</v>
-      </c>
-      <c r="J108" s="5">
-        <v>718</v>
-      </c>
-      <c r="K108" s="5">
-        <v>0</v>
-      </c>
-      <c r="L108" s="5">
-        <v>61</v>
-      </c>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5"/>
-      <c r="O108" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A109" s="5">
-        <v>134153891</v>
-      </c>
-      <c r="E109" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G109" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I109" s="5">
-        <v>42</v>
-      </c>
-      <c r="J109" s="5">
-        <v>718</v>
-      </c>
-      <c r="K109" s="5">
-        <v>0</v>
-      </c>
-      <c r="L109" s="5">
-        <v>61</v>
-      </c>
-      <c r="M109" s="5"/>
-      <c r="N109" s="5"/>
-      <c r="O109" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A110" s="5">
-        <v>134154101</v>
-      </c>
-      <c r="E110" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I110" s="5">
-        <v>42</v>
-      </c>
-      <c r="J110" s="5">
-        <v>718</v>
-      </c>
-      <c r="K110" s="5">
-        <v>0</v>
-      </c>
-      <c r="L110" s="5">
-        <v>61</v>
-      </c>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5"/>
-      <c r="O110" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A111" s="5">
-        <v>134154201</v>
-      </c>
-      <c r="E111" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I111" s="5">
-        <v>42</v>
-      </c>
-      <c r="J111" s="5">
-        <v>718</v>
-      </c>
-      <c r="K111" s="5">
-        <v>0</v>
-      </c>
-      <c r="L111" s="5">
-        <v>61</v>
-      </c>
-      <c r="M111" s="5"/>
-      <c r="N111" s="5"/>
-      <c r="O111" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A112" s="5">
-        <v>134156177</v>
-      </c>
-      <c r="E112" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I112" s="5">
-        <v>42</v>
-      </c>
-      <c r="J112" s="5">
-        <v>718</v>
-      </c>
-      <c r="K112" s="5">
-        <v>0</v>
-      </c>
-      <c r="L112" s="5">
-        <v>61</v>
-      </c>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5"/>
-      <c r="O112" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A113" s="5">
-        <v>134156858</v>
-      </c>
-      <c r="E113" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G113" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I113" s="5">
-        <v>42</v>
-      </c>
-      <c r="J113" s="5">
-        <v>718</v>
-      </c>
-      <c r="K113" s="5">
-        <v>0</v>
-      </c>
-      <c r="L113" s="5">
-        <v>61</v>
-      </c>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5"/>
-      <c r="O113" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A114" s="5">
-        <v>134157134</v>
-      </c>
-      <c r="E114" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G114" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I114" s="5">
-        <v>42</v>
-      </c>
-      <c r="J114" s="5">
-        <v>718</v>
-      </c>
-      <c r="K114" s="5">
-        <v>0</v>
-      </c>
-      <c r="L114" s="5">
-        <v>61</v>
-      </c>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5"/>
-      <c r="O114" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A115" s="5">
-        <v>134157377</v>
-      </c>
-      <c r="E115" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G115" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I115" s="5">
-        <v>42</v>
-      </c>
-      <c r="J115" s="5">
-        <v>718</v>
-      </c>
-      <c r="K115" s="5">
-        <v>0</v>
-      </c>
-      <c r="L115" s="5">
-        <v>61</v>
-      </c>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5"/>
-      <c r="O115" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A116" s="5">
-        <v>134157950</v>
-      </c>
-      <c r="E116" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I116" s="5">
-        <v>42</v>
-      </c>
-      <c r="J116" s="5">
-        <v>718</v>
-      </c>
-      <c r="K116" s="5">
-        <v>0</v>
-      </c>
-      <c r="L116" s="5">
-        <v>61</v>
-      </c>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5"/>
-      <c r="O116" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A117" s="5">
-        <v>134158172</v>
-      </c>
-      <c r="E117" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G117" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I117" s="5">
-        <v>42</v>
-      </c>
-      <c r="J117" s="5">
-        <v>718</v>
-      </c>
-      <c r="K117" s="5">
-        <v>0</v>
-      </c>
-      <c r="L117" s="5">
-        <v>61</v>
-      </c>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
-      <c r="O117" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A118" s="5">
-        <v>134158183</v>
-      </c>
-      <c r="E118" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G118" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I118" s="5">
-        <v>42</v>
-      </c>
-      <c r="J118" s="5">
-        <v>718</v>
-      </c>
-      <c r="K118" s="5">
-        <v>0</v>
-      </c>
-      <c r="L118" s="5">
-        <v>61</v>
-      </c>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5"/>
-      <c r="O118" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A119" s="5">
-        <v>134158560</v>
-      </c>
-      <c r="E119" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G119" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I119" s="5">
-        <v>42</v>
-      </c>
-      <c r="J119" s="5">
-        <v>718</v>
-      </c>
-      <c r="K119" s="5">
-        <v>0</v>
-      </c>
-      <c r="L119" s="5">
-        <v>61</v>
-      </c>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5"/>
-      <c r="O119" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A120" s="5">
-        <v>134158911</v>
-      </c>
-      <c r="E120" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I120" s="5">
-        <v>42</v>
-      </c>
-      <c r="J120" s="5">
-        <v>718</v>
-      </c>
-      <c r="K120" s="5">
-        <v>0</v>
-      </c>
-      <c r="L120" s="5">
-        <v>61</v>
-      </c>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5"/>
-      <c r="O120" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A121" s="5">
-        <v>134159383</v>
-      </c>
-      <c r="E121" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F121" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I121" s="5">
-        <v>42</v>
-      </c>
-      <c r="J121" s="5">
-        <v>718</v>
-      </c>
-      <c r="K121" s="5">
-        <v>0</v>
-      </c>
-      <c r="L121" s="5">
-        <v>61</v>
-      </c>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5"/>
-      <c r="O121" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O80" s="5"/>
+    </row>
+    <row r="81" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+    </row>
+    <row r="82" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+    </row>
+    <row r="83" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+    </row>
+    <row r="84" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+    </row>
+    <row r="85" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+    </row>
+    <row r="86" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+    </row>
+    <row r="87" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+    </row>
+    <row r="88" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+    </row>
+    <row r="89" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+    </row>
+    <row r="90" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+    </row>
+    <row r="91" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+    </row>
+    <row r="92" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+    </row>
+    <row r="93" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+    </row>
+    <row r="94" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+    </row>
+    <row r="95" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+    </row>
+    <row r="96" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+    </row>
+    <row r="97" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+    </row>
+    <row r="98" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+    </row>
+    <row r="99" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+    </row>
+    <row r="100" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+    </row>
+    <row r="101" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+    </row>
+    <row r="102" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F102" s="8"/>
+      <c r="G102" s="8"/>
+    </row>
+    <row r="103" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+    </row>
+    <row r="104" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F104" s="8"/>
+      <c r="G104" s="8"/>
+    </row>
+    <row r="105" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F105" s="8"/>
+      <c r="G105" s="8"/>
+    </row>
+    <row r="106" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+    </row>
+    <row r="107" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F107" s="8"/>
+      <c r="G107" s="8"/>
+    </row>
+    <row r="108" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+    </row>
+    <row r="109" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F109" s="8"/>
+      <c r="G109" s="8"/>
+    </row>
+    <row r="110" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
+    </row>
+    <row r="111" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F111" s="8"/>
+      <c r="G111" s="8"/>
+    </row>
+    <row r="112" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F112" s="8"/>
+      <c r="G112" s="8"/>
+    </row>
+    <row r="113" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F113" s="8"/>
+      <c r="G113" s="8"/>
+    </row>
+    <row r="114" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F114" s="8"/>
+      <c r="G114" s="8"/>
+    </row>
+    <row r="115" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F115" s="8"/>
+      <c r="G115" s="8"/>
+    </row>
+    <row r="116" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F116" s="8"/>
+      <c r="G116" s="8"/>
+    </row>
+    <row r="117" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F117" s="8"/>
+      <c r="G117" s="8"/>
+    </row>
+    <row r="118" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F118" s="8"/>
+      <c r="G118" s="8"/>
+    </row>
+    <row r="119" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F119" s="8"/>
+      <c r="G119" s="8"/>
+    </row>
+    <row r="120" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+    </row>
+    <row r="121" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F121" s="8"/>
+      <c r="G121" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5374EDB-ECDE-4844-85B3-C8350DE6BBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{D5374EDB-ECDE-4844-85B3-C8350DE6BBF9}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="FIEL" sheetId="1" r:id="rId1"/>
-    <sheet name="P3" sheetId="2" r:id="rId2"/>
+    <sheet name="FIEL" r:id="rId1" sheetId="1"/>
+    <sheet name="P3" r:id="rId2" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FIEL!$A$1:$O$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">FIEL!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5157" uniqueCount="19">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -78,11 +78,21 @@
   <si>
     <t>B</t>
   </si>
+  <si>
+    <t>Alerte: Liberação não efetuada!</t>
+  </si>
+  <si>
+    <t> Nível de autorização insuficiente para desbloqueio</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -147,42 +157,42 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{9A64B6ED-0441-41B2-A6F4-AEA4AC2561AE}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -199,10 +209,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -237,7 +247,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -289,7 +299,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -400,21 +410,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -431,7 +441,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -483,36 +493,36 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O967"/>
+  <dimension ref="A1:P967"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="23.42578125" style="5" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="35.85546875" style="5" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.5703125" style="5" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="21.28515625" style="5" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="48.42578125" style="8" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="32.28515625" style="8" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="24.28515625" style="5" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.42578125" style="5" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="17.85546875" style="5" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="16.7109375" style="5" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="19" style="5" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="41.42578125" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="56" style="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="28.42578125" style="1" customWidth="1" collapsed="1"/>
-    <col min="16" max="16384" width="9.140625" style="5" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="13.7109375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="5" width="23.42578125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="35.85546875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="5" width="24.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="5" width="21.28515625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="8" width="48.42578125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="8" width="32.28515625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="5" width="24.28515625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="5" width="18.42578125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="5" width="17.85546875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="5" width="16.7109375" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="5" width="19.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="41.42578125" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="1" width="56.0" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="1" width="28.42578125" collapsed="true"/>
+    <col min="16" max="16384" style="5" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -570,10 +580,14 @@
       <c r="L2" s="5">
         <v>61</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
+      <c r="M2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O2" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -584,10 +598,14 @@
       <c r="L3" s="5">
         <v>61</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O3" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -598,10 +616,14 @@
       <c r="L4" s="5">
         <v>61</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
+      <c r="M4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O4" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -612,10 +634,14 @@
       <c r="L5" s="5">
         <v>61</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
+      <c r="M5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O5" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -626,10 +652,14 @@
       <c r="L6" s="5">
         <v>61</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O6" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -640,10 +670,14 @@
       <c r="L7" s="5">
         <v>61</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
+      <c r="M7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O7" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -654,10 +688,14 @@
       <c r="L8" s="5">
         <v>61</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
+      <c r="M8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O8" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -668,10 +706,14 @@
       <c r="L9" s="5">
         <v>61</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
+      <c r="M9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O9" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -682,10 +724,14 @@
       <c r="L10" s="5">
         <v>61</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
+      <c r="M10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O10" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -696,10 +742,14 @@
       <c r="L11" s="5">
         <v>61</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
+      <c r="M11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O11" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -710,10 +760,14 @@
       <c r="L12" s="5">
         <v>61</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
+      <c r="M12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O12" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -724,10 +778,14 @@
       <c r="L13" s="5">
         <v>61</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
+      <c r="M13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O13" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -738,10 +796,14 @@
       <c r="L14" s="5">
         <v>61</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
+      <c r="M14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O14" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -752,10 +814,14 @@
       <c r="L15" s="5">
         <v>61</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
+      <c r="M15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O15" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -766,10 +832,14 @@
       <c r="L16" s="5">
         <v>61</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
+      <c r="M16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O16" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -780,10 +850,14 @@
       <c r="L17" s="5">
         <v>61</v>
       </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
+      <c r="M17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O17" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -794,10 +868,14 @@
       <c r="L18" s="5">
         <v>61</v>
       </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
+      <c r="M18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O18" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -808,10 +886,14 @@
       <c r="L19" s="5">
         <v>61</v>
       </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
+      <c r="M19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O19" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -822,10 +904,14 @@
       <c r="L20" s="5">
         <v>61</v>
       </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
+      <c r="M20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O20" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -836,10 +922,14 @@
       <c r="L21" s="5">
         <v>61</v>
       </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
+      <c r="M21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O21" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -850,10 +940,14 @@
       <c r="L22" s="5">
         <v>61</v>
       </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
+      <c r="M22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O22" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -864,10 +958,14 @@
       <c r="L23" s="5">
         <v>61</v>
       </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
+      <c r="M23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O23" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -878,10 +976,14 @@
       <c r="L24" s="5">
         <v>61</v>
       </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
+      <c r="M24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O24" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -892,10 +994,14 @@
       <c r="L25" s="5">
         <v>61</v>
       </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
+      <c r="M25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O25" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -906,10 +1012,14 @@
       <c r="L26" s="5">
         <v>61</v>
       </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
+      <c r="M26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O26" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -920,10 +1030,14 @@
       <c r="L27" s="5">
         <v>61</v>
       </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
+      <c r="M27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O27" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,10 +1048,14 @@
       <c r="L28" s="5">
         <v>61</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
+      <c r="M28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O28" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -948,10 +1066,14 @@
       <c r="L29" s="5">
         <v>61</v>
       </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
+      <c r="M29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O29" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -962,10 +1084,14 @@
       <c r="L30" s="5">
         <v>61</v>
       </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
+      <c r="M30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O30" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -976,10 +1102,14 @@
       <c r="L31" s="5">
         <v>61</v>
       </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
+      <c r="M31" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O31" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -990,10 +1120,14 @@
       <c r="L32" s="5">
         <v>61</v>
       </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
+      <c r="M32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O32" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -1004,10 +1138,14 @@
       <c r="L33" s="5">
         <v>61</v>
       </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
+      <c r="M33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O33" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -1018,10 +1156,14 @@
       <c r="L34" s="5">
         <v>61</v>
       </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
+      <c r="M34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O34" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -1032,10 +1174,14 @@
       <c r="L35" s="5">
         <v>61</v>
       </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
+      <c r="M35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O35" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -1046,10 +1192,14 @@
       <c r="L36" s="5">
         <v>61</v>
       </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
+      <c r="M36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O36" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -1060,10 +1210,14 @@
       <c r="L37" s="5">
         <v>61</v>
       </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
+      <c r="M37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O37" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -1074,10 +1228,14 @@
       <c r="L38" s="5">
         <v>61</v>
       </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
+      <c r="M38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O38" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -1088,10 +1246,14 @@
       <c r="L39" s="5">
         <v>61</v>
       </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
+      <c r="M39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O39" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -1102,10 +1264,14 @@
       <c r="L40" s="5">
         <v>61</v>
       </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
+      <c r="M40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O40" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -1116,10 +1282,14 @@
       <c r="L41" s="5">
         <v>61</v>
       </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
+      <c r="M41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O41" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -1130,10 +1300,14 @@
       <c r="L42" s="5">
         <v>61</v>
       </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
+      <c r="M42" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O42" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -1144,10 +1318,14 @@
       <c r="L43" s="5">
         <v>61</v>
       </c>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
+      <c r="M43" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O43" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -1158,10 +1336,14 @@
       <c r="L44" s="5">
         <v>61</v>
       </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
+      <c r="M44" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O44" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -1172,10 +1354,14 @@
       <c r="L45" s="5">
         <v>61</v>
       </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
+      <c r="M45" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O45" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -1186,10 +1372,14 @@
       <c r="L46" s="5">
         <v>61</v>
       </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
+      <c r="M46" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O46" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -1200,10 +1390,14 @@
       <c r="L47" s="5">
         <v>61</v>
       </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
+      <c r="M47" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N47" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O47" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -1214,10 +1408,14 @@
       <c r="L48" s="5">
         <v>61</v>
       </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
+      <c r="M48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N48" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O48" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -1228,10 +1426,14 @@
       <c r="L49" s="5">
         <v>61</v>
       </c>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
+      <c r="M49" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O49" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -1242,10 +1444,14 @@
       <c r="L50" s="5">
         <v>61</v>
       </c>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
+      <c r="M50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N50" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O50" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -1256,10 +1462,14 @@
       <c r="L51" s="5">
         <v>61</v>
       </c>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
+      <c r="M51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O51" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -1270,10 +1480,14 @@
       <c r="L52" s="5">
         <v>61</v>
       </c>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
+      <c r="M52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O52" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -1284,10 +1498,14 @@
       <c r="L53" s="5">
         <v>61</v>
       </c>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
+      <c r="M53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O53" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -1298,10 +1516,14 @@
       <c r="L54" s="5">
         <v>61</v>
       </c>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
+      <c r="M54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N54" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O54" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -1312,10 +1534,14 @@
       <c r="L55" s="5">
         <v>61</v>
       </c>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
+      <c r="M55" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N55" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O55" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -1326,10 +1552,14 @@
       <c r="L56" s="5">
         <v>61</v>
       </c>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
+      <c r="M56" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N56" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O56" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -1340,10 +1570,14 @@
       <c r="L57" s="5">
         <v>61</v>
       </c>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
+      <c r="M57" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O57" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
@@ -1354,10 +1588,14 @@
       <c r="L58" s="5">
         <v>61</v>
       </c>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5"/>
+      <c r="M58" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N58" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O58" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -1368,10 +1606,14 @@
       <c r="L59" s="5">
         <v>61</v>
       </c>
-      <c r="M59" s="5"/>
-      <c r="N59" s="5"/>
+      <c r="M59" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N59" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O59" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -1382,10 +1624,14 @@
       <c r="L60" s="5">
         <v>61</v>
       </c>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
+      <c r="M60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N60" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O60" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -1396,10 +1642,14 @@
       <c r="L61" s="5">
         <v>61</v>
       </c>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
+      <c r="M61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O61" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -1410,10 +1660,14 @@
       <c r="L62" s="5">
         <v>61</v>
       </c>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
+      <c r="M62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O62" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -1424,2050 +1678,3074 @@
       <c r="L63" s="5">
         <v>61</v>
       </c>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
+      <c r="M63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N63" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O63" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
+      <c r="M64" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N64" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O64" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
+      <c r="M65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N65" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O65" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
+      <c r="M66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N66" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O66" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
+      <c r="M67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N67" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O67" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
+      <c r="M68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N68" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O68" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
+      <c r="M69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N69" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O69" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
+      <c r="M70" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N70" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O70" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
+      <c r="M71" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O71" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
+      <c r="M72" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N72" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O72" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
+      <c r="M73" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N73" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O73" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
+      <c r="M74" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N74" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O74" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
+      <c r="M75" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N75" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O75" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
+      <c r="M76" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N76" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O76" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
+      <c r="M77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N77" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O77" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
-      <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
+      <c r="M78" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N78" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O78" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
-      <c r="M79" s="5"/>
-      <c r="N79" s="5"/>
+      <c r="M79" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N79" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O79" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
-      <c r="M80" s="5"/>
-      <c r="N80" s="5"/>
+      <c r="M80" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N80" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O80" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
+      <c r="M81" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N81" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O81" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
+      <c r="M82" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N82" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O82" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
-      <c r="M83" s="5"/>
-      <c r="N83" s="5"/>
+      <c r="M83" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N83" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O83" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
+      <c r="M84" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N84" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O84" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
-      <c r="M85" s="5"/>
-      <c r="N85" s="5"/>
+      <c r="M85" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N85" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O85" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
+      <c r="M86" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N86" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O86" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
+      <c r="M87" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N87" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O87" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
+      <c r="M88" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N88" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O88" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
+      <c r="M89" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N89" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O89" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
+      <c r="M90" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N90" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O90" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
+      <c r="M91" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N91" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O91" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
+      <c r="M92" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N92" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O92" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
+      <c r="M93" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N93" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O93" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
-      <c r="M94" s="5"/>
-      <c r="N94" s="5"/>
+      <c r="M94" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N94" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O94" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
-      <c r="M95" s="5"/>
-      <c r="N95" s="5"/>
+      <c r="M95" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N95" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O95" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
-      <c r="M96" s="5"/>
-      <c r="N96" s="5"/>
+      <c r="M96" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N96" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O96" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
-      <c r="M97" s="5"/>
-      <c r="N97" s="5"/>
+      <c r="M97" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N97" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O97" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
+      <c r="M98" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N98" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O98" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
+      <c r="M99" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N99" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O99" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
+      <c r="M100" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N100" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O100" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
-      <c r="M101" s="5"/>
-      <c r="N101" s="5"/>
+      <c r="M101" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O101" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="5"/>
+      <c r="M102" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N102" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O102" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5"/>
+      <c r="M103" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N103" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O103" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
+      <c r="M104" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N104" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O104" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
+      <c r="M105" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N105" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O105" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
+      <c r="M106" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N106" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O106" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5"/>
+      <c r="M107" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N107" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O107" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5"/>
+      <c r="M108" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N108" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O108" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="5"/>
+      <c r="M109" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N109" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O109" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5"/>
+      <c r="M110" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N110" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O110" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
-      <c r="M111" s="5"/>
-      <c r="N111" s="5"/>
+      <c r="M111" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N111" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O111" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5"/>
+      <c r="M112" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N112" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O112" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5"/>
+      <c r="M113" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N113" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O113" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5"/>
+      <c r="M114" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N114" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O114" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5"/>
+      <c r="M115" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N115" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O115" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5"/>
+      <c r="M116" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N116" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O116" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
+      <c r="M117" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N117" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O117" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5"/>
+      <c r="M118" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N118" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O118" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5"/>
+      <c r="M119" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N119" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O119" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5"/>
+      <c r="M120" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N120" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O120" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5"/>
+      <c r="M121" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N121" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O121" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
-      <c r="M122" s="5"/>
-      <c r="N122" s="5"/>
+      <c r="M122" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N122" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O122" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
-      <c r="M123" s="5"/>
-      <c r="N123" s="5"/>
+      <c r="M123" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N123" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O123" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
-      <c r="M124" s="5"/>
-      <c r="N124" s="5"/>
+      <c r="M124" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N124" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O124" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
-      <c r="M125" s="5"/>
-      <c r="N125" s="5"/>
+      <c r="M125" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N125" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O125" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="5"/>
+      <c r="M126" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N126" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O126" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
-      <c r="M127" s="5"/>
-      <c r="N127" s="5"/>
+      <c r="M127" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N127" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O127" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
-      <c r="M128" s="5"/>
-      <c r="N128" s="5"/>
+      <c r="M128" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N128" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O128" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
-      <c r="M129" s="5"/>
-      <c r="N129" s="5"/>
+      <c r="M129" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N129" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O129" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
-      <c r="M130" s="5"/>
-      <c r="N130" s="5"/>
+      <c r="M130" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N130" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O130" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
-      <c r="M131" s="5"/>
-      <c r="N131" s="5"/>
+      <c r="M131" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N131" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O131" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
-      <c r="M132" s="5"/>
-      <c r="N132" s="5"/>
+      <c r="M132" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N132" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O132" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
-      <c r="M133" s="5"/>
-      <c r="N133" s="5"/>
+      <c r="M133" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N133" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O133" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
-      <c r="M134" s="5"/>
-      <c r="N134" s="5"/>
+      <c r="M134" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N134" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O134" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
-      <c r="M135" s="5"/>
-      <c r="N135" s="5"/>
+      <c r="M135" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N135" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O135" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="5"/>
+      <c r="M136" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N136" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O136" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
-      <c r="M137" s="5"/>
-      <c r="N137" s="5"/>
+      <c r="M137" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N137" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O137" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
-      <c r="M138" s="5"/>
-      <c r="N138" s="5"/>
+      <c r="M138" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N138" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O138" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
-      <c r="M139" s="5"/>
-      <c r="N139" s="5"/>
+      <c r="M139" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N139" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O139" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
-      <c r="M140" s="5"/>
-      <c r="N140" s="5"/>
+      <c r="M140" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N140" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O140" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="5"/>
+      <c r="M141" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N141" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O141" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
-      <c r="M142" s="5"/>
-      <c r="N142" s="5"/>
+      <c r="M142" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N142" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O142" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
-      <c r="M143" s="5"/>
-      <c r="N143" s="5"/>
+      <c r="M143" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N143" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O143" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
-      <c r="M144" s="5"/>
-      <c r="N144" s="5"/>
+      <c r="M144" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N144" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O144" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
-      <c r="M145" s="5"/>
-      <c r="N145" s="5"/>
+      <c r="M145" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N145" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O145" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
-      <c r="M146" s="5"/>
-      <c r="N146" s="5"/>
+      <c r="M146" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N146" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O146" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
-      <c r="M147" s="5"/>
-      <c r="N147" s="5"/>
+      <c r="M147" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N147" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O147" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="5"/>
+      <c r="M148" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N148" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O148" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
-      <c r="M149" s="5"/>
-      <c r="N149" s="5"/>
+      <c r="M149" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N149" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O149" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
-      <c r="M150" s="5"/>
-      <c r="N150" s="5"/>
+      <c r="M150" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N150" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O150" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="5"/>
+      <c r="M151" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N151" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O151" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
-      <c r="M152" s="5"/>
-      <c r="N152" s="5"/>
+      <c r="M152" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N152" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O152" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
-      <c r="M153" s="5"/>
-      <c r="N153" s="5"/>
+      <c r="M153" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N153" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O153" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
-      <c r="M154" s="5"/>
-      <c r="N154" s="5"/>
+      <c r="M154" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N154" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O154" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
-      <c r="M155" s="5"/>
-      <c r="N155" s="5"/>
+      <c r="M155" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N155" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O155" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
-      <c r="M156" s="5"/>
-      <c r="N156" s="5"/>
+      <c r="M156" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N156" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O156" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="5"/>
+      <c r="M157" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N157" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O157" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="5"/>
+      <c r="M158" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N158" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O158" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="5"/>
+      <c r="M159" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N159" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O159" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
-      <c r="M160" s="5"/>
-      <c r="N160" s="5"/>
+      <c r="M160" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N160" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O160" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="5"/>
+      <c r="M161" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N161" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O161" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="5"/>
+      <c r="M162" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N162" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O162" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
-      <c r="M163" s="5"/>
-      <c r="N163" s="5"/>
+      <c r="M163" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N163" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O163" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
-      <c r="M164" s="5"/>
-      <c r="N164" s="5"/>
+      <c r="M164" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N164" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O164" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="5"/>
+      <c r="M165" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N165" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O165" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
-      <c r="M166" s="5"/>
-      <c r="N166" s="5"/>
+      <c r="M166" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N166" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O166" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
-      <c r="M167" s="5"/>
-      <c r="N167" s="5"/>
+      <c r="M167" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N167" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O167" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
-      <c r="M168" s="5"/>
-      <c r="N168" s="5"/>
+      <c r="M168" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N168" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O168" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
-      <c r="M169" s="5"/>
-      <c r="N169" s="5"/>
+      <c r="M169" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N169" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O169" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
-      <c r="M170" s="5"/>
-      <c r="N170" s="5"/>
+      <c r="M170" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N170" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O170" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
-      <c r="M171" s="5"/>
-      <c r="N171" s="5"/>
+      <c r="M171" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N171" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O171" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="5"/>
+      <c r="M172" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N172" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O172" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
-      <c r="M173" s="5"/>
-      <c r="N173" s="5"/>
+      <c r="M173" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N173" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O173" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
-      <c r="M174" s="5"/>
-      <c r="N174" s="5"/>
+      <c r="M174" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N174" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O174" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="5"/>
+      <c r="M175" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N175" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O175" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
-      <c r="M176" s="5"/>
-      <c r="N176" s="5"/>
+      <c r="M176" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N176" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O176" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
-      <c r="M177" s="5"/>
-      <c r="N177" s="5"/>
+      <c r="M177" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N177" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O177" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
-      <c r="M178" s="5"/>
-      <c r="N178" s="5"/>
+      <c r="M178" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N178" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O178" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
-      <c r="M179" s="5"/>
-      <c r="N179" s="5"/>
+      <c r="M179" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N179" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O179" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="5"/>
+      <c r="M180" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N180" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O180" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="5"/>
+      <c r="M181" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N181" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O181" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
-      <c r="M182" s="5"/>
-      <c r="N182" s="5"/>
+      <c r="M182" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N182" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O182" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
-      <c r="M183" s="5"/>
-      <c r="N183" s="5"/>
+      <c r="M183" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N183" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O183" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
-      <c r="M184" s="5"/>
-      <c r="N184" s="5"/>
+      <c r="M184" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N184" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O184" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
-      <c r="M185" s="5"/>
-      <c r="N185" s="5"/>
+      <c r="M185" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N185" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O185" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
-      <c r="M186" s="5"/>
-      <c r="N186" s="5"/>
+      <c r="M186" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N186" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O186" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="5"/>
+      <c r="M187" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N187" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O187" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
-      <c r="M188" s="5"/>
-      <c r="N188" s="5"/>
+      <c r="M188" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N188" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O188" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="5"/>
+      <c r="M189" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N189" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O189" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="5"/>
+      <c r="M190" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N190" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O190" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
-      <c r="M191" s="5"/>
-      <c r="N191" s="5"/>
+      <c r="M191" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N191" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O191" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
-      <c r="M192" s="5"/>
-      <c r="N192" s="5"/>
+      <c r="M192" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N192" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O192" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
-      <c r="M193" s="5"/>
-      <c r="N193" s="5"/>
+      <c r="M193" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N193" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O193" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
-      <c r="M194" s="5"/>
-      <c r="N194" s="5"/>
+      <c r="M194" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N194" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O194" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="5"/>
+      <c r="M195" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N195" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O195" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
-      <c r="M196" s="5"/>
-      <c r="N196" s="5"/>
+      <c r="M196" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N196" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O196" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
-      <c r="M197" s="5"/>
-      <c r="N197" s="5"/>
+      <c r="M197" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N197" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O197" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
-      <c r="M198" s="5"/>
-      <c r="N198" s="5"/>
+      <c r="M198" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N198" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O198" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="5"/>
+      <c r="M199" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N199" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O199" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="5"/>
+      <c r="M200" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N200" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O200" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
-      <c r="M201" s="5"/>
-      <c r="N201" s="5"/>
+      <c r="M201" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N201" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O201" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
-      <c r="M202" s="5"/>
-      <c r="N202" s="5"/>
+      <c r="M202" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N202" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O202" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="5"/>
-      <c r="M203" s="5"/>
-      <c r="N203" s="5"/>
+      <c r="M203" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N203" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O203" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="5"/>
-      <c r="M204" s="5"/>
-      <c r="N204" s="5"/>
+      <c r="M204" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N204" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O204" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="5"/>
-      <c r="M205" s="5"/>
-      <c r="N205" s="5"/>
+      <c r="M205" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N205" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O205" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="5"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="5"/>
+      <c r="M206" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N206" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O206" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="5"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="5"/>
+      <c r="M207" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N207" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O207" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" s="5"/>
-      <c r="M208" s="5"/>
-      <c r="N208" s="5"/>
+      <c r="M208" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N208" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O208" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="5"/>
-      <c r="M209" s="5"/>
-      <c r="N209" s="5"/>
+      <c r="M209" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N209" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O209" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="5"/>
-      <c r="M210" s="5"/>
-      <c r="N210" s="5"/>
+      <c r="M210" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N210" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O210" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="5"/>
-      <c r="M211" s="5"/>
-      <c r="N211" s="5"/>
+      <c r="M211" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N211" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O211" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" s="5"/>
-      <c r="M212" s="5"/>
-      <c r="N212" s="5"/>
+      <c r="M212" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N212" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O212" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" s="5"/>
-      <c r="M213" s="5"/>
-      <c r="N213" s="5"/>
+      <c r="M213" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N213" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O213" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="5"/>
-      <c r="M214" s="5"/>
-      <c r="N214" s="5"/>
+      <c r="M214" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N214" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O214" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="5"/>
-      <c r="M215" s="5"/>
-      <c r="N215" s="5"/>
+      <c r="M215" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N215" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O215" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="5"/>
-      <c r="M216" s="5"/>
-      <c r="N216" s="5"/>
+      <c r="M216" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N216" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O216" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" s="5"/>
-      <c r="M217" s="5"/>
-      <c r="N217" s="5"/>
+      <c r="M217" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N217" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O217" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" s="5"/>
-      <c r="M218" s="5"/>
-      <c r="N218" s="5"/>
+      <c r="M218" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N218" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O218" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="5"/>
-      <c r="M219" s="5"/>
-      <c r="N219" s="5"/>
+      <c r="M219" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N219" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O219" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="5"/>
-      <c r="M220" s="5"/>
-      <c r="N220" s="5"/>
+      <c r="M220" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N220" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O220" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="5"/>
-      <c r="M221" s="5"/>
-      <c r="N221" s="5"/>
+      <c r="M221" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N221" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O221" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="5"/>
-      <c r="M222" s="5"/>
-      <c r="N222" s="5"/>
+      <c r="M222" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N222" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O222" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="5"/>
-      <c r="M223" s="5"/>
-      <c r="N223" s="5"/>
+      <c r="M223" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N223" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O223" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="5"/>
-      <c r="M224" s="5"/>
-      <c r="N224" s="5"/>
+      <c r="M224" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N224" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O224" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="5"/>
-      <c r="M225" s="5"/>
-      <c r="N225" s="5"/>
+      <c r="M225" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N225" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O225" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="5"/>
-      <c r="M226" s="5"/>
-      <c r="N226" s="5"/>
+      <c r="M226" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N226" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O226" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="5"/>
-      <c r="M227" s="5"/>
-      <c r="N227" s="5"/>
+      <c r="M227" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N227" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O227" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" s="5"/>
-      <c r="M228" s="5"/>
-      <c r="N228" s="5"/>
+      <c r="M228" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N228" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O228" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" s="5"/>
-      <c r="M229" s="5"/>
-      <c r="N229" s="5"/>
+      <c r="M229" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N229" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O229" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" s="5"/>
-      <c r="M230" s="5"/>
-      <c r="N230" s="5"/>
+      <c r="M230" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N230" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O230" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" s="5"/>
-      <c r="M231" s="5"/>
-      <c r="N231" s="5"/>
+      <c r="M231" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N231" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O231" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" s="5"/>
-      <c r="M232" s="5"/>
-      <c r="N232" s="5"/>
+      <c r="M232" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N232" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O232" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="5"/>
-      <c r="M233" s="5"/>
-      <c r="N233" s="5"/>
+      <c r="M233" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N233" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O233" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="5"/>
-      <c r="M234" s="5"/>
-      <c r="N234" s="5"/>
+      <c r="M234" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N234" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O234" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="5"/>
-      <c r="M235" s="5"/>
-      <c r="N235" s="5"/>
+      <c r="M235" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N235" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O235" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="5"/>
-      <c r="M236" s="5"/>
-      <c r="N236" s="5"/>
+      <c r="M236" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N236" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O236" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="5"/>
-      <c r="M237" s="5"/>
-      <c r="N237" s="5"/>
+      <c r="M237" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N237" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O237" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="5"/>
-      <c r="M238" s="5"/>
-      <c r="N238" s="5"/>
+      <c r="M238" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N238" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O238" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="5"/>
-      <c r="M239" s="5"/>
-      <c r="N239" s="5"/>
+      <c r="M239" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N239" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O239" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="5"/>
-      <c r="M240" s="5"/>
-      <c r="N240" s="5"/>
+      <c r="M240" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N240" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O240" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="5"/>
-      <c r="M241" s="5"/>
-      <c r="N241" s="5"/>
+      <c r="M241" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N241" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O241" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="5"/>
-      <c r="M242" s="5"/>
-      <c r="N242" s="5"/>
+      <c r="M242" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N242" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O242" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="5"/>
-      <c r="M243" s="5"/>
-      <c r="N243" s="5"/>
+      <c r="M243" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N243" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O243" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="5"/>
-      <c r="M244" s="5"/>
-      <c r="N244" s="5"/>
+      <c r="M244" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N244" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O244" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="5"/>
-      <c r="M245" s="5"/>
-      <c r="N245" s="5"/>
+      <c r="M245" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N245" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O245" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="5"/>
-      <c r="M246" s="5"/>
-      <c r="N246" s="5"/>
+      <c r="M246" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N246" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O246" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="5"/>
-      <c r="M247" s="5"/>
-      <c r="N247" s="5"/>
+      <c r="M247" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N247" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O247" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="5"/>
-      <c r="M248" s="5"/>
-      <c r="N248" s="5"/>
+      <c r="M248" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N248" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O248" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="5"/>
-      <c r="M249" s="5"/>
-      <c r="N249" s="5"/>
+      <c r="M249" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N249" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O249" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="5"/>
-      <c r="M250" s="5"/>
-      <c r="N250" s="5"/>
+      <c r="M250" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N250" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O250" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="5"/>
-      <c r="M251" s="5"/>
-      <c r="N251" s="5"/>
+      <c r="M251" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N251" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O251" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="5"/>
-      <c r="M252" s="5"/>
-      <c r="N252" s="5"/>
+      <c r="M252" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N252" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O252" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="5"/>
-      <c r="M253" s="5"/>
-      <c r="N253" s="5"/>
+      <c r="M253" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N253" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O253" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="5"/>
-      <c r="M254" s="5"/>
-      <c r="N254" s="5"/>
+      <c r="M254" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N254" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O254" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="5"/>
-      <c r="M255" s="5"/>
-      <c r="N255" s="5"/>
+      <c r="M255" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N255" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O255" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256" s="5"/>
-      <c r="M256" s="5"/>
-      <c r="N256" s="5"/>
+      <c r="M256" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N256" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O256" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257" s="5"/>
-      <c r="M257" s="5"/>
-      <c r="N257" s="5"/>
+      <c r="M257" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N257" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O257" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258" s="5"/>
-      <c r="M258" s="5"/>
-      <c r="N258" s="5"/>
+      <c r="M258" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N258" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O258" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259" s="5"/>
-      <c r="M259" s="5"/>
-      <c r="N259" s="5"/>
+      <c r="M259" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N259" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O259" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260" s="5"/>
-      <c r="M260" s="5"/>
-      <c r="N260" s="5"/>
+      <c r="M260" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N260" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O260" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261" s="5"/>
-      <c r="M261" s="5"/>
-      <c r="N261" s="5"/>
+      <c r="M261" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N261" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O261" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262" s="5"/>
-      <c r="M262" s="5"/>
-      <c r="N262" s="5"/>
+      <c r="M262" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N262" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O262" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263" s="5"/>
-      <c r="M263" s="5"/>
-      <c r="N263" s="5"/>
+      <c r="M263" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N263" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O263" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264" s="5"/>
-      <c r="M264" s="5"/>
-      <c r="N264" s="5"/>
+      <c r="M264" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N264" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O264" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" s="5"/>
-      <c r="M265" s="5"/>
-      <c r="N265" s="5"/>
+      <c r="M265" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N265" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O265" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" s="5"/>
-      <c r="M266" s="5"/>
-      <c r="N266" s="5"/>
+      <c r="M266" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N266" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O266" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" s="5"/>
-      <c r="M267" s="5"/>
-      <c r="N267" s="5"/>
+      <c r="M267" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N267" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O267" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268" s="5"/>
-      <c r="M268" s="5"/>
-      <c r="N268" s="5"/>
+      <c r="M268" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N268" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O268" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" s="5"/>
-      <c r="M269" s="5"/>
-      <c r="N269" s="5"/>
+      <c r="M269" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N269" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O269" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" s="5"/>
-      <c r="M270" s="5"/>
-      <c r="N270" s="5"/>
+      <c r="M270" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N270" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O270" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" s="5"/>
-      <c r="M271" s="5"/>
-      <c r="N271" s="5"/>
+      <c r="M271" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N271" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O271" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" s="5"/>
-      <c r="M272" s="5"/>
-      <c r="N272" s="5"/>
+      <c r="M272" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N272" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O272" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" s="5"/>
-      <c r="M273" s="5"/>
-      <c r="N273" s="5"/>
+      <c r="M273" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N273" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O273" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" s="5"/>
-      <c r="M274" s="5"/>
-      <c r="N274" s="5"/>
+      <c r="M274" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N274" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O274" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" s="5"/>
-      <c r="M275" s="5"/>
-      <c r="N275" s="5"/>
+      <c r="M275" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N275" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O275" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="5"/>
-      <c r="M276" s="5"/>
-      <c r="N276" s="5"/>
+      <c r="M276" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N276" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O276" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" s="5"/>
-      <c r="M277" s="5"/>
-      <c r="N277" s="5"/>
+      <c r="M277" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N277" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O277" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" s="5"/>
-      <c r="M278" s="5"/>
-      <c r="N278" s="5"/>
+      <c r="M278" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N278" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O278" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" s="5"/>
-      <c r="M279" s="5"/>
-      <c r="N279" s="5"/>
+      <c r="M279" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N279" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O279" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" s="5"/>
-      <c r="M280" s="5"/>
-      <c r="N280" s="5"/>
+      <c r="M280" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N280" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O280" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" s="5"/>
-      <c r="M281" s="5"/>
-      <c r="N281" s="5"/>
+      <c r="M281" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N281" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O281" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" s="5"/>
-      <c r="M282" s="5"/>
-      <c r="N282" s="5"/>
+      <c r="M282" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N282" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O282" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="5"/>
-      <c r="M283" s="5"/>
-      <c r="N283" s="5"/>
+      <c r="M283" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N283" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O283" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" s="5"/>
-      <c r="M284" s="5"/>
-      <c r="N284" s="5"/>
+      <c r="M284" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N284" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O284" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" s="5"/>
-      <c r="M285" s="5"/>
-      <c r="N285" s="5"/>
+      <c r="M285" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N285" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O285" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" s="5"/>
-      <c r="M286" s="5"/>
-      <c r="N286" s="5"/>
+      <c r="M286" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N286" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O286" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" s="5"/>
-      <c r="M287" s="5"/>
-      <c r="N287" s="5"/>
+      <c r="M287" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N287" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O287" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" s="5"/>
-      <c r="M288" s="5"/>
-      <c r="N288" s="5"/>
+      <c r="M288" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N288" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O288" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" s="5"/>
-      <c r="M289" s="5"/>
-      <c r="N289" s="5"/>
+      <c r="M289" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N289" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O289" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" s="5"/>
-      <c r="M290" s="5"/>
-      <c r="N290" s="5"/>
+      <c r="M290" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N290" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O290" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" s="5"/>
-      <c r="M291" s="5"/>
-      <c r="N291" s="5"/>
+      <c r="M291" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N291" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O291" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" s="5"/>
-      <c r="M292" s="5"/>
-      <c r="N292" s="5"/>
+      <c r="M292" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N292" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O292" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" s="5"/>
-      <c r="M293" s="5"/>
-      <c r="N293" s="5"/>
+      <c r="M293" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N293" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O293" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" s="5"/>
-      <c r="M294" s="5"/>
-      <c r="N294" s="5"/>
+      <c r="M294" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N294" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O294" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" s="5"/>
-      <c r="M295" s="5"/>
-      <c r="N295" s="5"/>
+      <c r="M295" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N295" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O295" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" s="5"/>
-      <c r="M296" s="5"/>
-      <c r="N296" s="5"/>
+      <c r="M296" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N296" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O296" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" s="5"/>
-      <c r="M297" s="5"/>
-      <c r="N297" s="5"/>
+      <c r="M297" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N297" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O297" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" s="5"/>
-      <c r="M298" s="5"/>
-      <c r="N298" s="5"/>
+      <c r="M298" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N298" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O298" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" s="5"/>
-      <c r="M299" s="5"/>
-      <c r="N299" s="5"/>
+      <c r="M299" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N299" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O299" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" s="5"/>
-      <c r="M300" s="5"/>
-      <c r="N300" s="5"/>
+      <c r="M300" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N300" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O300" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" s="5"/>
-      <c r="M301" s="5"/>
-      <c r="N301" s="5"/>
+      <c r="M301" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N301" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O301" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="5"/>
-      <c r="M302" s="5"/>
-      <c r="N302" s="5"/>
+      <c r="M302" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N302" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O302" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="5"/>
-      <c r="M303" s="5"/>
-      <c r="N303" s="5"/>
+      <c r="M303" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N303" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O303" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="5"/>
-      <c r="M304" s="5"/>
-      <c r="N304" s="5"/>
+      <c r="M304" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N304" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O304" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" s="5"/>
-      <c r="M305" s="5"/>
-      <c r="N305" s="5"/>
+      <c r="M305" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N305" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O305" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" s="5"/>
-      <c r="M306" s="5"/>
-      <c r="N306" s="5"/>
+      <c r="M306" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N306" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O306" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="5"/>
-      <c r="M307" s="5"/>
-      <c r="N307" s="5"/>
+      <c r="M307" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N307" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O307" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308" s="5"/>
-      <c r="M308" s="5"/>
-      <c r="N308" s="5"/>
+      <c r="M308" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N308" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O308" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309" s="5"/>
-      <c r="M309" s="5"/>
-      <c r="N309" s="5"/>
+      <c r="M309" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N309" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O309" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310" s="5"/>
-      <c r="M310" s="5"/>
-      <c r="N310" s="5"/>
+      <c r="M310" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N310" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O310" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A311" s="5"/>
-      <c r="M311" s="5"/>
-      <c r="N311" s="5"/>
+      <c r="M311" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N311" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O311" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A312" s="5"/>
-      <c r="M312" s="5"/>
-      <c r="N312" s="5"/>
+      <c r="M312" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N312" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O312" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A313" s="5"/>
-      <c r="M313" s="5"/>
-      <c r="N313" s="5"/>
+      <c r="M313" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N313" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O313" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A314" s="5"/>
-      <c r="M314" s="5"/>
-      <c r="N314" s="5"/>
+      <c r="M314" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N314" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O314" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A315" s="5"/>
-      <c r="M315" s="5"/>
-      <c r="N315" s="5"/>
+      <c r="M315" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N315" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O315" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316" s="5"/>
-      <c r="M316" s="5"/>
-      <c r="N316" s="5"/>
+      <c r="M316" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N316" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O316" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="317" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A317" s="5"/>
-      <c r="M317" s="5"/>
-      <c r="N317" s="5"/>
+      <c r="M317" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N317" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O317" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="318" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A318" s="5"/>
-      <c r="M318" s="5"/>
-      <c r="N318" s="5"/>
+      <c r="M318" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N318" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="O318" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.25">
@@ -8665,22 +9943,22 @@
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0D0BED-8A1E-40E5-9E38-0B4586E94A24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0D0BED-8A1E-40E5-9E38-0B4586E94A24}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
 </worksheet>
 </file>
 

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F023381-08A8-469C-BEC4-91A7946E0289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443D215C-42DF-45FE-ACFD-4F20F9348D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,12 +79,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>5/9/2025</t>
-  </si>
-  <si>
-    <t>6/9/2025</t>
-  </si>
-  <si>
     <t>8/3/2023</t>
   </si>
   <si>
@@ -95,6 +89,12 @@
   </si>
   <si>
     <t>8/9/2025</t>
+  </si>
+  <si>
+    <t>9/9/2025</t>
+  </si>
+  <si>
+    <t>4/9/2025</t>
   </si>
 </sst>
 </file>
@@ -582,7 +582,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>134308020</v>
+        <v>123058958</v>
       </c>
       <c r="E2" s="5">
         <v>1211</v>
@@ -597,7 +597,7 @@
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -613,22 +613,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134317534</v>
+        <v>134276796</v>
       </c>
       <c r="E3" s="5">
         <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -644,13 +644,13 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>123058958</v>
+        <v>134297894</v>
       </c>
       <c r="E4" s="5">
         <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>19</v>
@@ -659,7 +659,7 @@
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -675,10 +675,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134276796</v>
+        <v>134349964</v>
       </c>
       <c r="E5" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>20</v>
@@ -690,7 +690,7 @@
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -706,22 +706,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>129831023</v>
+        <v>134350162</v>
       </c>
       <c r="E6" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>130243614</v>
+        <v>134350551</v>
       </c>
       <c r="E7" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -768,22 +768,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>130706103</v>
+        <v>134350719</v>
       </c>
       <c r="E8" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -799,22 +799,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>130944658</v>
+        <v>134352028</v>
       </c>
       <c r="E9" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -830,22 +830,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>132431451</v>
+        <v>134353103</v>
       </c>
       <c r="E10" s="5">
-        <v>1212</v>
+        <v>2013</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -861,22 +861,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>132848706</v>
+        <v>134353506</v>
       </c>
       <c r="E11" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -892,22 +892,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>132854520</v>
+        <v>134361087</v>
       </c>
       <c r="E12" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -923,22 +923,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>132943676</v>
+        <v>134361169</v>
       </c>
       <c r="E13" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -954,22 +954,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>133175141</v>
+        <v>134361370</v>
       </c>
       <c r="E14" s="5">
-        <v>1212</v>
+        <v>2013</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -985,22 +985,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>133386068</v>
+        <v>134364286</v>
       </c>
       <c r="E15" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1015,717 +1015,98 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>133551992</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="5">
-        <v>42</v>
-      </c>
-      <c r="J16" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K16" s="5">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5">
-        <v>61</v>
-      </c>
+      <c r="A16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
-      <c r="O16" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>134071948</v>
-      </c>
-      <c r="E17" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="5">
-        <v>42</v>
-      </c>
-      <c r="J17" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K17" s="5">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5">
-        <v>61</v>
-      </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>134084838</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="5">
-        <v>42</v>
-      </c>
-      <c r="J18" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K18" s="5">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5">
-        <v>61</v>
-      </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>134252487</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="5">
-        <v>42</v>
-      </c>
-      <c r="J19" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K19" s="5">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5">
-        <v>61</v>
-      </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>134252925</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="5">
-        <v>42</v>
-      </c>
-      <c r="J20" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K20" s="5">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5">
-        <v>61</v>
-      </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>129831023</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="5">
-        <v>42</v>
-      </c>
-      <c r="J21" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K21" s="5">
-        <v>0</v>
-      </c>
-      <c r="L21" s="5">
-        <v>61</v>
-      </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>130243614</v>
-      </c>
-      <c r="E22" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="5">
-        <v>42</v>
-      </c>
-      <c r="J22" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K22" s="5">
-        <v>0</v>
-      </c>
-      <c r="L22" s="5">
-        <v>61</v>
-      </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>130706103</v>
-      </c>
-      <c r="E23" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="5">
-        <v>42</v>
-      </c>
-      <c r="J23" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K23" s="5">
-        <v>0</v>
-      </c>
-      <c r="L23" s="5">
-        <v>61</v>
-      </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>130944658</v>
-      </c>
-      <c r="E24" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="5">
-        <v>42</v>
-      </c>
-      <c r="J24" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K24" s="5">
-        <v>0</v>
-      </c>
-      <c r="L24" s="5">
-        <v>61</v>
-      </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>132854520</v>
-      </c>
-      <c r="E25" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="5">
-        <v>42</v>
-      </c>
-      <c r="J25" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K25" s="5">
-        <v>0</v>
-      </c>
-      <c r="L25" s="5">
-        <v>61</v>
-      </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>133175141</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1212</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="5">
-        <v>42</v>
-      </c>
-      <c r="J26" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K26" s="5">
-        <v>0</v>
-      </c>
-      <c r="L26" s="5">
-        <v>61</v>
-      </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>134252487</v>
-      </c>
-      <c r="E27" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="5">
-        <v>42</v>
-      </c>
-      <c r="J27" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K27" s="5">
-        <v>0</v>
-      </c>
-      <c r="L27" s="5">
-        <v>61</v>
-      </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>134252925</v>
-      </c>
-      <c r="E28" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="5">
-        <v>42</v>
-      </c>
-      <c r="J28" s="5">
-        <v>8001</v>
-      </c>
-      <c r="K28" s="5">
-        <v>0</v>
-      </c>
-      <c r="L28" s="5">
-        <v>61</v>
-      </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>134329306</v>
-      </c>
-      <c r="E29" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="5">
-        <v>42</v>
-      </c>
-      <c r="J29" s="5">
-        <v>718</v>
-      </c>
-      <c r="K29" s="5">
-        <v>0</v>
-      </c>
-      <c r="L29" s="5">
-        <v>61</v>
-      </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
-        <v>134329657</v>
-      </c>
-      <c r="E30" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="5">
-        <v>42</v>
-      </c>
-      <c r="J30" s="5">
-        <v>718</v>
-      </c>
-      <c r="K30" s="5">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5">
-        <v>61</v>
-      </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
-        <v>134329750</v>
-      </c>
-      <c r="E31" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="5">
-        <v>42</v>
-      </c>
-      <c r="J31" s="5">
-        <v>718</v>
-      </c>
-      <c r="K31" s="5">
-        <v>0</v>
-      </c>
-      <c r="L31" s="5">
-        <v>61</v>
-      </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
-        <v>134329965</v>
-      </c>
-      <c r="E32" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="5">
-        <v>42</v>
-      </c>
-      <c r="J32" s="5">
-        <v>718</v>
-      </c>
-      <c r="K32" s="5">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <v>61</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
-        <v>134330822</v>
-      </c>
-      <c r="E33" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="5">
-        <v>42</v>
-      </c>
-      <c r="J33" s="5">
-        <v>718</v>
-      </c>
-      <c r="K33" s="5">
-        <v>0</v>
-      </c>
-      <c r="L33" s="5">
-        <v>61</v>
-      </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>134330855</v>
-      </c>
-      <c r="E34" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="5">
-        <v>42</v>
-      </c>
-      <c r="J34" s="5">
-        <v>718</v>
-      </c>
-      <c r="K34" s="5">
-        <v>0</v>
-      </c>
-      <c r="L34" s="5">
-        <v>61</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>134331284</v>
-      </c>
-      <c r="E35" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="5">
-        <v>42</v>
-      </c>
-      <c r="J35" s="5">
-        <v>718</v>
-      </c>
-      <c r="K35" s="5">
-        <v>0</v>
-      </c>
-      <c r="L35" s="5">
-        <v>61</v>
-      </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
-        <v>134332296</v>
-      </c>
-      <c r="E36" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="5">
-        <v>42</v>
-      </c>
-      <c r="J36" s="5">
-        <v>718</v>
-      </c>
-      <c r="K36" s="5">
-        <v>0</v>
-      </c>
-      <c r="L36" s="5">
-        <v>61</v>
-      </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>134340967</v>
-      </c>
-      <c r="E37" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="5">
-        <v>42</v>
-      </c>
-      <c r="J37" s="5">
-        <v>718</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0</v>
-      </c>
-      <c r="L37" s="5">
-        <v>61</v>
-      </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
-        <v>134342916</v>
-      </c>
-      <c r="E38" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="5">
-        <v>42</v>
-      </c>
-      <c r="J38" s="5">
-        <v>718</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5">
-        <v>61</v>
-      </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+    </row>
+    <row r="27" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+    </row>
+    <row r="28" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+    </row>
+    <row r="29" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+    </row>
+    <row r="30" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+    </row>
+    <row r="33" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+    </row>
+    <row r="34" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+    </row>
+    <row r="36" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+    </row>
+    <row r="38" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1750,31 +1131,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443D215C-42DF-45FE-ACFD-4F20F9348D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B4D0A0-3F4E-4E8D-A80B-8A07A91B6525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="26">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -94,7 +94,19 @@
     <t>9/9/2025</t>
   </si>
   <si>
-    <t>4/9/2025</t>
+    <t>10/9/2025</t>
+  </si>
+  <si>
+    <t>08/09/2025</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
+    <t>09/09/2025</t>
+  </si>
+  <si>
+    <t>06/09/2025</t>
   </si>
 </sst>
 </file>
@@ -512,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -582,22 +594,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>123058958</v>
+        <v>134320387</v>
       </c>
       <c r="E2" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -613,22 +625,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134276796</v>
+        <v>134321032</v>
       </c>
       <c r="E3" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8021</v>
+        <v>1118</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -644,22 +656,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>134297894</v>
+        <v>134329109</v>
       </c>
       <c r="E4" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>19</v>
-      </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>715</v>
+        <v>1118</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -675,22 +687,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134349964</v>
+        <v>134329188</v>
       </c>
       <c r="E5" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -706,22 +718,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134350162</v>
+        <v>134329574</v>
       </c>
       <c r="E6" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -737,22 +749,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134350551</v>
+        <v>134330389</v>
       </c>
       <c r="E7" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>718</v>
+        <v>1118</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -768,22 +780,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134350719</v>
+        <v>134331076</v>
       </c>
       <c r="E8" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>718</v>
+        <v>1118</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -799,22 +811,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134352028</v>
+        <v>134331085</v>
       </c>
       <c r="E9" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -830,22 +842,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134353103</v>
+        <v>134331471</v>
       </c>
       <c r="E10" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -861,22 +873,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>134353506</v>
+        <v>134331892</v>
       </c>
       <c r="E11" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -892,22 +904,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>134361087</v>
+        <v>134332218</v>
       </c>
       <c r="E12" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -923,22 +935,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134361169</v>
+        <v>134333703</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -954,22 +966,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134361370</v>
+        <v>134333740</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>1117</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -985,13 +997,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134364286</v>
+        <v>134334446</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>20</v>
@@ -1000,7 +1012,7 @@
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1015,98 +1027,4342 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="5">
+        <v>134337221</v>
+      </c>
+      <c r="E16" s="5">
+        <v>601</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="5">
+        <v>42</v>
+      </c>
+      <c r="J16" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>61</v>
+      </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-    </row>
-    <row r="32" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-    </row>
-    <row r="33" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-    </row>
-    <row r="34" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-    </row>
-    <row r="35" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-    </row>
-    <row r="36" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-    </row>
-    <row r="37" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-    </row>
-    <row r="38" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="O16" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>134337576</v>
+      </c>
+      <c r="E17" s="5">
+        <v>601</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="5">
+        <v>42</v>
+      </c>
+      <c r="J17" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>61</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>134339600</v>
+      </c>
+      <c r="E18" s="5">
+        <v>601</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="5">
+        <v>42</v>
+      </c>
+      <c r="J18" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>61</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>134339748</v>
+      </c>
+      <c r="E19" s="5">
+        <v>601</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="5">
+        <v>42</v>
+      </c>
+      <c r="J19" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>61</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>134339825</v>
+      </c>
+      <c r="E20" s="5">
+        <v>601</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="5">
+        <v>42</v>
+      </c>
+      <c r="J20" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>61</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>134340027</v>
+      </c>
+      <c r="E21" s="5">
+        <v>601</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="5">
+        <v>42</v>
+      </c>
+      <c r="J21" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <v>61</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>134340153</v>
+      </c>
+      <c r="E22" s="5">
+        <v>601</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="5">
+        <v>42</v>
+      </c>
+      <c r="J22" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>61</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>134340353</v>
+      </c>
+      <c r="E23" s="5">
+        <v>601</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="5">
+        <v>42</v>
+      </c>
+      <c r="J23" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5">
+        <v>61</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>134340527</v>
+      </c>
+      <c r="E24" s="5">
+        <v>601</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="5">
+        <v>42</v>
+      </c>
+      <c r="J24" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>61</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>134340744</v>
+      </c>
+      <c r="E25" s="5">
+        <v>601</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="5">
+        <v>42</v>
+      </c>
+      <c r="J25" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>61</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>134342197</v>
+      </c>
+      <c r="E26" s="5">
+        <v>601</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="5">
+        <v>42</v>
+      </c>
+      <c r="J26" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <v>61</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>134342905</v>
+      </c>
+      <c r="E27" s="5">
+        <v>601</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="5">
+        <v>42</v>
+      </c>
+      <c r="J27" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <v>61</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>134345130</v>
+      </c>
+      <c r="E28" s="5">
+        <v>601</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="5">
+        <v>42</v>
+      </c>
+      <c r="J28" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <v>61</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>134346537</v>
+      </c>
+      <c r="E29" s="5">
+        <v>601</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="5">
+        <v>42</v>
+      </c>
+      <c r="J29" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>61</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>134330782</v>
+      </c>
+      <c r="E30" s="5">
+        <v>601</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="5">
+        <v>42</v>
+      </c>
+      <c r="J30" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <v>61</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>134331451</v>
+      </c>
+      <c r="E31" s="5">
+        <v>601</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="5">
+        <v>42</v>
+      </c>
+      <c r="J31" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>61</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>134332251</v>
+      </c>
+      <c r="E32" s="5">
+        <v>601</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="5">
+        <v>42</v>
+      </c>
+      <c r="J32" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>61</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>134335142</v>
+      </c>
+      <c r="E33" s="5">
+        <v>601</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="5">
+        <v>42</v>
+      </c>
+      <c r="J33" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>61</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>134335608</v>
+      </c>
+      <c r="E34" s="5">
+        <v>601</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="5">
+        <v>42</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>61</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>134336592</v>
+      </c>
+      <c r="E35" s="5">
+        <v>601</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="5">
+        <v>42</v>
+      </c>
+      <c r="J35" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>61</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>134338576</v>
+      </c>
+      <c r="E36" s="5">
+        <v>601</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="5">
+        <v>42</v>
+      </c>
+      <c r="J36" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>61</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>134339316</v>
+      </c>
+      <c r="E37" s="5">
+        <v>601</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="5">
+        <v>42</v>
+      </c>
+      <c r="J37" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>61</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>134339861</v>
+      </c>
+      <c r="E38" s="5">
+        <v>601</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="5">
+        <v>42</v>
+      </c>
+      <c r="J38" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>61</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>134340501</v>
+      </c>
+      <c r="E39" s="5">
+        <v>601</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="5">
+        <v>42</v>
+      </c>
+      <c r="J39" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>61</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>134340555</v>
+      </c>
+      <c r="E40" s="5">
+        <v>601</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="5">
+        <v>42</v>
+      </c>
+      <c r="J40" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>61</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>134341091</v>
+      </c>
+      <c r="E41" s="5">
+        <v>601</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="5">
+        <v>42</v>
+      </c>
+      <c r="J41" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>61</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>134343065</v>
+      </c>
+      <c r="E42" s="5">
+        <v>601</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="5">
+        <v>42</v>
+      </c>
+      <c r="J42" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>61</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>134343346</v>
+      </c>
+      <c r="E43" s="5">
+        <v>601</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="5">
+        <v>42</v>
+      </c>
+      <c r="J43" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>61</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>134344259</v>
+      </c>
+      <c r="E44" s="5">
+        <v>601</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="5">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>61</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>134344720</v>
+      </c>
+      <c r="E45" s="5">
+        <v>601</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="5">
+        <v>42</v>
+      </c>
+      <c r="J45" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5">
+        <v>61</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>134344929</v>
+      </c>
+      <c r="E46" s="5">
+        <v>601</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="5">
+        <v>42</v>
+      </c>
+      <c r="J46" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>61</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>134345356</v>
+      </c>
+      <c r="E47" s="5">
+        <v>601</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="5">
+        <v>42</v>
+      </c>
+      <c r="J47" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>61</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>123058958</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="5">
+        <v>42</v>
+      </c>
+      <c r="J48" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <v>61</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>134276796</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="5">
+        <v>42</v>
+      </c>
+      <c r="J49" s="5">
+        <v>8021</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>61</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>130933097</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="5">
+        <v>42</v>
+      </c>
+      <c r="J50" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>61</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>131612652</v>
+      </c>
+      <c r="E51" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="5">
+        <v>42</v>
+      </c>
+      <c r="J51" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>61</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>132028482</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="5">
+        <v>42</v>
+      </c>
+      <c r="J52" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>61</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>133406741</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="5">
+        <v>42</v>
+      </c>
+      <c r="J53" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <v>61</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>133622327</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" s="5">
+        <v>42</v>
+      </c>
+      <c r="J54" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>61</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>131612652</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="5">
+        <v>42</v>
+      </c>
+      <c r="J55" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>61</v>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>134372150</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="5">
+        <v>42</v>
+      </c>
+      <c r="J56" s="5">
+        <v>718</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>61</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>134373221</v>
+      </c>
+      <c r="E57" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="5">
+        <v>42</v>
+      </c>
+      <c r="J57" s="5">
+        <v>718</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>61</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>134373422</v>
+      </c>
+      <c r="E58" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="5">
+        <v>42</v>
+      </c>
+      <c r="J58" s="5">
+        <v>718</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>61</v>
+      </c>
+      <c r="O58" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>134375651</v>
+      </c>
+      <c r="E59" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="5">
+        <v>42</v>
+      </c>
+      <c r="J59" s="5">
+        <v>718</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5">
+        <v>61</v>
+      </c>
+      <c r="O59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>134378443</v>
+      </c>
+      <c r="E60" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>718</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>134380944</v>
+      </c>
+      <c r="E61" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>718</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>134380962</v>
+      </c>
+      <c r="E62" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>718</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>134381177</v>
+      </c>
+      <c r="E63" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>718</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>134382742</v>
+      </c>
+      <c r="E64" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>718</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>134382782</v>
+      </c>
+      <c r="E65" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>718</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>134384858</v>
+      </c>
+      <c r="E66" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>718</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>134385414</v>
+      </c>
+      <c r="E67" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>718</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>133763662</v>
+      </c>
+      <c r="E68" s="5">
+        <v>601</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>133974045</v>
+      </c>
+      <c r="E69" s="5">
+        <v>601</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>133974259</v>
+      </c>
+      <c r="E70" s="5">
+        <v>601</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>134284630</v>
+      </c>
+      <c r="E71" s="5">
+        <v>601</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>134320387</v>
+      </c>
+      <c r="E72" s="5">
+        <v>601</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>134321032</v>
+      </c>
+      <c r="E73" s="5">
+        <v>601</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>134325993</v>
+      </c>
+      <c r="E74" s="5">
+        <v>601</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>134326501</v>
+      </c>
+      <c r="E75" s="5">
+        <v>601</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>134329109</v>
+      </c>
+      <c r="E76" s="5">
+        <v>601</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>134329188</v>
+      </c>
+      <c r="E77" s="5">
+        <v>601</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>134329574</v>
+      </c>
+      <c r="E78" s="5">
+        <v>601</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>134330389</v>
+      </c>
+      <c r="E79" s="5">
+        <v>601</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" s="5">
+        <v>42</v>
+      </c>
+      <c r="J79" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5">
+        <v>61</v>
+      </c>
+      <c r="O79" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>134330782</v>
+      </c>
+      <c r="E80" s="5">
+        <v>601</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I80" s="5">
+        <v>42</v>
+      </c>
+      <c r="J80" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>61</v>
+      </c>
+      <c r="O80" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>134331076</v>
+      </c>
+      <c r="E81" s="5">
+        <v>601</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" s="5">
+        <v>42</v>
+      </c>
+      <c r="J81" s="5">
+        <v>1118</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>61</v>
+      </c>
+      <c r="O81" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>134331085</v>
+      </c>
+      <c r="E82" s="5">
+        <v>601</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" s="5">
+        <v>42</v>
+      </c>
+      <c r="J82" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5">
+        <v>61</v>
+      </c>
+      <c r="O82" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>134331451</v>
+      </c>
+      <c r="E83" s="5">
+        <v>601</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I83" s="5">
+        <v>42</v>
+      </c>
+      <c r="J83" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5">
+        <v>61</v>
+      </c>
+      <c r="O83" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>134331471</v>
+      </c>
+      <c r="E84" s="5">
+        <v>601</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" s="5">
+        <v>42</v>
+      </c>
+      <c r="J84" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5">
+        <v>61</v>
+      </c>
+      <c r="O84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>134331892</v>
+      </c>
+      <c r="E85" s="5">
+        <v>601</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" s="5">
+        <v>42</v>
+      </c>
+      <c r="J85" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5">
+        <v>61</v>
+      </c>
+      <c r="O85" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>134332218</v>
+      </c>
+      <c r="E86" s="5">
+        <v>601</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="5">
+        <v>42</v>
+      </c>
+      <c r="J86" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5">
+        <v>61</v>
+      </c>
+      <c r="O86" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>134332251</v>
+      </c>
+      <c r="E87" s="5">
+        <v>601</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" s="5">
+        <v>42</v>
+      </c>
+      <c r="J87" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5">
+        <v>61</v>
+      </c>
+      <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>134333703</v>
+      </c>
+      <c r="E88" s="5">
+        <v>601</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>134333740</v>
+      </c>
+      <c r="E89" s="5">
+        <v>601</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      </c>
+      <c r="J89" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5">
+        <v>61</v>
+      </c>
+      <c r="O89" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>134334446</v>
+      </c>
+      <c r="E90" s="5">
+        <v>601</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I90" s="5">
+        <v>42</v>
+      </c>
+      <c r="J90" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5">
+        <v>61</v>
+      </c>
+      <c r="O90" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>134335142</v>
+      </c>
+      <c r="E91" s="5">
+        <v>601</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I91" s="5">
+        <v>42</v>
+      </c>
+      <c r="J91" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5">
+        <v>61</v>
+      </c>
+      <c r="O91" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>134335608</v>
+      </c>
+      <c r="E92" s="5">
+        <v>601</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" s="5">
+        <v>42</v>
+      </c>
+      <c r="J92" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5">
+        <v>61</v>
+      </c>
+      <c r="O92" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>134336592</v>
+      </c>
+      <c r="E93" s="5">
+        <v>601</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" s="5">
+        <v>42</v>
+      </c>
+      <c r="J93" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5">
+        <v>61</v>
+      </c>
+      <c r="O93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>134337221</v>
+      </c>
+      <c r="E94" s="5">
+        <v>601</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I94" s="5">
+        <v>42</v>
+      </c>
+      <c r="J94" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5">
+        <v>61</v>
+      </c>
+      <c r="O94" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>134337576</v>
+      </c>
+      <c r="E95" s="5">
+        <v>601</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" s="5">
+        <v>42</v>
+      </c>
+      <c r="J95" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>61</v>
+      </c>
+      <c r="O95" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>134338576</v>
+      </c>
+      <c r="E96" s="5">
+        <v>601</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" s="5">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5">
+        <v>61</v>
+      </c>
+      <c r="O96" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>134339316</v>
+      </c>
+      <c r="E97" s="5">
+        <v>601</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" s="5">
+        <v>42</v>
+      </c>
+      <c r="J97" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5">
+        <v>61</v>
+      </c>
+      <c r="O97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>134339600</v>
+      </c>
+      <c r="E98" s="5">
+        <v>601</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I98" s="5">
+        <v>42</v>
+      </c>
+      <c r="J98" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5">
+        <v>61</v>
+      </c>
+      <c r="O98" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>134339748</v>
+      </c>
+      <c r="E99" s="5">
+        <v>601</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I99" s="5">
+        <v>42</v>
+      </c>
+      <c r="J99" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
+        <v>61</v>
+      </c>
+      <c r="O99" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>134339825</v>
+      </c>
+      <c r="E100" s="5">
+        <v>601</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I100" s="5">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>61</v>
+      </c>
+      <c r="O100" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>134339861</v>
+      </c>
+      <c r="E101" s="5">
+        <v>601</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" s="5">
+        <v>42</v>
+      </c>
+      <c r="J101" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>61</v>
+      </c>
+      <c r="O101" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>134340027</v>
+      </c>
+      <c r="E102" s="5">
+        <v>601</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I102" s="5">
+        <v>42</v>
+      </c>
+      <c r="J102" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>61</v>
+      </c>
+      <c r="O102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>134340153</v>
+      </c>
+      <c r="E103" s="5">
+        <v>601</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I103" s="5">
+        <v>42</v>
+      </c>
+      <c r="J103" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>61</v>
+      </c>
+      <c r="O103" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>134340353</v>
+      </c>
+      <c r="E104" s="5">
+        <v>601</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I104" s="5">
+        <v>42</v>
+      </c>
+      <c r="J104" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5">
+        <v>61</v>
+      </c>
+      <c r="O104" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>134340501</v>
+      </c>
+      <c r="E105" s="5">
+        <v>601</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I105" s="5">
+        <v>42</v>
+      </c>
+      <c r="J105" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5">
+        <v>61</v>
+      </c>
+      <c r="O105" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>134340527</v>
+      </c>
+      <c r="E106" s="5">
+        <v>601</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" s="5">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5">
+        <v>61</v>
+      </c>
+      <c r="O106" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>134340555</v>
+      </c>
+      <c r="E107" s="5">
+        <v>601</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I107" s="5">
+        <v>42</v>
+      </c>
+      <c r="J107" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5">
+        <v>61</v>
+      </c>
+      <c r="O107" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>134340744</v>
+      </c>
+      <c r="E108" s="5">
+        <v>601</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I108" s="5">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5">
+        <v>61</v>
+      </c>
+      <c r="O108" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>134341091</v>
+      </c>
+      <c r="E109" s="5">
+        <v>601</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I109" s="5">
+        <v>42</v>
+      </c>
+      <c r="J109" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5">
+        <v>61</v>
+      </c>
+      <c r="O109" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>134342197</v>
+      </c>
+      <c r="E110" s="5">
+        <v>601</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110" s="5">
+        <v>42</v>
+      </c>
+      <c r="J110" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5">
+        <v>61</v>
+      </c>
+      <c r="O110" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>134342905</v>
+      </c>
+      <c r="E111" s="5">
+        <v>601</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111" s="5">
+        <v>42</v>
+      </c>
+      <c r="J111" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5">
+        <v>61</v>
+      </c>
+      <c r="O111" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>134343065</v>
+      </c>
+      <c r="E112" s="5">
+        <v>601</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" s="5">
+        <v>42</v>
+      </c>
+      <c r="J112" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5">
+        <v>61</v>
+      </c>
+      <c r="O112" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>134344259</v>
+      </c>
+      <c r="E113" s="5">
+        <v>601</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I113" s="5">
+        <v>42</v>
+      </c>
+      <c r="J113" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5">
+        <v>61</v>
+      </c>
+      <c r="O113" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>134344720</v>
+      </c>
+      <c r="E114" s="5">
+        <v>601</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" s="5">
+        <v>42</v>
+      </c>
+      <c r="J114" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5">
+        <v>61</v>
+      </c>
+      <c r="O114" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>134344929</v>
+      </c>
+      <c r="E115" s="5">
+        <v>601</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I115" s="5">
+        <v>42</v>
+      </c>
+      <c r="J115" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5">
+        <v>61</v>
+      </c>
+      <c r="O115" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>134345130</v>
+      </c>
+      <c r="E116" s="5">
+        <v>601</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" s="5">
+        <v>42</v>
+      </c>
+      <c r="J116" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" s="5">
+        <v>61</v>
+      </c>
+      <c r="O116" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>134345356</v>
+      </c>
+      <c r="E117" s="5">
+        <v>601</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I117" s="5">
+        <v>42</v>
+      </c>
+      <c r="J117" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" s="5">
+        <v>61</v>
+      </c>
+      <c r="O117" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>134346537</v>
+      </c>
+      <c r="E118" s="5">
+        <v>601</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I118" s="5">
+        <v>42</v>
+      </c>
+      <c r="J118" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5">
+        <v>61</v>
+      </c>
+      <c r="O118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>134349767</v>
+      </c>
+      <c r="E119" s="5">
+        <v>601</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I119" s="5">
+        <v>42</v>
+      </c>
+      <c r="J119" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5">
+        <v>61</v>
+      </c>
+      <c r="O119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>134349880</v>
+      </c>
+      <c r="E120" s="5">
+        <v>601</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I120" s="5">
+        <v>42</v>
+      </c>
+      <c r="J120" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5">
+        <v>61</v>
+      </c>
+      <c r="O120" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>134349894</v>
+      </c>
+      <c r="E121" s="5">
+        <v>601</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121" s="5">
+        <v>42</v>
+      </c>
+      <c r="J121" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5">
+        <v>61</v>
+      </c>
+      <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>134350061</v>
+      </c>
+      <c r="E122" s="5">
+        <v>601</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>134350067</v>
+      </c>
+      <c r="E123" s="5">
+        <v>601</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>134351256</v>
+      </c>
+      <c r="E124" s="5">
+        <v>601</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>134351406</v>
+      </c>
+      <c r="E125" s="5">
+        <v>601</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>134351479</v>
+      </c>
+      <c r="E126" s="5">
+        <v>601</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>134351891</v>
+      </c>
+      <c r="E127" s="5">
+        <v>601</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>134352306</v>
+      </c>
+      <c r="E128" s="5">
+        <v>601</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>134352398</v>
+      </c>
+      <c r="E129" s="5">
+        <v>601</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>134352784</v>
+      </c>
+      <c r="E130" s="5">
+        <v>601</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>134353960</v>
+      </c>
+      <c r="E131" s="5">
+        <v>601</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>134354100</v>
+      </c>
+      <c r="E132" s="5">
+        <v>601</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>134354918</v>
+      </c>
+      <c r="E133" s="5">
+        <v>601</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>134355364</v>
+      </c>
+      <c r="E134" s="5">
+        <v>601</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>134355545</v>
+      </c>
+      <c r="E135" s="5">
+        <v>601</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>134355571</v>
+      </c>
+      <c r="E136" s="5">
+        <v>601</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>134356554</v>
+      </c>
+      <c r="E137" s="5">
+        <v>601</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>134356753</v>
+      </c>
+      <c r="E138" s="5">
+        <v>601</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>134357017</v>
+      </c>
+      <c r="E139" s="5">
+        <v>601</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>134359251</v>
+      </c>
+      <c r="E140" s="5">
+        <v>601</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>134359846</v>
+      </c>
+      <c r="E141" s="5">
+        <v>601</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>134360550</v>
+      </c>
+      <c r="E142" s="5">
+        <v>601</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>134360845</v>
+      </c>
+      <c r="E143" s="5">
+        <v>601</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>134361018</v>
+      </c>
+      <c r="E144" s="5">
+        <v>601</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="O144" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>134361451</v>
+      </c>
+      <c r="E145" s="5">
+        <v>601</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I145" s="5">
+        <v>42</v>
+      </c>
+      <c r="J145" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="L145" s="5">
+        <v>61</v>
+      </c>
+      <c r="O145" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>134362356</v>
+      </c>
+      <c r="E146" s="5">
+        <v>601</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I146" s="5">
+        <v>42</v>
+      </c>
+      <c r="J146" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5">
+        <v>61</v>
+      </c>
+      <c r="O146" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>134362460</v>
+      </c>
+      <c r="E147" s="5">
+        <v>601</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I147" s="5">
+        <v>42</v>
+      </c>
+      <c r="J147" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5">
+        <v>61</v>
+      </c>
+      <c r="O147" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>134362578</v>
+      </c>
+      <c r="E148" s="5">
+        <v>601</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I148" s="5">
+        <v>42</v>
+      </c>
+      <c r="J148" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5">
+        <v>61</v>
+      </c>
+      <c r="O148" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>134362898</v>
+      </c>
+      <c r="E149" s="5">
+        <v>601</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I149" s="5">
+        <v>42</v>
+      </c>
+      <c r="J149" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5">
+        <v>61</v>
+      </c>
+      <c r="O149" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>134363204</v>
+      </c>
+      <c r="E150" s="5">
+        <v>601</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I150" s="5">
+        <v>42</v>
+      </c>
+      <c r="J150" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5">
+        <v>61</v>
+      </c>
+      <c r="O150" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>134364079</v>
+      </c>
+      <c r="E151" s="5">
+        <v>601</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I151" s="5">
+        <v>42</v>
+      </c>
+      <c r="J151" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5">
+        <v>61</v>
+      </c>
+      <c r="O151" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>134364412</v>
+      </c>
+      <c r="E152" s="5">
+        <v>601</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I152" s="5">
+        <v>42</v>
+      </c>
+      <c r="J152" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="L152" s="5">
+        <v>61</v>
+      </c>
+      <c r="O152" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>134364701</v>
+      </c>
+      <c r="E153" s="5">
+        <v>601</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I153" s="5">
+        <v>42</v>
+      </c>
+      <c r="J153" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K153" s="5">
+        <v>0</v>
+      </c>
+      <c r="L153" s="5">
+        <v>61</v>
+      </c>
+      <c r="O153" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>134365013</v>
+      </c>
+      <c r="E154" s="5">
+        <v>601</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I154" s="5">
+        <v>42</v>
+      </c>
+      <c r="J154" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K154" s="5">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5">
+        <v>61</v>
+      </c>
+      <c r="O154" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>134365222</v>
+      </c>
+      <c r="E155" s="5">
+        <v>601</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I155" s="5">
+        <v>42</v>
+      </c>
+      <c r="J155" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K155" s="5">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5">
+        <v>61</v>
+      </c>
+      <c r="O155" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>134366099</v>
+      </c>
+      <c r="E156" s="5">
+        <v>601</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I156" s="5">
+        <v>42</v>
+      </c>
+      <c r="J156" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K156" s="5">
+        <v>0</v>
+      </c>
+      <c r="L156" s="5">
+        <v>61</v>
+      </c>
+      <c r="O156" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>134366246</v>
+      </c>
+      <c r="E157" s="5">
+        <v>601</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I157" s="5">
+        <v>42</v>
+      </c>
+      <c r="J157" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K157" s="5">
+        <v>0</v>
+      </c>
+      <c r="L157" s="5">
+        <v>61</v>
+      </c>
+      <c r="O157" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>134366886</v>
+      </c>
+      <c r="E158" s="5">
+        <v>601</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I158" s="5">
+        <v>42</v>
+      </c>
+      <c r="J158" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K158" s="5">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5">
+        <v>61</v>
+      </c>
+      <c r="O158" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>134368233</v>
+      </c>
+      <c r="E159" s="5">
+        <v>601</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I159" s="5">
+        <v>42</v>
+      </c>
+      <c r="J159" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K159" s="5">
+        <v>0</v>
+      </c>
+      <c r="L159" s="5">
+        <v>61</v>
+      </c>
+      <c r="O159" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>134368277</v>
+      </c>
+      <c r="E160" s="5">
+        <v>601</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I160" s="5">
+        <v>42</v>
+      </c>
+      <c r="J160" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K160" s="5">
+        <v>0</v>
+      </c>
+      <c r="L160" s="5">
+        <v>61</v>
+      </c>
+      <c r="O160" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>134368534</v>
+      </c>
+      <c r="E161" s="5">
+        <v>601</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I161" s="5">
+        <v>42</v>
+      </c>
+      <c r="J161" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K161" s="5">
+        <v>0</v>
+      </c>
+      <c r="L161" s="5">
+        <v>61</v>
+      </c>
+      <c r="O161" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>134368697</v>
+      </c>
+      <c r="E162" s="5">
+        <v>601</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I162" s="5">
+        <v>42</v>
+      </c>
+      <c r="J162" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K162" s="5">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5">
+        <v>61</v>
+      </c>
+      <c r="O162" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>134368771</v>
+      </c>
+      <c r="E163" s="5">
+        <v>601</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I163" s="5">
+        <v>42</v>
+      </c>
+      <c r="J163" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K163" s="5">
+        <v>0</v>
+      </c>
+      <c r="L163" s="5">
+        <v>61</v>
+      </c>
+      <c r="O163" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1131,31 +5387,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60476871-C915-4222-8DBF-83BF4E6E60C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A9EED9-15BD-415A-8F16-950A5B10715E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="20">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -85,19 +85,10 @@
     <t>10/3/2023</t>
   </si>
   <si>
-    <t>16/9/2025</t>
+    <t>15/9/2025</t>
   </si>
   <si>
-    <t>15/09/2025</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>12/09/2025</t>
-  </si>
-  <si>
-    <t>16/09/2025</t>
+    <t>17/9/2025</t>
   </si>
 </sst>
 </file>
@@ -515,7 +506,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -616,22 +607,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134465575</v>
+        <v>129649325</v>
       </c>
       <c r="E3" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -647,22 +638,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>134466039</v>
+        <v>129725766</v>
       </c>
       <c r="E4" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -678,22 +669,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134466064</v>
+        <v>130688142</v>
       </c>
       <c r="E5" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -709,22 +700,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134467237</v>
+        <v>131050625</v>
       </c>
       <c r="E6" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -740,22 +731,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134467792</v>
+        <v>131323664</v>
       </c>
       <c r="E7" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -771,22 +762,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134467975</v>
+        <v>131443092</v>
       </c>
       <c r="E8" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -802,22 +793,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134468866</v>
+        <v>131915064</v>
       </c>
       <c r="E9" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -833,22 +824,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134468937</v>
+        <v>132888235</v>
       </c>
       <c r="E10" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -864,22 +855,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>134469083</v>
+        <v>133779653</v>
       </c>
       <c r="E11" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -895,22 +886,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>134469344</v>
+        <v>133886402</v>
       </c>
       <c r="E12" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -926,22 +917,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134469436</v>
+        <v>129649325</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -957,22 +948,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134469452</v>
+        <v>129725766</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -988,22 +979,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134469541</v>
+        <v>131050625</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1019,22 +1010,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>134469577</v>
+        <v>131915064</v>
       </c>
       <c r="E16" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1050,22 +1041,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>134469591</v>
+        <v>132888235</v>
       </c>
       <c r="E17" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1081,16 +1072,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>134469658</v>
+        <v>134488168</v>
       </c>
       <c r="E18" s="5">
         <v>2013</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1112,16 +1103,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>134469669</v>
+        <v>134488238</v>
       </c>
       <c r="E19" s="5">
         <v>2013</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1143,16 +1134,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>134469679</v>
+        <v>134488239</v>
       </c>
       <c r="E20" s="5">
         <v>2013</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1174,16 +1165,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>134469701</v>
+        <v>134488248</v>
       </c>
       <c r="E21" s="5">
         <v>2013</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1205,16 +1196,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>134469744</v>
+        <v>134488267</v>
       </c>
       <c r="E22" s="5">
         <v>2013</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
@@ -1236,16 +1227,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>134469767</v>
+        <v>134488285</v>
       </c>
       <c r="E23" s="5">
         <v>2013</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1267,16 +1258,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>134469799</v>
+        <v>134488302</v>
       </c>
       <c r="E24" s="5">
         <v>2013</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1298,16 +1289,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>134470102</v>
+        <v>134488357</v>
       </c>
       <c r="E25" s="5">
         <v>2013</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1329,16 +1320,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>134470116</v>
+        <v>134488396</v>
       </c>
       <c r="E26" s="5">
         <v>2013</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1360,16 +1351,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>134470307</v>
+        <v>134488442</v>
       </c>
       <c r="E27" s="5">
         <v>2013</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
@@ -1391,16 +1382,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>134470792</v>
+        <v>134488475</v>
       </c>
       <c r="E28" s="5">
         <v>2013</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
@@ -1422,16 +1413,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>134471541</v>
+        <v>134488498</v>
       </c>
       <c r="E29" s="5">
         <v>2013</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
@@ -1453,16 +1444,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>134471901</v>
+        <v>134488518</v>
       </c>
       <c r="E30" s="5">
         <v>2013</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
@@ -1484,16 +1475,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>134472098</v>
+        <v>134488545</v>
       </c>
       <c r="E31" s="5">
         <v>2013</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
@@ -1515,16 +1506,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>134472209</v>
+        <v>134488578</v>
       </c>
       <c r="E32" s="5">
         <v>2013</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
@@ -1546,16 +1537,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>134472211</v>
+        <v>134488614</v>
       </c>
       <c r="E33" s="5">
         <v>2013</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
@@ -1577,16 +1568,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>134472255</v>
+        <v>134488639</v>
       </c>
       <c r="E34" s="5">
         <v>2013</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1608,16 +1599,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>134472392</v>
+        <v>134488661</v>
       </c>
       <c r="E35" s="5">
         <v>2013</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
@@ -1639,16 +1630,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>134472418</v>
+        <v>134488689</v>
       </c>
       <c r="E36" s="5">
         <v>2013</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
@@ -1670,16 +1661,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>134472490</v>
+        <v>134488695</v>
       </c>
       <c r="E37" s="5">
         <v>2013</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
@@ -1701,16 +1692,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>134472493</v>
+        <v>134488746</v>
       </c>
       <c r="E38" s="5">
         <v>2013</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
@@ -1732,16 +1723,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>134472543</v>
+        <v>134488833</v>
       </c>
       <c r="E39" s="5">
         <v>2013</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
@@ -1763,16 +1754,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>134472554</v>
+        <v>134488965</v>
       </c>
       <c r="E40" s="5">
         <v>2013</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
@@ -1794,16 +1785,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>134472572</v>
+        <v>134489047</v>
       </c>
       <c r="E41" s="5">
         <v>2013</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
@@ -1825,16 +1816,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>134472603</v>
+        <v>134490427</v>
       </c>
       <c r="E42" s="5">
         <v>2013</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
@@ -1856,16 +1847,16 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>134472613</v>
+        <v>134490661</v>
       </c>
       <c r="E43" s="5">
         <v>2013</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I43" s="5">
         <v>42</v>
@@ -1887,16 +1878,16 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>134472653</v>
+        <v>134490687</v>
       </c>
       <c r="E44" s="5">
         <v>2013</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
@@ -1918,16 +1909,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>134472733</v>
+        <v>134491295</v>
       </c>
       <c r="E45" s="5">
         <v>2013</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
@@ -1949,16 +1940,16 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>134472763</v>
+        <v>134492079</v>
       </c>
       <c r="E46" s="5">
         <v>2013</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I46" s="5">
         <v>42</v>
@@ -1980,16 +1971,16 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>134472874</v>
+        <v>134492186</v>
       </c>
       <c r="E47" s="5">
         <v>2013</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
@@ -2011,16 +2002,16 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>134474470</v>
+        <v>134492516</v>
       </c>
       <c r="E48" s="5">
         <v>2013</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
@@ -2042,16 +2033,16 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>134474527</v>
+        <v>134492937</v>
       </c>
       <c r="E49" s="5">
         <v>2013</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
@@ -2073,16 +2064,16 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>134476207</v>
+        <v>134493036</v>
       </c>
       <c r="E50" s="5">
         <v>2013</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
@@ -2104,16 +2095,16 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>134476261</v>
+        <v>134493197</v>
       </c>
       <c r="E51" s="5">
         <v>2013</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
@@ -2135,16 +2126,16 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>134476270</v>
+        <v>134493522</v>
       </c>
       <c r="E52" s="5">
         <v>2013</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
@@ -2166,16 +2157,16 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>134476324</v>
+        <v>134493631</v>
       </c>
       <c r="E53" s="5">
         <v>2013</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
@@ -2197,16 +2188,16 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>134476389</v>
+        <v>134493716</v>
       </c>
       <c r="E54" s="5">
         <v>2013</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
@@ -2228,16 +2219,16 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>134476627</v>
+        <v>134493843</v>
       </c>
       <c r="E55" s="5">
         <v>2013</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
@@ -2259,16 +2250,16 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>134476915</v>
+        <v>134493970</v>
       </c>
       <c r="E56" s="5">
         <v>2013</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
@@ -2290,16 +2281,16 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>134476981</v>
+        <v>134494018</v>
       </c>
       <c r="E57" s="5">
         <v>2013</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
@@ -2321,16 +2312,16 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>134477023</v>
+        <v>134494098</v>
       </c>
       <c r="E58" s="5">
         <v>2013</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
@@ -2352,16 +2343,16 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>134477061</v>
+        <v>134494183</v>
       </c>
       <c r="E59" s="5">
         <v>2013</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
@@ -2383,16 +2374,16 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>134477147</v>
+        <v>134494476</v>
       </c>
       <c r="E60" s="5">
         <v>2013</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
@@ -2413,17 +2404,17 @@
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
-        <v>134477239</v>
+      <c r="A61" s="6">
+        <v>134494636</v>
       </c>
       <c r="E61" s="5">
         <v>2013</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
@@ -2437,24 +2428,22 @@
       <c r="L61" s="5">
         <v>61</v>
       </c>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
       <c r="O61" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
-        <v>134477256</v>
+      <c r="A62" s="6">
+        <v>134494883</v>
       </c>
       <c r="E62" s="5">
         <v>2013</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I62" s="5">
         <v>42</v>
@@ -2468,24 +2457,22 @@
       <c r="L62" s="5">
         <v>61</v>
       </c>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
       <c r="O62" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
-        <v>134477270</v>
+      <c r="A63" s="6">
+        <v>134494888</v>
       </c>
       <c r="E63" s="5">
         <v>2013</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
@@ -2499,24 +2486,22 @@
       <c r="L63" s="5">
         <v>61</v>
       </c>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
       <c r="O63" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
-        <v>134477276</v>
+      <c r="A64" s="6">
+        <v>134494902</v>
       </c>
       <c r="E64" s="5">
         <v>2013</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
@@ -2530,24 +2515,22 @@
       <c r="L64" s="5">
         <v>61</v>
       </c>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
       <c r="O64" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
-        <v>134477305</v>
+      <c r="A65" s="6">
+        <v>134495033</v>
       </c>
       <c r="E65" s="5">
         <v>2013</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
@@ -2561,24 +2544,22 @@
       <c r="L65" s="5">
         <v>61</v>
       </c>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
       <c r="O65" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
-        <v>134477331</v>
+      <c r="A66" s="6">
+        <v>134495091</v>
       </c>
       <c r="E66" s="5">
         <v>2013</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
@@ -2592,24 +2573,22 @@
       <c r="L66" s="5">
         <v>61</v>
       </c>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
       <c r="O66" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
-        <v>134477356</v>
+      <c r="A67" s="6">
+        <v>134495699</v>
       </c>
       <c r="E67" s="5">
         <v>2013</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
@@ -2623,24 +2602,22 @@
       <c r="L67" s="5">
         <v>61</v>
       </c>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
       <c r="O67" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
-        <v>134477390</v>
+      <c r="A68" s="6">
+        <v>134495942</v>
       </c>
       <c r="E68" s="5">
         <v>2013</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
@@ -2654,24 +2631,22 @@
       <c r="L68" s="5">
         <v>61</v>
       </c>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
       <c r="O68" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
-        <v>134477408</v>
+      <c r="A69" s="6">
+        <v>134496086</v>
       </c>
       <c r="E69" s="5">
         <v>2013</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
@@ -2685,24 +2660,22 @@
       <c r="L69" s="5">
         <v>61</v>
       </c>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
       <c r="O69" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
-        <v>134477413</v>
+      <c r="A70" s="6">
+        <v>134496200</v>
       </c>
       <c r="E70" s="5">
         <v>2013</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
@@ -2716,24 +2689,22 @@
       <c r="L70" s="5">
         <v>61</v>
       </c>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
       <c r="O70" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="5">
-        <v>134477416</v>
+      <c r="A71" s="6">
+        <v>134496245</v>
       </c>
       <c r="E71" s="5">
         <v>2013</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
@@ -2747,24 +2718,22 @@
       <c r="L71" s="5">
         <v>61</v>
       </c>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
       <c r="O71" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="5">
-        <v>134477422</v>
+      <c r="A72" s="6">
+        <v>134496376</v>
       </c>
       <c r="E72" s="5">
         <v>2013</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I72" s="5">
         <v>42</v>
@@ -2778,24 +2747,22 @@
       <c r="L72" s="5">
         <v>61</v>
       </c>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
       <c r="O72" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="5">
-        <v>134477438</v>
+      <c r="A73" s="6">
+        <v>134496496</v>
       </c>
       <c r="E73" s="5">
         <v>2013</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
@@ -2809,24 +2776,22 @@
       <c r="L73" s="5">
         <v>61</v>
       </c>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
       <c r="O73" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" s="5">
-        <v>134477474</v>
+      <c r="A74" s="6">
+        <v>134496505</v>
       </c>
       <c r="E74" s="5">
         <v>2013</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
@@ -2840,24 +2805,22 @@
       <c r="L74" s="5">
         <v>61</v>
       </c>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
       <c r="O74" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="5">
-        <v>134477476</v>
+      <c r="A75" s="6">
+        <v>134496608</v>
       </c>
       <c r="E75" s="5">
         <v>2013</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
@@ -2871,24 +2834,22 @@
       <c r="L75" s="5">
         <v>61</v>
       </c>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
       <c r="O75" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="5">
-        <v>134477489</v>
+      <c r="A76" s="6">
+        <v>134496640</v>
       </c>
       <c r="E76" s="5">
         <v>2013</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
@@ -2902,24 +2863,22 @@
       <c r="L76" s="5">
         <v>61</v>
       </c>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
       <c r="O76" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5">
-        <v>134477551</v>
+      <c r="A77" s="6">
+        <v>134496742</v>
       </c>
       <c r="E77" s="5">
         <v>2013</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
@@ -2933,24 +2892,22 @@
       <c r="L77" s="5">
         <v>61</v>
       </c>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
       <c r="O77" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
-        <v>134477615</v>
+      <c r="A78" s="6">
+        <v>134496918</v>
       </c>
       <c r="E78" s="5">
         <v>2013</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I78" s="5">
         <v>42</v>
@@ -2964,24 +2921,22 @@
       <c r="L78" s="5">
         <v>61</v>
       </c>
-      <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
       <c r="O78" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="5">
-        <v>134477657</v>
+      <c r="A79" s="6">
+        <v>134497086</v>
       </c>
       <c r="E79" s="5">
         <v>2013</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I79" s="5">
         <v>42</v>
@@ -2995,24 +2950,22 @@
       <c r="L79" s="5">
         <v>61</v>
       </c>
-      <c r="M79" s="5"/>
-      <c r="N79" s="5"/>
       <c r="O79" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
-        <v>134477720</v>
+      <c r="A80" s="6">
+        <v>134497113</v>
       </c>
       <c r="E80" s="5">
         <v>2013</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I80" s="5">
         <v>42</v>
@@ -3026,24 +2979,22 @@
       <c r="L80" s="5">
         <v>61</v>
       </c>
-      <c r="M80" s="5"/>
-      <c r="N80" s="5"/>
       <c r="O80" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" s="5">
-        <v>134477728</v>
+      <c r="A81" s="6">
+        <v>134497163</v>
       </c>
       <c r="E81" s="5">
         <v>2013</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I81" s="5">
         <v>42</v>
@@ -3057,24 +3008,22 @@
       <c r="L81" s="5">
         <v>61</v>
       </c>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
       <c r="O81" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="5">
-        <v>134477922</v>
+      <c r="A82" s="6">
+        <v>134497494</v>
       </c>
       <c r="E82" s="5">
         <v>2013</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I82" s="5">
         <v>42</v>
@@ -3088,24 +3037,22 @@
       <c r="L82" s="5">
         <v>61</v>
       </c>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
       <c r="O82" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
-        <v>134477983</v>
+      <c r="A83" s="6">
+        <v>134497639</v>
       </c>
       <c r="E83" s="5">
         <v>2013</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I83" s="5">
         <v>42</v>
@@ -3119,24 +3066,22 @@
       <c r="L83" s="5">
         <v>61</v>
       </c>
-      <c r="M83" s="5"/>
-      <c r="N83" s="5"/>
       <c r="O83" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
-        <v>134477989</v>
+      <c r="A84" s="6">
+        <v>134497745</v>
       </c>
       <c r="E84" s="5">
         <v>2013</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I84" s="5">
         <v>42</v>
@@ -3150,24 +3095,22 @@
       <c r="L84" s="5">
         <v>61</v>
       </c>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
       <c r="O84" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
-        <v>134477997</v>
+      <c r="A85" s="6">
+        <v>134497823</v>
       </c>
       <c r="E85" s="5">
         <v>2013</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I85" s="5">
         <v>42</v>
@@ -3181,24 +3124,22 @@
       <c r="L85" s="5">
         <v>61</v>
       </c>
-      <c r="M85" s="5"/>
-      <c r="N85" s="5"/>
       <c r="O85" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="5">
-        <v>134478079</v>
+      <c r="A86" s="6">
+        <v>134497839</v>
       </c>
       <c r="E86" s="5">
         <v>2013</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I86" s="5">
         <v>42</v>
@@ -3212,24 +3153,22 @@
       <c r="L86" s="5">
         <v>61</v>
       </c>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
       <c r="O86" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
-        <v>134479439</v>
+      <c r="A87" s="6">
+        <v>134498144</v>
       </c>
       <c r="E87" s="5">
         <v>2013</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I87" s="5">
         <v>42</v>
@@ -3243,24 +3182,22 @@
       <c r="L87" s="5">
         <v>61</v>
       </c>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
       <c r="O87" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" s="5">
-        <v>134480245</v>
+      <c r="A88" s="6">
+        <v>134498162</v>
       </c>
       <c r="E88" s="5">
         <v>2013</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I88" s="5">
         <v>42</v>
@@ -3274,24 +3211,22 @@
       <c r="L88" s="5">
         <v>61</v>
       </c>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
       <c r="O88" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" s="5">
-        <v>134480334</v>
+      <c r="A89" s="6">
+        <v>134498187</v>
       </c>
       <c r="E89" s="5">
         <v>2013</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I89" s="5">
         <v>42</v>
@@ -3305,24 +3240,22 @@
       <c r="L89" s="5">
         <v>61</v>
       </c>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
       <c r="O89" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="5">
-        <v>134480672</v>
+      <c r="A90" s="6">
+        <v>134498230</v>
       </c>
       <c r="E90" s="5">
         <v>2013</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I90" s="5">
         <v>42</v>
@@ -3336,24 +3269,22 @@
       <c r="L90" s="5">
         <v>61</v>
       </c>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
       <c r="O90" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="5">
-        <v>134480950</v>
+      <c r="A91" s="6">
+        <v>134498335</v>
       </c>
       <c r="E91" s="5">
         <v>2013</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I91" s="5">
         <v>42</v>
@@ -3367,24 +3298,22 @@
       <c r="L91" s="5">
         <v>61</v>
       </c>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
       <c r="O91" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="5">
-        <v>134481244</v>
+      <c r="A92" s="6">
+        <v>134498348</v>
       </c>
       <c r="E92" s="5">
         <v>2013</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I92" s="5">
         <v>42</v>
@@ -3398,24 +3327,22 @@
       <c r="L92" s="5">
         <v>61</v>
       </c>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
       <c r="O92" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" s="5">
-        <v>134481448</v>
+      <c r="A93" s="6">
+        <v>134498539</v>
       </c>
       <c r="E93" s="5">
         <v>2013</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I93" s="5">
         <v>42</v>
@@ -3429,24 +3356,22 @@
       <c r="L93" s="5">
         <v>61</v>
       </c>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
       <c r="O93" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="5">
-        <v>134481497</v>
+      <c r="A94" s="6">
+        <v>134498566</v>
       </c>
       <c r="E94" s="5">
         <v>2013</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I94" s="5">
         <v>42</v>
@@ -3460,24 +3385,22 @@
       <c r="L94" s="5">
         <v>61</v>
       </c>
-      <c r="M94" s="5"/>
-      <c r="N94" s="5"/>
       <c r="O94" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="5">
-        <v>134481616</v>
+      <c r="A95" s="6">
+        <v>134498649</v>
       </c>
       <c r="E95" s="5">
         <v>2013</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I95" s="5">
         <v>42</v>
@@ -3491,24 +3414,22 @@
       <c r="L95" s="5">
         <v>61</v>
       </c>
-      <c r="M95" s="5"/>
-      <c r="N95" s="5"/>
       <c r="O95" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="5">
-        <v>134481717</v>
+      <c r="A96" s="6">
+        <v>134498685</v>
       </c>
       <c r="E96" s="5">
         <v>2013</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I96" s="5">
         <v>42</v>
@@ -3522,24 +3443,22 @@
       <c r="L96" s="5">
         <v>61</v>
       </c>
-      <c r="M96" s="5"/>
-      <c r="N96" s="5"/>
       <c r="O96" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" s="5">
-        <v>134481996</v>
+      <c r="A97" s="6">
+        <v>134498754</v>
       </c>
       <c r="E97" s="5">
         <v>2013</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I97" s="5">
         <v>42</v>
@@ -3553,24 +3472,22 @@
       <c r="L97" s="5">
         <v>61</v>
       </c>
-      <c r="M97" s="5"/>
-      <c r="N97" s="5"/>
       <c r="O97" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="5">
-        <v>134482018</v>
+      <c r="A98" s="6">
+        <v>134498848</v>
       </c>
       <c r="E98" s="5">
         <v>2013</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I98" s="5">
         <v>42</v>
@@ -3584,24 +3501,22 @@
       <c r="L98" s="5">
         <v>61</v>
       </c>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
       <c r="O98" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" s="5">
-        <v>134482233</v>
+      <c r="A99" s="6">
+        <v>134498893</v>
       </c>
       <c r="E99" s="5">
         <v>2013</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I99" s="5">
         <v>42</v>
@@ -3615,18 +3530,16 @@
       <c r="L99" s="5">
         <v>61</v>
       </c>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
       <c r="O99" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="5">
-        <v>133936181</v>
+      <c r="A100" s="6">
+        <v>134499483</v>
       </c>
       <c r="E100" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>19</v>
@@ -3638,7 +3551,7 @@
         <v>42</v>
       </c>
       <c r="J100" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K100" s="5">
         <v>0</v>
@@ -3646,30 +3559,28 @@
       <c r="L100" s="5">
         <v>61</v>
       </c>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
       <c r="O100" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="5">
-        <v>134218329</v>
+      <c r="A101" s="6">
+        <v>134499538</v>
       </c>
       <c r="E101" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I101" s="5">
         <v>42</v>
       </c>
       <c r="J101" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K101" s="5">
         <v>0</v>
@@ -3677,30 +3588,28 @@
       <c r="L101" s="5">
         <v>61</v>
       </c>
-      <c r="M101" s="5"/>
-      <c r="N101" s="5"/>
       <c r="O101" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A102" s="5">
-        <v>134432402</v>
+      <c r="A102" s="6">
+        <v>134499629</v>
       </c>
       <c r="E102" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I102" s="5">
         <v>42</v>
       </c>
       <c r="J102" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K102" s="5">
         <v>0</v>
@@ -3708,18 +3617,16 @@
       <c r="L102" s="5">
         <v>61</v>
       </c>
-      <c r="M102" s="5"/>
-      <c r="N102" s="5"/>
       <c r="O102" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="5">
-        <v>134443864</v>
+      <c r="A103" s="6">
+        <v>134499659</v>
       </c>
       <c r="E103" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>19</v>
@@ -3731,7 +3638,7 @@
         <v>42</v>
       </c>
       <c r="J103" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K103" s="5">
         <v>0</v>
@@ -3739,18 +3646,16 @@
       <c r="L103" s="5">
         <v>61</v>
       </c>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5"/>
       <c r="O103" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="5">
-        <v>134444646</v>
+      <c r="A104" s="6">
+        <v>134499813</v>
       </c>
       <c r="E104" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>19</v>
@@ -3762,7 +3667,7 @@
         <v>42</v>
       </c>
       <c r="J104" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K104" s="5">
         <v>0</v>
@@ -3770,18 +3675,16 @@
       <c r="L104" s="5">
         <v>61</v>
       </c>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
       <c r="O104" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
-        <v>134444739</v>
+      <c r="A105" s="6">
+        <v>134500132</v>
       </c>
       <c r="E105" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>19</v>
@@ -3793,7 +3696,7 @@
         <v>42</v>
       </c>
       <c r="J105" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K105" s="5">
         <v>0</v>
@@ -3801,18 +3704,16 @@
       <c r="L105" s="5">
         <v>61</v>
       </c>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
       <c r="O105" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A106" s="5">
-        <v>134444753</v>
+      <c r="A106" s="6">
+        <v>134500190</v>
       </c>
       <c r="E106" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>19</v>
@@ -3824,7 +3725,7 @@
         <v>42</v>
       </c>
       <c r="J106" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
@@ -3832,21 +3733,19 @@
       <c r="L106" s="5">
         <v>61</v>
       </c>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
       <c r="O106" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A107" s="5">
-        <v>134444882</v>
+      <c r="A107" s="6">
+        <v>134500251</v>
       </c>
       <c r="E107" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>19</v>
@@ -3855,7 +3754,7 @@
         <v>42</v>
       </c>
       <c r="J107" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K107" s="5">
         <v>0</v>
@@ -3863,18 +3762,16 @@
       <c r="L107" s="5">
         <v>61</v>
       </c>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5"/>
       <c r="O107" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A108" s="5">
-        <v>134445120</v>
+      <c r="A108" s="6">
+        <v>134500318</v>
       </c>
       <c r="E108" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>19</v>
@@ -3886,7 +3783,7 @@
         <v>42</v>
       </c>
       <c r="J108" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K108" s="5">
         <v>0</v>
@@ -3894,18 +3791,16 @@
       <c r="L108" s="5">
         <v>61</v>
       </c>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5"/>
       <c r="O108" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A109" s="5">
-        <v>134445588</v>
+      <c r="A109" s="6">
+        <v>134500382</v>
       </c>
       <c r="E109" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>19</v>
@@ -3917,7 +3812,7 @@
         <v>42</v>
       </c>
       <c r="J109" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
@@ -3925,18 +3820,16 @@
       <c r="L109" s="5">
         <v>61</v>
       </c>
-      <c r="M109" s="5"/>
-      <c r="N109" s="5"/>
       <c r="O109" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A110" s="5">
-        <v>134446829</v>
+      <c r="A110" s="6">
+        <v>134500467</v>
       </c>
       <c r="E110" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>19</v>
@@ -3948,7 +3841,7 @@
         <v>42</v>
       </c>
       <c r="J110" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K110" s="5">
         <v>0</v>
@@ -3956,18 +3849,16 @@
       <c r="L110" s="5">
         <v>61</v>
       </c>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5"/>
       <c r="O110" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A111" s="5">
-        <v>134447523</v>
+      <c r="A111" s="6">
+        <v>134500468</v>
       </c>
       <c r="E111" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>19</v>
@@ -3979,7 +3870,7 @@
         <v>42</v>
       </c>
       <c r="J111" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K111" s="5">
         <v>0</v>
@@ -3987,18 +3878,16 @@
       <c r="L111" s="5">
         <v>61</v>
       </c>
-      <c r="M111" s="5"/>
-      <c r="N111" s="5"/>
       <c r="O111" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A112" s="5">
-        <v>134450595</v>
+      <c r="A112" s="6">
+        <v>134500519</v>
       </c>
       <c r="E112" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>19</v>
@@ -4010,7 +3899,7 @@
         <v>42</v>
       </c>
       <c r="J112" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K112" s="5">
         <v>0</v>
@@ -4018,18 +3907,16 @@
       <c r="L112" s="5">
         <v>61</v>
       </c>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5"/>
       <c r="O112" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A113" s="5">
-        <v>134450614</v>
+      <c r="A113" s="6">
+        <v>134500682</v>
       </c>
       <c r="E113" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>19</v>
@@ -4041,7 +3928,7 @@
         <v>42</v>
       </c>
       <c r="J113" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
@@ -4049,18 +3936,16 @@
       <c r="L113" s="5">
         <v>61</v>
       </c>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5"/>
       <c r="O113" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A114" s="5">
-        <v>134451888</v>
+      <c r="A114" s="6">
+        <v>134500889</v>
       </c>
       <c r="E114" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>19</v>
@@ -4072,7 +3957,7 @@
         <v>42</v>
       </c>
       <c r="J114" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K114" s="5">
         <v>0</v>
@@ -4080,18 +3965,16 @@
       <c r="L114" s="5">
         <v>61</v>
       </c>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5"/>
       <c r="O114" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A115" s="5">
-        <v>134452170</v>
+      <c r="A115" s="6">
+        <v>134500899</v>
       </c>
       <c r="E115" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>19</v>
@@ -4103,7 +3986,7 @@
         <v>42</v>
       </c>
       <c r="J115" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K115" s="5">
         <v>0</v>
@@ -4111,18 +3994,16 @@
       <c r="L115" s="5">
         <v>61</v>
       </c>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5"/>
       <c r="O115" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A116" s="5">
-        <v>134452307</v>
+      <c r="A116" s="6">
+        <v>134500924</v>
       </c>
       <c r="E116" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>19</v>
@@ -4134,7 +4015,7 @@
         <v>42</v>
       </c>
       <c r="J116" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K116" s="5">
         <v>0</v>
@@ -4142,18 +4023,16 @@
       <c r="L116" s="5">
         <v>61</v>
       </c>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5"/>
       <c r="O116" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A117" s="5">
-        <v>134452434</v>
+      <c r="A117" s="6">
+        <v>134500981</v>
       </c>
       <c r="E117" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>19</v>
@@ -4165,7 +4044,7 @@
         <v>42</v>
       </c>
       <c r="J117" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K117" s="5">
         <v>0</v>
@@ -4173,18 +4052,16 @@
       <c r="L117" s="5">
         <v>61</v>
       </c>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
       <c r="O117" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A118" s="5">
-        <v>134452572</v>
+      <c r="A118" s="6">
+        <v>134501228</v>
       </c>
       <c r="E118" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>19</v>
@@ -4196,7 +4073,7 @@
         <v>42</v>
       </c>
       <c r="J118" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K118" s="5">
         <v>0</v>
@@ -4204,18 +4081,16 @@
       <c r="L118" s="5">
         <v>61</v>
       </c>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5"/>
       <c r="O118" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A119" s="5">
-        <v>134452935</v>
+      <c r="A119" s="6">
+        <v>134501266</v>
       </c>
       <c r="E119" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>19</v>
@@ -4227,7 +4102,7 @@
         <v>42</v>
       </c>
       <c r="J119" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K119" s="5">
         <v>0</v>
@@ -4235,18 +4110,16 @@
       <c r="L119" s="5">
         <v>61</v>
       </c>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5"/>
       <c r="O119" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A120" s="5">
-        <v>134453061</v>
+      <c r="A120" s="6">
+        <v>134501759</v>
       </c>
       <c r="E120" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>19</v>
@@ -4258,7 +4131,7 @@
         <v>42</v>
       </c>
       <c r="J120" s="5">
-        <v>1118</v>
+        <v>718</v>
       </c>
       <c r="K120" s="5">
         <v>0</v>
@@ -4266,18 +4139,16 @@
       <c r="L120" s="5">
         <v>61</v>
       </c>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5"/>
       <c r="O120" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A121" s="5">
-        <v>134453077</v>
+      <c r="A121" s="6">
+        <v>134501948</v>
       </c>
       <c r="E121" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>19</v>
@@ -4289,7 +4160,7 @@
         <v>42</v>
       </c>
       <c r="J121" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K121" s="5">
         <v>0</v>
@@ -4297,18 +4168,16 @@
       <c r="L121" s="5">
         <v>61</v>
       </c>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5"/>
       <c r="O121" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A122" s="5">
-        <v>134453548</v>
+      <c r="A122" s="6">
+        <v>134502114</v>
       </c>
       <c r="E122" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>19</v>
@@ -4320,7 +4189,7 @@
         <v>42</v>
       </c>
       <c r="J122" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K122" s="5">
         <v>0</v>
@@ -4328,18 +4197,16 @@
       <c r="L122" s="5">
         <v>61</v>
       </c>
-      <c r="M122" s="5"/>
-      <c r="N122" s="5"/>
       <c r="O122" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A123" s="5">
-        <v>134453796</v>
+      <c r="A123" s="6">
+        <v>134502369</v>
       </c>
       <c r="E123" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>19</v>
@@ -4351,7 +4218,7 @@
         <v>42</v>
       </c>
       <c r="J123" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K123" s="5">
         <v>0</v>
@@ -4359,18 +4226,16 @@
       <c r="L123" s="5">
         <v>61</v>
       </c>
-      <c r="M123" s="5"/>
-      <c r="N123" s="5"/>
       <c r="O123" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A124" s="5">
-        <v>134455628</v>
+      <c r="A124" s="6">
+        <v>134502841</v>
       </c>
       <c r="E124" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>19</v>
@@ -4382,7 +4247,7 @@
         <v>42</v>
       </c>
       <c r="J124" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K124" s="5">
         <v>0</v>
@@ -4390,18 +4255,16 @@
       <c r="L124" s="5">
         <v>61</v>
       </c>
-      <c r="M124" s="5"/>
-      <c r="N124" s="5"/>
       <c r="O124" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A125" s="5">
-        <v>134456066</v>
+      <c r="A125" s="6">
+        <v>134503881</v>
       </c>
       <c r="E125" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>19</v>
@@ -4413,7 +4276,7 @@
         <v>42</v>
       </c>
       <c r="J125" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K125" s="5">
         <v>0</v>
@@ -4421,381 +4284,7 @@
       <c r="L125" s="5">
         <v>61</v>
       </c>
-      <c r="M125" s="5"/>
-      <c r="N125" s="5"/>
       <c r="O125" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A126" s="5">
-        <v>134456097</v>
-      </c>
-      <c r="E126" s="5">
-        <v>601</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I126" s="5">
-        <v>42</v>
-      </c>
-      <c r="J126" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K126" s="5">
-        <v>0</v>
-      </c>
-      <c r="L126" s="5">
-        <v>61</v>
-      </c>
-      <c r="M126" s="5"/>
-      <c r="N126" s="5"/>
-      <c r="O126" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A127" s="5">
-        <v>134456328</v>
-      </c>
-      <c r="E127" s="5">
-        <v>601</v>
-      </c>
-      <c r="F127" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I127" s="5">
-        <v>42</v>
-      </c>
-      <c r="J127" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K127" s="5">
-        <v>0</v>
-      </c>
-      <c r="L127" s="5">
-        <v>61</v>
-      </c>
-      <c r="M127" s="5"/>
-      <c r="N127" s="5"/>
-      <c r="O127" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A128" s="5">
-        <v>134456434</v>
-      </c>
-      <c r="E128" s="5">
-        <v>601</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I128" s="5">
-        <v>42</v>
-      </c>
-      <c r="J128" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K128" s="5">
-        <v>0</v>
-      </c>
-      <c r="L128" s="5">
-        <v>61</v>
-      </c>
-      <c r="M128" s="5"/>
-      <c r="N128" s="5"/>
-      <c r="O128" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A129" s="5">
-        <v>134459536</v>
-      </c>
-      <c r="E129" s="5">
-        <v>601</v>
-      </c>
-      <c r="F129" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I129" s="5">
-        <v>42</v>
-      </c>
-      <c r="J129" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K129" s="5">
-        <v>0</v>
-      </c>
-      <c r="L129" s="5">
-        <v>61</v>
-      </c>
-      <c r="M129" s="5"/>
-      <c r="N129" s="5"/>
-      <c r="O129" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A130" s="5">
-        <v>134459569</v>
-      </c>
-      <c r="E130" s="5">
-        <v>601</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I130" s="5">
-        <v>42</v>
-      </c>
-      <c r="J130" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K130" s="5">
-        <v>0</v>
-      </c>
-      <c r="L130" s="5">
-        <v>61</v>
-      </c>
-      <c r="M130" s="5"/>
-      <c r="N130" s="5"/>
-      <c r="O130" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A131" s="5">
-        <v>134460381</v>
-      </c>
-      <c r="E131" s="5">
-        <v>601</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I131" s="5">
-        <v>42</v>
-      </c>
-      <c r="J131" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K131" s="5">
-        <v>0</v>
-      </c>
-      <c r="L131" s="5">
-        <v>61</v>
-      </c>
-      <c r="M131" s="5"/>
-      <c r="N131" s="5"/>
-      <c r="O131" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A132" s="5">
-        <v>134461447</v>
-      </c>
-      <c r="E132" s="5">
-        <v>601</v>
-      </c>
-      <c r="F132" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I132" s="5">
-        <v>42</v>
-      </c>
-      <c r="J132" s="5">
-        <v>8013</v>
-      </c>
-      <c r="K132" s="5">
-        <v>0</v>
-      </c>
-      <c r="L132" s="5">
-        <v>61</v>
-      </c>
-      <c r="M132" s="5"/>
-      <c r="N132" s="5"/>
-      <c r="O132" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A133" s="5">
-        <v>134462089</v>
-      </c>
-      <c r="E133" s="5">
-        <v>601</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I133" s="5">
-        <v>42</v>
-      </c>
-      <c r="J133" s="5">
-        <v>8013</v>
-      </c>
-      <c r="K133" s="5">
-        <v>0</v>
-      </c>
-      <c r="L133" s="5">
-        <v>61</v>
-      </c>
-      <c r="M133" s="5"/>
-      <c r="N133" s="5"/>
-      <c r="O133" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A134" s="5">
-        <v>134462100</v>
-      </c>
-      <c r="E134" s="5">
-        <v>601</v>
-      </c>
-      <c r="F134" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G134" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I134" s="5">
-        <v>42</v>
-      </c>
-      <c r="J134" s="5">
-        <v>8013</v>
-      </c>
-      <c r="K134" s="5">
-        <v>0</v>
-      </c>
-      <c r="L134" s="5">
-        <v>61</v>
-      </c>
-      <c r="M134" s="5"/>
-      <c r="N134" s="5"/>
-      <c r="O134" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A135" s="5">
-        <v>134462108</v>
-      </c>
-      <c r="E135" s="5">
-        <v>601</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I135" s="5">
-        <v>42</v>
-      </c>
-      <c r="J135" s="5">
-        <v>8013</v>
-      </c>
-      <c r="K135" s="5">
-        <v>0</v>
-      </c>
-      <c r="L135" s="5">
-        <v>61</v>
-      </c>
-      <c r="M135" s="5"/>
-      <c r="N135" s="5"/>
-      <c r="O135" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A136" s="5">
-        <v>134462141</v>
-      </c>
-      <c r="E136" s="5">
-        <v>601</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I136" s="5">
-        <v>42</v>
-      </c>
-      <c r="J136" s="5">
-        <v>8013</v>
-      </c>
-      <c r="K136" s="5">
-        <v>0</v>
-      </c>
-      <c r="L136" s="5">
-        <v>61</v>
-      </c>
-      <c r="M136" s="5"/>
-      <c r="N136" s="5"/>
-      <c r="O136" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A137" s="5">
-        <v>134462156</v>
-      </c>
-      <c r="E137" s="5">
-        <v>601</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G137" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I137" s="5">
-        <v>42</v>
-      </c>
-      <c r="J137" s="5">
-        <v>8013</v>
-      </c>
-      <c r="K137" s="5">
-        <v>0</v>
-      </c>
-      <c r="L137" s="5">
-        <v>61</v>
-      </c>
-      <c r="M137" s="5"/>
-      <c r="N137" s="5"/>
-      <c r="O137" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4822,31 +4311,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6DE6EF-9F6D-4CE8-BDCA-5CC32D41A767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40570CED-2235-424F-AF50-414666B26235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="20">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -88,13 +88,7 @@
     <t>10/3/2023</t>
   </si>
   <si>
-    <t>18/9/2025</t>
-  </si>
-  <si>
-    <t>20/9/2025</t>
-  </si>
-  <si>
-    <t>22/9/2025</t>
+    <t>23/9/2025</t>
   </si>
 </sst>
 </file>
@@ -582,22 +576,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>134511523</v>
+        <v>134537077</v>
       </c>
       <c r="E2" s="5">
         <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -613,22 +607,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134512115</v>
+        <v>134538558</v>
       </c>
       <c r="E3" s="5">
         <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -644,16 +638,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>134513662</v>
+        <v>134541522</v>
       </c>
       <c r="E4" s="5">
         <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
@@ -675,16 +669,16 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134514055</v>
+        <v>134541767</v>
       </c>
       <c r="E5" s="5">
         <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
@@ -706,16 +700,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134514814</v>
+        <v>134543415</v>
       </c>
       <c r="E6" s="5">
         <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
@@ -737,22 +731,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134515263</v>
+        <v>134544152</v>
       </c>
       <c r="E7" s="5">
         <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -768,16 +762,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134516660</v>
+        <v>134544649</v>
       </c>
       <c r="E8" s="5">
         <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
@@ -799,22 +793,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134516682</v>
+        <v>134546009</v>
       </c>
       <c r="E9" s="5">
         <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -830,16 +824,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134517442</v>
+        <v>134546210</v>
       </c>
       <c r="E10" s="5">
         <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
@@ -861,16 +855,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>134517482</v>
+        <v>134546415</v>
       </c>
       <c r="E11" s="5">
         <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
@@ -892,16 +886,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>134517899</v>
+        <v>134546875</v>
       </c>
       <c r="E12" s="5">
         <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
@@ -923,22 +917,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134520643</v>
+        <v>134548407</v>
       </c>
       <c r="E13" s="5">
         <v>601</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -954,22 +948,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134520683</v>
+        <v>134549876</v>
       </c>
       <c r="E14" s="5">
         <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -985,22 +979,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134520973</v>
+        <v>134550384</v>
       </c>
       <c r="E15" s="5">
         <v>601</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1016,13 +1010,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>134521404</v>
+        <v>134550964</v>
       </c>
       <c r="E16" s="5">
         <v>601</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>16</v>
@@ -1031,7 +1025,7 @@
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1047,16 +1041,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>134523906</v>
+        <v>134552543</v>
       </c>
       <c r="E17" s="5">
         <v>601</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1078,16 +1072,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>134524385</v>
+        <v>134534690</v>
       </c>
       <c r="E18" s="5">
         <v>601</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1109,16 +1103,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>134524906</v>
+        <v>134538285</v>
       </c>
       <c r="E19" s="5">
         <v>601</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1140,16 +1134,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>134525472</v>
+        <v>134538430</v>
       </c>
       <c r="E20" s="5">
         <v>601</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1171,16 +1165,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>134526132</v>
+        <v>134538910</v>
       </c>
       <c r="E21" s="5">
         <v>601</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1202,22 +1196,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>134526308</v>
+        <v>134546956</v>
       </c>
       <c r="E22" s="5">
         <v>601</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1233,16 +1227,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>134526758</v>
+        <v>134547276</v>
       </c>
       <c r="E23" s="5">
         <v>601</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1264,16 +1258,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>134526766</v>
+        <v>134548430</v>
       </c>
       <c r="E24" s="5">
         <v>601</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1295,16 +1289,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>134526767</v>
+        <v>134548518</v>
       </c>
       <c r="E25" s="5">
         <v>601</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1326,16 +1320,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>134526769</v>
+        <v>134556319</v>
       </c>
       <c r="E26" s="5">
         <v>601</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1357,22 +1351,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>134526986</v>
+        <v>123058958</v>
       </c>
       <c r="E27" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1388,22 +1382,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>134527040</v>
+        <v>134479095</v>
       </c>
       <c r="E28" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1419,22 +1413,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>134527677</v>
+        <v>134546070</v>
       </c>
       <c r="E29" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
       </c>
       <c r="J29" s="5">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -1450,10 +1444,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>134528052</v>
+        <v>134583576</v>
       </c>
       <c r="E30" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>19</v>
@@ -1465,7 +1459,7 @@
         <v>42</v>
       </c>
       <c r="J30" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -1481,10 +1475,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>134528053</v>
+        <v>134583605</v>
       </c>
       <c r="E31" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>19</v>
@@ -1496,7 +1490,7 @@
         <v>42</v>
       </c>
       <c r="J31" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K31" s="5">
         <v>0</v>
@@ -1512,10 +1506,10 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>134528058</v>
+        <v>134583627</v>
       </c>
       <c r="E32" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>19</v>
@@ -1527,7 +1521,7 @@
         <v>42</v>
       </c>
       <c r="J32" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -1543,10 +1537,10 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>134528412</v>
+        <v>134584603</v>
       </c>
       <c r="E33" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>19</v>
@@ -1558,7 +1552,7 @@
         <v>42</v>
       </c>
       <c r="J33" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -1574,10 +1568,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>134528882</v>
+        <v>134584625</v>
       </c>
       <c r="E34" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>19</v>
@@ -1589,7 +1583,7 @@
         <v>42</v>
       </c>
       <c r="J34" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -1605,10 +1599,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>134529087</v>
+        <v>134584727</v>
       </c>
       <c r="E35" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>19</v>
@@ -1620,7 +1614,7 @@
         <v>42</v>
       </c>
       <c r="J35" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -1636,10 +1630,10 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>134529444</v>
+        <v>134584751</v>
       </c>
       <c r="E36" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>19</v>
@@ -1651,7 +1645,7 @@
         <v>42</v>
       </c>
       <c r="J36" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -1667,10 +1661,10 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>134529621</v>
+        <v>134584768</v>
       </c>
       <c r="E37" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>19</v>
@@ -1682,7 +1676,7 @@
         <v>42</v>
       </c>
       <c r="J37" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -1698,10 +1692,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>134529979</v>
+        <v>134584805</v>
       </c>
       <c r="E38" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>19</v>
@@ -1713,7 +1707,7 @@
         <v>42</v>
       </c>
       <c r="J38" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
@@ -1729,10 +1723,10 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>134512097</v>
+        <v>134584913</v>
       </c>
       <c r="E39" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>19</v>
@@ -1744,7 +1738,7 @@
         <v>42</v>
       </c>
       <c r="J39" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K39" s="5">
         <v>0</v>
@@ -1760,10 +1754,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>134513966</v>
+        <v>134585014</v>
       </c>
       <c r="E40" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>19</v>
@@ -1775,7 +1769,7 @@
         <v>42</v>
       </c>
       <c r="J40" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -1791,10 +1785,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>134514738</v>
+        <v>134585333</v>
       </c>
       <c r="E41" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>19</v>
@@ -1806,7 +1800,7 @@
         <v>42</v>
       </c>
       <c r="J41" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -1822,10 +1816,10 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>134515657</v>
+        <v>134585831</v>
       </c>
       <c r="E42" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>19</v>
@@ -1837,7 +1831,7 @@
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -1853,10 +1847,10 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>134516508</v>
+        <v>134585939</v>
       </c>
       <c r="E43" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>19</v>
@@ -1868,7 +1862,7 @@
         <v>42</v>
       </c>
       <c r="J43" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -1884,10 +1878,10 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>134518540</v>
+        <v>134586241</v>
       </c>
       <c r="E44" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>19</v>
@@ -1899,7 +1893,7 @@
         <v>42</v>
       </c>
       <c r="J44" s="5">
-        <v>1117</v>
+        <v>718</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -1915,10 +1909,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>134519969</v>
+        <v>134586269</v>
       </c>
       <c r="E45" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>19</v>
@@ -1930,7 +1924,7 @@
         <v>42</v>
       </c>
       <c r="J45" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -1946,10 +1940,10 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>134521473</v>
+        <v>134587010</v>
       </c>
       <c r="E46" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>19</v>
@@ -1961,7 +1955,7 @@
         <v>42</v>
       </c>
       <c r="J46" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
@@ -1977,10 +1971,10 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>134521902</v>
+        <v>134587102</v>
       </c>
       <c r="E47" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>19</v>
@@ -1992,7 +1986,7 @@
         <v>42</v>
       </c>
       <c r="J47" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -2008,10 +2002,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>134522123</v>
+        <v>134588356</v>
       </c>
       <c r="E48" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>19</v>
@@ -2023,7 +2017,7 @@
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2039,10 +2033,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>134522786</v>
+        <v>134589336</v>
       </c>
       <c r="E49" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>19</v>
@@ -2054,7 +2048,7 @@
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2070,10 +2064,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>134523790</v>
+        <v>134592302</v>
       </c>
       <c r="E50" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>19</v>
@@ -2085,7 +2079,7 @@
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2101,10 +2095,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>134523911</v>
+        <v>134592606</v>
       </c>
       <c r="E51" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>19</v>
@@ -2116,7 +2110,7 @@
         <v>42</v>
       </c>
       <c r="J51" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -2132,10 +2126,10 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>134524464</v>
+        <v>134594786</v>
       </c>
       <c r="E52" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>19</v>
@@ -2147,7 +2141,7 @@
         <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>8003</v>
+        <v>718</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -2163,10 +2157,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>134525567</v>
+        <v>134594833</v>
       </c>
       <c r="E53" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>19</v>
@@ -2178,7 +2172,7 @@
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2194,10 +2188,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>134528159</v>
+        <v>134598193</v>
       </c>
       <c r="E54" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>19</v>
@@ -2209,7 +2203,7 @@
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2225,10 +2219,10 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>134529553</v>
+        <v>134598981</v>
       </c>
       <c r="E55" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>19</v>
@@ -2240,7 +2234,7 @@
         <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -2256,22 +2250,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>134536282</v>
+        <v>134599190</v>
       </c>
       <c r="E56" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
       </c>
       <c r="J56" s="5">
-        <v>1735</v>
+        <v>718</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -2287,22 +2281,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>134548913</v>
+        <v>134599275</v>
       </c>
       <c r="E57" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>1735</v>
+        <v>718</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -2318,22 +2312,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>123058958</v>
+        <v>134600131</v>
       </c>
       <c r="E58" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
       </c>
       <c r="J58" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -2349,22 +2343,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>134479095</v>
+        <v>134601349</v>
       </c>
       <c r="E59" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>8021</v>
+        <v>718</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2379,926 +2373,162 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
-        <v>134546070</v>
-      </c>
-      <c r="E60" s="5">
-        <v>1211</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="5">
-        <v>42</v>
-      </c>
-      <c r="J60" s="5">
-        <v>8021</v>
-      </c>
-      <c r="K60" s="5">
-        <v>0</v>
-      </c>
-      <c r="L60" s="5">
-        <v>61</v>
-      </c>
+      <c r="A60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O60" s="5"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
-        <v>134541909</v>
-      </c>
-      <c r="E61" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" s="5">
-        <v>42</v>
-      </c>
-      <c r="J61" s="5">
-        <v>718</v>
-      </c>
-      <c r="K61" s="5">
-        <v>0</v>
-      </c>
-      <c r="L61" s="5">
-        <v>61</v>
-      </c>
+      <c r="A61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O61" s="5"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
-        <v>134544997</v>
-      </c>
-      <c r="E62" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62" s="5">
-        <v>42</v>
-      </c>
-      <c r="J62" s="5">
-        <v>718</v>
-      </c>
-      <c r="K62" s="5">
-        <v>0</v>
-      </c>
-      <c r="L62" s="5">
-        <v>61</v>
-      </c>
+      <c r="A62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O62" s="5"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
-        <v>134545900</v>
-      </c>
-      <c r="E63" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I63" s="5">
-        <v>42</v>
-      </c>
-      <c r="J63" s="5">
-        <v>718</v>
-      </c>
-      <c r="K63" s="5">
-        <v>0</v>
-      </c>
-      <c r="L63" s="5">
-        <v>61</v>
-      </c>
+      <c r="A63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O63" s="5"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
-        <v>134546672</v>
-      </c>
-      <c r="E64" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="5">
-        <v>42</v>
-      </c>
-      <c r="J64" s="5">
-        <v>718</v>
-      </c>
-      <c r="K64" s="5">
-        <v>0</v>
-      </c>
-      <c r="L64" s="5">
-        <v>61</v>
-      </c>
+      <c r="A64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
-        <v>134547392</v>
-      </c>
-      <c r="E65" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" s="5">
-        <v>42</v>
-      </c>
-      <c r="J65" s="5">
-        <v>718</v>
-      </c>
-      <c r="K65" s="5">
-        <v>0</v>
-      </c>
-      <c r="L65" s="5">
-        <v>61</v>
-      </c>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
-        <v>134548131</v>
-      </c>
-      <c r="E66" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="5">
-        <v>42</v>
-      </c>
-      <c r="J66" s="5">
-        <v>718</v>
-      </c>
-      <c r="K66" s="5">
-        <v>0</v>
-      </c>
-      <c r="L66" s="5">
-        <v>61</v>
-      </c>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
-        <v>134548597</v>
-      </c>
-      <c r="E67" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I67" s="5">
-        <v>42</v>
-      </c>
-      <c r="J67" s="5">
-        <v>718</v>
-      </c>
-      <c r="K67" s="5">
-        <v>0</v>
-      </c>
-      <c r="L67" s="5">
-        <v>61</v>
-      </c>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
-        <v>134548805</v>
-      </c>
-      <c r="E68" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I68" s="5">
-        <v>42</v>
-      </c>
-      <c r="J68" s="5">
-        <v>718</v>
-      </c>
-      <c r="K68" s="5">
-        <v>0</v>
-      </c>
-      <c r="L68" s="5">
-        <v>61</v>
-      </c>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
-        <v>134549806</v>
-      </c>
-      <c r="E69" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" s="5">
-        <v>42</v>
-      </c>
-      <c r="J69" s="5">
-        <v>718</v>
-      </c>
-      <c r="K69" s="5">
-        <v>0</v>
-      </c>
-      <c r="L69" s="5">
-        <v>61</v>
-      </c>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
-        <v>134551928</v>
-      </c>
-      <c r="E70" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I70" s="5">
-        <v>42</v>
-      </c>
-      <c r="J70" s="5">
-        <v>718</v>
-      </c>
-      <c r="K70" s="5">
-        <v>0</v>
-      </c>
-      <c r="L70" s="5">
-        <v>61</v>
-      </c>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="5">
-        <v>134554161</v>
-      </c>
-      <c r="E71" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I71" s="5">
-        <v>42</v>
-      </c>
-      <c r="J71" s="5">
-        <v>718</v>
-      </c>
-      <c r="K71" s="5">
-        <v>0</v>
-      </c>
-      <c r="L71" s="5">
-        <v>61</v>
-      </c>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="5">
-        <v>134562792</v>
-      </c>
-      <c r="E72" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" s="5">
-        <v>42</v>
-      </c>
-      <c r="J72" s="5">
-        <v>718</v>
-      </c>
-      <c r="K72" s="5">
-        <v>0</v>
-      </c>
-      <c r="L72" s="5">
-        <v>61</v>
-      </c>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="5">
-        <v>134566786</v>
-      </c>
-      <c r="E73" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I73" s="5">
-        <v>42</v>
-      </c>
-      <c r="J73" s="5">
-        <v>718</v>
-      </c>
-      <c r="K73" s="5">
-        <v>0</v>
-      </c>
-      <c r="L73" s="5">
-        <v>61</v>
-      </c>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
-      <c r="O73" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" s="5">
-        <v>134567466</v>
-      </c>
-      <c r="E74" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I74" s="5">
-        <v>42</v>
-      </c>
-      <c r="J74" s="5">
-        <v>718</v>
-      </c>
-      <c r="K74" s="5">
-        <v>0</v>
-      </c>
-      <c r="L74" s="5">
-        <v>61</v>
-      </c>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="5">
-        <v>134570044</v>
-      </c>
-      <c r="E75" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I75" s="5">
-        <v>42</v>
-      </c>
-      <c r="J75" s="5">
-        <v>718</v>
-      </c>
-      <c r="K75" s="5">
-        <v>0</v>
-      </c>
-      <c r="L75" s="5">
-        <v>61</v>
-      </c>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
-      <c r="O75" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="5">
-        <v>134570350</v>
-      </c>
-      <c r="E76" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I76" s="5">
-        <v>42</v>
-      </c>
-      <c r="J76" s="5">
-        <v>718</v>
-      </c>
-      <c r="K76" s="5">
-        <v>0</v>
-      </c>
-      <c r="L76" s="5">
-        <v>61</v>
-      </c>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5">
-        <v>134570366</v>
-      </c>
-      <c r="E77" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77" s="5">
-        <v>42</v>
-      </c>
-      <c r="J77" s="5">
-        <v>718</v>
-      </c>
-      <c r="K77" s="5">
-        <v>0</v>
-      </c>
-      <c r="L77" s="5">
-        <v>61</v>
-      </c>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
-      <c r="O77" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
-        <v>134570396</v>
-      </c>
-      <c r="E78" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I78" s="5">
-        <v>42</v>
-      </c>
-      <c r="J78" s="5">
-        <v>718</v>
-      </c>
-      <c r="K78" s="5">
-        <v>0</v>
-      </c>
-      <c r="L78" s="5">
-        <v>61</v>
-      </c>
-      <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
-      <c r="O78" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="5">
-        <v>134572175</v>
-      </c>
-      <c r="E79" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79" s="5">
-        <v>42</v>
-      </c>
-      <c r="J79" s="5">
-        <v>718</v>
-      </c>
-      <c r="K79" s="5">
-        <v>0</v>
-      </c>
-      <c r="L79" s="5">
-        <v>61</v>
-      </c>
-      <c r="M79" s="5"/>
-      <c r="N79" s="5"/>
-      <c r="O79" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
-        <v>134572862</v>
-      </c>
-      <c r="E80" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I80" s="5">
-        <v>42</v>
-      </c>
-      <c r="J80" s="5">
-        <v>718</v>
-      </c>
-      <c r="K80" s="5">
-        <v>0</v>
-      </c>
-      <c r="L80" s="5">
-        <v>61</v>
-      </c>
-      <c r="M80" s="5"/>
-      <c r="N80" s="5"/>
-      <c r="O80" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" s="5">
-        <v>134573848</v>
-      </c>
-      <c r="E81" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I81" s="5">
-        <v>42</v>
-      </c>
-      <c r="J81" s="5">
-        <v>718</v>
-      </c>
-      <c r="K81" s="5">
-        <v>0</v>
-      </c>
-      <c r="L81" s="5">
-        <v>61</v>
-      </c>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="5">
-        <v>134575269</v>
-      </c>
-      <c r="E82" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I82" s="5">
-        <v>42</v>
-      </c>
-      <c r="J82" s="5">
-        <v>718</v>
-      </c>
-      <c r="K82" s="5">
-        <v>0</v>
-      </c>
-      <c r="L82" s="5">
-        <v>61</v>
-      </c>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
-      <c r="O82" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
-        <v>134575340</v>
-      </c>
-      <c r="E83" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I83" s="5">
-        <v>42</v>
-      </c>
-      <c r="J83" s="5">
-        <v>718</v>
-      </c>
-      <c r="K83" s="5">
-        <v>0</v>
-      </c>
-      <c r="L83" s="5">
-        <v>61</v>
-      </c>
-      <c r="M83" s="5"/>
-      <c r="N83" s="5"/>
-      <c r="O83" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
-        <v>134575390</v>
-      </c>
-      <c r="E84" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I84" s="5">
-        <v>42</v>
-      </c>
-      <c r="J84" s="5">
-        <v>718</v>
-      </c>
-      <c r="K84" s="5">
-        <v>0</v>
-      </c>
-      <c r="L84" s="5">
-        <v>61</v>
-      </c>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
-        <v>134575445</v>
-      </c>
-      <c r="E85" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I85" s="5">
-        <v>42</v>
-      </c>
-      <c r="J85" s="5">
-        <v>718</v>
-      </c>
-      <c r="K85" s="5">
-        <v>0</v>
-      </c>
-      <c r="L85" s="5">
-        <v>61</v>
-      </c>
-      <c r="M85" s="5"/>
-      <c r="N85" s="5"/>
-      <c r="O85" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="5">
-        <v>134576027</v>
-      </c>
-      <c r="E86" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I86" s="5">
-        <v>42</v>
-      </c>
-      <c r="J86" s="5">
-        <v>718</v>
-      </c>
-      <c r="K86" s="5">
-        <v>0</v>
-      </c>
-      <c r="L86" s="5">
-        <v>61</v>
-      </c>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
-      <c r="O86" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
-        <v>134576871</v>
-      </c>
-      <c r="E87" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87" s="5">
-        <v>42</v>
-      </c>
-      <c r="J87" s="5">
-        <v>718</v>
-      </c>
-      <c r="K87" s="5">
-        <v>0</v>
-      </c>
-      <c r="L87" s="5">
-        <v>61</v>
-      </c>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
-      <c r="O87" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" s="5"/>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
-      <c r="O88" s="5"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" s="5"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
-      <c r="O89" s="5"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="5"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
-      <c r="O90" s="5"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="5"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="5"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-      <c r="O92" s="5"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" s="5"/>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
-      <c r="O93" s="5"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="5"/>
-      <c r="M94" s="5"/>
-      <c r="N94" s="5"/>
-      <c r="O94" s="5"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="5"/>
-      <c r="M95" s="5"/>
-      <c r="N95" s="5"/>
-      <c r="O95" s="5"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="5"/>
-      <c r="M96" s="5"/>
-      <c r="N96" s="5"/>
-      <c r="O96" s="5"/>
+      <c r="O64" s="5"/>
+    </row>
+    <row r="65" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+    </row>
+    <row r="66" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+    </row>
+    <row r="67" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+    </row>
+    <row r="68" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+    </row>
+    <row r="69" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+    </row>
+    <row r="70" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+    </row>
+    <row r="71" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+    </row>
+    <row r="72" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+    </row>
+    <row r="73" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+    </row>
+    <row r="74" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+    </row>
+    <row r="75" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+    </row>
+    <row r="76" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+    </row>
+    <row r="77" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+    </row>
+    <row r="78" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+    </row>
+    <row r="79" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+    </row>
+    <row r="80" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+    </row>
+    <row r="81" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+    </row>
+    <row r="82" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+    </row>
+    <row r="83" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+    </row>
+    <row r="84" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+    </row>
+    <row r="85" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+    </row>
+    <row r="86" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+    </row>
+    <row r="87" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+    </row>
+    <row r="88" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+    </row>
+    <row r="89" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+    </row>
+    <row r="90" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+    </row>
+    <row r="91" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+    </row>
+    <row r="92" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+    </row>
+    <row r="93" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+    </row>
+    <row r="94" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+    </row>
+    <row r="95" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+    </row>
+    <row r="96" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
     </row>
     <row r="97" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F97" s="8"/>
@@ -3759,31 +2989,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40570CED-2235-424F-AF50-414666B26235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BEC5FB-1247-418C-B0C0-7EE1DFDE1857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>23/9/2025</t>
+  </si>
+  <si>
+    <t>22/9/2025</t>
+  </si>
+  <si>
+    <t>24/9/2025</t>
   </si>
 </sst>
 </file>
@@ -576,22 +582,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>134537077</v>
+        <v>134562531</v>
       </c>
       <c r="E2" s="5">
         <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -607,22 +613,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134538558</v>
+        <v>134562728</v>
       </c>
       <c r="E3" s="5">
         <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>1117</v>
+        <v>8013</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -638,16 +644,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>134541522</v>
+        <v>134563556</v>
       </c>
       <c r="E4" s="5">
         <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
@@ -669,16 +675,16 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134541767</v>
+        <v>134564249</v>
       </c>
       <c r="E5" s="5">
         <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
@@ -700,16 +706,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134543415</v>
+        <v>134564423</v>
       </c>
       <c r="E6" s="5">
         <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
@@ -731,22 +737,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134544152</v>
+        <v>134564540</v>
       </c>
       <c r="E7" s="5">
         <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -762,22 +768,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134544649</v>
+        <v>134564555</v>
       </c>
       <c r="E8" s="5">
         <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -793,22 +799,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134546009</v>
+        <v>134565014</v>
       </c>
       <c r="E9" s="5">
         <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -824,16 +830,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134546210</v>
+        <v>134568315</v>
       </c>
       <c r="E10" s="5">
         <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
@@ -855,16 +861,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>134546415</v>
+        <v>134571167</v>
       </c>
       <c r="E11" s="5">
         <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
@@ -886,22 +892,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>134546875</v>
+        <v>134572425</v>
       </c>
       <c r="E12" s="5">
         <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -917,16 +923,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134548407</v>
+        <v>134572428</v>
       </c>
       <c r="E13" s="5">
         <v>601</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
@@ -948,22 +954,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134549876</v>
+        <v>134572537</v>
       </c>
       <c r="E14" s="5">
         <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -979,22 +985,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134550384</v>
+        <v>134574942</v>
       </c>
       <c r="E15" s="5">
         <v>601</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1010,22 +1016,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>134550964</v>
+        <v>134574945</v>
       </c>
       <c r="E16" s="5">
         <v>601</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1041,22 +1047,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>134552543</v>
+        <v>134574950</v>
       </c>
       <c r="E17" s="5">
         <v>601</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1072,22 +1078,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>134534690</v>
+        <v>134574956</v>
       </c>
       <c r="E18" s="5">
         <v>601</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1103,22 +1109,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>134538285</v>
+        <v>134574960</v>
       </c>
       <c r="E19" s="5">
         <v>601</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1134,16 +1140,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>134538430</v>
+        <v>134575522</v>
       </c>
       <c r="E20" s="5">
         <v>601</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1165,16 +1171,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>134538910</v>
+        <v>134577292</v>
       </c>
       <c r="E21" s="5">
         <v>601</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1196,22 +1202,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>134546956</v>
+        <v>134577295</v>
       </c>
       <c r="E22" s="5">
         <v>601</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1227,16 +1233,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>134547276</v>
+        <v>134578128</v>
       </c>
       <c r="E23" s="5">
         <v>601</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1258,16 +1264,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>134548430</v>
+        <v>134578970</v>
       </c>
       <c r="E24" s="5">
         <v>601</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1289,22 +1295,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>134548518</v>
+        <v>134579188</v>
       </c>
       <c r="E25" s="5">
         <v>601</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
       </c>
       <c r="J25" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -1320,22 +1326,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>134556319</v>
+        <v>134579436</v>
       </c>
       <c r="E26" s="5">
         <v>601</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1351,22 +1357,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>123058958</v>
+        <v>134579772</v>
       </c>
       <c r="E27" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1382,22 +1388,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>134479095</v>
+        <v>134562605</v>
       </c>
       <c r="E28" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1413,22 +1419,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>134546070</v>
+        <v>134564067</v>
       </c>
       <c r="E29" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
       </c>
       <c r="J29" s="5">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -1444,22 +1450,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>134583576</v>
+        <v>134564102</v>
       </c>
       <c r="E30" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
       </c>
       <c r="J30" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -1475,22 +1481,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>134583605</v>
+        <v>134564557</v>
       </c>
       <c r="E31" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
       </c>
       <c r="J31" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K31" s="5">
         <v>0</v>
@@ -1506,22 +1512,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>134583627</v>
+        <v>134567405</v>
       </c>
       <c r="E32" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
       </c>
       <c r="J32" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -1537,22 +1543,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>134584603</v>
+        <v>134568926</v>
       </c>
       <c r="E33" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
       </c>
       <c r="J33" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -1568,22 +1574,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>134584625</v>
+        <v>134570219</v>
       </c>
       <c r="E34" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
       </c>
       <c r="J34" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -1599,22 +1605,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>134584727</v>
+        <v>134571973</v>
       </c>
       <c r="E35" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
       </c>
       <c r="J35" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -1630,22 +1636,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>134584751</v>
+        <v>134573050</v>
       </c>
       <c r="E36" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
       </c>
       <c r="J36" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -1661,22 +1667,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>134584768</v>
+        <v>134575546</v>
       </c>
       <c r="E37" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
       </c>
       <c r="J37" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -1692,22 +1698,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>134584805</v>
+        <v>134575846</v>
       </c>
       <c r="E38" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
       </c>
       <c r="J38" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
@@ -1723,22 +1729,22 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>134584913</v>
+        <v>123058958</v>
       </c>
       <c r="E39" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
       </c>
       <c r="J39" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K39" s="5">
         <v>0</v>
@@ -1754,22 +1760,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>134585014</v>
+        <v>134479095</v>
       </c>
       <c r="E40" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
       </c>
       <c r="J40" s="5">
-        <v>718</v>
+        <v>8021</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -1785,22 +1791,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>134585333</v>
+        <v>134546070</v>
       </c>
       <c r="E41" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
       </c>
       <c r="J41" s="5">
-        <v>718</v>
+        <v>8021</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -1816,13 +1822,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>134585831</v>
+        <v>130159652</v>
       </c>
       <c r="E42" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>19</v>
@@ -1831,7 +1837,7 @@
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -1847,13 +1853,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>134585939</v>
+        <v>131482612</v>
       </c>
       <c r="E43" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>19</v>
@@ -1862,7 +1868,7 @@
         <v>42</v>
       </c>
       <c r="J43" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -1878,13 +1884,13 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>134586241</v>
+        <v>131519591</v>
       </c>
       <c r="E44" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>19</v>
@@ -1893,7 +1899,7 @@
         <v>42</v>
       </c>
       <c r="J44" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -1909,22 +1915,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>134586269</v>
+        <v>131724175</v>
       </c>
       <c r="E45" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
       </c>
       <c r="J45" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -1940,13 +1946,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>134587010</v>
+        <v>131848472</v>
       </c>
       <c r="E46" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>19</v>
@@ -1955,7 +1961,7 @@
         <v>42</v>
       </c>
       <c r="J46" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
@@ -1971,22 +1977,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>134587102</v>
+        <v>132130662</v>
       </c>
       <c r="E47" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
       </c>
       <c r="J47" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -2002,22 +2008,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>134588356</v>
+        <v>132404201</v>
       </c>
       <c r="E48" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2033,22 +2039,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>134589336</v>
+        <v>132480682</v>
       </c>
       <c r="E49" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2064,22 +2070,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>134592302</v>
+        <v>132487035</v>
       </c>
       <c r="E50" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2095,13 +2101,13 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>134592606</v>
+        <v>132809600</v>
       </c>
       <c r="E51" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>19</v>
@@ -2110,7 +2116,7 @@
         <v>42</v>
       </c>
       <c r="J51" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -2126,22 +2132,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>134594786</v>
+        <v>133025770</v>
       </c>
       <c r="E52" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -2157,22 +2163,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>134594833</v>
+        <v>133312458</v>
       </c>
       <c r="E53" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2188,13 +2194,13 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>134598193</v>
+        <v>133633310</v>
       </c>
       <c r="E54" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>19</v>
@@ -2203,7 +2209,7 @@
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2219,22 +2225,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>134598981</v>
+        <v>134229976</v>
       </c>
       <c r="E55" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -2250,22 +2256,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>134599190</v>
+        <v>134374312</v>
       </c>
       <c r="E56" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
       </c>
       <c r="J56" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -2281,13 +2287,13 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>134599275</v>
+        <v>130159652</v>
       </c>
       <c r="E57" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>19</v>
@@ -2296,7 +2302,7 @@
         <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -2312,13 +2318,13 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>134600131</v>
+        <v>131482612</v>
       </c>
       <c r="E58" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>19</v>
@@ -2327,7 +2333,7 @@
         <v>42</v>
       </c>
       <c r="J58" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -2343,22 +2349,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>134601349</v>
+        <v>132130662</v>
       </c>
       <c r="E59" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2373,98 +2379,605 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
+      <c r="A60" s="5">
+        <v>132480682</v>
+      </c>
+      <c r="E60" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
+      <c r="A61" s="5">
+        <v>132487035</v>
+      </c>
+      <c r="E61" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
+      <c r="A62" s="5">
+        <v>133312458</v>
+      </c>
+      <c r="E62" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="5"/>
+      <c r="A63" s="5">
+        <v>134607926</v>
+      </c>
+      <c r="E63" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>718</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
+      <c r="A64" s="5">
+        <v>134608107</v>
+      </c>
+      <c r="E64" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>718</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
-    </row>
-    <row r="65" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-    </row>
-    <row r="66" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-    </row>
-    <row r="67" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-    </row>
-    <row r="68" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-    </row>
-    <row r="69" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-    </row>
-    <row r="70" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-    </row>
-    <row r="71" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-    </row>
-    <row r="72" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-    </row>
-    <row r="73" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-    </row>
-    <row r="74" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-    </row>
-    <row r="75" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-    </row>
-    <row r="76" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-    </row>
-    <row r="77" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-    </row>
-    <row r="78" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-    </row>
-    <row r="79" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-    </row>
-    <row r="80" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>134608208</v>
+      </c>
+      <c r="E65" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>718</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>134608316</v>
+      </c>
+      <c r="E66" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>718</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>134608399</v>
+      </c>
+      <c r="E67" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>718</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>134608416</v>
+      </c>
+      <c r="E68" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>718</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>134608424</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>718</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>134611956</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>718</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>134612201</v>
+      </c>
+      <c r="E71" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>718</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>134614731</v>
+      </c>
+      <c r="E72" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>718</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>134615492</v>
+      </c>
+      <c r="E73" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>718</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>134617146</v>
+      </c>
+      <c r="E74" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>718</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>134618697</v>
+      </c>
+      <c r="E75" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
+        <v>718</v>
+      </c>
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>134620961</v>
+      </c>
+      <c r="E76" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>718</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>134621074</v>
+      </c>
+      <c r="E77" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>718</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>134624156</v>
+      </c>
+      <c r="E78" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>718</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
     </row>
     <row r="81" spans="6:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F81" s="8"/>
@@ -2989,31 +3502,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07F0AA4-B917-456E-BE65-BEBE2A202B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5074206A-E84C-4303-8B38-9F540C103CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="21">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>6/10/2025</t>
+  </si>
+  <si>
+    <t>8/10/2025</t>
   </si>
   <si>
     <t>8/3/2023</t>
@@ -503,7 +509,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -573,22 +579,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>123058958</v>
+        <v>134782091</v>
       </c>
       <c r="E2" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -604,22 +610,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134810826</v>
+        <v>134793188</v>
       </c>
       <c r="E3" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -635,22 +641,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>134811334</v>
+        <v>134794207</v>
       </c>
       <c r="E4" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -666,22 +672,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134812278</v>
+        <v>134798359</v>
       </c>
       <c r="E5" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -697,22 +703,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134812573</v>
+        <v>134798518</v>
       </c>
       <c r="E6" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -728,22 +734,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134814767</v>
+        <v>134799661</v>
       </c>
       <c r="E7" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -759,22 +765,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134816565</v>
+        <v>134800252</v>
       </c>
       <c r="E8" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -790,22 +796,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134818494</v>
+        <v>134802002</v>
       </c>
       <c r="E9" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -821,22 +827,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134818565</v>
+        <v>134802043</v>
       </c>
       <c r="E10" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -852,22 +858,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>134818866</v>
+        <v>134803957</v>
       </c>
       <c r="E11" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -883,22 +889,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>134819040</v>
+        <v>134804455</v>
       </c>
       <c r="E12" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -914,22 +920,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134819414</v>
+        <v>134805086</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -945,22 +951,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134819496</v>
+        <v>134805542</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -976,22 +982,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134820288</v>
+        <v>134805577</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1002,6 +1008,2920 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>134049594</v>
+      </c>
+      <c r="E16" s="5">
+        <v>601</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="5">
+        <v>42</v>
+      </c>
+      <c r="J16" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>61</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>134049656</v>
+      </c>
+      <c r="E17" s="5">
+        <v>601</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="5">
+        <v>42</v>
+      </c>
+      <c r="J17" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>61</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>134049703</v>
+      </c>
+      <c r="E18" s="5">
+        <v>601</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="5">
+        <v>42</v>
+      </c>
+      <c r="J18" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>61</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>134049726</v>
+      </c>
+      <c r="E19" s="5">
+        <v>601</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="5">
+        <v>42</v>
+      </c>
+      <c r="J19" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>61</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>134049776</v>
+      </c>
+      <c r="E20" s="5">
+        <v>601</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="5">
+        <v>42</v>
+      </c>
+      <c r="J20" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>61</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>134791786</v>
+      </c>
+      <c r="E21" s="5">
+        <v>601</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="5">
+        <v>42</v>
+      </c>
+      <c r="J21" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <v>61</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>134792685</v>
+      </c>
+      <c r="E22" s="5">
+        <v>601</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="5">
+        <v>42</v>
+      </c>
+      <c r="J22" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>61</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>134795017</v>
+      </c>
+      <c r="E23" s="5">
+        <v>601</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="5">
+        <v>42</v>
+      </c>
+      <c r="J23" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5">
+        <v>61</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>134800126</v>
+      </c>
+      <c r="E24" s="5">
+        <v>601</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="5">
+        <v>42</v>
+      </c>
+      <c r="J24" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>61</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>134800422</v>
+      </c>
+      <c r="E25" s="5">
+        <v>601</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="5">
+        <v>42</v>
+      </c>
+      <c r="J25" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>61</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>134801322</v>
+      </c>
+      <c r="E26" s="5">
+        <v>601</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="5">
+        <v>42</v>
+      </c>
+      <c r="J26" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <v>61</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>134801354</v>
+      </c>
+      <c r="E27" s="5">
+        <v>601</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="5">
+        <v>42</v>
+      </c>
+      <c r="J27" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <v>61</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>134801748</v>
+      </c>
+      <c r="E28" s="5">
+        <v>601</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="5">
+        <v>42</v>
+      </c>
+      <c r="J28" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <v>61</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>134803562</v>
+      </c>
+      <c r="E29" s="5">
+        <v>601</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="5">
+        <v>42</v>
+      </c>
+      <c r="J29" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>61</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>134804020</v>
+      </c>
+      <c r="E30" s="5">
+        <v>601</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="5">
+        <v>42</v>
+      </c>
+      <c r="J30" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <v>61</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>123058958</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="5">
+        <v>42</v>
+      </c>
+      <c r="J31" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>61</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>129942044</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="5">
+        <v>42</v>
+      </c>
+      <c r="J32" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>61</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>130048197</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="5">
+        <v>42</v>
+      </c>
+      <c r="J33" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>61</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>130067501</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="5">
+        <v>42</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>61</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>130115441</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="5">
+        <v>42</v>
+      </c>
+      <c r="J35" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>61</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>130390129</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="5">
+        <v>42</v>
+      </c>
+      <c r="J36" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>61</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>130468846</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="5">
+        <v>42</v>
+      </c>
+      <c r="J37" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>61</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>130871218</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="5">
+        <v>42</v>
+      </c>
+      <c r="J38" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>61</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>131067382</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="5">
+        <v>42</v>
+      </c>
+      <c r="J39" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>61</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>131312355</v>
+      </c>
+      <c r="E40" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="5">
+        <v>42</v>
+      </c>
+      <c r="J40" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>61</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>131409786</v>
+      </c>
+      <c r="E41" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="5">
+        <v>42</v>
+      </c>
+      <c r="J41" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>61</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>131745589</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="5">
+        <v>42</v>
+      </c>
+      <c r="J42" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>61</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>132082804</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="5">
+        <v>42</v>
+      </c>
+      <c r="J43" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>61</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>132215249</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="5">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>61</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>132521930</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="5">
+        <v>42</v>
+      </c>
+      <c r="J45" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5">
+        <v>61</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>132891382</v>
+      </c>
+      <c r="E46" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="5">
+        <v>42</v>
+      </c>
+      <c r="J46" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>61</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>132998349</v>
+      </c>
+      <c r="E47" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="5">
+        <v>42</v>
+      </c>
+      <c r="J47" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>61</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>133004043</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="5">
+        <v>42</v>
+      </c>
+      <c r="J48" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <v>61</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>133241739</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="5">
+        <v>42</v>
+      </c>
+      <c r="J49" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>61</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>133440678</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="5">
+        <v>42</v>
+      </c>
+      <c r="J50" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>61</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>133694014</v>
+      </c>
+      <c r="E51" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="5">
+        <v>42</v>
+      </c>
+      <c r="J51" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>61</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>133794060</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="5">
+        <v>42</v>
+      </c>
+      <c r="J52" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>61</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>133812108</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="5">
+        <v>42</v>
+      </c>
+      <c r="J53" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <v>61</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>133830012</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="5">
+        <v>42</v>
+      </c>
+      <c r="J54" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>61</v>
+      </c>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>133876074</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" s="5">
+        <v>42</v>
+      </c>
+      <c r="J55" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>61</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>134044334</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="5">
+        <v>42</v>
+      </c>
+      <c r="J56" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>61</v>
+      </c>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>134347588</v>
+      </c>
+      <c r="E57" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="5">
+        <v>42</v>
+      </c>
+      <c r="J57" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>61</v>
+      </c>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>134415746</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="5">
+        <v>42</v>
+      </c>
+      <c r="J58" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>61</v>
+      </c>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>134470689</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="5">
+        <v>42</v>
+      </c>
+      <c r="J59" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5">
+        <v>61</v>
+      </c>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>134476918</v>
+      </c>
+      <c r="E60" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>134533973</v>
+      </c>
+      <c r="E61" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>134666166</v>
+      </c>
+      <c r="E62" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>134722520</v>
+      </c>
+      <c r="E63" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>134723349</v>
+      </c>
+      <c r="E64" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>134774522</v>
+      </c>
+      <c r="E65" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>134778448</v>
+      </c>
+      <c r="E66" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>134782739</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>129942044</v>
+      </c>
+      <c r="E68" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>130048197</v>
+      </c>
+      <c r="E69" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>130115441</v>
+      </c>
+      <c r="E70" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>130468846</v>
+      </c>
+      <c r="E71" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>132082804</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>132521930</v>
+      </c>
+      <c r="E73" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>132891382</v>
+      </c>
+      <c r="E74" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>132998349</v>
+      </c>
+      <c r="E75" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>133004043</v>
+      </c>
+      <c r="E76" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>133241739</v>
+      </c>
+      <c r="E77" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>133694014</v>
+      </c>
+      <c r="E78" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>133794060</v>
+      </c>
+      <c r="E79" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="5">
+        <v>42</v>
+      </c>
+      <c r="J79" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5">
+        <v>61</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>133812108</v>
+      </c>
+      <c r="E80" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="5">
+        <v>42</v>
+      </c>
+      <c r="J80" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>61</v>
+      </c>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>134476918</v>
+      </c>
+      <c r="E81" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="5">
+        <v>42</v>
+      </c>
+      <c r="J81" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>61</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>134722520</v>
+      </c>
+      <c r="E82" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="5">
+        <v>42</v>
+      </c>
+      <c r="J82" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5">
+        <v>61</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>134723349</v>
+      </c>
+      <c r="E83" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="5">
+        <v>42</v>
+      </c>
+      <c r="J83" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5">
+        <v>61</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>134774522</v>
+      </c>
+      <c r="E84" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="5">
+        <v>42</v>
+      </c>
+      <c r="J84" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5">
+        <v>61</v>
+      </c>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>134778448</v>
+      </c>
+      <c r="E85" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" s="5">
+        <v>42</v>
+      </c>
+      <c r="J85" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5">
+        <v>61</v>
+      </c>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>134782739</v>
+      </c>
+      <c r="E86" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I86" s="5">
+        <v>42</v>
+      </c>
+      <c r="J86" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5">
+        <v>61</v>
+      </c>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>134830177</v>
+      </c>
+      <c r="E87" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" s="5">
+        <v>42</v>
+      </c>
+      <c r="J87" s="5">
+        <v>718</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5">
+        <v>61</v>
+      </c>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>134830908</v>
+      </c>
+      <c r="E88" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>718</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>134831345</v>
+      </c>
+      <c r="E89" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      </c>
+      <c r="J89" s="5">
+        <v>718</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5">
+        <v>61</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
+        <v>134831706</v>
+      </c>
+      <c r="E90" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" s="5">
+        <v>42</v>
+      </c>
+      <c r="J90" s="5">
+        <v>718</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5">
+        <v>61</v>
+      </c>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>134833259</v>
+      </c>
+      <c r="E91" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="5">
+        <v>42</v>
+      </c>
+      <c r="J91" s="5">
+        <v>718</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5">
+        <v>61</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
+        <v>134833985</v>
+      </c>
+      <c r="E92" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92" s="5">
+        <v>42</v>
+      </c>
+      <c r="J92" s="5">
+        <v>718</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5">
+        <v>61</v>
+      </c>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>134835485</v>
+      </c>
+      <c r="E93" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93" s="5">
+        <v>42</v>
+      </c>
+      <c r="J93" s="5">
+        <v>718</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5">
+        <v>61</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
+        <v>134837818</v>
+      </c>
+      <c r="E94" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" s="5">
+        <v>42</v>
+      </c>
+      <c r="J94" s="5">
+        <v>718</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5">
+        <v>61</v>
+      </c>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>134838232</v>
+      </c>
+      <c r="E95" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95" s="5">
+        <v>42</v>
+      </c>
+      <c r="J95" s="5">
+        <v>718</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>61</v>
+      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="5">
+        <v>134840130</v>
+      </c>
+      <c r="E96" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="5">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5">
+        <v>718</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5">
+        <v>61</v>
+      </c>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
+        <v>134840587</v>
+      </c>
+      <c r="E97" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97" s="5">
+        <v>42</v>
+      </c>
+      <c r="J97" s="5">
+        <v>718</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5">
+        <v>61</v>
+      </c>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="5">
+        <v>134843882</v>
+      </c>
+      <c r="E98" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="5">
+        <v>42</v>
+      </c>
+      <c r="J98" s="5">
+        <v>718</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5">
+        <v>61</v>
+      </c>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
+        <v>134844126</v>
+      </c>
+      <c r="E99" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" s="5">
+        <v>42</v>
+      </c>
+      <c r="J99" s="5">
+        <v>718</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
+        <v>61</v>
+      </c>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="5">
+        <v>134845484</v>
+      </c>
+      <c r="E100" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="5">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5">
+        <v>718</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>61</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>134845934</v>
+      </c>
+      <c r="E101" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="5">
+        <v>42</v>
+      </c>
+      <c r="J101" s="5">
+        <v>718</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>61</v>
+      </c>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="5">
+        <v>134846101</v>
+      </c>
+      <c r="E102" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="5">
+        <v>42</v>
+      </c>
+      <c r="J102" s="5">
+        <v>718</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>61</v>
+      </c>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
+        <v>134846393</v>
+      </c>
+      <c r="E103" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="5">
+        <v>42</v>
+      </c>
+      <c r="J103" s="5">
+        <v>718</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>61</v>
+      </c>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="5">
+        <v>134847088</v>
+      </c>
+      <c r="E104" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104" s="5">
+        <v>42</v>
+      </c>
+      <c r="J104" s="5">
+        <v>718</v>
+      </c>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5">
+        <v>61</v>
+      </c>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
+        <v>134847367</v>
+      </c>
+      <c r="E105" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="5">
+        <v>42</v>
+      </c>
+      <c r="J105" s="5">
+        <v>718</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5">
+        <v>61</v>
+      </c>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="5">
+        <v>134847430</v>
+      </c>
+      <c r="E106" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="5">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5">
+        <v>718</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5">
+        <v>61</v>
+      </c>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="5">
+        <v>134847472</v>
+      </c>
+      <c r="E107" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="5">
+        <v>42</v>
+      </c>
+      <c r="J107" s="5">
+        <v>718</v>
+      </c>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5">
+        <v>61</v>
+      </c>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="5">
+        <v>134847636</v>
+      </c>
+      <c r="E108" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="5">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5">
+        <v>718</v>
+      </c>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5">
+        <v>61</v>
+      </c>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="5">
+        <v>134847983</v>
+      </c>
+      <c r="E109" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" s="5">
+        <v>42</v>
+      </c>
+      <c r="J109" s="5">
+        <v>718</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5">
+        <v>61</v>
+      </c>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5074206A-E84C-4303-8B38-9F540C103CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888B8A6F-2A14-416B-99C8-27B20454DE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="21">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,9 +79,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>6/10/2025</t>
-  </si>
-  <si>
     <t>8/10/2025</t>
   </si>
   <si>
@@ -92,6 +89,9 @@
   </si>
   <si>
     <t>7/10/2025</t>
+  </si>
+  <si>
+    <t>9/10/2025</t>
   </si>
 </sst>
 </file>
@@ -579,22 +579,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>134782091</v>
+        <v>134811412</v>
       </c>
       <c r="E2" s="5">
         <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -610,22 +610,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134793188</v>
+        <v>134811416</v>
       </c>
       <c r="E3" s="5">
         <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -641,16 +641,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>134794207</v>
+        <v>134811706</v>
       </c>
       <c r="E4" s="5">
         <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
@@ -672,22 +672,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134798359</v>
+        <v>134813291</v>
       </c>
       <c r="E5" s="5">
         <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -703,16 +703,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134798518</v>
+        <v>134813682</v>
       </c>
       <c r="E6" s="5">
         <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
@@ -734,22 +734,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134799661</v>
+        <v>134813689</v>
       </c>
       <c r="E7" s="5">
         <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -765,22 +765,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134800252</v>
+        <v>134814142</v>
       </c>
       <c r="E8" s="5">
         <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -796,22 +796,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134802002</v>
+        <v>134814152</v>
       </c>
       <c r="E9" s="5">
         <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -827,22 +827,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134802043</v>
+        <v>134814744</v>
       </c>
       <c r="E10" s="5">
         <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -858,16 +858,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>134803957</v>
+        <v>134819020</v>
       </c>
       <c r="E11" s="5">
         <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>134804455</v>
+        <v>134819133</v>
       </c>
       <c r="E12" s="5">
         <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -920,22 +920,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134805086</v>
+        <v>134823483</v>
       </c>
       <c r="E13" s="5">
         <v>601</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -951,16 +951,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134805542</v>
+        <v>134824702</v>
       </c>
       <c r="E14" s="5">
         <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
@@ -982,16 +982,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134805577</v>
+        <v>134825809</v>
       </c>
       <c r="E15" s="5">
         <v>601</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
@@ -1013,16 +1013,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>134049594</v>
+        <v>134825847</v>
       </c>
       <c r="E16" s="5">
         <v>601</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
@@ -1044,16 +1044,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>134049656</v>
+        <v>134826056</v>
       </c>
       <c r="E17" s="5">
         <v>601</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1075,16 +1075,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>134049703</v>
+        <v>134826075</v>
       </c>
       <c r="E18" s="5">
         <v>601</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1106,16 +1106,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>134049726</v>
+        <v>134827548</v>
       </c>
       <c r="E19" s="5">
         <v>601</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1137,16 +1137,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>134049776</v>
+        <v>134814457</v>
       </c>
       <c r="E20" s="5">
         <v>601</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1168,16 +1168,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>134791786</v>
+        <v>134814727</v>
       </c>
       <c r="E21" s="5">
         <v>601</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1199,16 +1199,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>134792685</v>
+        <v>134820710</v>
       </c>
       <c r="E22" s="5">
         <v>601</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
@@ -1230,22 +1230,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>134795017</v>
+        <v>134822682</v>
       </c>
       <c r="E23" s="5">
         <v>601</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1261,16 +1261,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>134800126</v>
+        <v>134822982</v>
       </c>
       <c r="E24" s="5">
         <v>601</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1292,16 +1292,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>134800422</v>
+        <v>134825500</v>
       </c>
       <c r="E25" s="5">
         <v>601</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1323,22 +1323,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>134801322</v>
+        <v>123058958</v>
       </c>
       <c r="E26" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1354,13 +1354,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>134801354</v>
+        <v>134829018</v>
       </c>
       <c r="E27" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>16</v>
@@ -1369,7 +1369,7 @@
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1385,22 +1385,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>134801748</v>
+        <v>129928741</v>
       </c>
       <c r="E28" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1416,22 +1416,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>134803562</v>
+        <v>130148331</v>
       </c>
       <c r="E29" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
       </c>
       <c r="J29" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -1447,22 +1447,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>134804020</v>
+        <v>130378523</v>
       </c>
       <c r="E30" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
       </c>
       <c r="J30" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -1478,13 +1478,13 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>123058958</v>
+        <v>130541971</v>
       </c>
       <c r="E31" s="5">
         <v>1211</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>19</v>
@@ -1509,16 +1509,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>129942044</v>
+        <v>130635577</v>
       </c>
       <c r="E32" s="5">
         <v>1211</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
@@ -1540,16 +1540,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>130048197</v>
+        <v>130771453</v>
       </c>
       <c r="E33" s="5">
         <v>1211</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
@@ -1571,16 +1571,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>130067501</v>
+        <v>130854496</v>
       </c>
       <c r="E34" s="5">
         <v>1211</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1602,16 +1602,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>130115441</v>
+        <v>131035148</v>
       </c>
       <c r="E35" s="5">
         <v>1211</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
@@ -1633,16 +1633,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>130390129</v>
+        <v>131068658</v>
       </c>
       <c r="E36" s="5">
         <v>1211</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
@@ -1664,16 +1664,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>130468846</v>
+        <v>131386138</v>
       </c>
       <c r="E37" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
@@ -1695,16 +1695,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>130871218</v>
+        <v>131387489</v>
       </c>
       <c r="E38" s="5">
         <v>1211</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
@@ -1726,16 +1726,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>131067382</v>
+        <v>131481897</v>
       </c>
       <c r="E39" s="5">
         <v>1211</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
@@ -1757,16 +1757,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>131312355</v>
+        <v>131584526</v>
       </c>
       <c r="E40" s="5">
         <v>1211</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
@@ -1788,16 +1788,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>131409786</v>
+        <v>131800260</v>
       </c>
       <c r="E41" s="5">
         <v>1211</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
@@ -1819,16 +1819,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>131745589</v>
+        <v>131831632</v>
       </c>
       <c r="E42" s="5">
         <v>1211</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
@@ -1850,16 +1850,16 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>132082804</v>
+        <v>131850543</v>
       </c>
       <c r="E43" s="5">
         <v>1211</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I43" s="5">
         <v>42</v>
@@ -1881,16 +1881,16 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>132215249</v>
+        <v>131879113</v>
       </c>
       <c r="E44" s="5">
         <v>1211</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
@@ -1912,16 +1912,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>132521930</v>
+        <v>132005790</v>
       </c>
       <c r="E45" s="5">
         <v>1211</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
@@ -1943,16 +1943,16 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>132891382</v>
+        <v>132035838</v>
       </c>
       <c r="E46" s="5">
         <v>1211</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" s="5">
         <v>42</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>132998349</v>
+        <v>132355733</v>
       </c>
       <c r="E47" s="5">
         <v>1211</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
@@ -2005,16 +2005,16 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>133004043</v>
+        <v>133024327</v>
       </c>
       <c r="E48" s="5">
         <v>1211</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
@@ -2036,16 +2036,16 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>133241739</v>
+        <v>133130215</v>
       </c>
       <c r="E49" s="5">
         <v>1211</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
@@ -2067,16 +2067,16 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>133440678</v>
+        <v>133397746</v>
       </c>
       <c r="E50" s="5">
         <v>1211</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
@@ -2098,16 +2098,16 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>133694014</v>
+        <v>133533274</v>
       </c>
       <c r="E51" s="5">
         <v>1211</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
@@ -2129,16 +2129,16 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>133794060</v>
+        <v>133732454</v>
       </c>
       <c r="E52" s="5">
         <v>1211</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
@@ -2160,16 +2160,16 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>133812108</v>
+        <v>133734242</v>
       </c>
       <c r="E53" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
@@ -2191,16 +2191,16 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>133830012</v>
+        <v>133743028</v>
       </c>
       <c r="E54" s="5">
         <v>1211</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
@@ -2222,16 +2222,16 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>133876074</v>
+        <v>133797114</v>
       </c>
       <c r="E55" s="5">
         <v>1211</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
@@ -2253,16 +2253,16 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>134044334</v>
+        <v>134093132</v>
       </c>
       <c r="E56" s="5">
         <v>1211</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
@@ -2284,16 +2284,16 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>134347588</v>
+        <v>134282419</v>
       </c>
       <c r="E57" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
@@ -2315,16 +2315,16 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>134415746</v>
+        <v>134300032</v>
       </c>
       <c r="E58" s="5">
         <v>1211</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
@@ -2346,16 +2346,16 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>134470689</v>
+        <v>134321680</v>
       </c>
       <c r="E59" s="5">
         <v>1211</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
@@ -2377,16 +2377,16 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>134476918</v>
+        <v>134337781</v>
       </c>
       <c r="E60" s="5">
         <v>1211</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
@@ -2408,16 +2408,16 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>134533973</v>
+        <v>134418374</v>
       </c>
       <c r="E61" s="5">
         <v>1211</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
@@ -2439,16 +2439,16 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>134666166</v>
+        <v>134620227</v>
       </c>
       <c r="E62" s="5">
         <v>1211</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I62" s="5">
         <v>42</v>
@@ -2470,16 +2470,16 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>134722520</v>
+        <v>134692484</v>
       </c>
       <c r="E63" s="5">
         <v>1211</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
@@ -2501,16 +2501,16 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>134723349</v>
+        <v>134792075</v>
       </c>
       <c r="E64" s="5">
         <v>1211</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
@@ -2532,16 +2532,16 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>134774522</v>
+        <v>129928741</v>
       </c>
       <c r="E65" s="5">
         <v>1211</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
@@ -2563,16 +2563,16 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>134778448</v>
+        <v>130148331</v>
       </c>
       <c r="E66" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>134782739</v>
+        <v>130378523</v>
       </c>
       <c r="E67" s="5">
         <v>1211</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
@@ -2625,16 +2625,16 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>129942044</v>
+        <v>130771453</v>
       </c>
       <c r="E68" s="5">
         <v>1211</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>130048197</v>
+        <v>131068658</v>
       </c>
       <c r="E69" s="5">
         <v>1211</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
@@ -2687,16 +2687,16 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>130115441</v>
+        <v>131386138</v>
       </c>
       <c r="E70" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
@@ -2718,16 +2718,16 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>130468846</v>
+        <v>131387489</v>
       </c>
       <c r="E71" s="5">
         <v>1211</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
@@ -2749,16 +2749,16 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>132082804</v>
+        <v>131584526</v>
       </c>
       <c r="E72" s="5">
         <v>1211</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I72" s="5">
         <v>42</v>
@@ -2780,16 +2780,16 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>132521930</v>
+        <v>132005790</v>
       </c>
       <c r="E73" s="5">
         <v>1211</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
@@ -2811,16 +2811,16 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>132891382</v>
+        <v>132035838</v>
       </c>
       <c r="E74" s="5">
         <v>1211</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
@@ -2842,16 +2842,16 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>132998349</v>
+        <v>133024327</v>
       </c>
       <c r="E75" s="5">
         <v>1211</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
@@ -2873,16 +2873,16 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>133004043</v>
+        <v>133732454</v>
       </c>
       <c r="E76" s="5">
         <v>1211</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
@@ -2904,16 +2904,16 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>133241739</v>
+        <v>133734242</v>
       </c>
       <c r="E77" s="5">
         <v>1211</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
@@ -2935,16 +2935,16 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>133694014</v>
+        <v>134321680</v>
       </c>
       <c r="E78" s="5">
         <v>1211</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I78" s="5">
         <v>42</v>
@@ -2966,16 +2966,16 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>133794060</v>
+        <v>134418374</v>
       </c>
       <c r="E79" s="5">
         <v>1211</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I79" s="5">
         <v>42</v>
@@ -2997,16 +2997,16 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>133812108</v>
+        <v>134792075</v>
       </c>
       <c r="E80" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I80" s="5">
         <v>42</v>
@@ -3028,22 +3028,22 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>134476918</v>
+        <v>134852934</v>
       </c>
       <c r="E81" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I81" s="5">
         <v>42</v>
       </c>
       <c r="J81" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K81" s="5">
         <v>0</v>
@@ -3059,22 +3059,22 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>134722520</v>
+        <v>134852961</v>
       </c>
       <c r="E82" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I82" s="5">
         <v>42</v>
       </c>
       <c r="J82" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K82" s="5">
         <v>0</v>
@@ -3090,22 +3090,22 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>134723349</v>
+        <v>134853159</v>
       </c>
       <c r="E83" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I83" s="5">
         <v>42</v>
       </c>
       <c r="J83" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K83" s="5">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>134774522</v>
+        <v>134856817</v>
       </c>
       <c r="E84" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I84" s="5">
         <v>42</v>
       </c>
       <c r="J84" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K84" s="5">
         <v>0</v>
@@ -3152,22 +3152,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>134778448</v>
+        <v>134857058</v>
       </c>
       <c r="E85" s="5">
-        <v>1212</v>
+        <v>2013</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I85" s="5">
         <v>42</v>
       </c>
       <c r="J85" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K85" s="5">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>134782739</v>
+        <v>134858427</v>
       </c>
       <c r="E86" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I86" s="5">
         <v>42</v>
       </c>
       <c r="J86" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K86" s="5">
         <v>0</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>134830177</v>
+        <v>134858528</v>
       </c>
       <c r="E87" s="5">
         <v>2013</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I87" s="5">
         <v>42</v>
@@ -3245,16 +3245,16 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
-        <v>134830908</v>
+        <v>134861069</v>
       </c>
       <c r="E88" s="5">
         <v>2013</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I88" s="5">
         <v>42</v>
@@ -3276,16 +3276,16 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>134831345</v>
+        <v>134861287</v>
       </c>
       <c r="E89" s="5">
         <v>2013</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I89" s="5">
         <v>42</v>
@@ -3307,16 +3307,16 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>134831706</v>
+        <v>134861370</v>
       </c>
       <c r="E90" s="5">
         <v>2013</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I90" s="5">
         <v>42</v>
@@ -3338,16 +3338,16 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>134833259</v>
+        <v>134861649</v>
       </c>
       <c r="E91" s="5">
         <v>2013</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I91" s="5">
         <v>42</v>
@@ -3369,16 +3369,16 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>134833985</v>
+        <v>134861730</v>
       </c>
       <c r="E92" s="5">
         <v>2013</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I92" s="5">
         <v>42</v>
@@ -3400,16 +3400,16 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>134835485</v>
+        <v>134865641</v>
       </c>
       <c r="E93" s="5">
         <v>2013</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I93" s="5">
         <v>42</v>
@@ -3431,16 +3431,16 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>134837818</v>
+        <v>134866574</v>
       </c>
       <c r="E94" s="5">
         <v>2013</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I94" s="5">
         <v>42</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>134838232</v>
+        <v>134867172</v>
       </c>
       <c r="E95" s="5">
         <v>2013</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I95" s="5">
         <v>42</v>
@@ -3493,16 +3493,16 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>134840130</v>
+        <v>134867507</v>
       </c>
       <c r="E96" s="5">
         <v>2013</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I96" s="5">
         <v>42</v>
@@ -3524,16 +3524,16 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>134840587</v>
+        <v>134868505</v>
       </c>
       <c r="E97" s="5">
         <v>2013</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I97" s="5">
         <v>42</v>
@@ -3554,376 +3554,76 @@
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="5">
-        <v>134843882</v>
-      </c>
-      <c r="E98" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I98" s="5">
-        <v>42</v>
-      </c>
-      <c r="J98" s="5">
-        <v>718</v>
-      </c>
-      <c r="K98" s="5">
-        <v>0</v>
-      </c>
-      <c r="L98" s="5">
-        <v>61</v>
-      </c>
+      <c r="A98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="5"/>
-      <c r="O98" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O98" s="5"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" s="5">
-        <v>134844126</v>
-      </c>
-      <c r="E99" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I99" s="5">
-        <v>42</v>
-      </c>
-      <c r="J99" s="5">
-        <v>718</v>
-      </c>
-      <c r="K99" s="5">
-        <v>0</v>
-      </c>
-      <c r="L99" s="5">
-        <v>61</v>
-      </c>
+      <c r="A99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="5"/>
-      <c r="O99" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O99" s="5"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="5">
-        <v>134845484</v>
-      </c>
-      <c r="E100" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I100" s="5">
-        <v>42</v>
-      </c>
-      <c r="J100" s="5">
-        <v>718</v>
-      </c>
-      <c r="K100" s="5">
-        <v>0</v>
-      </c>
-      <c r="L100" s="5">
-        <v>61</v>
-      </c>
+      <c r="A100" s="5"/>
       <c r="M100" s="5"/>
       <c r="N100" s="5"/>
-      <c r="O100" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O100" s="5"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="5">
-        <v>134845934</v>
-      </c>
-      <c r="E101" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I101" s="5">
-        <v>42</v>
-      </c>
-      <c r="J101" s="5">
-        <v>718</v>
-      </c>
-      <c r="K101" s="5">
-        <v>0</v>
-      </c>
-      <c r="L101" s="5">
-        <v>61</v>
-      </c>
+      <c r="A101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="5"/>
-      <c r="O101" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O101" s="5"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A102" s="5">
-        <v>134846101</v>
-      </c>
-      <c r="E102" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="5">
-        <v>42</v>
-      </c>
-      <c r="J102" s="5">
-        <v>718</v>
-      </c>
-      <c r="K102" s="5">
-        <v>0</v>
-      </c>
-      <c r="L102" s="5">
-        <v>61</v>
-      </c>
+      <c r="A102" s="5"/>
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
-      <c r="O102" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O102" s="5"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="5">
-        <v>134846393</v>
-      </c>
-      <c r="E103" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I103" s="5">
-        <v>42</v>
-      </c>
-      <c r="J103" s="5">
-        <v>718</v>
-      </c>
-      <c r="K103" s="5">
-        <v>0</v>
-      </c>
-      <c r="L103" s="5">
-        <v>61</v>
-      </c>
+      <c r="A103" s="5"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
-      <c r="O103" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O103" s="5"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="5">
-        <v>134847088</v>
-      </c>
-      <c r="E104" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I104" s="5">
-        <v>42</v>
-      </c>
-      <c r="J104" s="5">
-        <v>718</v>
-      </c>
-      <c r="K104" s="5">
-        <v>0</v>
-      </c>
-      <c r="L104" s="5">
-        <v>61</v>
-      </c>
+      <c r="A104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="5"/>
-      <c r="O104" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O104" s="5"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
-        <v>134847367</v>
-      </c>
-      <c r="E105" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I105" s="5">
-        <v>42</v>
-      </c>
-      <c r="J105" s="5">
-        <v>718</v>
-      </c>
-      <c r="K105" s="5">
-        <v>0</v>
-      </c>
-      <c r="L105" s="5">
-        <v>61</v>
-      </c>
+      <c r="A105" s="5"/>
       <c r="M105" s="5"/>
       <c r="N105" s="5"/>
-      <c r="O105" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O105" s="5"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A106" s="5">
-        <v>134847430</v>
-      </c>
-      <c r="E106" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I106" s="5">
-        <v>42</v>
-      </c>
-      <c r="J106" s="5">
-        <v>718</v>
-      </c>
-      <c r="K106" s="5">
-        <v>0</v>
-      </c>
-      <c r="L106" s="5">
-        <v>61</v>
-      </c>
+      <c r="A106" s="5"/>
       <c r="M106" s="5"/>
       <c r="N106" s="5"/>
-      <c r="O106" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O106" s="5"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A107" s="5">
-        <v>134847472</v>
-      </c>
-      <c r="E107" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I107" s="5">
-        <v>42</v>
-      </c>
-      <c r="J107" s="5">
-        <v>718</v>
-      </c>
-      <c r="K107" s="5">
-        <v>0</v>
-      </c>
-      <c r="L107" s="5">
-        <v>61</v>
-      </c>
+      <c r="A107" s="5"/>
       <c r="M107" s="5"/>
       <c r="N107" s="5"/>
-      <c r="O107" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O107" s="5"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A108" s="5">
-        <v>134847636</v>
-      </c>
-      <c r="E108" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G108" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I108" s="5">
-        <v>42</v>
-      </c>
-      <c r="J108" s="5">
-        <v>718</v>
-      </c>
-      <c r="K108" s="5">
-        <v>0</v>
-      </c>
-      <c r="L108" s="5">
-        <v>61</v>
-      </c>
+      <c r="A108" s="5"/>
       <c r="M108" s="5"/>
       <c r="N108" s="5"/>
-      <c r="O108" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O108" s="5"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A109" s="5">
-        <v>134847983</v>
-      </c>
-      <c r="E109" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G109" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I109" s="5">
-        <v>42</v>
-      </c>
-      <c r="J109" s="5">
-        <v>718</v>
-      </c>
-      <c r="K109" s="5">
-        <v>0</v>
-      </c>
-      <c r="L109" s="5">
-        <v>61</v>
-      </c>
+      <c r="A109" s="5"/>
       <c r="M109" s="5"/>
       <c r="N109" s="5"/>
-      <c r="O109" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O109" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3948,31 +3648,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57C9118-2596-47C0-ADC3-E0F8E72219C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CAC8F7-7078-42C6-961E-C244D19AF0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -88,13 +88,13 @@
     <t>15/10/2025</t>
   </si>
   <si>
-    <t>19/10/2025</t>
+    <t>21/10/2025</t>
   </si>
   <si>
-    <t>16/10/2025</t>
+    <t>20/10/2025</t>
   </si>
   <si>
-    <t>21/10/2025</t>
+    <t>22/10/2025</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -644,16 +644,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>132608764</v>
+        <v>129977252</v>
       </c>
       <c r="E4" s="5">
         <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
@@ -675,16 +675,16 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134744389</v>
+        <v>129981041</v>
       </c>
       <c r="E5" s="5">
         <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
@@ -706,16 +706,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134980163</v>
+        <v>130103261</v>
       </c>
       <c r="E6" s="5">
         <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134744389</v>
+        <v>130140731</v>
       </c>
       <c r="E7" s="5">
         <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
@@ -768,16 +768,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134980163</v>
+        <v>130171644</v>
       </c>
       <c r="E8" s="5">
         <v>1211</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134967766</v>
+        <v>130331228</v>
       </c>
       <c r="E9" s="5">
         <v>1211</v>
@@ -814,7 +814,7 @@
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -830,22 +830,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>135021734</v>
+        <v>130392502</v>
       </c>
       <c r="E10" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -861,22 +861,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>135021837</v>
+        <v>130415042</v>
       </c>
       <c r="E11" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -892,13 +892,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>135021852</v>
+        <v>130447785</v>
       </c>
       <c r="E12" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>21</v>
@@ -907,7 +907,7 @@
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -923,22 +923,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>135024746</v>
+        <v>130453805</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -954,22 +954,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>135024960</v>
+        <v>130646132</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -985,22 +985,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>135025541</v>
+        <v>131014796</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1016,22 +1016,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>135025859</v>
+        <v>131051469</v>
       </c>
       <c r="E16" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1047,22 +1047,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>135026030</v>
+        <v>131510171</v>
       </c>
       <c r="E17" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1078,22 +1078,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>135027280</v>
+        <v>131542663</v>
       </c>
       <c r="E18" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1109,22 +1109,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>135027873</v>
+        <v>131831662</v>
       </c>
       <c r="E19" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1140,22 +1140,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>135028844</v>
+        <v>132009444</v>
       </c>
       <c r="E20" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>135030072</v>
+        <v>132054028</v>
       </c>
       <c r="E21" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1202,22 +1202,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>135030361</v>
+        <v>132476887</v>
       </c>
       <c r="E22" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1233,22 +1233,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>135033549</v>
+        <v>132507159</v>
       </c>
       <c r="E23" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1264,13 +1264,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>135035076</v>
+        <v>132742671</v>
       </c>
       <c r="E24" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>21</v>
@@ -1279,7 +1279,7 @@
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1295,22 +1295,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>135036709</v>
+        <v>132743090</v>
       </c>
       <c r="E25" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
       </c>
       <c r="J25" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -1326,22 +1326,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>135037287</v>
+        <v>132751247</v>
       </c>
       <c r="E26" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1357,22 +1357,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>135037517</v>
+        <v>132752800</v>
       </c>
       <c r="E27" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1388,22 +1388,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>135038291</v>
+        <v>132848916</v>
       </c>
       <c r="E28" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1414,6 +1414,4036 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>133183256</v>
+      </c>
+      <c r="E29" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <v>42</v>
+      </c>
+      <c r="J29" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>61</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>133260531</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <v>42</v>
+      </c>
+      <c r="J30" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <v>61</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>133318874</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <v>42</v>
+      </c>
+      <c r="J31" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>61</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>133345787</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <v>42</v>
+      </c>
+      <c r="J32" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>61</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>133475129</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <v>42</v>
+      </c>
+      <c r="J33" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>61</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>133481610</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <v>42</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>61</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>133658353</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="5">
+        <v>42</v>
+      </c>
+      <c r="J35" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>61</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>133714070</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="5">
+        <v>42</v>
+      </c>
+      <c r="J36" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>61</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>133814114</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="5">
+        <v>42</v>
+      </c>
+      <c r="J37" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>61</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>133875664</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="5">
+        <v>42</v>
+      </c>
+      <c r="J38" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>61</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>133952625</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="5">
+        <v>42</v>
+      </c>
+      <c r="J39" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>61</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>133961979</v>
+      </c>
+      <c r="E40" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="5">
+        <v>42</v>
+      </c>
+      <c r="J40" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>61</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>133962691</v>
+      </c>
+      <c r="E41" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="5">
+        <v>42</v>
+      </c>
+      <c r="J41" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>61</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>133983512</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="5">
+        <v>42</v>
+      </c>
+      <c r="J42" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>61</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>134109915</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="5">
+        <v>42</v>
+      </c>
+      <c r="J43" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>61</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>134135007</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="5">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>61</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>134141742</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="5">
+        <v>42</v>
+      </c>
+      <c r="J45" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5">
+        <v>61</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>134237542</v>
+      </c>
+      <c r="E46" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="5">
+        <v>42</v>
+      </c>
+      <c r="J46" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>61</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>134306687</v>
+      </c>
+      <c r="E47" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="5">
+        <v>42</v>
+      </c>
+      <c r="J47" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>61</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>134459197</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="5">
+        <v>42</v>
+      </c>
+      <c r="J48" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <v>61</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>134477436</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="5">
+        <v>42</v>
+      </c>
+      <c r="J49" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>61</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>134606947</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="5">
+        <v>42</v>
+      </c>
+      <c r="J50" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>61</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>134686697</v>
+      </c>
+      <c r="E51" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="5">
+        <v>42</v>
+      </c>
+      <c r="J51" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>61</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>134707711</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="5">
+        <v>42</v>
+      </c>
+      <c r="J52" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>61</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>134760910</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="5">
+        <v>42</v>
+      </c>
+      <c r="J53" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <v>61</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>134776713</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="5">
+        <v>42</v>
+      </c>
+      <c r="J54" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>61</v>
+      </c>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>134891202</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" s="5">
+        <v>42</v>
+      </c>
+      <c r="J55" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>61</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>134915300</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="5">
+        <v>42</v>
+      </c>
+      <c r="J56" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>61</v>
+      </c>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>134938843</v>
+      </c>
+      <c r="E57" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="5">
+        <v>42</v>
+      </c>
+      <c r="J57" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>61</v>
+      </c>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>134944152</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="5">
+        <v>42</v>
+      </c>
+      <c r="J58" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>61</v>
+      </c>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>134953423</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="5">
+        <v>42</v>
+      </c>
+      <c r="J59" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5">
+        <v>61</v>
+      </c>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>134966417</v>
+      </c>
+      <c r="E60" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>134980004</v>
+      </c>
+      <c r="E61" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>129977252</v>
+      </c>
+      <c r="E62" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>129981041</v>
+      </c>
+      <c r="E63" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>130103261</v>
+      </c>
+      <c r="E64" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>130140731</v>
+      </c>
+      <c r="E65" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>130171644</v>
+      </c>
+      <c r="E66" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>130331228</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>130392502</v>
+      </c>
+      <c r="E68" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>130415042</v>
+      </c>
+      <c r="E69" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>130447785</v>
+      </c>
+      <c r="E70" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>130453805</v>
+      </c>
+      <c r="E71" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>130646132</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>131014796</v>
+      </c>
+      <c r="E73" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>131051469</v>
+      </c>
+      <c r="E74" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>131510171</v>
+      </c>
+      <c r="E75" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>131542663</v>
+      </c>
+      <c r="E76" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>132009444</v>
+      </c>
+      <c r="E77" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>132476887</v>
+      </c>
+      <c r="E78" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>132507159</v>
+      </c>
+      <c r="E79" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="5">
+        <v>42</v>
+      </c>
+      <c r="J79" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5">
+        <v>61</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>132742671</v>
+      </c>
+      <c r="E80" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="5">
+        <v>42</v>
+      </c>
+      <c r="J80" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>61</v>
+      </c>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>132751247</v>
+      </c>
+      <c r="E81" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="5">
+        <v>42</v>
+      </c>
+      <c r="J81" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>61</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>132752800</v>
+      </c>
+      <c r="E82" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" s="5">
+        <v>42</v>
+      </c>
+      <c r="J82" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5">
+        <v>61</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>132848916</v>
+      </c>
+      <c r="E83" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="5">
+        <v>42</v>
+      </c>
+      <c r="J83" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5">
+        <v>61</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>133260531</v>
+      </c>
+      <c r="E84" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="5">
+        <v>42</v>
+      </c>
+      <c r="J84" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5">
+        <v>61</v>
+      </c>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>133345787</v>
+      </c>
+      <c r="E85" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" s="5">
+        <v>42</v>
+      </c>
+      <c r="J85" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5">
+        <v>61</v>
+      </c>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>133475129</v>
+      </c>
+      <c r="E86" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" s="5">
+        <v>42</v>
+      </c>
+      <c r="J86" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5">
+        <v>61</v>
+      </c>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>133481610</v>
+      </c>
+      <c r="E87" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="5">
+        <v>42</v>
+      </c>
+      <c r="J87" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5">
+        <v>61</v>
+      </c>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>133658353</v>
+      </c>
+      <c r="E88" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>133814114</v>
+      </c>
+      <c r="E89" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      </c>
+      <c r="J89" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5">
+        <v>61</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>133952625</v>
+      </c>
+      <c r="E90" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="5">
+        <v>42</v>
+      </c>
+      <c r="J90" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5">
+        <v>61</v>
+      </c>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>133961979</v>
+      </c>
+      <c r="E91" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="5">
+        <v>42</v>
+      </c>
+      <c r="J91" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5">
+        <v>61</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>133983512</v>
+      </c>
+      <c r="E92" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" s="5">
+        <v>42</v>
+      </c>
+      <c r="J92" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5">
+        <v>61</v>
+      </c>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>134109915</v>
+      </c>
+      <c r="E93" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I93" s="5">
+        <v>42</v>
+      </c>
+      <c r="J93" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5">
+        <v>61</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>134237542</v>
+      </c>
+      <c r="E94" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I94" s="5">
+        <v>42</v>
+      </c>
+      <c r="J94" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5">
+        <v>61</v>
+      </c>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>134686697</v>
+      </c>
+      <c r="E95" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" s="5">
+        <v>42</v>
+      </c>
+      <c r="J95" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>61</v>
+      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>134760910</v>
+      </c>
+      <c r="E96" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" s="5">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5">
+        <v>61</v>
+      </c>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>134891202</v>
+      </c>
+      <c r="E97" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" s="5">
+        <v>42</v>
+      </c>
+      <c r="J97" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5">
+        <v>61</v>
+      </c>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>134938843</v>
+      </c>
+      <c r="E98" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" s="5">
+        <v>42</v>
+      </c>
+      <c r="J98" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5">
+        <v>61</v>
+      </c>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>134944152</v>
+      </c>
+      <c r="E99" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="5">
+        <v>42</v>
+      </c>
+      <c r="J99" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
+        <v>61</v>
+      </c>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>134953423</v>
+      </c>
+      <c r="E100" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" s="5">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>61</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>134980004</v>
+      </c>
+      <c r="E101" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" s="5">
+        <v>42</v>
+      </c>
+      <c r="J101" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>61</v>
+      </c>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>135043617</v>
+      </c>
+      <c r="E102" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I102" s="5">
+        <v>42</v>
+      </c>
+      <c r="J102" s="5">
+        <v>718</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>61</v>
+      </c>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>135045049</v>
+      </c>
+      <c r="E103" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I103" s="5">
+        <v>42</v>
+      </c>
+      <c r="J103" s="5">
+        <v>718</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>61</v>
+      </c>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>135045490</v>
+      </c>
+      <c r="E104" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I104" s="5">
+        <v>42</v>
+      </c>
+      <c r="J104" s="5">
+        <v>718</v>
+      </c>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5">
+        <v>61</v>
+      </c>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>135046507</v>
+      </c>
+      <c r="E105" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I105" s="5">
+        <v>42</v>
+      </c>
+      <c r="J105" s="5">
+        <v>718</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5">
+        <v>61</v>
+      </c>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>135046715</v>
+      </c>
+      <c r="E106" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I106" s="5">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5">
+        <v>718</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5">
+        <v>61</v>
+      </c>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>135047676</v>
+      </c>
+      <c r="E107" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I107" s="5">
+        <v>42</v>
+      </c>
+      <c r="J107" s="5">
+        <v>718</v>
+      </c>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5">
+        <v>61</v>
+      </c>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>135047737</v>
+      </c>
+      <c r="E108" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108" s="5">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5">
+        <v>718</v>
+      </c>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5">
+        <v>61</v>
+      </c>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>135048170</v>
+      </c>
+      <c r="E109" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I109" s="5">
+        <v>42</v>
+      </c>
+      <c r="J109" s="5">
+        <v>718</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5">
+        <v>61</v>
+      </c>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>135048242</v>
+      </c>
+      <c r="E110" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I110" s="5">
+        <v>42</v>
+      </c>
+      <c r="J110" s="5">
+        <v>718</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5">
+        <v>61</v>
+      </c>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>135049734</v>
+      </c>
+      <c r="E111" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I111" s="5">
+        <v>42</v>
+      </c>
+      <c r="J111" s="5">
+        <v>718</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5">
+        <v>61</v>
+      </c>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>135050261</v>
+      </c>
+      <c r="E112" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I112" s="5">
+        <v>42</v>
+      </c>
+      <c r="J112" s="5">
+        <v>718</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5">
+        <v>61</v>
+      </c>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>135054724</v>
+      </c>
+      <c r="E113" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I113" s="5">
+        <v>42</v>
+      </c>
+      <c r="J113" s="5">
+        <v>718</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5">
+        <v>61</v>
+      </c>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>135055320</v>
+      </c>
+      <c r="E114" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I114" s="5">
+        <v>42</v>
+      </c>
+      <c r="J114" s="5">
+        <v>718</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5">
+        <v>61</v>
+      </c>
+      <c r="M114" s="5"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>135056134</v>
+      </c>
+      <c r="E115" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I115" s="5">
+        <v>42</v>
+      </c>
+      <c r="J115" s="5">
+        <v>718</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5">
+        <v>61</v>
+      </c>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>135056785</v>
+      </c>
+      <c r="E116" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I116" s="5">
+        <v>42</v>
+      </c>
+      <c r="J116" s="5">
+        <v>718</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" s="5">
+        <v>61</v>
+      </c>
+      <c r="M116" s="5"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>135057310</v>
+      </c>
+      <c r="E117" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I117" s="5">
+        <v>42</v>
+      </c>
+      <c r="J117" s="5">
+        <v>718</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" s="5">
+        <v>61</v>
+      </c>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>135057564</v>
+      </c>
+      <c r="E118" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I118" s="5">
+        <v>42</v>
+      </c>
+      <c r="J118" s="5">
+        <v>718</v>
+      </c>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5">
+        <v>61</v>
+      </c>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5"/>
+      <c r="O118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>135057943</v>
+      </c>
+      <c r="E119" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I119" s="5">
+        <v>42</v>
+      </c>
+      <c r="J119" s="5">
+        <v>718</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5">
+        <v>61</v>
+      </c>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>135058004</v>
+      </c>
+      <c r="E120" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I120" s="5">
+        <v>42</v>
+      </c>
+      <c r="J120" s="5">
+        <v>718</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5">
+        <v>61</v>
+      </c>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>135058046</v>
+      </c>
+      <c r="E121" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I121" s="5">
+        <v>42</v>
+      </c>
+      <c r="J121" s="5">
+        <v>718</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5">
+        <v>61</v>
+      </c>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>135058133</v>
+      </c>
+      <c r="E122" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>718</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>135058276</v>
+      </c>
+      <c r="E123" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>718</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>135058318</v>
+      </c>
+      <c r="E124" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>718</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>135005840</v>
+      </c>
+      <c r="E125" s="5">
+        <v>601</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>135007801</v>
+      </c>
+      <c r="E126" s="5">
+        <v>601</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>135008673</v>
+      </c>
+      <c r="E127" s="5">
+        <v>601</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>135008702</v>
+      </c>
+      <c r="E128" s="5">
+        <v>601</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>135009273</v>
+      </c>
+      <c r="E129" s="5">
+        <v>601</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>135009726</v>
+      </c>
+      <c r="E130" s="5">
+        <v>601</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>135010001</v>
+      </c>
+      <c r="E131" s="5">
+        <v>601</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>135013454</v>
+      </c>
+      <c r="E132" s="5">
+        <v>601</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>135014109</v>
+      </c>
+      <c r="E133" s="5">
+        <v>601</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="M133" s="5"/>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>135014470</v>
+      </c>
+      <c r="E134" s="5">
+        <v>601</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>1117</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="M134" s="5"/>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>135015256</v>
+      </c>
+      <c r="E135" s="5">
+        <v>601</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>135015671</v>
+      </c>
+      <c r="E136" s="5">
+        <v>601</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="M136" s="5"/>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>135016555</v>
+      </c>
+      <c r="E137" s="5">
+        <v>601</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="M137" s="5"/>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>135016984</v>
+      </c>
+      <c r="E138" s="5">
+        <v>601</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="M138" s="5"/>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>135017017</v>
+      </c>
+      <c r="E139" s="5">
+        <v>601</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+      <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>135017310</v>
+      </c>
+      <c r="E140" s="5">
+        <v>601</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>135017800</v>
+      </c>
+      <c r="E141" s="5">
+        <v>601</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>135017859</v>
+      </c>
+      <c r="E142" s="5">
+        <v>601</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="M142" s="5"/>
+      <c r="N142" s="5"/>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>135022025</v>
+      </c>
+      <c r="E143" s="5">
+        <v>601</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="M143" s="5"/>
+      <c r="N143" s="5"/>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>135022057</v>
+      </c>
+      <c r="E144" s="5">
+        <v>601</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="M144" s="5"/>
+      <c r="N144" s="5"/>
+      <c r="O144" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>135022058</v>
+      </c>
+      <c r="E145" s="5">
+        <v>601</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I145" s="5">
+        <v>42</v>
+      </c>
+      <c r="J145" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="L145" s="5">
+        <v>61</v>
+      </c>
+      <c r="M145" s="5"/>
+      <c r="N145" s="5"/>
+      <c r="O145" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>135022605</v>
+      </c>
+      <c r="E146" s="5">
+        <v>601</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" s="5">
+        <v>42</v>
+      </c>
+      <c r="J146" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5">
+        <v>61</v>
+      </c>
+      <c r="M146" s="5"/>
+      <c r="N146" s="5"/>
+      <c r="O146" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>135022625</v>
+      </c>
+      <c r="E147" s="5">
+        <v>601</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" s="5">
+        <v>42</v>
+      </c>
+      <c r="J147" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5">
+        <v>61</v>
+      </c>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>135023256</v>
+      </c>
+      <c r="E148" s="5">
+        <v>601</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" s="5">
+        <v>42</v>
+      </c>
+      <c r="J148" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5">
+        <v>61</v>
+      </c>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>135025110</v>
+      </c>
+      <c r="E149" s="5">
+        <v>601</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I149" s="5">
+        <v>42</v>
+      </c>
+      <c r="J149" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5">
+        <v>61</v>
+      </c>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
+      <c r="O149" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>135025942</v>
+      </c>
+      <c r="E150" s="5">
+        <v>601</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I150" s="5">
+        <v>42</v>
+      </c>
+      <c r="J150" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5">
+        <v>61</v>
+      </c>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>135026874</v>
+      </c>
+      <c r="E151" s="5">
+        <v>601</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I151" s="5">
+        <v>42</v>
+      </c>
+      <c r="J151" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5">
+        <v>61</v>
+      </c>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>135030096</v>
+      </c>
+      <c r="E152" s="5">
+        <v>601</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I152" s="5">
+        <v>42</v>
+      </c>
+      <c r="J152" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="L152" s="5">
+        <v>61</v>
+      </c>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>135031016</v>
+      </c>
+      <c r="E153" s="5">
+        <v>601</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I153" s="5">
+        <v>42</v>
+      </c>
+      <c r="J153" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K153" s="5">
+        <v>0</v>
+      </c>
+      <c r="L153" s="5">
+        <v>61</v>
+      </c>
+      <c r="M153" s="5"/>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>135031403</v>
+      </c>
+      <c r="E154" s="5">
+        <v>601</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I154" s="5">
+        <v>42</v>
+      </c>
+      <c r="J154" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K154" s="5">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5">
+        <v>61</v>
+      </c>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>135034070</v>
+      </c>
+      <c r="E155" s="5">
+        <v>601</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I155" s="5">
+        <v>42</v>
+      </c>
+      <c r="J155" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K155" s="5">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5">
+        <v>61</v>
+      </c>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>135035027</v>
+      </c>
+      <c r="E156" s="5">
+        <v>601</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I156" s="5">
+        <v>42</v>
+      </c>
+      <c r="J156" s="5">
+        <v>8013</v>
+      </c>
+      <c r="K156" s="5">
+        <v>0</v>
+      </c>
+      <c r="L156" s="5">
+        <v>61</v>
+      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>135037736</v>
+      </c>
+      <c r="E157" s="5">
+        <v>601</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I157" s="5">
+        <v>42</v>
+      </c>
+      <c r="J157" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K157" s="5">
+        <v>0</v>
+      </c>
+      <c r="L157" s="5">
+        <v>61</v>
+      </c>
+      <c r="M157" s="5"/>
+      <c r="N157" s="5"/>
+      <c r="O157" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>135039418</v>
+      </c>
+      <c r="E158" s="5">
+        <v>601</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I158" s="5">
+        <v>42</v>
+      </c>
+      <c r="J158" s="5">
+        <v>8004</v>
+      </c>
+      <c r="K158" s="5">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5">
+        <v>61</v>
+      </c>
+      <c r="M158" s="5"/>
+      <c r="N158" s="5"/>
+      <c r="O158" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1440,31 +5470,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CAC8F7-7078-42C6-961E-C244D19AF0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA9579A-ED4D-4ED3-8D4E-CB6ABC4F8AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -91,10 +91,10 @@
     <t>21/10/2025</t>
   </si>
   <si>
-    <t>20/10/2025</t>
+    <t>22/10/2025</t>
   </si>
   <si>
-    <t>22/10/2025</t>
+    <t>23/10/2025</t>
   </si>
 </sst>
 </file>
@@ -644,16 +644,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>129977252</v>
+        <v>130163198</v>
       </c>
       <c r="E4" s="5">
         <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
@@ -675,16 +675,16 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>129981041</v>
+        <v>130357845</v>
       </c>
       <c r="E5" s="5">
         <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
@@ -706,16 +706,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>130103261</v>
+        <v>130648070</v>
       </c>
       <c r="E6" s="5">
         <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>130140731</v>
+        <v>130700751</v>
       </c>
       <c r="E7" s="5">
         <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
@@ -768,16 +768,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>130171644</v>
+        <v>130807992</v>
       </c>
       <c r="E8" s="5">
         <v>1211</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
@@ -799,16 +799,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>130331228</v>
+        <v>130893078</v>
       </c>
       <c r="E9" s="5">
         <v>1211</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
@@ -830,16 +830,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>130392502</v>
+        <v>130935010</v>
       </c>
       <c r="E10" s="5">
         <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
@@ -861,16 +861,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>130415042</v>
+        <v>131105452</v>
       </c>
       <c r="E11" s="5">
         <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
@@ -892,16 +892,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>130447785</v>
+        <v>131166519</v>
       </c>
       <c r="E12" s="5">
         <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
@@ -923,16 +923,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>130453805</v>
+        <v>131290857</v>
       </c>
       <c r="E13" s="5">
         <v>1211</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
@@ -954,16 +954,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>130646132</v>
+        <v>131328250</v>
       </c>
       <c r="E14" s="5">
         <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
@@ -985,16 +985,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>131014796</v>
+        <v>131364017</v>
       </c>
       <c r="E15" s="5">
         <v>1211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
@@ -1016,13 +1016,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>131051469</v>
+        <v>131372974</v>
       </c>
       <c r="E16" s="5">
         <v>1211</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>20</v>
@@ -1047,16 +1047,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>131510171</v>
+        <v>131389570</v>
       </c>
       <c r="E17" s="5">
         <v>1211</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1078,16 +1078,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>131542663</v>
+        <v>131389739</v>
       </c>
       <c r="E18" s="5">
         <v>1211</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1109,16 +1109,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>131831662</v>
+        <v>131467353</v>
       </c>
       <c r="E19" s="5">
         <v>1211</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1140,16 +1140,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>132009444</v>
+        <v>131580294</v>
       </c>
       <c r="E20" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1171,16 +1171,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>132054028</v>
+        <v>131625281</v>
       </c>
       <c r="E21" s="5">
         <v>1211</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1202,16 +1202,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>132476887</v>
+        <v>131634683</v>
       </c>
       <c r="E22" s="5">
         <v>1211</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
@@ -1233,16 +1233,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>132507159</v>
+        <v>131795838</v>
       </c>
       <c r="E23" s="5">
         <v>1211</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1264,16 +1264,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>132742671</v>
+        <v>131827690</v>
       </c>
       <c r="E24" s="5">
         <v>1211</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1295,16 +1295,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>132743090</v>
+        <v>131927013</v>
       </c>
       <c r="E25" s="5">
         <v>1211</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1326,16 +1326,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>132751247</v>
+        <v>131963376</v>
       </c>
       <c r="E26" s="5">
         <v>1212</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1357,16 +1357,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>132752800</v>
+        <v>131981889</v>
       </c>
       <c r="E27" s="5">
         <v>1211</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
@@ -1388,16 +1388,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>132848916</v>
+        <v>132014472</v>
       </c>
       <c r="E28" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
@@ -1419,16 +1419,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>133183256</v>
+        <v>132176336</v>
       </c>
       <c r="E29" s="5">
         <v>1211</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
@@ -1450,16 +1450,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>133260531</v>
+        <v>132210720</v>
       </c>
       <c r="E30" s="5">
         <v>1211</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
@@ -1481,16 +1481,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>133318874</v>
+        <v>132341755</v>
       </c>
       <c r="E31" s="5">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
@@ -1512,16 +1512,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>133345787</v>
+        <v>132367511</v>
       </c>
       <c r="E32" s="5">
         <v>1211</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
@@ -1543,16 +1543,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>133475129</v>
+        <v>132410009</v>
       </c>
       <c r="E33" s="5">
         <v>1211</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>133481610</v>
+        <v>132532245</v>
       </c>
       <c r="E34" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>133658353</v>
+        <v>132551923</v>
       </c>
       <c r="E35" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>19</v>
@@ -1636,16 +1636,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>133714070</v>
+        <v>132601165</v>
       </c>
       <c r="E36" s="5">
         <v>1211</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
@@ -1667,16 +1667,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>133814114</v>
+        <v>132646501</v>
       </c>
       <c r="E37" s="5">
         <v>1211</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
@@ -1698,16 +1698,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>133875664</v>
+        <v>132711163</v>
       </c>
       <c r="E38" s="5">
         <v>1211</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
@@ -1729,16 +1729,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>133952625</v>
+        <v>132764693</v>
       </c>
       <c r="E39" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
@@ -1760,16 +1760,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>133961979</v>
+        <v>132784348</v>
       </c>
       <c r="E40" s="5">
         <v>1211</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
@@ -1791,16 +1791,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>133962691</v>
+        <v>132830414</v>
       </c>
       <c r="E41" s="5">
         <v>1211</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
@@ -1822,16 +1822,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>133983512</v>
+        <v>132866437</v>
       </c>
       <c r="E42" s="5">
         <v>1211</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
@@ -1853,13 +1853,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>134109915</v>
+        <v>132980699</v>
       </c>
       <c r="E43" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>19</v>
@@ -1884,16 +1884,16 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>134135007</v>
+        <v>133036090</v>
       </c>
       <c r="E44" s="5">
         <v>1211</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
@@ -1915,16 +1915,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>134141742</v>
+        <v>133221193</v>
       </c>
       <c r="E45" s="5">
         <v>1211</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
@@ -1946,16 +1946,16 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>134237542</v>
+        <v>133350254</v>
       </c>
       <c r="E46" s="5">
         <v>1211</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" s="5">
         <v>42</v>
@@ -1977,16 +1977,16 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>134306687</v>
+        <v>133369987</v>
       </c>
       <c r="E47" s="5">
         <v>1211</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
@@ -2008,16 +2008,16 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>134459197</v>
+        <v>133434380</v>
       </c>
       <c r="E48" s="5">
         <v>1211</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
@@ -2039,16 +2039,16 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>134477436</v>
+        <v>133451921</v>
       </c>
       <c r="E49" s="5">
         <v>1211</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
@@ -2070,16 +2070,16 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>134606947</v>
+        <v>133526248</v>
       </c>
       <c r="E50" s="5">
         <v>1211</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
@@ -2101,16 +2101,16 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>134686697</v>
+        <v>133732783</v>
       </c>
       <c r="E51" s="5">
         <v>1211</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
@@ -2132,16 +2132,16 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>134707711</v>
+        <v>133740872</v>
       </c>
       <c r="E52" s="5">
         <v>1211</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
@@ -2163,16 +2163,16 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>134760910</v>
+        <v>133742287</v>
       </c>
       <c r="E53" s="5">
         <v>1211</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>134776713</v>
+        <v>133751534</v>
       </c>
       <c r="E54" s="5">
         <v>1211</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
@@ -2225,16 +2225,16 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>134891202</v>
+        <v>133770590</v>
       </c>
       <c r="E55" s="5">
         <v>1211</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
@@ -2256,16 +2256,16 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>134915300</v>
+        <v>133820662</v>
       </c>
       <c r="E56" s="5">
         <v>1211</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
@@ -2287,16 +2287,16 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>134938843</v>
+        <v>133837416</v>
       </c>
       <c r="E57" s="5">
         <v>1211</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
@@ -2318,16 +2318,16 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>134944152</v>
+        <v>133859581</v>
       </c>
       <c r="E58" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
@@ -2349,16 +2349,16 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>134953423</v>
+        <v>133872436</v>
       </c>
       <c r="E59" s="5">
         <v>1211</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>134966417</v>
+        <v>134022910</v>
       </c>
       <c r="E60" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>19</v>
@@ -2411,16 +2411,16 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>134980004</v>
+        <v>134050350</v>
       </c>
       <c r="E61" s="5">
         <v>1211</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
@@ -2442,13 +2442,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>129977252</v>
+        <v>134056738</v>
       </c>
       <c r="E62" s="5">
         <v>1211</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>20</v>
@@ -2473,16 +2473,16 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>129981041</v>
+        <v>134072551</v>
       </c>
       <c r="E63" s="5">
         <v>1211</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
@@ -2504,16 +2504,16 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>130103261</v>
+        <v>134080385</v>
       </c>
       <c r="E64" s="5">
         <v>1211</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
@@ -2535,16 +2535,16 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>130140731</v>
+        <v>134196447</v>
       </c>
       <c r="E65" s="5">
         <v>1211</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
@@ -2566,16 +2566,16 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>130171644</v>
+        <v>134205178</v>
       </c>
       <c r="E66" s="5">
         <v>1211</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
@@ -2597,16 +2597,16 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>130331228</v>
+        <v>134205358</v>
       </c>
       <c r="E67" s="5">
         <v>1211</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
@@ -2628,16 +2628,16 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>130392502</v>
+        <v>134281611</v>
       </c>
       <c r="E68" s="5">
         <v>1211</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
@@ -2659,16 +2659,16 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>130415042</v>
+        <v>134344680</v>
       </c>
       <c r="E69" s="5">
         <v>1211</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
@@ -2690,16 +2690,16 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>130447785</v>
+        <v>134365678</v>
       </c>
       <c r="E70" s="5">
         <v>1211</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
@@ -2721,16 +2721,16 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>130453805</v>
+        <v>134382285</v>
       </c>
       <c r="E71" s="5">
         <v>1211</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
@@ -2752,13 +2752,13 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>130646132</v>
+        <v>134547306</v>
       </c>
       <c r="E72" s="5">
         <v>1211</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>20</v>
@@ -2783,16 +2783,16 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>131014796</v>
+        <v>134636046</v>
       </c>
       <c r="E73" s="5">
         <v>1211</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>131051469</v>
+        <v>134690759</v>
       </c>
       <c r="E74" s="5">
         <v>1211</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
@@ -2845,16 +2845,16 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>131510171</v>
+        <v>134724180</v>
       </c>
       <c r="E75" s="5">
         <v>1211</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
@@ -2876,16 +2876,16 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>131542663</v>
+        <v>134726649</v>
       </c>
       <c r="E76" s="5">
         <v>1211</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
@@ -2907,16 +2907,16 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>132009444</v>
+        <v>134849543</v>
       </c>
       <c r="E77" s="5">
         <v>1211</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
@@ -2938,16 +2938,16 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>132476887</v>
+        <v>134897648</v>
       </c>
       <c r="E78" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I78" s="5">
         <v>42</v>
@@ -2969,16 +2969,16 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>132507159</v>
+        <v>134902314</v>
       </c>
       <c r="E79" s="5">
         <v>1211</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I79" s="5">
         <v>42</v>
@@ -3000,16 +3000,16 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>132742671</v>
+        <v>134912797</v>
       </c>
       <c r="E80" s="5">
         <v>1211</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I80" s="5">
         <v>42</v>
@@ -3031,16 +3031,16 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>132751247</v>
+        <v>134933019</v>
       </c>
       <c r="E81" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I81" s="5">
         <v>42</v>
@@ -3062,16 +3062,16 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>132752800</v>
+        <v>134935891</v>
       </c>
       <c r="E82" s="5">
         <v>1211</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I82" s="5">
         <v>42</v>
@@ -3093,16 +3093,16 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>132848916</v>
+        <v>134938783</v>
       </c>
       <c r="E83" s="5">
         <v>1211</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I83" s="5">
         <v>42</v>
@@ -3124,16 +3124,16 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>133260531</v>
+        <v>134965993</v>
       </c>
       <c r="E84" s="5">
         <v>1211</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I84" s="5">
         <v>42</v>
@@ -3155,16 +3155,16 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>133345787</v>
+        <v>134982118</v>
       </c>
       <c r="E85" s="5">
         <v>1211</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I85" s="5">
         <v>42</v>
@@ -3186,16 +3186,16 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>133475129</v>
+        <v>134985661</v>
       </c>
       <c r="E86" s="5">
         <v>1211</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I86" s="5">
         <v>42</v>
@@ -3217,16 +3217,16 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>133481610</v>
+        <v>135002196</v>
       </c>
       <c r="E87" s="5">
         <v>1211</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I87" s="5">
         <v>42</v>
@@ -3248,13 +3248,13 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>133658353</v>
+        <v>135004558</v>
       </c>
       <c r="E88" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>19</v>
@@ -3279,16 +3279,16 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>133814114</v>
+        <v>135005675</v>
       </c>
       <c r="E89" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I89" s="5">
         <v>42</v>
@@ -3310,16 +3310,16 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>133952625</v>
+        <v>135012836</v>
       </c>
       <c r="E90" s="5">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I90" s="5">
         <v>42</v>
@@ -3341,16 +3341,16 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>133961979</v>
+        <v>135013026</v>
       </c>
       <c r="E91" s="5">
         <v>1211</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I91" s="5">
         <v>42</v>
@@ -3372,16 +3372,16 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>133983512</v>
+        <v>135015058</v>
       </c>
       <c r="E92" s="5">
         <v>1211</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I92" s="5">
         <v>42</v>
@@ -3403,13 +3403,13 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>134109915</v>
+        <v>135017729</v>
       </c>
       <c r="E93" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>19</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>134237542</v>
+        <v>135033750</v>
       </c>
       <c r="E94" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I94" s="5">
         <v>42</v>
@@ -3465,16 +3465,16 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>134686697</v>
+        <v>130163198</v>
       </c>
       <c r="E95" s="5">
         <v>1211</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I95" s="5">
         <v>42</v>
@@ -3496,16 +3496,16 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>134760910</v>
+        <v>130357845</v>
       </c>
       <c r="E96" s="5">
         <v>1211</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I96" s="5">
         <v>42</v>
@@ -3527,16 +3527,16 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>134891202</v>
+        <v>130648070</v>
       </c>
       <c r="E97" s="5">
         <v>1211</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I97" s="5">
         <v>42</v>
@@ -3558,16 +3558,16 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>134938843</v>
+        <v>130700751</v>
       </c>
       <c r="E98" s="5">
         <v>1211</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I98" s="5">
         <v>42</v>
@@ -3589,16 +3589,16 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>134944152</v>
+        <v>130893078</v>
       </c>
       <c r="E99" s="5">
         <v>1211</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I99" s="5">
         <v>42</v>
@@ -3620,16 +3620,16 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>134953423</v>
+        <v>131328250</v>
       </c>
       <c r="E100" s="5">
         <v>1211</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I100" s="5">
         <v>42</v>
@@ -3651,16 +3651,16 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>134980004</v>
+        <v>131364017</v>
       </c>
       <c r="E101" s="5">
         <v>1211</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I101" s="5">
         <v>42</v>
@@ -3682,22 +3682,22 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>135043617</v>
+        <v>131372974</v>
       </c>
       <c r="E102" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I102" s="5">
         <v>42</v>
       </c>
       <c r="J102" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K102" s="5">
         <v>0</v>
@@ -3713,22 +3713,22 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>135045049</v>
+        <v>131389570</v>
       </c>
       <c r="E103" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I103" s="5">
         <v>42</v>
       </c>
       <c r="J103" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K103" s="5">
         <v>0</v>
@@ -3744,22 +3744,22 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>135045490</v>
+        <v>131580294</v>
       </c>
       <c r="E104" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I104" s="5">
         <v>42</v>
       </c>
       <c r="J104" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K104" s="5">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>135046507</v>
+        <v>131625281</v>
       </c>
       <c r="E105" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I105" s="5">
         <v>42</v>
       </c>
       <c r="J105" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K105" s="5">
         <v>0</v>
@@ -3806,22 +3806,22 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>135046715</v>
+        <v>131634683</v>
       </c>
       <c r="E106" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I106" s="5">
         <v>42</v>
       </c>
       <c r="J106" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
@@ -3837,22 +3837,22 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>135047676</v>
+        <v>132176336</v>
       </c>
       <c r="E107" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I107" s="5">
         <v>42</v>
       </c>
       <c r="J107" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K107" s="5">
         <v>0</v>
@@ -3868,22 +3868,22 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>135047737</v>
+        <v>132210720</v>
       </c>
       <c r="E108" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I108" s="5">
         <v>42</v>
       </c>
       <c r="J108" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K108" s="5">
         <v>0</v>
@@ -3899,22 +3899,22 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>135048170</v>
+        <v>132341755</v>
       </c>
       <c r="E109" s="5">
-        <v>2013</v>
+        <v>1213</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I109" s="5">
         <v>42</v>
       </c>
       <c r="J109" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
@@ -3930,22 +3930,22 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>135048242</v>
+        <v>132367511</v>
       </c>
       <c r="E110" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I110" s="5">
         <v>42</v>
       </c>
       <c r="J110" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K110" s="5">
         <v>0</v>
@@ -3961,22 +3961,22 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>135049734</v>
+        <v>132410009</v>
       </c>
       <c r="E111" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I111" s="5">
         <v>42</v>
       </c>
       <c r="J111" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K111" s="5">
         <v>0</v>
@@ -3992,22 +3992,22 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>135050261</v>
+        <v>132551923</v>
       </c>
       <c r="E112" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I112" s="5">
         <v>42</v>
       </c>
       <c r="J112" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K112" s="5">
         <v>0</v>
@@ -4023,22 +4023,22 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>135054724</v>
+        <v>132601165</v>
       </c>
       <c r="E113" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I113" s="5">
         <v>42</v>
       </c>
       <c r="J113" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
@@ -4054,22 +4054,22 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>135055320</v>
+        <v>132646501</v>
       </c>
       <c r="E114" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I114" s="5">
         <v>42</v>
       </c>
       <c r="J114" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K114" s="5">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>135056134</v>
+        <v>132866437</v>
       </c>
       <c r="E115" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I115" s="5">
         <v>42</v>
       </c>
       <c r="J115" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K115" s="5">
         <v>0</v>
@@ -4116,22 +4116,22 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>135056785</v>
+        <v>132980699</v>
       </c>
       <c r="E116" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I116" s="5">
         <v>42</v>
       </c>
       <c r="J116" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K116" s="5">
         <v>0</v>
@@ -4147,22 +4147,22 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>135057310</v>
+        <v>133036090</v>
       </c>
       <c r="E117" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I117" s="5">
         <v>42</v>
       </c>
       <c r="J117" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K117" s="5">
         <v>0</v>
@@ -4178,22 +4178,22 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>135057564</v>
+        <v>133221193</v>
       </c>
       <c r="E118" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I118" s="5">
         <v>42</v>
       </c>
       <c r="J118" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K118" s="5">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>135057943</v>
+        <v>133451921</v>
       </c>
       <c r="E119" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I119" s="5">
         <v>42</v>
       </c>
       <c r="J119" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K119" s="5">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>135058004</v>
+        <v>133732783</v>
       </c>
       <c r="E120" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I120" s="5">
         <v>42</v>
       </c>
       <c r="J120" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K120" s="5">
         <v>0</v>
@@ -4271,22 +4271,22 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>135058046</v>
+        <v>133742287</v>
       </c>
       <c r="E121" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I121" s="5">
         <v>42</v>
       </c>
       <c r="J121" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K121" s="5">
         <v>0</v>
@@ -4302,22 +4302,22 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>135058133</v>
+        <v>133751534</v>
       </c>
       <c r="E122" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I122" s="5">
         <v>42</v>
       </c>
       <c r="J122" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K122" s="5">
         <v>0</v>
@@ -4333,22 +4333,22 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>135058276</v>
+        <v>133820662</v>
       </c>
       <c r="E123" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I123" s="5">
         <v>42</v>
       </c>
       <c r="J123" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K123" s="5">
         <v>0</v>
@@ -4364,22 +4364,22 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>135058318</v>
+        <v>133837416</v>
       </c>
       <c r="E124" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I124" s="5">
         <v>42</v>
       </c>
       <c r="J124" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K124" s="5">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>135005840</v>
+        <v>133859581</v>
       </c>
       <c r="E125" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I125" s="5">
         <v>42</v>
       </c>
       <c r="J125" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K125" s="5">
         <v>0</v>
@@ -4426,22 +4426,22 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
-        <v>135007801</v>
+        <v>134072551</v>
       </c>
       <c r="E126" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I126" s="5">
         <v>42</v>
       </c>
       <c r="J126" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K126" s="5">
         <v>0</v>
@@ -4457,22 +4457,22 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
-        <v>135008673</v>
+        <v>134080385</v>
       </c>
       <c r="E127" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I127" s="5">
         <v>42</v>
       </c>
       <c r="J127" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K127" s="5">
         <v>0</v>
@@ -4488,22 +4488,22 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>135008702</v>
+        <v>134196447</v>
       </c>
       <c r="E128" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I128" s="5">
         <v>42</v>
       </c>
       <c r="J128" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K128" s="5">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>135009273</v>
+        <v>134205178</v>
       </c>
       <c r="E129" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I129" s="5">
         <v>42</v>
       </c>
       <c r="J129" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K129" s="5">
         <v>0</v>
@@ -4550,22 +4550,22 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
-        <v>135009726</v>
+        <v>134205358</v>
       </c>
       <c r="E130" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I130" s="5">
         <v>42</v>
       </c>
       <c r="J130" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K130" s="5">
         <v>0</v>
@@ -4581,22 +4581,22 @@
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>135010001</v>
+        <v>134382285</v>
       </c>
       <c r="E131" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I131" s="5">
         <v>42</v>
       </c>
       <c r="J131" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K131" s="5">
         <v>0</v>
@@ -4612,22 +4612,22 @@
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
-        <v>135013454</v>
+        <v>134636046</v>
       </c>
       <c r="E132" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I132" s="5">
         <v>42</v>
       </c>
       <c r="J132" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K132" s="5">
         <v>0</v>
@@ -4643,22 +4643,22 @@
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
-        <v>135014109</v>
+        <v>134690759</v>
       </c>
       <c r="E133" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I133" s="5">
         <v>42</v>
       </c>
       <c r="J133" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K133" s="5">
         <v>0</v>
@@ -4674,22 +4674,22 @@
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
-        <v>135014470</v>
+        <v>134726649</v>
       </c>
       <c r="E134" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I134" s="5">
         <v>42</v>
       </c>
       <c r="J134" s="5">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="K134" s="5">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>135015256</v>
+        <v>134897648</v>
       </c>
       <c r="E135" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I135" s="5">
         <v>42</v>
       </c>
       <c r="J135" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K135" s="5">
         <v>0</v>
@@ -4736,22 +4736,22 @@
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>135015671</v>
+        <v>134902314</v>
       </c>
       <c r="E136" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I136" s="5">
         <v>42</v>
       </c>
       <c r="J136" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K136" s="5">
         <v>0</v>
@@ -4767,22 +4767,22 @@
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
-        <v>135016555</v>
+        <v>134933019</v>
       </c>
       <c r="E137" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I137" s="5">
         <v>42</v>
       </c>
       <c r="J137" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K137" s="5">
         <v>0</v>
@@ -4798,22 +4798,22 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>135016984</v>
+        <v>134935891</v>
       </c>
       <c r="E138" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I138" s="5">
         <v>42</v>
       </c>
       <c r="J138" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K138" s="5">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
-        <v>135017017</v>
+        <v>134938783</v>
       </c>
       <c r="E139" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I139" s="5">
         <v>42</v>
       </c>
       <c r="J139" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K139" s="5">
         <v>0</v>
@@ -4860,22 +4860,22 @@
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>135017310</v>
+        <v>135012836</v>
       </c>
       <c r="E140" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I140" s="5">
         <v>42</v>
       </c>
       <c r="J140" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K140" s="5">
         <v>0</v>
@@ -4891,22 +4891,22 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>135017800</v>
+        <v>135015058</v>
       </c>
       <c r="E141" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I141" s="5">
         <v>42</v>
       </c>
       <c r="J141" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K141" s="5">
         <v>0</v>
@@ -4922,22 +4922,22 @@
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>135017859</v>
+        <v>135017729</v>
       </c>
       <c r="E142" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I142" s="5">
         <v>42</v>
       </c>
       <c r="J142" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K142" s="5">
         <v>0</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>135022025</v>
+        <v>135033750</v>
       </c>
       <c r="E143" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>19</v>
@@ -4968,7 +4968,7 @@
         <v>42</v>
       </c>
       <c r="J143" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K143" s="5">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>135022057</v>
+        <v>135063057</v>
       </c>
       <c r="E144" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I144" s="5">
         <v>42</v>
       </c>
       <c r="J144" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K144" s="5">
         <v>0</v>
@@ -5015,22 +5015,22 @@
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>135022058</v>
+        <v>135063985</v>
       </c>
       <c r="E145" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I145" s="5">
         <v>42</v>
       </c>
       <c r="J145" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K145" s="5">
         <v>0</v>
@@ -5046,22 +5046,22 @@
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>135022605</v>
+        <v>135068273</v>
       </c>
       <c r="E146" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I146" s="5">
         <v>42</v>
       </c>
       <c r="J146" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K146" s="5">
         <v>0</v>
@@ -5077,22 +5077,22 @@
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>135022625</v>
+        <v>135074418</v>
       </c>
       <c r="E147" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I147" s="5">
         <v>42</v>
       </c>
       <c r="J147" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K147" s="5">
         <v>0</v>
@@ -5108,22 +5108,22 @@
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>135023256</v>
+        <v>135075981</v>
       </c>
       <c r="E148" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I148" s="5">
         <v>42</v>
       </c>
       <c r="J148" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K148" s="5">
         <v>0</v>
@@ -5139,22 +5139,22 @@
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>135025110</v>
+        <v>135076283</v>
       </c>
       <c r="E149" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I149" s="5">
         <v>42</v>
       </c>
       <c r="J149" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K149" s="5">
         <v>0</v>
@@ -5170,22 +5170,22 @@
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>135025942</v>
+        <v>135076506</v>
       </c>
       <c r="E150" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I150" s="5">
         <v>42</v>
       </c>
       <c r="J150" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K150" s="5">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>135026874</v>
+        <v>135077041</v>
       </c>
       <c r="E151" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I151" s="5">
         <v>42</v>
       </c>
       <c r="J151" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K151" s="5">
         <v>0</v>
@@ -5232,22 +5232,22 @@
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>135030096</v>
+        <v>135077317</v>
       </c>
       <c r="E152" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I152" s="5">
         <v>42</v>
       </c>
       <c r="J152" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K152" s="5">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>135031016</v>
+        <v>135077753</v>
       </c>
       <c r="E153" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I153" s="5">
         <v>42</v>
       </c>
       <c r="J153" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K153" s="5">
         <v>0</v>
@@ -5294,22 +5294,22 @@
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>135031403</v>
+        <v>135079915</v>
       </c>
       <c r="E154" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I154" s="5">
         <v>42</v>
       </c>
       <c r="J154" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K154" s="5">
         <v>0</v>
@@ -5324,128 +5324,24 @@
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
-        <v>135034070</v>
-      </c>
-      <c r="E155" s="5">
-        <v>601</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G155" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I155" s="5">
-        <v>42</v>
-      </c>
-      <c r="J155" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K155" s="5">
-        <v>0</v>
-      </c>
-      <c r="L155" s="5">
-        <v>61</v>
-      </c>
       <c r="M155" s="5"/>
       <c r="N155" s="5"/>
-      <c r="O155" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O155" s="5"/>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
-        <v>135035027</v>
-      </c>
-      <c r="E156" s="5">
-        <v>601</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I156" s="5">
-        <v>42</v>
-      </c>
-      <c r="J156" s="5">
-        <v>8013</v>
-      </c>
-      <c r="K156" s="5">
-        <v>0</v>
-      </c>
-      <c r="L156" s="5">
-        <v>61</v>
-      </c>
       <c r="M156" s="5"/>
       <c r="N156" s="5"/>
-      <c r="O156" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O156" s="5"/>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
-        <v>135037736</v>
-      </c>
-      <c r="E157" s="5">
-        <v>601</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I157" s="5">
-        <v>42</v>
-      </c>
-      <c r="J157" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K157" s="5">
-        <v>0</v>
-      </c>
-      <c r="L157" s="5">
-        <v>61</v>
-      </c>
       <c r="M157" s="5"/>
       <c r="N157" s="5"/>
-      <c r="O157" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O157" s="5"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
-        <v>135039418</v>
-      </c>
-      <c r="E158" s="5">
-        <v>601</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G158" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I158" s="5">
-        <v>42</v>
-      </c>
-      <c r="J158" s="5">
-        <v>8004</v>
-      </c>
-      <c r="K158" s="5">
-        <v>0</v>
-      </c>
-      <c r="L158" s="5">
-        <v>61</v>
-      </c>
       <c r="M158" s="5"/>
       <c r="N158" s="5"/>
-      <c r="O158" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O158" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -5470,31 +5366,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429137A3-A94F-4EF0-BDF0-1446026E9572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9561AFA-5BC4-4E74-9D7C-FE1152153D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,42 +79,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>30/09/2025</t>
-  </si>
-  <si>
-    <t>02/10/2025</t>
-  </si>
-  <si>
-    <t>03/10/2025</t>
-  </si>
-  <si>
-    <t>08/10/2025</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>07/10/2025</t>
-  </si>
-  <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
-    <t>14/10/2025</t>
-  </si>
-  <si>
-    <t>15/10/2025</t>
-  </si>
-  <si>
-    <t>16/10/2025</t>
-  </si>
-  <si>
-    <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>21/10/2025</t>
-  </si>
-  <si>
     <t>23/10/2025</t>
   </si>
   <si>
@@ -122,6 +86,15 @@
   </si>
   <si>
     <t>25/10/2025</t>
+  </si>
+  <si>
+    <t>8/3/2023</t>
+  </si>
+  <si>
+    <t>10/3/2023</t>
+  </si>
+  <si>
+    <t>27/10/2025</t>
   </si>
 </sst>
 </file>
@@ -539,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O185"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -609,22 +582,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>134708897</v>
+        <v>123058958</v>
       </c>
       <c r="E2" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -640,22 +613,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>134742937</v>
+        <v>130198926</v>
       </c>
       <c r="E3" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -671,10 +644,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>134758583</v>
+        <v>130262968</v>
       </c>
       <c r="E4" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>17</v>
@@ -686,7 +659,7 @@
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -702,22 +675,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>134767374</v>
+        <v>130445094</v>
       </c>
       <c r="E5" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -733,13 +706,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>134776839</v>
+        <v>130685548</v>
       </c>
       <c r="E6" s="5">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>18</v>
@@ -748,7 +721,7 @@
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -764,22 +737,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>134791357</v>
+        <v>130789357</v>
       </c>
       <c r="E7" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -795,22 +768,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>134807041</v>
+        <v>130820463</v>
       </c>
       <c r="E8" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -826,13 +799,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134811267</v>
+        <v>131006461</v>
       </c>
       <c r="E9" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>21</v>
@@ -841,7 +814,7 @@
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -857,22 +830,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>134811717</v>
+        <v>131022722</v>
       </c>
       <c r="E10" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -888,22 +861,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>134823511</v>
+        <v>131069320</v>
       </c>
       <c r="E11" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -919,22 +892,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>134840956</v>
+        <v>131377001</v>
       </c>
       <c r="E12" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -950,22 +923,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>134841372</v>
+        <v>131522570</v>
       </c>
       <c r="E13" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -981,22 +954,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>134842475</v>
+        <v>131559293</v>
       </c>
       <c r="E14" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -1012,22 +985,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>134845793</v>
+        <v>131662792</v>
       </c>
       <c r="E15" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1043,22 +1016,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>134846518</v>
+        <v>131714657</v>
       </c>
       <c r="E16" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1074,22 +1047,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>134858228</v>
+        <v>131762002</v>
       </c>
       <c r="E17" s="5">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1105,22 +1078,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>134863585</v>
+        <v>131788065</v>
       </c>
       <c r="E18" s="5">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1136,22 +1109,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>134866225</v>
+        <v>131789232</v>
       </c>
       <c r="E19" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1167,22 +1140,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>134872011</v>
+        <v>131892896</v>
       </c>
       <c r="E20" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1198,22 +1171,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>134872147</v>
+        <v>131970942</v>
       </c>
       <c r="E21" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1229,22 +1202,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>134872251</v>
+        <v>131988160</v>
       </c>
       <c r="E22" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1260,22 +1233,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>134872505</v>
+        <v>132155781</v>
       </c>
       <c r="E23" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1291,22 +1264,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>134925005</v>
+        <v>132167376</v>
       </c>
       <c r="E24" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1322,22 +1295,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>134925297</v>
+        <v>132190895</v>
       </c>
       <c r="E25" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
       </c>
       <c r="J25" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -1353,22 +1326,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>134925738</v>
+        <v>132208300</v>
       </c>
       <c r="E26" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1384,22 +1357,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>134929893</v>
+        <v>132245617</v>
       </c>
       <c r="E27" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1415,22 +1388,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>134931450</v>
+        <v>132251045</v>
       </c>
       <c r="E28" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1446,22 +1419,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>134947048</v>
+        <v>132285115</v>
       </c>
       <c r="E29" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
       </c>
       <c r="J29" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -1477,22 +1450,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>134947886</v>
+        <v>132345509</v>
       </c>
       <c r="E30" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
       </c>
       <c r="J30" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -1508,22 +1481,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>134948348</v>
+        <v>132363154</v>
       </c>
       <c r="E31" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
       </c>
       <c r="J31" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K31" s="5">
         <v>0</v>
@@ -1539,22 +1512,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>134953026</v>
+        <v>132368755</v>
       </c>
       <c r="E32" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
       </c>
       <c r="J32" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -1570,22 +1543,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>134959685</v>
+        <v>132442220</v>
       </c>
       <c r="E33" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
       </c>
       <c r="J33" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -1601,22 +1574,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>134976088</v>
+        <v>132485974</v>
       </c>
       <c r="E34" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
       </c>
       <c r="J34" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -1632,22 +1605,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>134976885</v>
+        <v>132495197</v>
       </c>
       <c r="E35" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
       </c>
       <c r="J35" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -1663,22 +1636,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>134978222</v>
+        <v>132497216</v>
       </c>
       <c r="E36" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
       </c>
       <c r="J36" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -1694,22 +1667,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>134991672</v>
+        <v>132526893</v>
       </c>
       <c r="E37" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
       </c>
       <c r="J37" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -1725,22 +1698,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>134994567</v>
+        <v>132562843</v>
       </c>
       <c r="E38" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
       </c>
       <c r="J38" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
@@ -1756,22 +1729,22 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>134996702</v>
+        <v>132597051</v>
       </c>
       <c r="E39" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
       </c>
       <c r="J39" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K39" s="5">
         <v>0</v>
@@ -1787,22 +1760,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>135039317</v>
+        <v>132659613</v>
       </c>
       <c r="E40" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
       </c>
       <c r="J40" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -1818,22 +1791,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>135056533</v>
+        <v>132711190</v>
       </c>
       <c r="E41" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
       </c>
       <c r="J41" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -1849,22 +1822,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>135062936</v>
+        <v>132845017</v>
       </c>
       <c r="E42" s="5">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I42" s="5">
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -1880,22 +1853,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>135063731</v>
+        <v>132851128</v>
       </c>
       <c r="E43" s="5">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I43" s="5">
         <v>42</v>
       </c>
       <c r="J43" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -1911,22 +1884,22 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>135064182</v>
+        <v>132907551</v>
       </c>
       <c r="E44" s="5">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I44" s="5">
         <v>42</v>
       </c>
       <c r="J44" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -1942,22 +1915,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>135065552</v>
+        <v>132912887</v>
       </c>
       <c r="E45" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
       </c>
       <c r="J45" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -1973,22 +1946,22 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>135065554</v>
+        <v>132945805</v>
       </c>
       <c r="E46" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I46" s="5">
         <v>42</v>
       </c>
       <c r="J46" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
@@ -2004,22 +1977,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>135065671</v>
+        <v>132955455</v>
       </c>
       <c r="E47" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
       </c>
       <c r="J47" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -2035,22 +2008,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>135067369</v>
+        <v>132957595</v>
       </c>
       <c r="E48" s="5">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2066,22 +2039,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>135067677</v>
+        <v>133079856</v>
       </c>
       <c r="E49" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2097,22 +2070,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>135068470</v>
+        <v>133085101</v>
       </c>
       <c r="E50" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2128,22 +2101,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>135072434</v>
+        <v>133114355</v>
       </c>
       <c r="E51" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
       </c>
       <c r="J51" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -2159,22 +2132,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>135072875</v>
+        <v>133137391</v>
       </c>
       <c r="E52" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -2190,22 +2163,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>135073020</v>
+        <v>133138297</v>
       </c>
       <c r="E53" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2221,22 +2194,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>135073051</v>
+        <v>133230827</v>
       </c>
       <c r="E54" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2252,22 +2225,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>135073380</v>
+        <v>133237573</v>
       </c>
       <c r="E55" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -2283,22 +2256,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>135073531</v>
+        <v>133237921</v>
       </c>
       <c r="E56" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
       </c>
       <c r="J56" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -2314,22 +2287,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>135075206</v>
+        <v>133241141</v>
       </c>
       <c r="E57" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -2345,22 +2318,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>135075217</v>
+        <v>133320957</v>
       </c>
       <c r="E58" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
       </c>
       <c r="J58" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -2376,22 +2349,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>135075628</v>
+        <v>133365537</v>
       </c>
       <c r="E59" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2407,22 +2380,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>135075829</v>
+        <v>133368489</v>
       </c>
       <c r="E60" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
       </c>
       <c r="J60" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K60" s="5">
         <v>0</v>
@@ -2438,22 +2411,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>135076094</v>
+        <v>133393611</v>
       </c>
       <c r="E61" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
       </c>
       <c r="J61" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K61" s="5">
         <v>0</v>
@@ -2469,22 +2442,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>135076259</v>
+        <v>133415184</v>
       </c>
       <c r="E62" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I62" s="5">
         <v>42</v>
       </c>
       <c r="J62" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K62" s="5">
         <v>0</v>
@@ -2500,22 +2473,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>135077478</v>
+        <v>133416352</v>
       </c>
       <c r="E63" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I63" s="5">
         <v>42</v>
       </c>
       <c r="J63" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K63" s="5">
         <v>0</v>
@@ -2531,22 +2504,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>135079242</v>
+        <v>133473046</v>
       </c>
       <c r="E64" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
       </c>
       <c r="J64" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K64" s="5">
         <v>0</v>
@@ -2562,22 +2535,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>135080347</v>
+        <v>133536743</v>
       </c>
       <c r="E65" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
       </c>
       <c r="J65" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K65" s="5">
         <v>0</v>
@@ -2593,22 +2566,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>135084236</v>
+        <v>133554710</v>
       </c>
       <c r="E66" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
       </c>
       <c r="J66" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -2624,22 +2597,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>135084933</v>
+        <v>133602815</v>
       </c>
       <c r="E67" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
       </c>
       <c r="J67" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K67" s="5">
         <v>0</v>
@@ -2655,22 +2628,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>135085245</v>
+        <v>133653445</v>
       </c>
       <c r="E68" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
       </c>
       <c r="J68" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K68" s="5">
         <v>0</v>
@@ -2686,22 +2659,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>135086012</v>
+        <v>133660903</v>
       </c>
       <c r="E69" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
       </c>
       <c r="J69" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
@@ -2717,22 +2690,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>135086957</v>
+        <v>133662580</v>
       </c>
       <c r="E70" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I70" s="5">
         <v>42</v>
       </c>
       <c r="J70" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
@@ -2748,22 +2721,22 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>135087904</v>
+        <v>133663007</v>
       </c>
       <c r="E71" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I71" s="5">
         <v>42</v>
       </c>
       <c r="J71" s="5">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="K71" s="5">
         <v>0</v>
@@ -2779,22 +2752,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>135093975</v>
+        <v>133679633</v>
       </c>
       <c r="E72" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I72" s="5">
         <v>42</v>
       </c>
       <c r="J72" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K72" s="5">
         <v>0</v>
@@ -2810,22 +2783,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>135094959</v>
+        <v>133716171</v>
       </c>
       <c r="E73" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I73" s="5">
         <v>42</v>
       </c>
       <c r="J73" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K73" s="5">
         <v>0</v>
@@ -2841,22 +2814,22 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>135095376</v>
+        <v>133816168</v>
       </c>
       <c r="E74" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I74" s="5">
         <v>42</v>
       </c>
       <c r="J74" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K74" s="5">
         <v>0</v>
@@ -2872,22 +2845,22 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>135097247</v>
+        <v>133827722</v>
       </c>
       <c r="E75" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I75" s="5">
         <v>42</v>
       </c>
       <c r="J75" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K75" s="5">
         <v>0</v>
@@ -2903,22 +2876,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>135097255</v>
+        <v>133835807</v>
       </c>
       <c r="E76" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I76" s="5">
         <v>42</v>
       </c>
       <c r="J76" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K76" s="5">
         <v>0</v>
@@ -2934,22 +2907,22 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>135097266</v>
+        <v>133852448</v>
       </c>
       <c r="E77" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I77" s="5">
         <v>42</v>
       </c>
       <c r="J77" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K77" s="5">
         <v>0</v>
@@ -2965,22 +2938,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>135097271</v>
+        <v>133872269</v>
       </c>
       <c r="E78" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I78" s="5">
         <v>42</v>
       </c>
       <c r="J78" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K78" s="5">
         <v>0</v>
@@ -2996,22 +2969,22 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>135097282</v>
+        <v>133903373</v>
       </c>
       <c r="E79" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I79" s="5">
         <v>42</v>
       </c>
       <c r="J79" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K79" s="5">
         <v>0</v>
@@ -3027,22 +3000,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>135097311</v>
+        <v>134046989</v>
       </c>
       <c r="E80" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I80" s="5">
         <v>42</v>
       </c>
       <c r="J80" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K80" s="5">
         <v>0</v>
@@ -3058,22 +3031,22 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>135098028</v>
+        <v>134057527</v>
       </c>
       <c r="E81" s="5">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I81" s="5">
         <v>42</v>
       </c>
       <c r="J81" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K81" s="5">
         <v>0</v>
@@ -3089,22 +3062,22 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>135098510</v>
+        <v>134061532</v>
       </c>
       <c r="E82" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I82" s="5">
         <v>42</v>
       </c>
       <c r="J82" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K82" s="5">
         <v>0</v>
@@ -3120,22 +3093,22 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>135099363</v>
+        <v>134094427</v>
       </c>
       <c r="E83" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I83" s="5">
         <v>42</v>
       </c>
       <c r="J83" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K83" s="5">
         <v>0</v>
@@ -3151,22 +3124,22 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>135099370</v>
+        <v>134128469</v>
       </c>
       <c r="E84" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I84" s="5">
         <v>42</v>
       </c>
       <c r="J84" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K84" s="5">
         <v>0</v>
@@ -3182,22 +3155,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>135099442</v>
+        <v>134180610</v>
       </c>
       <c r="E85" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I85" s="5">
         <v>42</v>
       </c>
       <c r="J85" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K85" s="5">
         <v>0</v>
@@ -3213,22 +3186,22 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>135100536</v>
+        <v>134189062</v>
       </c>
       <c r="E86" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I86" s="5">
         <v>42</v>
       </c>
       <c r="J86" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K86" s="5">
         <v>0</v>
@@ -3244,22 +3217,22 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>135104251</v>
+        <v>134230633</v>
       </c>
       <c r="E87" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I87" s="5">
         <v>42</v>
       </c>
       <c r="J87" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K87" s="5">
         <v>0</v>
@@ -3270,6 +3243,2848 @@
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
       <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>134253081</v>
+      </c>
+      <c r="E88" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>134365749</v>
+      </c>
+      <c r="E89" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      </c>
+      <c r="J89" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5">
+        <v>61</v>
+      </c>
+      <c r="O89" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>134392843</v>
+      </c>
+      <c r="E90" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" s="5">
+        <v>42</v>
+      </c>
+      <c r="J90" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5">
+        <v>61</v>
+      </c>
+      <c r="O90" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>134409374</v>
+      </c>
+      <c r="E91" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="5">
+        <v>42</v>
+      </c>
+      <c r="J91" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5">
+        <v>61</v>
+      </c>
+      <c r="O91" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>134490850</v>
+      </c>
+      <c r="E92" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I92" s="5">
+        <v>42</v>
+      </c>
+      <c r="J92" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5">
+        <v>61</v>
+      </c>
+      <c r="O92" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>134544175</v>
+      </c>
+      <c r="E93" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" s="5">
+        <v>42</v>
+      </c>
+      <c r="J93" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5">
+        <v>61</v>
+      </c>
+      <c r="O93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>134569332</v>
+      </c>
+      <c r="E94" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" s="5">
+        <v>42</v>
+      </c>
+      <c r="J94" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5">
+        <v>61</v>
+      </c>
+      <c r="O94" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>134594592</v>
+      </c>
+      <c r="E95" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" s="5">
+        <v>42</v>
+      </c>
+      <c r="J95" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>61</v>
+      </c>
+      <c r="O95" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>134676785</v>
+      </c>
+      <c r="E96" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="5">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5">
+        <v>61</v>
+      </c>
+      <c r="O96" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>134679002</v>
+      </c>
+      <c r="E97" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" s="5">
+        <v>42</v>
+      </c>
+      <c r="J97" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5">
+        <v>61</v>
+      </c>
+      <c r="O97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>134731649</v>
+      </c>
+      <c r="E98" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" s="5">
+        <v>42</v>
+      </c>
+      <c r="J98" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5">
+        <v>61</v>
+      </c>
+      <c r="O98" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>134780397</v>
+      </c>
+      <c r="E99" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="5">
+        <v>42</v>
+      </c>
+      <c r="J99" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
+        <v>61</v>
+      </c>
+      <c r="O99" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>134787417</v>
+      </c>
+      <c r="E100" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="5">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>61</v>
+      </c>
+      <c r="O100" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>134793074</v>
+      </c>
+      <c r="E101" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I101" s="5">
+        <v>42</v>
+      </c>
+      <c r="J101" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>61</v>
+      </c>
+      <c r="O101" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>134820673</v>
+      </c>
+      <c r="E102" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="5">
+        <v>42</v>
+      </c>
+      <c r="J102" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>61</v>
+      </c>
+      <c r="O102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>134842007</v>
+      </c>
+      <c r="E103" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="5">
+        <v>42</v>
+      </c>
+      <c r="J103" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>61</v>
+      </c>
+      <c r="O103" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>134842116</v>
+      </c>
+      <c r="E104" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" s="5">
+        <v>42</v>
+      </c>
+      <c r="J104" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5">
+        <v>61</v>
+      </c>
+      <c r="O104" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>134854885</v>
+      </c>
+      <c r="E105" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="5">
+        <v>42</v>
+      </c>
+      <c r="J105" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5">
+        <v>61</v>
+      </c>
+      <c r="O105" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>134866169</v>
+      </c>
+      <c r="E106" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" s="5">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5">
+        <v>61</v>
+      </c>
+      <c r="O106" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>134922338</v>
+      </c>
+      <c r="E107" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107" s="5">
+        <v>42</v>
+      </c>
+      <c r="J107" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5">
+        <v>61</v>
+      </c>
+      <c r="O107" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>134973101</v>
+      </c>
+      <c r="E108" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="5">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5">
+        <v>61</v>
+      </c>
+      <c r="O108" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>134986369</v>
+      </c>
+      <c r="E109" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I109" s="5">
+        <v>42</v>
+      </c>
+      <c r="J109" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5">
+        <v>61</v>
+      </c>
+      <c r="O109" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>135009180</v>
+      </c>
+      <c r="E110" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I110" s="5">
+        <v>42</v>
+      </c>
+      <c r="J110" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5">
+        <v>61</v>
+      </c>
+      <c r="O110" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>135024147</v>
+      </c>
+      <c r="E111" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" s="5">
+        <v>42</v>
+      </c>
+      <c r="J111" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5">
+        <v>61</v>
+      </c>
+      <c r="O111" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>135029383</v>
+      </c>
+      <c r="E112" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="5">
+        <v>42</v>
+      </c>
+      <c r="J112" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5">
+        <v>61</v>
+      </c>
+      <c r="O112" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>135039543</v>
+      </c>
+      <c r="E113" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="5">
+        <v>42</v>
+      </c>
+      <c r="J113" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5">
+        <v>61</v>
+      </c>
+      <c r="O113" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>135043179</v>
+      </c>
+      <c r="E114" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" s="5">
+        <v>42</v>
+      </c>
+      <c r="J114" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5">
+        <v>61</v>
+      </c>
+      <c r="O114" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>135043635</v>
+      </c>
+      <c r="E115" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I115" s="5">
+        <v>42</v>
+      </c>
+      <c r="J115" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5">
+        <v>61</v>
+      </c>
+      <c r="O115" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>135049135</v>
+      </c>
+      <c r="E116" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116" s="5">
+        <v>42</v>
+      </c>
+      <c r="J116" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" s="5">
+        <v>61</v>
+      </c>
+      <c r="O116" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>135054152</v>
+      </c>
+      <c r="E117" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I117" s="5">
+        <v>42</v>
+      </c>
+      <c r="J117" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" s="5">
+        <v>61</v>
+      </c>
+      <c r="O117" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>135057608</v>
+      </c>
+      <c r="E118" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" s="5">
+        <v>42</v>
+      </c>
+      <c r="J118" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5">
+        <v>61</v>
+      </c>
+      <c r="O118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>135072756</v>
+      </c>
+      <c r="E119" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" s="5">
+        <v>42</v>
+      </c>
+      <c r="J119" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5">
+        <v>61</v>
+      </c>
+      <c r="O119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>130198926</v>
+      </c>
+      <c r="E120" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I120" s="5">
+        <v>42</v>
+      </c>
+      <c r="J120" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5">
+        <v>61</v>
+      </c>
+      <c r="O120" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>130262968</v>
+      </c>
+      <c r="E121" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" s="5">
+        <v>42</v>
+      </c>
+      <c r="J121" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5">
+        <v>61</v>
+      </c>
+      <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>130445094</v>
+      </c>
+      <c r="E122" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>131006461</v>
+      </c>
+      <c r="E123" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>131377001</v>
+      </c>
+      <c r="E124" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>131522570</v>
+      </c>
+      <c r="E125" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>131662792</v>
+      </c>
+      <c r="E126" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>131788065</v>
+      </c>
+      <c r="E127" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>132167376</v>
+      </c>
+      <c r="E128" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>132190895</v>
+      </c>
+      <c r="E129" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>132345509</v>
+      </c>
+      <c r="E130" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>132363154</v>
+      </c>
+      <c r="E131" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>132485974</v>
+      </c>
+      <c r="E132" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>132526893</v>
+      </c>
+      <c r="E133" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>132845017</v>
+      </c>
+      <c r="E134" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>132851128</v>
+      </c>
+      <c r="E135" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>132907551</v>
+      </c>
+      <c r="E136" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>132955455</v>
+      </c>
+      <c r="E137" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>133079856</v>
+      </c>
+      <c r="E138" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>133237921</v>
+      </c>
+      <c r="E139" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>133416352</v>
+      </c>
+      <c r="E140" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>133602815</v>
+      </c>
+      <c r="E141" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>133660903</v>
+      </c>
+      <c r="E142" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>133816168</v>
+      </c>
+      <c r="E143" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>133827722</v>
+      </c>
+      <c r="E144" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="O144" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>133852448</v>
+      </c>
+      <c r="E145" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" s="5">
+        <v>42</v>
+      </c>
+      <c r="J145" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="L145" s="5">
+        <v>61</v>
+      </c>
+      <c r="O145" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>133872269</v>
+      </c>
+      <c r="E146" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" s="5">
+        <v>42</v>
+      </c>
+      <c r="J146" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5">
+        <v>61</v>
+      </c>
+      <c r="O146" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>134046989</v>
+      </c>
+      <c r="E147" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" s="5">
+        <v>42</v>
+      </c>
+      <c r="J147" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5">
+        <v>61</v>
+      </c>
+      <c r="O147" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>134057527</v>
+      </c>
+      <c r="E148" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148" s="5">
+        <v>42</v>
+      </c>
+      <c r="J148" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5">
+        <v>61</v>
+      </c>
+      <c r="O148" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>134061532</v>
+      </c>
+      <c r="E149" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I149" s="5">
+        <v>42</v>
+      </c>
+      <c r="J149" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5">
+        <v>61</v>
+      </c>
+      <c r="O149" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>134180610</v>
+      </c>
+      <c r="E150" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I150" s="5">
+        <v>42</v>
+      </c>
+      <c r="J150" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5">
+        <v>61</v>
+      </c>
+      <c r="O150" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>134189062</v>
+      </c>
+      <c r="E151" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I151" s="5">
+        <v>42</v>
+      </c>
+      <c r="J151" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5">
+        <v>61</v>
+      </c>
+      <c r="O151" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>134392843</v>
+      </c>
+      <c r="E152" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" s="5">
+        <v>42</v>
+      </c>
+      <c r="J152" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="L152" s="5">
+        <v>61</v>
+      </c>
+      <c r="O152" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>134490850</v>
+      </c>
+      <c r="E153" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I153" s="5">
+        <v>42</v>
+      </c>
+      <c r="J153" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K153" s="5">
+        <v>0</v>
+      </c>
+      <c r="L153" s="5">
+        <v>61</v>
+      </c>
+      <c r="O153" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>134731649</v>
+      </c>
+      <c r="E154" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I154" s="5">
+        <v>42</v>
+      </c>
+      <c r="J154" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K154" s="5">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5">
+        <v>61</v>
+      </c>
+      <c r="O154" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>134787417</v>
+      </c>
+      <c r="E155" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" s="5">
+        <v>42</v>
+      </c>
+      <c r="J155" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K155" s="5">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5">
+        <v>61</v>
+      </c>
+      <c r="O155" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>134820673</v>
+      </c>
+      <c r="E156" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" s="5">
+        <v>42</v>
+      </c>
+      <c r="J156" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K156" s="5">
+        <v>0</v>
+      </c>
+      <c r="L156" s="5">
+        <v>61</v>
+      </c>
+      <c r="O156" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>134866169</v>
+      </c>
+      <c r="E157" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I157" s="5">
+        <v>42</v>
+      </c>
+      <c r="J157" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K157" s="5">
+        <v>0</v>
+      </c>
+      <c r="L157" s="5">
+        <v>61</v>
+      </c>
+      <c r="O157" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>134973101</v>
+      </c>
+      <c r="E158" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" s="5">
+        <v>42</v>
+      </c>
+      <c r="J158" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K158" s="5">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5">
+        <v>61</v>
+      </c>
+      <c r="O158" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>134986369</v>
+      </c>
+      <c r="E159" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I159" s="5">
+        <v>42</v>
+      </c>
+      <c r="J159" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K159" s="5">
+        <v>0</v>
+      </c>
+      <c r="L159" s="5">
+        <v>61</v>
+      </c>
+      <c r="O159" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>135043179</v>
+      </c>
+      <c r="E160" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" s="5">
+        <v>42</v>
+      </c>
+      <c r="J160" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K160" s="5">
+        <v>0</v>
+      </c>
+      <c r="L160" s="5">
+        <v>61</v>
+      </c>
+      <c r="O160" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>135043635</v>
+      </c>
+      <c r="E161" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I161" s="5">
+        <v>42</v>
+      </c>
+      <c r="J161" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K161" s="5">
+        <v>0</v>
+      </c>
+      <c r="L161" s="5">
+        <v>61</v>
+      </c>
+      <c r="O161" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>135049135</v>
+      </c>
+      <c r="E162" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I162" s="5">
+        <v>42</v>
+      </c>
+      <c r="J162" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K162" s="5">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5">
+        <v>61</v>
+      </c>
+      <c r="O162" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>135054152</v>
+      </c>
+      <c r="E163" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I163" s="5">
+        <v>42</v>
+      </c>
+      <c r="J163" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K163" s="5">
+        <v>0</v>
+      </c>
+      <c r="L163" s="5">
+        <v>61</v>
+      </c>
+      <c r="O163" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>135072756</v>
+      </c>
+      <c r="E164" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" s="5">
+        <v>42</v>
+      </c>
+      <c r="J164" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K164" s="5">
+        <v>0</v>
+      </c>
+      <c r="L164" s="5">
+        <v>61</v>
+      </c>
+      <c r="O164" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>135066194</v>
+      </c>
+      <c r="E165" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I165" s="5">
+        <v>42</v>
+      </c>
+      <c r="J165" s="5">
+        <v>715</v>
+      </c>
+      <c r="K165" s="5">
+        <v>0</v>
+      </c>
+      <c r="L165" s="5">
+        <v>61</v>
+      </c>
+      <c r="O165" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>135110151</v>
+      </c>
+      <c r="E166" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I166" s="5">
+        <v>42</v>
+      </c>
+      <c r="J166" s="5">
+        <v>718</v>
+      </c>
+      <c r="K166" s="5">
+        <v>0</v>
+      </c>
+      <c r="L166" s="5">
+        <v>61</v>
+      </c>
+      <c r="O166" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>135110567</v>
+      </c>
+      <c r="E167" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I167" s="5">
+        <v>42</v>
+      </c>
+      <c r="J167" s="5">
+        <v>718</v>
+      </c>
+      <c r="K167" s="5">
+        <v>0</v>
+      </c>
+      <c r="L167" s="5">
+        <v>61</v>
+      </c>
+      <c r="O167" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>135111971</v>
+      </c>
+      <c r="E168" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I168" s="5">
+        <v>42</v>
+      </c>
+      <c r="J168" s="5">
+        <v>718</v>
+      </c>
+      <c r="K168" s="5">
+        <v>0</v>
+      </c>
+      <c r="L168" s="5">
+        <v>61</v>
+      </c>
+      <c r="O168" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>135112732</v>
+      </c>
+      <c r="E169" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I169" s="5">
+        <v>42</v>
+      </c>
+      <c r="J169" s="5">
+        <v>718</v>
+      </c>
+      <c r="K169" s="5">
+        <v>0</v>
+      </c>
+      <c r="L169" s="5">
+        <v>61</v>
+      </c>
+      <c r="O169" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>135115406</v>
+      </c>
+      <c r="E170" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I170" s="5">
+        <v>42</v>
+      </c>
+      <c r="J170" s="5">
+        <v>718</v>
+      </c>
+      <c r="K170" s="5">
+        <v>0</v>
+      </c>
+      <c r="L170" s="5">
+        <v>61</v>
+      </c>
+      <c r="O170" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>135115520</v>
+      </c>
+      <c r="E171" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I171" s="5">
+        <v>42</v>
+      </c>
+      <c r="J171" s="5">
+        <v>718</v>
+      </c>
+      <c r="K171" s="5">
+        <v>0</v>
+      </c>
+      <c r="L171" s="5">
+        <v>61</v>
+      </c>
+      <c r="O171" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>135115698</v>
+      </c>
+      <c r="E172" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I172" s="5">
+        <v>42</v>
+      </c>
+      <c r="J172" s="5">
+        <v>718</v>
+      </c>
+      <c r="K172" s="5">
+        <v>0</v>
+      </c>
+      <c r="L172" s="5">
+        <v>61</v>
+      </c>
+      <c r="O172" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>135115923</v>
+      </c>
+      <c r="E173" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I173" s="5">
+        <v>42</v>
+      </c>
+      <c r="J173" s="5">
+        <v>718</v>
+      </c>
+      <c r="K173" s="5">
+        <v>0</v>
+      </c>
+      <c r="L173" s="5">
+        <v>61</v>
+      </c>
+      <c r="O173" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>135116010</v>
+      </c>
+      <c r="E174" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I174" s="5">
+        <v>42</v>
+      </c>
+      <c r="J174" s="5">
+        <v>718</v>
+      </c>
+      <c r="K174" s="5">
+        <v>0</v>
+      </c>
+      <c r="L174" s="5">
+        <v>61</v>
+      </c>
+      <c r="O174" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" s="6">
+        <v>135116503</v>
+      </c>
+      <c r="E175" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I175" s="5">
+        <v>42</v>
+      </c>
+      <c r="J175" s="5">
+        <v>718</v>
+      </c>
+      <c r="K175" s="5">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5">
+        <v>61</v>
+      </c>
+      <c r="O175" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" s="6">
+        <v>135118707</v>
+      </c>
+      <c r="E176" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I176" s="5">
+        <v>42</v>
+      </c>
+      <c r="J176" s="5">
+        <v>718</v>
+      </c>
+      <c r="K176" s="5">
+        <v>0</v>
+      </c>
+      <c r="L176" s="5">
+        <v>61</v>
+      </c>
+      <c r="O176" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" s="6">
+        <v>135119150</v>
+      </c>
+      <c r="E177" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I177" s="5">
+        <v>42</v>
+      </c>
+      <c r="J177" s="5">
+        <v>718</v>
+      </c>
+      <c r="K177" s="5">
+        <v>0</v>
+      </c>
+      <c r="L177" s="5">
+        <v>61</v>
+      </c>
+      <c r="O177" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" s="6">
+        <v>135119540</v>
+      </c>
+      <c r="E178" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I178" s="5">
+        <v>42</v>
+      </c>
+      <c r="J178" s="5">
+        <v>718</v>
+      </c>
+      <c r="K178" s="5">
+        <v>0</v>
+      </c>
+      <c r="L178" s="5">
+        <v>61</v>
+      </c>
+      <c r="O178" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="6">
+        <v>135119627</v>
+      </c>
+      <c r="E179" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I179" s="5">
+        <v>42</v>
+      </c>
+      <c r="J179" s="5">
+        <v>718</v>
+      </c>
+      <c r="K179" s="5">
+        <v>0</v>
+      </c>
+      <c r="L179" s="5">
+        <v>61</v>
+      </c>
+      <c r="O179" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" s="6">
+        <v>135120067</v>
+      </c>
+      <c r="E180" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I180" s="5">
+        <v>42</v>
+      </c>
+      <c r="J180" s="5">
+        <v>718</v>
+      </c>
+      <c r="K180" s="5">
+        <v>0</v>
+      </c>
+      <c r="L180" s="5">
+        <v>61</v>
+      </c>
+      <c r="O180" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" s="6">
+        <v>135120128</v>
+      </c>
+      <c r="E181" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I181" s="5">
+        <v>42</v>
+      </c>
+      <c r="J181" s="5">
+        <v>718</v>
+      </c>
+      <c r="K181" s="5">
+        <v>0</v>
+      </c>
+      <c r="L181" s="5">
+        <v>61</v>
+      </c>
+      <c r="O181" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
+        <v>135120174</v>
+      </c>
+      <c r="E182" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I182" s="5">
+        <v>42</v>
+      </c>
+      <c r="J182" s="5">
+        <v>718</v>
+      </c>
+      <c r="K182" s="5">
+        <v>0</v>
+      </c>
+      <c r="L182" s="5">
+        <v>61</v>
+      </c>
+      <c r="O182" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183" s="6">
+        <v>135121464</v>
+      </c>
+      <c r="E183" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I183" s="5">
+        <v>42</v>
+      </c>
+      <c r="J183" s="5">
+        <v>718</v>
+      </c>
+      <c r="K183" s="5">
+        <v>0</v>
+      </c>
+      <c r="L183" s="5">
+        <v>61</v>
+      </c>
+      <c r="O183" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
+        <v>135121592</v>
+      </c>
+      <c r="E184" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I184" s="5">
+        <v>42</v>
+      </c>
+      <c r="J184" s="5">
+        <v>718</v>
+      </c>
+      <c r="K184" s="5">
+        <v>0</v>
+      </c>
+      <c r="L184" s="5">
+        <v>61</v>
+      </c>
+      <c r="O184" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" s="6">
+        <v>135122132</v>
+      </c>
+      <c r="E185" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I185" s="5">
+        <v>42</v>
+      </c>
+      <c r="J185" s="5">
+        <v>718</v>
+      </c>
+      <c r="K185" s="5">
+        <v>0</v>
+      </c>
+      <c r="L185" s="5">
+        <v>61</v>
+      </c>
+      <c r="O185" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3296,31 +6111,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CCF915-0927-4A49-AB60-617A76EB4000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1459B4-57AD-483D-A9BD-7E7AEF1F61C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1809,31 +1809,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1459B4-57AD-483D-A9BD-7E7AEF1F61C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AABA2BC-3ACE-4D7A-8C8E-63858B99CAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIEL" sheetId="1" r:id="rId1"/>
@@ -1809,31 +1809,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AABA2BC-3ACE-4D7A-8C8E-63858B99CAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE1038A-74F6-4B96-9FC9-96A56EED99B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="23">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,6 +79,12 @@
     <t>B</t>
   </si>
   <si>
+    <t>27/10/2025</t>
+  </si>
+  <si>
+    <t>28/10/2025</t>
+  </si>
+  <si>
     <t>8/3/2023</t>
   </si>
   <si>
@@ -88,7 +94,7 @@
     <t>23/10/2025</t>
   </si>
   <si>
-    <t>28/10/2025</t>
+    <t>29/10/2025</t>
   </si>
   <si>
     <t>24/10/2025</t>
@@ -509,7 +515,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -579,22 +585,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>123058958</v>
+        <v>135108743</v>
       </c>
       <c r="E2" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -610,22 +616,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>130278085</v>
+        <v>135117575</v>
       </c>
       <c r="E3" s="5">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -641,22 +647,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>130757552</v>
+        <v>135119916</v>
       </c>
       <c r="E4" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -672,22 +678,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>132822826</v>
+        <v>135121703</v>
       </c>
       <c r="E5" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -703,22 +709,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>133137905</v>
+        <v>135121795</v>
       </c>
       <c r="E6" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -734,22 +740,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>133213701</v>
+        <v>135123306</v>
       </c>
       <c r="E7" s="5">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -765,22 +771,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>133729848</v>
+        <v>135110602</v>
       </c>
       <c r="E8" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -796,22 +802,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>133917350</v>
+        <v>135113787</v>
       </c>
       <c r="E9" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -827,22 +833,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>130278085</v>
+        <v>135116007</v>
       </c>
       <c r="E10" s="5">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -858,22 +864,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>132822826</v>
+        <v>135116165</v>
       </c>
       <c r="E11" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -889,22 +895,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133137905</v>
+        <v>135116691</v>
       </c>
       <c r="E12" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -920,22 +926,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>135129018</v>
+        <v>135117697</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -951,22 +957,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>135129407</v>
+        <v>135123246</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -982,13 +988,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>135130424</v>
+        <v>123058958</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>19</v>
@@ -997,7 +1003,7 @@
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1013,22 +1019,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>135131359</v>
+        <v>130367567</v>
       </c>
       <c r="E16" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1044,22 +1050,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>135131627</v>
+        <v>130594794</v>
       </c>
       <c r="E17" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1075,22 +1081,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>135134781</v>
+        <v>131266893</v>
       </c>
       <c r="E18" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1106,22 +1112,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>135135113</v>
+        <v>132958141</v>
       </c>
       <c r="E19" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1137,22 +1143,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>135135148</v>
+        <v>133147258</v>
       </c>
       <c r="E20" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1168,22 +1174,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>135135149</v>
+        <v>133567617</v>
       </c>
       <c r="E21" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1199,22 +1205,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>135135350</v>
+        <v>130594794</v>
       </c>
       <c r="E22" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1230,22 +1236,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>135135610</v>
+        <v>131266893</v>
       </c>
       <c r="E23" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1261,22 +1267,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>135136082</v>
+        <v>133147258</v>
       </c>
       <c r="E24" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1292,16 +1298,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>135136344</v>
+        <v>135146892</v>
       </c>
       <c r="E25" s="5">
         <v>2013</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1323,16 +1329,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>135136422</v>
+        <v>135147586</v>
       </c>
       <c r="E26" s="5">
         <v>2013</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1354,16 +1360,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>135136631</v>
+        <v>135147883</v>
       </c>
       <c r="E27" s="5">
         <v>2013</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
@@ -1385,16 +1391,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>135136894</v>
+        <v>135148882</v>
       </c>
       <c r="E28" s="5">
         <v>2013</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
@@ -1416,16 +1422,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>135136968</v>
+        <v>135149189</v>
       </c>
       <c r="E29" s="5">
         <v>2013</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I29" s="5">
         <v>42</v>
@@ -1447,16 +1453,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>135136974</v>
+        <v>135151876</v>
       </c>
       <c r="E30" s="5">
         <v>2013</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I30" s="5">
         <v>42</v>
@@ -1478,16 +1484,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>135137285</v>
+        <v>135152918</v>
       </c>
       <c r="E31" s="5">
         <v>2013</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I31" s="5">
         <v>42</v>
@@ -1509,16 +1515,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>135137418</v>
+        <v>135153201</v>
       </c>
       <c r="E32" s="5">
         <v>2013</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
@@ -1540,16 +1546,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>135137888</v>
+        <v>135153219</v>
       </c>
       <c r="E33" s="5">
         <v>2013</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
@@ -1571,16 +1577,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>135138006</v>
+        <v>135153265</v>
       </c>
       <c r="E34" s="5">
         <v>2013</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1602,16 +1608,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>135138046</v>
+        <v>135153337</v>
       </c>
       <c r="E35" s="5">
         <v>2013</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I35" s="5">
         <v>42</v>
@@ -1633,16 +1639,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>135138384</v>
+        <v>135155022</v>
       </c>
       <c r="E36" s="5">
         <v>2013</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I36" s="5">
         <v>42</v>
@@ -1664,16 +1670,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>135138759</v>
+        <v>135155361</v>
       </c>
       <c r="E37" s="5">
         <v>2013</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I37" s="5">
         <v>42</v>
@@ -1695,16 +1701,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>135139211</v>
+        <v>135155481</v>
       </c>
       <c r="E38" s="5">
         <v>2013</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I38" s="5">
         <v>42</v>
@@ -1726,16 +1732,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>135142437</v>
+        <v>135155628</v>
       </c>
       <c r="E39" s="5">
         <v>2013</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
@@ -1757,16 +1763,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>135143032</v>
+        <v>135155803</v>
       </c>
       <c r="E40" s="5">
         <v>2013</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I40" s="5">
         <v>42</v>
@@ -1783,6 +1789,192 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>135156555</v>
+      </c>
+      <c r="E41" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="5">
+        <v>42</v>
+      </c>
+      <c r="J41" s="5">
+        <v>718</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>61</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>135156674</v>
+      </c>
+      <c r="E42" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="5">
+        <v>42</v>
+      </c>
+      <c r="J42" s="5">
+        <v>718</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>61</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>135157131</v>
+      </c>
+      <c r="E43" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="5">
+        <v>42</v>
+      </c>
+      <c r="J43" s="5">
+        <v>718</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>61</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>135158953</v>
+      </c>
+      <c r="E44" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="5">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>718</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>61</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>135160354</v>
+      </c>
+      <c r="E45" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="5">
+        <v>42</v>
+      </c>
+      <c r="J45" s="5">
+        <v>718</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5">
+        <v>61</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>135160642</v>
+      </c>
+      <c r="E46" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="5">
+        <v>42</v>
+      </c>
+      <c r="J46" s="5">
+        <v>718</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>61</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE1038A-74F6-4B96-9FC9-96A56EED99B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156CE5E0-B12F-4406-AA6F-C9141E62C077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -91,13 +91,10 @@
     <t>10/3/2023</t>
   </si>
   <si>
-    <t>23/10/2025</t>
-  </si>
-  <si>
-    <t>29/10/2025</t>
-  </si>
-  <si>
-    <t>24/10/2025</t>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>26/10/2025</t>
   </si>
 </sst>
 </file>
@@ -515,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -585,22 +582,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>135108743</v>
+        <v>123058958</v>
       </c>
       <c r="E2" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -616,22 +613,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>135117575</v>
+        <v>130927495</v>
       </c>
       <c r="E3" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -647,22 +644,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>135119916</v>
+        <v>132431450</v>
       </c>
       <c r="E4" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -678,22 +675,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>135121703</v>
+        <v>132862401</v>
       </c>
       <c r="E5" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -709,22 +706,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>135121795</v>
+        <v>133214012</v>
       </c>
       <c r="E6" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -740,22 +737,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>135123306</v>
+        <v>133291944</v>
       </c>
       <c r="E7" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -771,22 +768,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>135110602</v>
+        <v>133607051</v>
       </c>
       <c r="E8" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -802,22 +799,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>135113787</v>
+        <v>134085181</v>
       </c>
       <c r="E9" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -833,22 +830,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>135116007</v>
+        <v>130927495</v>
       </c>
       <c r="E10" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -864,22 +861,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>135116165</v>
+        <v>133214012</v>
       </c>
       <c r="E11" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -895,22 +892,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>135116691</v>
+        <v>133607051</v>
       </c>
       <c r="E12" s="5">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -926,22 +923,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>135117697</v>
+        <v>135167341</v>
       </c>
       <c r="E13" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -957,22 +954,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>135123246</v>
+        <v>135167878</v>
       </c>
       <c r="E14" s="5">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>8013</v>
+        <v>718</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -988,22 +985,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>123058958</v>
+        <v>135168409</v>
       </c>
       <c r="E15" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1019,22 +1016,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>130367567</v>
+        <v>135168534</v>
       </c>
       <c r="E16" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1050,22 +1047,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>130594794</v>
+        <v>135169890</v>
       </c>
       <c r="E17" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1081,22 +1078,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>131266893</v>
+        <v>135169936</v>
       </c>
       <c r="E18" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1112,22 +1109,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>132958141</v>
+        <v>135170125</v>
       </c>
       <c r="E19" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1143,22 +1140,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>133147258</v>
+        <v>135170182</v>
       </c>
       <c r="E20" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1174,22 +1171,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>133567617</v>
+        <v>135170221</v>
       </c>
       <c r="E21" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1205,22 +1202,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>130594794</v>
+        <v>135171051</v>
       </c>
       <c r="E22" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1236,22 +1233,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>131266893</v>
+        <v>135171413</v>
       </c>
       <c r="E23" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1267,22 +1264,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>133147258</v>
+        <v>135174600</v>
       </c>
       <c r="E24" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1293,688 +1290,6 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>135146892</v>
-      </c>
-      <c r="E25" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="5">
-        <v>42</v>
-      </c>
-      <c r="J25" s="5">
-        <v>718</v>
-      </c>
-      <c r="K25" s="5">
-        <v>0</v>
-      </c>
-      <c r="L25" s="5">
-        <v>61</v>
-      </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>135147586</v>
-      </c>
-      <c r="E26" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="5">
-        <v>42</v>
-      </c>
-      <c r="J26" s="5">
-        <v>718</v>
-      </c>
-      <c r="K26" s="5">
-        <v>0</v>
-      </c>
-      <c r="L26" s="5">
-        <v>61</v>
-      </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>135147883</v>
-      </c>
-      <c r="E27" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="5">
-        <v>42</v>
-      </c>
-      <c r="J27" s="5">
-        <v>718</v>
-      </c>
-      <c r="K27" s="5">
-        <v>0</v>
-      </c>
-      <c r="L27" s="5">
-        <v>61</v>
-      </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>135148882</v>
-      </c>
-      <c r="E28" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="5">
-        <v>42</v>
-      </c>
-      <c r="J28" s="5">
-        <v>718</v>
-      </c>
-      <c r="K28" s="5">
-        <v>0</v>
-      </c>
-      <c r="L28" s="5">
-        <v>61</v>
-      </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>135149189</v>
-      </c>
-      <c r="E29" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="5">
-        <v>42</v>
-      </c>
-      <c r="J29" s="5">
-        <v>718</v>
-      </c>
-      <c r="K29" s="5">
-        <v>0</v>
-      </c>
-      <c r="L29" s="5">
-        <v>61</v>
-      </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
-        <v>135151876</v>
-      </c>
-      <c r="E30" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="5">
-        <v>42</v>
-      </c>
-      <c r="J30" s="5">
-        <v>718</v>
-      </c>
-      <c r="K30" s="5">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5">
-        <v>61</v>
-      </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
-        <v>135152918</v>
-      </c>
-      <c r="E31" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="5">
-        <v>42</v>
-      </c>
-      <c r="J31" s="5">
-        <v>718</v>
-      </c>
-      <c r="K31" s="5">
-        <v>0</v>
-      </c>
-      <c r="L31" s="5">
-        <v>61</v>
-      </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
-        <v>135153201</v>
-      </c>
-      <c r="E32" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="5">
-        <v>42</v>
-      </c>
-      <c r="J32" s="5">
-        <v>718</v>
-      </c>
-      <c r="K32" s="5">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <v>61</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
-        <v>135153219</v>
-      </c>
-      <c r="E33" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="5">
-        <v>42</v>
-      </c>
-      <c r="J33" s="5">
-        <v>718</v>
-      </c>
-      <c r="K33" s="5">
-        <v>0</v>
-      </c>
-      <c r="L33" s="5">
-        <v>61</v>
-      </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>135153265</v>
-      </c>
-      <c r="E34" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="5">
-        <v>42</v>
-      </c>
-      <c r="J34" s="5">
-        <v>718</v>
-      </c>
-      <c r="K34" s="5">
-        <v>0</v>
-      </c>
-      <c r="L34" s="5">
-        <v>61</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>135153337</v>
-      </c>
-      <c r="E35" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="5">
-        <v>42</v>
-      </c>
-      <c r="J35" s="5">
-        <v>718</v>
-      </c>
-      <c r="K35" s="5">
-        <v>0</v>
-      </c>
-      <c r="L35" s="5">
-        <v>61</v>
-      </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
-        <v>135155022</v>
-      </c>
-      <c r="E36" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="5">
-        <v>42</v>
-      </c>
-      <c r="J36" s="5">
-        <v>718</v>
-      </c>
-      <c r="K36" s="5">
-        <v>0</v>
-      </c>
-      <c r="L36" s="5">
-        <v>61</v>
-      </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>135155361</v>
-      </c>
-      <c r="E37" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="5">
-        <v>42</v>
-      </c>
-      <c r="J37" s="5">
-        <v>718</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0</v>
-      </c>
-      <c r="L37" s="5">
-        <v>61</v>
-      </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
-        <v>135155481</v>
-      </c>
-      <c r="E38" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="5">
-        <v>42</v>
-      </c>
-      <c r="J38" s="5">
-        <v>718</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5">
-        <v>61</v>
-      </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
-        <v>135155628</v>
-      </c>
-      <c r="E39" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="5">
-        <v>42</v>
-      </c>
-      <c r="J39" s="5">
-        <v>718</v>
-      </c>
-      <c r="K39" s="5">
-        <v>0</v>
-      </c>
-      <c r="L39" s="5">
-        <v>61</v>
-      </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
-        <v>135155803</v>
-      </c>
-      <c r="E40" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="5">
-        <v>42</v>
-      </c>
-      <c r="J40" s="5">
-        <v>718</v>
-      </c>
-      <c r="K40" s="5">
-        <v>0</v>
-      </c>
-      <c r="L40" s="5">
-        <v>61</v>
-      </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
-        <v>135156555</v>
-      </c>
-      <c r="E41" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="5">
-        <v>42</v>
-      </c>
-      <c r="J41" s="5">
-        <v>718</v>
-      </c>
-      <c r="K41" s="5">
-        <v>0</v>
-      </c>
-      <c r="L41" s="5">
-        <v>61</v>
-      </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>135156674</v>
-      </c>
-      <c r="E42" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="5">
-        <v>42</v>
-      </c>
-      <c r="J42" s="5">
-        <v>718</v>
-      </c>
-      <c r="K42" s="5">
-        <v>0</v>
-      </c>
-      <c r="L42" s="5">
-        <v>61</v>
-      </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>135157131</v>
-      </c>
-      <c r="E43" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="5">
-        <v>42</v>
-      </c>
-      <c r="J43" s="5">
-        <v>718</v>
-      </c>
-      <c r="K43" s="5">
-        <v>0</v>
-      </c>
-      <c r="L43" s="5">
-        <v>61</v>
-      </c>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
-        <v>135158953</v>
-      </c>
-      <c r="E44" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44" s="5">
-        <v>42</v>
-      </c>
-      <c r="J44" s="5">
-        <v>718</v>
-      </c>
-      <c r="K44" s="5">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5">
-        <v>61</v>
-      </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>135160354</v>
-      </c>
-      <c r="E45" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45" s="5">
-        <v>42</v>
-      </c>
-      <c r="J45" s="5">
-        <v>718</v>
-      </c>
-      <c r="K45" s="5">
-        <v>0</v>
-      </c>
-      <c r="L45" s="5">
-        <v>61</v>
-      </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
-        <v>135160642</v>
-      </c>
-      <c r="E46" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="5">
-        <v>42</v>
-      </c>
-      <c r="J46" s="5">
-        <v>718</v>
-      </c>
-      <c r="K46" s="5">
-        <v>0</v>
-      </c>
-      <c r="L46" s="5">
-        <v>61</v>
-      </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2001,31 +1316,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156CE5E0-B12F-4406-AA6F-C9141E62C077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEFA5E6-1399-4BA5-8E07-21F8074C4F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -79,12 +79,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>27/10/2025</t>
-  </si>
-  <si>
-    <t>28/10/2025</t>
-  </si>
-  <si>
     <t>8/3/2023</t>
   </si>
   <si>
@@ -94,7 +88,13 @@
     <t>30/10/2025</t>
   </si>
   <si>
-    <t>26/10/2025</t>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>29/10/2025</t>
+  </si>
+  <si>
+    <t>1/11/2025</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -582,13 +582,13 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>123058958</v>
+        <v>135186979</v>
       </c>
       <c r="E2" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>19</v>
@@ -597,7 +597,7 @@
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -613,22 +613,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>130927495</v>
+        <v>135194079</v>
       </c>
       <c r="E3" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -644,22 +644,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>132431450</v>
+        <v>135197069</v>
       </c>
       <c r="E4" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -675,22 +675,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>132862401</v>
+        <v>135197235</v>
       </c>
       <c r="E5" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -706,22 +706,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>133214012</v>
+        <v>135198310</v>
       </c>
       <c r="E6" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>133291944</v>
+        <v>135198722</v>
       </c>
       <c r="E7" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -768,22 +768,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>133607051</v>
+        <v>135200108</v>
       </c>
       <c r="E8" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -799,22 +799,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>134085181</v>
+        <v>135200583</v>
       </c>
       <c r="E9" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -830,22 +830,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>130927495</v>
+        <v>135201404</v>
       </c>
       <c r="E10" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -861,22 +861,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>133214012</v>
+        <v>135201485</v>
       </c>
       <c r="E11" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -892,22 +892,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>133607051</v>
+        <v>135201942</v>
       </c>
       <c r="E12" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -923,22 +923,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>135167341</v>
+        <v>135100352</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -954,10 +954,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>135167878</v>
+        <v>135150541</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>135168409</v>
+        <v>135151100</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>20</v>
@@ -1000,7 +1000,7 @@
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>135168534</v>
+        <v>135152811</v>
       </c>
       <c r="E16" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>20</v>
@@ -1031,7 +1031,7 @@
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1047,22 +1047,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>135169890</v>
+        <v>135193609</v>
       </c>
       <c r="E17" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1078,22 +1078,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>135169936</v>
+        <v>135195308</v>
       </c>
       <c r="E18" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1109,22 +1109,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>135170125</v>
+        <v>135200355</v>
       </c>
       <c r="E19" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1140,22 +1140,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>135170182</v>
+        <v>135177081</v>
       </c>
       <c r="E20" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>135170221</v>
+        <v>123058958</v>
       </c>
       <c r="E21" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1202,22 +1202,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>135171051</v>
+        <v>130113222</v>
       </c>
       <c r="E22" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1233,22 +1233,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>135171413</v>
+        <v>130281045</v>
       </c>
       <c r="E23" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1264,22 +1264,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>135174600</v>
+        <v>130396445</v>
       </c>
       <c r="E24" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1290,6 +1290,5927 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>130577396</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="5">
+        <v>42</v>
+      </c>
+      <c r="J25" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>61</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>130611329</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="5">
+        <v>42</v>
+      </c>
+      <c r="J26" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <v>61</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>130613360</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="5">
+        <v>42</v>
+      </c>
+      <c r="J27" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <v>61</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>130670144</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="5">
+        <v>42</v>
+      </c>
+      <c r="J28" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <v>61</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>130687284</v>
+      </c>
+      <c r="E29" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="5">
+        <v>42</v>
+      </c>
+      <c r="J29" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>61</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>130772599</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="5">
+        <v>42</v>
+      </c>
+      <c r="J30" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <v>61</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>130813330</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="5">
+        <v>42</v>
+      </c>
+      <c r="J31" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>61</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>131013792</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="5">
+        <v>42</v>
+      </c>
+      <c r="J32" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>61</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>131017896</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="5">
+        <v>42</v>
+      </c>
+      <c r="J33" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>61</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>131035973</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="5">
+        <v>42</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>61</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>131083429</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="5">
+        <v>42</v>
+      </c>
+      <c r="J35" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>61</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>131108839</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="5">
+        <v>42</v>
+      </c>
+      <c r="J36" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>61</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>131112693</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="5">
+        <v>42</v>
+      </c>
+      <c r="J37" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>61</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>131183426</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="5">
+        <v>42</v>
+      </c>
+      <c r="J38" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>61</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>131187771</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="5">
+        <v>42</v>
+      </c>
+      <c r="J39" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>61</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>131221343</v>
+      </c>
+      <c r="E40" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="5">
+        <v>42</v>
+      </c>
+      <c r="J40" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>61</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>131310262</v>
+      </c>
+      <c r="E41" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="5">
+        <v>42</v>
+      </c>
+      <c r="J41" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>61</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>131313269</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="5">
+        <v>42</v>
+      </c>
+      <c r="J42" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>61</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>131320933</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="5">
+        <v>42</v>
+      </c>
+      <c r="J43" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>61</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>131336492</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="5">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>61</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>131412058</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="5">
+        <v>42</v>
+      </c>
+      <c r="J45" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5">
+        <v>61</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>131457571</v>
+      </c>
+      <c r="E46" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="5">
+        <v>42</v>
+      </c>
+      <c r="J46" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>61</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>131459027</v>
+      </c>
+      <c r="E47" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="5">
+        <v>42</v>
+      </c>
+      <c r="J47" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>61</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>131472321</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="5">
+        <v>42</v>
+      </c>
+      <c r="J48" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <v>61</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>131480065</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="5">
+        <v>42</v>
+      </c>
+      <c r="J49" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>61</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>131536159</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="5">
+        <v>42</v>
+      </c>
+      <c r="J50" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>61</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>131539616</v>
+      </c>
+      <c r="E51" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="5">
+        <v>42</v>
+      </c>
+      <c r="J51" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>61</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>131540045</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="5">
+        <v>42</v>
+      </c>
+      <c r="J52" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>61</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>131541477</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="5">
+        <v>42</v>
+      </c>
+      <c r="J53" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <v>61</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>131552641</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="5">
+        <v>42</v>
+      </c>
+      <c r="J54" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>61</v>
+      </c>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>131687216</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="5">
+        <v>42</v>
+      </c>
+      <c r="J55" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>61</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>131814197</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="5">
+        <v>42</v>
+      </c>
+      <c r="J56" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>61</v>
+      </c>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>131843361</v>
+      </c>
+      <c r="E57" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="5">
+        <v>42</v>
+      </c>
+      <c r="J57" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>61</v>
+      </c>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>131856490</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="5">
+        <v>42</v>
+      </c>
+      <c r="J58" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>61</v>
+      </c>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>131889470</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="5">
+        <v>42</v>
+      </c>
+      <c r="J59" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5">
+        <v>61</v>
+      </c>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>131909917</v>
+      </c>
+      <c r="E60" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>131914086</v>
+      </c>
+      <c r="E61" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>132179489</v>
+      </c>
+      <c r="E62" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>132219153</v>
+      </c>
+      <c r="E63" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>132246004</v>
+      </c>
+      <c r="E64" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>132268010</v>
+      </c>
+      <c r="E65" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>132346097</v>
+      </c>
+      <c r="E66" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>132397795</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>132420150</v>
+      </c>
+      <c r="E68" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>132423709</v>
+      </c>
+      <c r="E69" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>132474988</v>
+      </c>
+      <c r="E70" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>132618900</v>
+      </c>
+      <c r="E71" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>132686867</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>132796002</v>
+      </c>
+      <c r="E73" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>132915901</v>
+      </c>
+      <c r="E74" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>132920131</v>
+      </c>
+      <c r="E75" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>132935466</v>
+      </c>
+      <c r="E76" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>133004508</v>
+      </c>
+      <c r="E77" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>133026668</v>
+      </c>
+      <c r="E78" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>133046257</v>
+      </c>
+      <c r="E79" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I79" s="5">
+        <v>42</v>
+      </c>
+      <c r="J79" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5">
+        <v>61</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>133049831</v>
+      </c>
+      <c r="E80" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" s="5">
+        <v>42</v>
+      </c>
+      <c r="J80" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>61</v>
+      </c>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>133059352</v>
+      </c>
+      <c r="E81" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" s="5">
+        <v>42</v>
+      </c>
+      <c r="J81" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>61</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>133104179</v>
+      </c>
+      <c r="E82" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I82" s="5">
+        <v>42</v>
+      </c>
+      <c r="J82" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5">
+        <v>61</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>133123524</v>
+      </c>
+      <c r="E83" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" s="5">
+        <v>42</v>
+      </c>
+      <c r="J83" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5">
+        <v>61</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>133134240</v>
+      </c>
+      <c r="E84" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" s="5">
+        <v>42</v>
+      </c>
+      <c r="J84" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5">
+        <v>61</v>
+      </c>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>133175544</v>
+      </c>
+      <c r="E85" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I85" s="5">
+        <v>42</v>
+      </c>
+      <c r="J85" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5">
+        <v>61</v>
+      </c>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>133203131</v>
+      </c>
+      <c r="E86" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" s="5">
+        <v>42</v>
+      </c>
+      <c r="J86" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5">
+        <v>61</v>
+      </c>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>133227536</v>
+      </c>
+      <c r="E87" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" s="5">
+        <v>42</v>
+      </c>
+      <c r="J87" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5">
+        <v>61</v>
+      </c>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>133260755</v>
+      </c>
+      <c r="E88" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>133283493</v>
+      </c>
+      <c r="E89" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      </c>
+      <c r="J89" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5">
+        <v>61</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>133298893</v>
+      </c>
+      <c r="E90" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I90" s="5">
+        <v>42</v>
+      </c>
+      <c r="J90" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5">
+        <v>61</v>
+      </c>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>133356166</v>
+      </c>
+      <c r="E91" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="5">
+        <v>42</v>
+      </c>
+      <c r="J91" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5">
+        <v>61</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>133430269</v>
+      </c>
+      <c r="E92" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" s="5">
+        <v>42</v>
+      </c>
+      <c r="J92" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5">
+        <v>61</v>
+      </c>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>133510356</v>
+      </c>
+      <c r="E93" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I93" s="5">
+        <v>42</v>
+      </c>
+      <c r="J93" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5">
+        <v>61</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>133617274</v>
+      </c>
+      <c r="E94" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" s="5">
+        <v>42</v>
+      </c>
+      <c r="J94" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5">
+        <v>61</v>
+      </c>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>133722128</v>
+      </c>
+      <c r="E95" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I95" s="5">
+        <v>42</v>
+      </c>
+      <c r="J95" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>61</v>
+      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>133841061</v>
+      </c>
+      <c r="E96" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I96" s="5">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5">
+        <v>61</v>
+      </c>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>133855313</v>
+      </c>
+      <c r="E97" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I97" s="5">
+        <v>42</v>
+      </c>
+      <c r="J97" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5">
+        <v>61</v>
+      </c>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>133931792</v>
+      </c>
+      <c r="E98" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I98" s="5">
+        <v>42</v>
+      </c>
+      <c r="J98" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5">
+        <v>61</v>
+      </c>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>133976715</v>
+      </c>
+      <c r="E99" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I99" s="5">
+        <v>42</v>
+      </c>
+      <c r="J99" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
+        <v>61</v>
+      </c>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>134021585</v>
+      </c>
+      <c r="E100" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I100" s="5">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>61</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>134027864</v>
+      </c>
+      <c r="E101" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I101" s="5">
+        <v>42</v>
+      </c>
+      <c r="J101" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>61</v>
+      </c>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>134131754</v>
+      </c>
+      <c r="E102" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I102" s="5">
+        <v>42</v>
+      </c>
+      <c r="J102" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>61</v>
+      </c>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>134229263</v>
+      </c>
+      <c r="E103" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I103" s="5">
+        <v>42</v>
+      </c>
+      <c r="J103" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>61</v>
+      </c>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>134240719</v>
+      </c>
+      <c r="E104" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I104" s="5">
+        <v>42</v>
+      </c>
+      <c r="J104" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5">
+        <v>61</v>
+      </c>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>134282440</v>
+      </c>
+      <c r="E105" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I105" s="5">
+        <v>42</v>
+      </c>
+      <c r="J105" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5">
+        <v>61</v>
+      </c>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>134384730</v>
+      </c>
+      <c r="E106" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I106" s="5">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5">
+        <v>61</v>
+      </c>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>134397404</v>
+      </c>
+      <c r="E107" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I107" s="5">
+        <v>42</v>
+      </c>
+      <c r="J107" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5">
+        <v>61</v>
+      </c>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>134549084</v>
+      </c>
+      <c r="E108" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I108" s="5">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5">
+        <v>61</v>
+      </c>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>134554725</v>
+      </c>
+      <c r="E109" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I109" s="5">
+        <v>42</v>
+      </c>
+      <c r="J109" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5">
+        <v>61</v>
+      </c>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>134592762</v>
+      </c>
+      <c r="E110" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I110" s="5">
+        <v>42</v>
+      </c>
+      <c r="J110" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5">
+        <v>61</v>
+      </c>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>134601502</v>
+      </c>
+      <c r="E111" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I111" s="5">
+        <v>42</v>
+      </c>
+      <c r="J111" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5">
+        <v>61</v>
+      </c>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>134707278</v>
+      </c>
+      <c r="E112" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I112" s="5">
+        <v>42</v>
+      </c>
+      <c r="J112" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5">
+        <v>61</v>
+      </c>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>134769050</v>
+      </c>
+      <c r="E113" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I113" s="5">
+        <v>42</v>
+      </c>
+      <c r="J113" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5">
+        <v>61</v>
+      </c>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>134771665</v>
+      </c>
+      <c r="E114" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I114" s="5">
+        <v>42</v>
+      </c>
+      <c r="J114" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5">
+        <v>61</v>
+      </c>
+      <c r="M114" s="5"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>134778323</v>
+      </c>
+      <c r="E115" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I115" s="5">
+        <v>42</v>
+      </c>
+      <c r="J115" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5">
+        <v>61</v>
+      </c>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>134787572</v>
+      </c>
+      <c r="E116" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I116" s="5">
+        <v>42</v>
+      </c>
+      <c r="J116" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" s="5">
+        <v>61</v>
+      </c>
+      <c r="M116" s="5"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>134841554</v>
+      </c>
+      <c r="E117" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I117" s="5">
+        <v>42</v>
+      </c>
+      <c r="J117" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" s="5">
+        <v>61</v>
+      </c>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>134883168</v>
+      </c>
+      <c r="E118" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I118" s="5">
+        <v>42</v>
+      </c>
+      <c r="J118" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5">
+        <v>61</v>
+      </c>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5"/>
+      <c r="O118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>135006892</v>
+      </c>
+      <c r="E119" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I119" s="5">
+        <v>42</v>
+      </c>
+      <c r="J119" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5">
+        <v>61</v>
+      </c>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>135023406</v>
+      </c>
+      <c r="E120" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I120" s="5">
+        <v>42</v>
+      </c>
+      <c r="J120" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5">
+        <v>61</v>
+      </c>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>135026582</v>
+      </c>
+      <c r="E121" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I121" s="5">
+        <v>42</v>
+      </c>
+      <c r="J121" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5">
+        <v>61</v>
+      </c>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>135066635</v>
+      </c>
+      <c r="E122" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I122" s="5">
+        <v>42</v>
+      </c>
+      <c r="J122" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5">
+        <v>61</v>
+      </c>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>135072359</v>
+      </c>
+      <c r="E123" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I123" s="5">
+        <v>42</v>
+      </c>
+      <c r="J123" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5">
+        <v>61</v>
+      </c>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>135079171</v>
+      </c>
+      <c r="E124" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I124" s="5">
+        <v>42</v>
+      </c>
+      <c r="J124" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5">
+        <v>61</v>
+      </c>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>135095800</v>
+      </c>
+      <c r="E125" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I125" s="5">
+        <v>42</v>
+      </c>
+      <c r="J125" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="5">
+        <v>61</v>
+      </c>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>135102232</v>
+      </c>
+      <c r="E126" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I126" s="5">
+        <v>42</v>
+      </c>
+      <c r="J126" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5">
+        <v>61</v>
+      </c>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>135123836</v>
+      </c>
+      <c r="E127" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I127" s="5">
+        <v>42</v>
+      </c>
+      <c r="J127" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5">
+        <v>61</v>
+      </c>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>135142095</v>
+      </c>
+      <c r="E128" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I128" s="5">
+        <v>42</v>
+      </c>
+      <c r="J128" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5">
+        <v>61</v>
+      </c>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>135144026</v>
+      </c>
+      <c r="E129" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I129" s="5">
+        <v>42</v>
+      </c>
+      <c r="J129" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
+        <v>61</v>
+      </c>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>135157018</v>
+      </c>
+      <c r="E130" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I130" s="5">
+        <v>42</v>
+      </c>
+      <c r="J130" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5">
+        <v>61</v>
+      </c>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>135160910</v>
+      </c>
+      <c r="E131" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I131" s="5">
+        <v>42</v>
+      </c>
+      <c r="J131" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5">
+        <v>61</v>
+      </c>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>135161194</v>
+      </c>
+      <c r="E132" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I132" s="5">
+        <v>42</v>
+      </c>
+      <c r="J132" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5">
+        <v>61</v>
+      </c>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>135168402</v>
+      </c>
+      <c r="E133" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I133" s="5">
+        <v>42</v>
+      </c>
+      <c r="J133" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5">
+        <v>61</v>
+      </c>
+      <c r="M133" s="5"/>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>135172005</v>
+      </c>
+      <c r="E134" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I134" s="5">
+        <v>42</v>
+      </c>
+      <c r="J134" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5">
+        <v>61</v>
+      </c>
+      <c r="M134" s="5"/>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>130113222</v>
+      </c>
+      <c r="E135" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I135" s="5">
+        <v>42</v>
+      </c>
+      <c r="J135" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" s="5">
+        <v>61</v>
+      </c>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>130281045</v>
+      </c>
+      <c r="E136" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I136" s="5">
+        <v>42</v>
+      </c>
+      <c r="J136" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5">
+        <v>61</v>
+      </c>
+      <c r="M136" s="5"/>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>130396445</v>
+      </c>
+      <c r="E137" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I137" s="5">
+        <v>42</v>
+      </c>
+      <c r="J137" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5">
+        <v>61</v>
+      </c>
+      <c r="M137" s="5"/>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>130613360</v>
+      </c>
+      <c r="E138" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" s="5">
+        <v>42</v>
+      </c>
+      <c r="J138" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5">
+        <v>61</v>
+      </c>
+      <c r="M138" s="5"/>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>130813330</v>
+      </c>
+      <c r="E139" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I139" s="5">
+        <v>42</v>
+      </c>
+      <c r="J139" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5">
+        <v>61</v>
+      </c>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+      <c r="O139" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>131013792</v>
+      </c>
+      <c r="E140" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I140" s="5">
+        <v>42</v>
+      </c>
+      <c r="J140" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5">
+        <v>61</v>
+      </c>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>131035973</v>
+      </c>
+      <c r="E141" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I141" s="5">
+        <v>42</v>
+      </c>
+      <c r="J141" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="L141" s="5">
+        <v>61</v>
+      </c>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
+      <c r="O141" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>131083429</v>
+      </c>
+      <c r="E142" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I142" s="5">
+        <v>42</v>
+      </c>
+      <c r="J142" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5">
+        <v>61</v>
+      </c>
+      <c r="M142" s="5"/>
+      <c r="N142" s="5"/>
+      <c r="O142" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>131108839</v>
+      </c>
+      <c r="E143" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I143" s="5">
+        <v>42</v>
+      </c>
+      <c r="J143" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="L143" s="5">
+        <v>61</v>
+      </c>
+      <c r="M143" s="5"/>
+      <c r="N143" s="5"/>
+      <c r="O143" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>131112693</v>
+      </c>
+      <c r="E144" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I144" s="5">
+        <v>42</v>
+      </c>
+      <c r="J144" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5">
+        <v>61</v>
+      </c>
+      <c r="M144" s="5"/>
+      <c r="N144" s="5"/>
+      <c r="O144" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>131183426</v>
+      </c>
+      <c r="E145" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I145" s="5">
+        <v>42</v>
+      </c>
+      <c r="J145" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="L145" s="5">
+        <v>61</v>
+      </c>
+      <c r="M145" s="5"/>
+      <c r="N145" s="5"/>
+      <c r="O145" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>131310262</v>
+      </c>
+      <c r="E146" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" s="5">
+        <v>42</v>
+      </c>
+      <c r="J146" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5">
+        <v>61</v>
+      </c>
+      <c r="M146" s="5"/>
+      <c r="N146" s="5"/>
+      <c r="O146" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>131336492</v>
+      </c>
+      <c r="E147" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" s="5">
+        <v>42</v>
+      </c>
+      <c r="J147" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5">
+        <v>61</v>
+      </c>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>131457571</v>
+      </c>
+      <c r="E148" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" s="5">
+        <v>42</v>
+      </c>
+      <c r="J148" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5">
+        <v>61</v>
+      </c>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>131472321</v>
+      </c>
+      <c r="E149" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I149" s="5">
+        <v>42</v>
+      </c>
+      <c r="J149" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5">
+        <v>61</v>
+      </c>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
+      <c r="O149" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>131480065</v>
+      </c>
+      <c r="E150" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I150" s="5">
+        <v>42</v>
+      </c>
+      <c r="J150" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5">
+        <v>61</v>
+      </c>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>131539616</v>
+      </c>
+      <c r="E151" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I151" s="5">
+        <v>42</v>
+      </c>
+      <c r="J151" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5">
+        <v>61</v>
+      </c>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>131540045</v>
+      </c>
+      <c r="E152" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I152" s="5">
+        <v>42</v>
+      </c>
+      <c r="J152" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="L152" s="5">
+        <v>61</v>
+      </c>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>131541477</v>
+      </c>
+      <c r="E153" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I153" s="5">
+        <v>42</v>
+      </c>
+      <c r="J153" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K153" s="5">
+        <v>0</v>
+      </c>
+      <c r="L153" s="5">
+        <v>61</v>
+      </c>
+      <c r="M153" s="5"/>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>131552641</v>
+      </c>
+      <c r="E154" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I154" s="5">
+        <v>42</v>
+      </c>
+      <c r="J154" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K154" s="5">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5">
+        <v>61</v>
+      </c>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>131814197</v>
+      </c>
+      <c r="E155" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I155" s="5">
+        <v>42</v>
+      </c>
+      <c r="J155" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K155" s="5">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5">
+        <v>61</v>
+      </c>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>131843361</v>
+      </c>
+      <c r="E156" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I156" s="5">
+        <v>42</v>
+      </c>
+      <c r="J156" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K156" s="5">
+        <v>0</v>
+      </c>
+      <c r="L156" s="5">
+        <v>61</v>
+      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>131889470</v>
+      </c>
+      <c r="E157" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I157" s="5">
+        <v>42</v>
+      </c>
+      <c r="J157" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K157" s="5">
+        <v>0</v>
+      </c>
+      <c r="L157" s="5">
+        <v>61</v>
+      </c>
+      <c r="M157" s="5"/>
+      <c r="N157" s="5"/>
+      <c r="O157" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>132219153</v>
+      </c>
+      <c r="E158" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I158" s="5">
+        <v>42</v>
+      </c>
+      <c r="J158" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K158" s="5">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5">
+        <v>61</v>
+      </c>
+      <c r="M158" s="5"/>
+      <c r="N158" s="5"/>
+      <c r="O158" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>132397795</v>
+      </c>
+      <c r="E159" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I159" s="5">
+        <v>42</v>
+      </c>
+      <c r="J159" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K159" s="5">
+        <v>0</v>
+      </c>
+      <c r="L159" s="5">
+        <v>61</v>
+      </c>
+      <c r="M159" s="5"/>
+      <c r="N159" s="5"/>
+      <c r="O159" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>132915901</v>
+      </c>
+      <c r="E160" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I160" s="5">
+        <v>42</v>
+      </c>
+      <c r="J160" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K160" s="5">
+        <v>0</v>
+      </c>
+      <c r="L160" s="5">
+        <v>61</v>
+      </c>
+      <c r="M160" s="5"/>
+      <c r="N160" s="5"/>
+      <c r="O160" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>132920131</v>
+      </c>
+      <c r="E161" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I161" s="5">
+        <v>42</v>
+      </c>
+      <c r="J161" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K161" s="5">
+        <v>0</v>
+      </c>
+      <c r="L161" s="5">
+        <v>61</v>
+      </c>
+      <c r="M161" s="5"/>
+      <c r="N161" s="5"/>
+      <c r="O161" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>133004508</v>
+      </c>
+      <c r="E162" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I162" s="5">
+        <v>42</v>
+      </c>
+      <c r="J162" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K162" s="5">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5">
+        <v>61</v>
+      </c>
+      <c r="M162" s="5"/>
+      <c r="N162" s="5"/>
+      <c r="O162" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>133026668</v>
+      </c>
+      <c r="E163" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I163" s="5">
+        <v>42</v>
+      </c>
+      <c r="J163" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K163" s="5">
+        <v>0</v>
+      </c>
+      <c r="L163" s="5">
+        <v>61</v>
+      </c>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
+      <c r="O163" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>133104179</v>
+      </c>
+      <c r="E164" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I164" s="5">
+        <v>42</v>
+      </c>
+      <c r="J164" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K164" s="5">
+        <v>0</v>
+      </c>
+      <c r="L164" s="5">
+        <v>61</v>
+      </c>
+      <c r="M164" s="5"/>
+      <c r="N164" s="5"/>
+      <c r="O164" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>133123524</v>
+      </c>
+      <c r="E165" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I165" s="5">
+        <v>42</v>
+      </c>
+      <c r="J165" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K165" s="5">
+        <v>0</v>
+      </c>
+      <c r="L165" s="5">
+        <v>61</v>
+      </c>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+      <c r="O165" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>133203131</v>
+      </c>
+      <c r="E166" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I166" s="5">
+        <v>42</v>
+      </c>
+      <c r="J166" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K166" s="5">
+        <v>0</v>
+      </c>
+      <c r="L166" s="5">
+        <v>61</v>
+      </c>
+      <c r="M166" s="5"/>
+      <c r="N166" s="5"/>
+      <c r="O166" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>133260755</v>
+      </c>
+      <c r="E167" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I167" s="5">
+        <v>42</v>
+      </c>
+      <c r="J167" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K167" s="5">
+        <v>0</v>
+      </c>
+      <c r="L167" s="5">
+        <v>61</v>
+      </c>
+      <c r="M167" s="5"/>
+      <c r="N167" s="5"/>
+      <c r="O167" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>133298893</v>
+      </c>
+      <c r="E168" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I168" s="5">
+        <v>42</v>
+      </c>
+      <c r="J168" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K168" s="5">
+        <v>0</v>
+      </c>
+      <c r="L168" s="5">
+        <v>61</v>
+      </c>
+      <c r="M168" s="5"/>
+      <c r="N168" s="5"/>
+      <c r="O168" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>133430269</v>
+      </c>
+      <c r="E169" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I169" s="5">
+        <v>42</v>
+      </c>
+      <c r="J169" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K169" s="5">
+        <v>0</v>
+      </c>
+      <c r="L169" s="5">
+        <v>61</v>
+      </c>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>133510356</v>
+      </c>
+      <c r="E170" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I170" s="5">
+        <v>42</v>
+      </c>
+      <c r="J170" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K170" s="5">
+        <v>0</v>
+      </c>
+      <c r="L170" s="5">
+        <v>61</v>
+      </c>
+      <c r="M170" s="5"/>
+      <c r="N170" s="5"/>
+      <c r="O170" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>133855313</v>
+      </c>
+      <c r="E171" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I171" s="5">
+        <v>42</v>
+      </c>
+      <c r="J171" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K171" s="5">
+        <v>0</v>
+      </c>
+      <c r="L171" s="5">
+        <v>61</v>
+      </c>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>133931792</v>
+      </c>
+      <c r="E172" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I172" s="5">
+        <v>42</v>
+      </c>
+      <c r="J172" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K172" s="5">
+        <v>0</v>
+      </c>
+      <c r="L172" s="5">
+        <v>61</v>
+      </c>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+      <c r="O172" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>133976715</v>
+      </c>
+      <c r="E173" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I173" s="5">
+        <v>42</v>
+      </c>
+      <c r="J173" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K173" s="5">
+        <v>0</v>
+      </c>
+      <c r="L173" s="5">
+        <v>61</v>
+      </c>
+      <c r="M173" s="5"/>
+      <c r="N173" s="5"/>
+      <c r="O173" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>134027864</v>
+      </c>
+      <c r="E174" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I174" s="5">
+        <v>42</v>
+      </c>
+      <c r="J174" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K174" s="5">
+        <v>0</v>
+      </c>
+      <c r="L174" s="5">
+        <v>61</v>
+      </c>
+      <c r="M174" s="5"/>
+      <c r="N174" s="5"/>
+      <c r="O174" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" s="6">
+        <v>134131754</v>
+      </c>
+      <c r="E175" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I175" s="5">
+        <v>42</v>
+      </c>
+      <c r="J175" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K175" s="5">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5">
+        <v>61</v>
+      </c>
+      <c r="M175" s="5"/>
+      <c r="N175" s="5"/>
+      <c r="O175" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" s="6">
+        <v>134384730</v>
+      </c>
+      <c r="E176" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I176" s="5">
+        <v>42</v>
+      </c>
+      <c r="J176" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K176" s="5">
+        <v>0</v>
+      </c>
+      <c r="L176" s="5">
+        <v>61</v>
+      </c>
+      <c r="M176" s="5"/>
+      <c r="N176" s="5"/>
+      <c r="O176" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" s="6">
+        <v>134549084</v>
+      </c>
+      <c r="E177" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I177" s="5">
+        <v>42</v>
+      </c>
+      <c r="J177" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K177" s="5">
+        <v>0</v>
+      </c>
+      <c r="L177" s="5">
+        <v>61</v>
+      </c>
+      <c r="M177" s="5"/>
+      <c r="N177" s="5"/>
+      <c r="O177" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" s="6">
+        <v>134601502</v>
+      </c>
+      <c r="E178" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I178" s="5">
+        <v>42</v>
+      </c>
+      <c r="J178" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K178" s="5">
+        <v>0</v>
+      </c>
+      <c r="L178" s="5">
+        <v>61</v>
+      </c>
+      <c r="M178" s="5"/>
+      <c r="N178" s="5"/>
+      <c r="O178" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="6">
+        <v>134707278</v>
+      </c>
+      <c r="E179" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I179" s="5">
+        <v>42</v>
+      </c>
+      <c r="J179" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K179" s="5">
+        <v>0</v>
+      </c>
+      <c r="L179" s="5">
+        <v>61</v>
+      </c>
+      <c r="M179" s="5"/>
+      <c r="N179" s="5"/>
+      <c r="O179" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" s="6">
+        <v>134769050</v>
+      </c>
+      <c r="E180" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I180" s="5">
+        <v>42</v>
+      </c>
+      <c r="J180" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K180" s="5">
+        <v>0</v>
+      </c>
+      <c r="L180" s="5">
+        <v>61</v>
+      </c>
+      <c r="M180" s="5"/>
+      <c r="N180" s="5"/>
+      <c r="O180" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" s="6">
+        <v>134841554</v>
+      </c>
+      <c r="E181" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I181" s="5">
+        <v>42</v>
+      </c>
+      <c r="J181" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K181" s="5">
+        <v>0</v>
+      </c>
+      <c r="L181" s="5">
+        <v>61</v>
+      </c>
+      <c r="M181" s="5"/>
+      <c r="N181" s="5"/>
+      <c r="O181" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
+        <v>134883168</v>
+      </c>
+      <c r="E182" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I182" s="5">
+        <v>42</v>
+      </c>
+      <c r="J182" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K182" s="5">
+        <v>0</v>
+      </c>
+      <c r="L182" s="5">
+        <v>61</v>
+      </c>
+      <c r="M182" s="5"/>
+      <c r="N182" s="5"/>
+      <c r="O182" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183" s="6">
+        <v>135006892</v>
+      </c>
+      <c r="E183" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I183" s="5">
+        <v>42</v>
+      </c>
+      <c r="J183" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K183" s="5">
+        <v>0</v>
+      </c>
+      <c r="L183" s="5">
+        <v>61</v>
+      </c>
+      <c r="M183" s="5"/>
+      <c r="N183" s="5"/>
+      <c r="O183" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
+        <v>135072359</v>
+      </c>
+      <c r="E184" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I184" s="5">
+        <v>42</v>
+      </c>
+      <c r="J184" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K184" s="5">
+        <v>0</v>
+      </c>
+      <c r="L184" s="5">
+        <v>61</v>
+      </c>
+      <c r="M184" s="5"/>
+      <c r="N184" s="5"/>
+      <c r="O184" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" s="6">
+        <v>135079171</v>
+      </c>
+      <c r="E185" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I185" s="5">
+        <v>42</v>
+      </c>
+      <c r="J185" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K185" s="5">
+        <v>0</v>
+      </c>
+      <c r="L185" s="5">
+        <v>61</v>
+      </c>
+      <c r="M185" s="5"/>
+      <c r="N185" s="5"/>
+      <c r="O185" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186" s="6">
+        <v>135095800</v>
+      </c>
+      <c r="E186" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I186" s="5">
+        <v>42</v>
+      </c>
+      <c r="J186" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K186" s="5">
+        <v>0</v>
+      </c>
+      <c r="L186" s="5">
+        <v>61</v>
+      </c>
+      <c r="M186" s="5"/>
+      <c r="N186" s="5"/>
+      <c r="O186" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187" s="6">
+        <v>135102232</v>
+      </c>
+      <c r="E187" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I187" s="5">
+        <v>42</v>
+      </c>
+      <c r="J187" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K187" s="5">
+        <v>0</v>
+      </c>
+      <c r="L187" s="5">
+        <v>61</v>
+      </c>
+      <c r="M187" s="5"/>
+      <c r="N187" s="5"/>
+      <c r="O187" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" s="6">
+        <v>135142095</v>
+      </c>
+      <c r="E188" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I188" s="5">
+        <v>42</v>
+      </c>
+      <c r="J188" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K188" s="5">
+        <v>0</v>
+      </c>
+      <c r="L188" s="5">
+        <v>61</v>
+      </c>
+      <c r="M188" s="5"/>
+      <c r="N188" s="5"/>
+      <c r="O188" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189" s="6">
+        <v>135144026</v>
+      </c>
+      <c r="E189" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I189" s="5">
+        <v>42</v>
+      </c>
+      <c r="J189" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K189" s="5">
+        <v>0</v>
+      </c>
+      <c r="L189" s="5">
+        <v>61</v>
+      </c>
+      <c r="M189" s="5"/>
+      <c r="N189" s="5"/>
+      <c r="O189" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190" s="6">
+        <v>135157018</v>
+      </c>
+      <c r="E190" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I190" s="5">
+        <v>42</v>
+      </c>
+      <c r="J190" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K190" s="5">
+        <v>0</v>
+      </c>
+      <c r="L190" s="5">
+        <v>61</v>
+      </c>
+      <c r="M190" s="5"/>
+      <c r="N190" s="5"/>
+      <c r="O190" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191" s="6">
+        <v>135161194</v>
+      </c>
+      <c r="E191" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I191" s="5">
+        <v>42</v>
+      </c>
+      <c r="J191" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K191" s="5">
+        <v>0</v>
+      </c>
+      <c r="L191" s="5">
+        <v>61</v>
+      </c>
+      <c r="M191" s="5"/>
+      <c r="N191" s="5"/>
+      <c r="O191" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192" s="6">
+        <v>135168402</v>
+      </c>
+      <c r="E192" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I192" s="5">
+        <v>42</v>
+      </c>
+      <c r="J192" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K192" s="5">
+        <v>0</v>
+      </c>
+      <c r="L192" s="5">
+        <v>61</v>
+      </c>
+      <c r="M192" s="5"/>
+      <c r="N192" s="5"/>
+      <c r="O192" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A193" s="6">
+        <v>135172005</v>
+      </c>
+      <c r="E193" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I193" s="5">
+        <v>42</v>
+      </c>
+      <c r="J193" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K193" s="5">
+        <v>0</v>
+      </c>
+      <c r="L193" s="5">
+        <v>61</v>
+      </c>
+      <c r="M193" s="5"/>
+      <c r="N193" s="5"/>
+      <c r="O193" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A194" s="6">
+        <v>135185326</v>
+      </c>
+      <c r="E194" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I194" s="5">
+        <v>42</v>
+      </c>
+      <c r="J194" s="5">
+        <v>718</v>
+      </c>
+      <c r="K194" s="5">
+        <v>0</v>
+      </c>
+      <c r="L194" s="5">
+        <v>61</v>
+      </c>
+      <c r="M194" s="5"/>
+      <c r="N194" s="5"/>
+      <c r="O194" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A195" s="6">
+        <v>135186003</v>
+      </c>
+      <c r="E195" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I195" s="5">
+        <v>42</v>
+      </c>
+      <c r="J195" s="5">
+        <v>718</v>
+      </c>
+      <c r="K195" s="5">
+        <v>0</v>
+      </c>
+      <c r="L195" s="5">
+        <v>61</v>
+      </c>
+      <c r="M195" s="5"/>
+      <c r="N195" s="5"/>
+      <c r="O195" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A196" s="6">
+        <v>135186702</v>
+      </c>
+      <c r="E196" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I196" s="5">
+        <v>42</v>
+      </c>
+      <c r="J196" s="5">
+        <v>718</v>
+      </c>
+      <c r="K196" s="5">
+        <v>0</v>
+      </c>
+      <c r="L196" s="5">
+        <v>61</v>
+      </c>
+      <c r="M196" s="5"/>
+      <c r="N196" s="5"/>
+      <c r="O196" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197" s="6">
+        <v>135190893</v>
+      </c>
+      <c r="E197" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I197" s="5">
+        <v>42</v>
+      </c>
+      <c r="J197" s="5">
+        <v>718</v>
+      </c>
+      <c r="K197" s="5">
+        <v>0</v>
+      </c>
+      <c r="L197" s="5">
+        <v>61</v>
+      </c>
+      <c r="M197" s="5"/>
+      <c r="N197" s="5"/>
+      <c r="O197" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198" s="6">
+        <v>135194923</v>
+      </c>
+      <c r="E198" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I198" s="5">
+        <v>42</v>
+      </c>
+      <c r="J198" s="5">
+        <v>718</v>
+      </c>
+      <c r="K198" s="5">
+        <v>0</v>
+      </c>
+      <c r="L198" s="5">
+        <v>61</v>
+      </c>
+      <c r="M198" s="5"/>
+      <c r="N198" s="5"/>
+      <c r="O198" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A199" s="6">
+        <v>135195258</v>
+      </c>
+      <c r="E199" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I199" s="5">
+        <v>42</v>
+      </c>
+      <c r="J199" s="5">
+        <v>718</v>
+      </c>
+      <c r="K199" s="5">
+        <v>0</v>
+      </c>
+      <c r="L199" s="5">
+        <v>61</v>
+      </c>
+      <c r="M199" s="5"/>
+      <c r="N199" s="5"/>
+      <c r="O199" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A200" s="6">
+        <v>135195955</v>
+      </c>
+      <c r="E200" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I200" s="5">
+        <v>42</v>
+      </c>
+      <c r="J200" s="5">
+        <v>718</v>
+      </c>
+      <c r="K200" s="5">
+        <v>0</v>
+      </c>
+      <c r="L200" s="5">
+        <v>61</v>
+      </c>
+      <c r="M200" s="5"/>
+      <c r="N200" s="5"/>
+      <c r="O200" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A201" s="6">
+        <v>135198059</v>
+      </c>
+      <c r="E201" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I201" s="5">
+        <v>42</v>
+      </c>
+      <c r="J201" s="5">
+        <v>718</v>
+      </c>
+      <c r="K201" s="5">
+        <v>0</v>
+      </c>
+      <c r="L201" s="5">
+        <v>61</v>
+      </c>
+      <c r="M201" s="5"/>
+      <c r="N201" s="5"/>
+      <c r="O201" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A202" s="6">
+        <v>135198324</v>
+      </c>
+      <c r="E202" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I202" s="5">
+        <v>42</v>
+      </c>
+      <c r="J202" s="5">
+        <v>718</v>
+      </c>
+      <c r="K202" s="5">
+        <v>0</v>
+      </c>
+      <c r="L202" s="5">
+        <v>61</v>
+      </c>
+      <c r="M202" s="5"/>
+      <c r="N202" s="5"/>
+      <c r="O202" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203" s="6">
+        <v>135198363</v>
+      </c>
+      <c r="E203" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I203" s="5">
+        <v>42</v>
+      </c>
+      <c r="J203" s="5">
+        <v>718</v>
+      </c>
+      <c r="K203" s="5">
+        <v>0</v>
+      </c>
+      <c r="L203" s="5">
+        <v>61</v>
+      </c>
+      <c r="M203" s="5"/>
+      <c r="N203" s="5"/>
+      <c r="O203" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204" s="6">
+        <v>135198435</v>
+      </c>
+      <c r="E204" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I204" s="5">
+        <v>42</v>
+      </c>
+      <c r="J204" s="5">
+        <v>718</v>
+      </c>
+      <c r="K204" s="5">
+        <v>0</v>
+      </c>
+      <c r="L204" s="5">
+        <v>61</v>
+      </c>
+      <c r="M204" s="5"/>
+      <c r="N204" s="5"/>
+      <c r="O204" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A205" s="6">
+        <v>135198653</v>
+      </c>
+      <c r="E205" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I205" s="5">
+        <v>42</v>
+      </c>
+      <c r="J205" s="5">
+        <v>718</v>
+      </c>
+      <c r="K205" s="5">
+        <v>0</v>
+      </c>
+      <c r="L205" s="5">
+        <v>61</v>
+      </c>
+      <c r="M205" s="5"/>
+      <c r="N205" s="5"/>
+      <c r="O205" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206" s="6">
+        <v>135198805</v>
+      </c>
+      <c r="E206" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I206" s="5">
+        <v>42</v>
+      </c>
+      <c r="J206" s="5">
+        <v>718</v>
+      </c>
+      <c r="K206" s="5">
+        <v>0</v>
+      </c>
+      <c r="L206" s="5">
+        <v>61</v>
+      </c>
+      <c r="M206" s="5"/>
+      <c r="N206" s="5"/>
+      <c r="O206" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207" s="6">
+        <v>135198965</v>
+      </c>
+      <c r="E207" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I207" s="5">
+        <v>42</v>
+      </c>
+      <c r="J207" s="5">
+        <v>718</v>
+      </c>
+      <c r="K207" s="5">
+        <v>0</v>
+      </c>
+      <c r="L207" s="5">
+        <v>61</v>
+      </c>
+      <c r="M207" s="5"/>
+      <c r="N207" s="5"/>
+      <c r="O207" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208" s="6">
+        <v>135199038</v>
+      </c>
+      <c r="E208" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I208" s="5">
+        <v>42</v>
+      </c>
+      <c r="J208" s="5">
+        <v>718</v>
+      </c>
+      <c r="K208" s="5">
+        <v>0</v>
+      </c>
+      <c r="L208" s="5">
+        <v>61</v>
+      </c>
+      <c r="M208" s="5"/>
+      <c r="N208" s="5"/>
+      <c r="O208" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209" s="6">
+        <v>135199343</v>
+      </c>
+      <c r="E209" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I209" s="5">
+        <v>42</v>
+      </c>
+      <c r="J209" s="5">
+        <v>718</v>
+      </c>
+      <c r="K209" s="5">
+        <v>0</v>
+      </c>
+      <c r="L209" s="5">
+        <v>61</v>
+      </c>
+      <c r="M209" s="5"/>
+      <c r="N209" s="5"/>
+      <c r="O209" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210" s="6">
+        <v>135199463</v>
+      </c>
+      <c r="E210" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I210" s="5">
+        <v>42</v>
+      </c>
+      <c r="J210" s="5">
+        <v>718</v>
+      </c>
+      <c r="K210" s="5">
+        <v>0</v>
+      </c>
+      <c r="L210" s="5">
+        <v>61</v>
+      </c>
+      <c r="M210" s="5"/>
+      <c r="N210" s="5"/>
+      <c r="O210" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A211" s="6">
+        <v>135199576</v>
+      </c>
+      <c r="E211" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I211" s="5">
+        <v>42</v>
+      </c>
+      <c r="J211" s="5">
+        <v>718</v>
+      </c>
+      <c r="K211" s="5">
+        <v>0</v>
+      </c>
+      <c r="L211" s="5">
+        <v>61</v>
+      </c>
+      <c r="M211" s="5"/>
+      <c r="N211" s="5"/>
+      <c r="O211" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A212" s="6">
+        <v>135199639</v>
+      </c>
+      <c r="E212" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I212" s="5">
+        <v>42</v>
+      </c>
+      <c r="J212" s="5">
+        <v>718</v>
+      </c>
+      <c r="K212" s="5">
+        <v>0</v>
+      </c>
+      <c r="L212" s="5">
+        <v>61</v>
+      </c>
+      <c r="M212" s="5"/>
+      <c r="N212" s="5"/>
+      <c r="O212" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A213" s="6">
+        <v>135199909</v>
+      </c>
+      <c r="E213" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I213" s="5">
+        <v>42</v>
+      </c>
+      <c r="J213" s="5">
+        <v>718</v>
+      </c>
+      <c r="K213" s="5">
+        <v>0</v>
+      </c>
+      <c r="L213" s="5">
+        <v>61</v>
+      </c>
+      <c r="M213" s="5"/>
+      <c r="N213" s="5"/>
+      <c r="O213" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A214" s="6">
+        <v>135200028</v>
+      </c>
+      <c r="E214" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I214" s="5">
+        <v>42</v>
+      </c>
+      <c r="J214" s="5">
+        <v>718</v>
+      </c>
+      <c r="K214" s="5">
+        <v>0</v>
+      </c>
+      <c r="L214" s="5">
+        <v>61</v>
+      </c>
+      <c r="M214" s="5"/>
+      <c r="N214" s="5"/>
+      <c r="O214" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215" s="6">
+        <v>135200131</v>
+      </c>
+      <c r="E215" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I215" s="5">
+        <v>42</v>
+      </c>
+      <c r="J215" s="5">
+        <v>718</v>
+      </c>
+      <c r="K215" s="5">
+        <v>0</v>
+      </c>
+      <c r="L215" s="5">
+        <v>61</v>
+      </c>
+      <c r="M215" s="5"/>
+      <c r="N215" s="5"/>
+      <c r="O215" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1316,31 +7237,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B4592A-B213-46E3-8BB9-DC04AECCA8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6930B905-2A08-4F4B-867F-199005DFAD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1651,31 +1651,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6930B905-2A08-4F4B-867F-199005DFAD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD273D0-08A1-48FC-A627-8876CCB6E0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="19">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -85,10 +85,7 @@
     <t>10/3/2023</t>
   </si>
   <si>
-    <t>1/11/2025</t>
-  </si>
-  <si>
-    <t>3/11/2025</t>
+    <t>4/11/2025</t>
   </si>
 </sst>
 </file>
@@ -607,22 +604,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>130419021</v>
+        <v>135226676</v>
       </c>
       <c r="E3" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -638,22 +635,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>131349551</v>
+        <v>135228087</v>
       </c>
       <c r="E4" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -669,22 +666,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>132424858</v>
+        <v>135228630</v>
       </c>
       <c r="E5" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -700,22 +697,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>131349551</v>
+        <v>135228660</v>
       </c>
       <c r="E6" s="5">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -731,16 +728,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>135206940</v>
+        <v>135229504</v>
       </c>
       <c r="E7" s="5">
         <v>2013</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
@@ -762,16 +759,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>135208516</v>
+        <v>135229573</v>
       </c>
       <c r="E8" s="5">
         <v>2013</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
@@ -793,16 +790,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>135208661</v>
+        <v>135229726</v>
       </c>
       <c r="E9" s="5">
         <v>2013</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
@@ -824,16 +821,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>135209972</v>
+        <v>135230110</v>
       </c>
       <c r="E10" s="5">
         <v>2013</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
@@ -855,16 +852,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>135210324</v>
+        <v>135230169</v>
       </c>
       <c r="E11" s="5">
         <v>2013</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
@@ -886,16 +883,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>135210830</v>
+        <v>135230331</v>
       </c>
       <c r="E12" s="5">
         <v>2013</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
@@ -917,16 +914,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>135211581</v>
+        <v>135230580</v>
       </c>
       <c r="E13" s="5">
         <v>2013</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
@@ -948,16 +945,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>135211904</v>
+        <v>135230691</v>
       </c>
       <c r="E14" s="5">
         <v>2013</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
@@ -979,16 +976,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>135212321</v>
+        <v>135231194</v>
       </c>
       <c r="E15" s="5">
         <v>2013</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I15" s="5">
         <v>42</v>
@@ -1010,16 +1007,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>135212399</v>
+        <v>135231258</v>
       </c>
       <c r="E16" s="5">
         <v>2013</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I16" s="5">
         <v>42</v>
@@ -1041,16 +1038,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>135212564</v>
+        <v>135231593</v>
       </c>
       <c r="E17" s="5">
         <v>2013</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1072,16 +1069,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>135212642</v>
+        <v>135231719</v>
       </c>
       <c r="E18" s="5">
         <v>2013</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1103,16 +1100,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>135212731</v>
+        <v>135231798</v>
       </c>
       <c r="E19" s="5">
         <v>2013</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I19" s="5">
         <v>42</v>
@@ -1134,16 +1131,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>135212922</v>
+        <v>135231928</v>
       </c>
       <c r="E20" s="5">
         <v>2013</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1165,16 +1162,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>135214191</v>
+        <v>135232411</v>
       </c>
       <c r="E21" s="5">
         <v>2013</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1196,16 +1193,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>135214252</v>
+        <v>135232611</v>
       </c>
       <c r="E22" s="5">
         <v>2013</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I22" s="5">
         <v>42</v>
@@ -1227,16 +1224,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>135214363</v>
+        <v>135233005</v>
       </c>
       <c r="E23" s="5">
         <v>2013</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1258,16 +1255,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>135214383</v>
+        <v>135235881</v>
       </c>
       <c r="E24" s="5">
         <v>2013</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I24" s="5">
         <v>42</v>
@@ -1289,16 +1286,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>135214429</v>
+        <v>135239623</v>
       </c>
       <c r="E25" s="5">
         <v>2013</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I25" s="5">
         <v>42</v>
@@ -1320,16 +1317,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>135214616</v>
+        <v>135239650</v>
       </c>
       <c r="E26" s="5">
         <v>2013</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1351,16 +1348,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>135216541</v>
+        <v>135240358</v>
       </c>
       <c r="E27" s="5">
         <v>2013</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I27" s="5">
         <v>42</v>
@@ -1382,16 +1379,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>135217017</v>
+        <v>135241219</v>
       </c>
       <c r="E28" s="5">
         <v>2013</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
@@ -1412,221 +1409,39 @@
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>135217476</v>
-      </c>
-      <c r="E29" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="5">
-        <v>42</v>
-      </c>
-      <c r="J29" s="5">
-        <v>718</v>
-      </c>
-      <c r="K29" s="5">
-        <v>0</v>
-      </c>
-      <c r="L29" s="5">
-        <v>61</v>
-      </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>135217589</v>
-      </c>
-      <c r="E30" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="5">
-        <v>42</v>
-      </c>
-      <c r="J30" s="5">
-        <v>718</v>
-      </c>
-      <c r="K30" s="5">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5">
-        <v>61</v>
-      </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>135220092</v>
-      </c>
-      <c r="E31" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I31" s="5">
-        <v>42</v>
-      </c>
-      <c r="J31" s="5">
-        <v>718</v>
-      </c>
-      <c r="K31" s="5">
-        <v>0</v>
-      </c>
-      <c r="L31" s="5">
-        <v>61</v>
-      </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O31" s="5"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>135220177</v>
-      </c>
-      <c r="E32" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="5">
-        <v>42</v>
-      </c>
-      <c r="J32" s="5">
-        <v>718</v>
-      </c>
-      <c r="K32" s="5">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <v>61</v>
-      </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>135220945</v>
-      </c>
-      <c r="E33" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="5">
-        <v>42</v>
-      </c>
-      <c r="J33" s="5">
-        <v>718</v>
-      </c>
-      <c r="K33" s="5">
-        <v>0</v>
-      </c>
-      <c r="L33" s="5">
-        <v>61</v>
-      </c>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" spans="13:15" x14ac:dyDescent="0.25">
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>135221210</v>
-      </c>
-      <c r="E34" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I34" s="5">
-        <v>42</v>
-      </c>
-      <c r="J34" s="5">
-        <v>718</v>
-      </c>
-      <c r="K34" s="5">
-        <v>0</v>
-      </c>
-      <c r="L34" s="5">
-        <v>61</v>
-      </c>
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" spans="13:15" x14ac:dyDescent="0.25">
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>135221561</v>
-      </c>
-      <c r="E35" s="5">
-        <v>2013</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="5">
-        <v>42</v>
-      </c>
-      <c r="J35" s="5">
-        <v>718</v>
-      </c>
-      <c r="K35" s="5">
-        <v>0</v>
-      </c>
-      <c r="L35" s="5">
-        <v>61</v>
-      </c>
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" spans="13:15" x14ac:dyDescent="0.25">
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="O35" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1651,31 +1466,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD273D0-08A1-48FC-A627-8876CCB6E0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6C685B-A495-4949-AD9B-B870BCE29E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -86,6 +86,15 @@
   </si>
   <si>
     <t>4/11/2025</t>
+  </si>
+  <si>
+    <t>3/11/2025</t>
+  </si>
+  <si>
+    <t>5/11/2025</t>
+  </si>
+  <si>
+    <t>31/10/2025</t>
   </si>
 </sst>
 </file>
@@ -503,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -573,22 +582,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>123058958</v>
+        <v>135207192</v>
       </c>
       <c r="E2" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -604,22 +613,22 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>135226676</v>
+        <v>135207425</v>
       </c>
       <c r="E3" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -635,22 +644,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>135228087</v>
+        <v>135212006</v>
       </c>
       <c r="E4" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -666,22 +675,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>135228630</v>
+        <v>135216909</v>
       </c>
       <c r="E5" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -697,22 +706,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>135228660</v>
+        <v>135208851</v>
       </c>
       <c r="E6" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
       </c>
       <c r="J6" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -728,22 +737,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>135229504</v>
+        <v>135212751</v>
       </c>
       <c r="E7" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
       </c>
       <c r="J7" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -759,22 +768,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>135229573</v>
+        <v>135214800</v>
       </c>
       <c r="E8" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
       </c>
       <c r="J8" s="5">
-        <v>718</v>
+        <v>1117</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -790,22 +799,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>135229726</v>
+        <v>135222454</v>
       </c>
       <c r="E9" s="5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
       </c>
       <c r="J9" s="5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -821,22 +830,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>135230110</v>
+        <v>123058958</v>
       </c>
       <c r="E10" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -852,22 +861,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>135230169</v>
+        <v>130298854</v>
       </c>
       <c r="E11" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -883,13 +892,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>135230331</v>
+        <v>130637043</v>
       </c>
       <c r="E12" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>18</v>
@@ -898,7 +907,7 @@
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -914,22 +923,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>135230580</v>
+        <v>130691637</v>
       </c>
       <c r="E13" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -945,13 +954,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>135230691</v>
+        <v>130917673</v>
       </c>
       <c r="E14" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>18</v>
@@ -960,7 +969,7 @@
         <v>42</v>
       </c>
       <c r="J14" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -976,13 +985,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>135231194</v>
+        <v>131181344</v>
       </c>
       <c r="E15" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>18</v>
@@ -991,7 +1000,7 @@
         <v>42</v>
       </c>
       <c r="J15" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1007,13 +1016,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>135231258</v>
+        <v>131485072</v>
       </c>
       <c r="E16" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>18</v>
@@ -1022,7 +1031,7 @@
         <v>42</v>
       </c>
       <c r="J16" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1038,22 +1047,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>135231593</v>
+        <v>132104464</v>
       </c>
       <c r="E17" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
       </c>
       <c r="J17" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K17" s="5">
         <v>0</v>
@@ -1069,13 +1078,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>135231719</v>
+        <v>132242374</v>
       </c>
       <c r="E18" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>18</v>
@@ -1084,7 +1093,7 @@
         <v>42</v>
       </c>
       <c r="J18" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -1100,13 +1109,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>135231798</v>
+        <v>132322487</v>
       </c>
       <c r="E19" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>18</v>
@@ -1115,7 +1124,7 @@
         <v>42</v>
       </c>
       <c r="J19" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -1131,22 +1140,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>135231928</v>
+        <v>132620051</v>
       </c>
       <c r="E20" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
       </c>
       <c r="J20" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -1162,22 +1171,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>135232411</v>
+        <v>132786812</v>
       </c>
       <c r="E21" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
       </c>
       <c r="J21" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K21" s="5">
         <v>0</v>
@@ -1193,13 +1202,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>135232611</v>
+        <v>132859110</v>
       </c>
       <c r="E22" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>18</v>
@@ -1208,7 +1217,7 @@
         <v>42</v>
       </c>
       <c r="J22" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K22" s="5">
         <v>0</v>
@@ -1224,13 +1233,13 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>135233005</v>
+        <v>133351628</v>
       </c>
       <c r="E23" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>18</v>
@@ -1239,7 +1248,7 @@
         <v>42</v>
       </c>
       <c r="J23" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -1255,13 +1264,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>135235881</v>
+        <v>133686201</v>
       </c>
       <c r="E24" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>18</v>
@@ -1270,7 +1279,7 @@
         <v>42</v>
       </c>
       <c r="J24" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -1286,13 +1295,13 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>135239623</v>
+        <v>133695981</v>
       </c>
       <c r="E25" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>18</v>
@@ -1301,7 +1310,7 @@
         <v>42</v>
       </c>
       <c r="J25" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -1317,13 +1326,13 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>135239650</v>
+        <v>133959327</v>
       </c>
       <c r="E26" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>18</v>
@@ -1332,7 +1341,7 @@
         <v>42</v>
       </c>
       <c r="J26" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -1348,13 +1357,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>135240358</v>
+        <v>133966020</v>
       </c>
       <c r="E27" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>18</v>
@@ -1363,7 +1372,7 @@
         <v>42</v>
       </c>
       <c r="J27" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K27" s="5">
         <v>0</v>
@@ -1379,22 +1388,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>135241219</v>
+        <v>134010928</v>
       </c>
       <c r="E28" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
       </c>
       <c r="J28" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -1409,39 +1418,1236 @@
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>134107654</v>
+      </c>
+      <c r="E29" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="5">
+        <v>42</v>
+      </c>
+      <c r="J29" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>61</v>
+      </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
+      <c r="O29" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>134224614</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="5">
+        <v>42</v>
+      </c>
+      <c r="J30" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <v>61</v>
+      </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
+      <c r="O30" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>134437598</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="5">
+        <v>42</v>
+      </c>
+      <c r="J31" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>61</v>
+      </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
+      <c r="O31" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>134722457</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="5">
+        <v>42</v>
+      </c>
+      <c r="J32" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>61</v>
+      </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-    </row>
-    <row r="33" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="O32" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>134908836</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="5">
+        <v>42</v>
+      </c>
+      <c r="J33" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>61</v>
+      </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-    </row>
-    <row r="34" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="O33" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>135192496</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="5">
+        <v>42</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>61</v>
+      </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-    </row>
-    <row r="35" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="O34" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>130298854</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="5">
+        <v>42</v>
+      </c>
+      <c r="J35" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>61</v>
+      </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
+      <c r="O35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>130637043</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="5">
+        <v>42</v>
+      </c>
+      <c r="J36" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>61</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>130917673</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="5">
+        <v>42</v>
+      </c>
+      <c r="J37" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>61</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>131181344</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="5">
+        <v>42</v>
+      </c>
+      <c r="J38" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>61</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>132242374</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="5">
+        <v>42</v>
+      </c>
+      <c r="J39" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>61</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>132322487</v>
+      </c>
+      <c r="E40" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="5">
+        <v>42</v>
+      </c>
+      <c r="J40" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>61</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>132786812</v>
+      </c>
+      <c r="E41" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="5">
+        <v>42</v>
+      </c>
+      <c r="J41" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>61</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>132859110</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="5">
+        <v>42</v>
+      </c>
+      <c r="J42" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>61</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>133686201</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="5">
+        <v>42</v>
+      </c>
+      <c r="J43" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>61</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>133966020</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="5">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>61</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>134010928</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="5">
+        <v>42</v>
+      </c>
+      <c r="J45" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5">
+        <v>61</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>134107654</v>
+      </c>
+      <c r="E46" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="5">
+        <v>42</v>
+      </c>
+      <c r="J46" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>61</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>135192496</v>
+      </c>
+      <c r="E47" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="5">
+        <v>42</v>
+      </c>
+      <c r="J47" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>61</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>135193982</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="5">
+        <v>42</v>
+      </c>
+      <c r="J48" s="5">
+        <v>715</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <v>61</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>135248139</v>
+      </c>
+      <c r="E49" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="5">
+        <v>42</v>
+      </c>
+      <c r="J49" s="5">
+        <v>718</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>61</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>135249587</v>
+      </c>
+      <c r="E50" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="5">
+        <v>42</v>
+      </c>
+      <c r="J50" s="5">
+        <v>718</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>61</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>135249661</v>
+      </c>
+      <c r="E51" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="5">
+        <v>42</v>
+      </c>
+      <c r="J51" s="5">
+        <v>718</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>61</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>135249921</v>
+      </c>
+      <c r="E52" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="5">
+        <v>42</v>
+      </c>
+      <c r="J52" s="5">
+        <v>718</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>61</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>135250911</v>
+      </c>
+      <c r="E53" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="5">
+        <v>42</v>
+      </c>
+      <c r="J53" s="5">
+        <v>718</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <v>61</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>135251121</v>
+      </c>
+      <c r="E54" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="5">
+        <v>42</v>
+      </c>
+      <c r="J54" s="5">
+        <v>718</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>61</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>135252177</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" s="5">
+        <v>42</v>
+      </c>
+      <c r="J55" s="5">
+        <v>718</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>61</v>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>135252379</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="5">
+        <v>42</v>
+      </c>
+      <c r="J56" s="5">
+        <v>718</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>61</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>135252492</v>
+      </c>
+      <c r="E57" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="5">
+        <v>42</v>
+      </c>
+      <c r="J57" s="5">
+        <v>718</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>61</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>135252704</v>
+      </c>
+      <c r="E58" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="5">
+        <v>42</v>
+      </c>
+      <c r="J58" s="5">
+        <v>718</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>61</v>
+      </c>
+      <c r="O58" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>135253514</v>
+      </c>
+      <c r="E59" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="5">
+        <v>42</v>
+      </c>
+      <c r="J59" s="5">
+        <v>718</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5">
+        <v>61</v>
+      </c>
+      <c r="O59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>135253903</v>
+      </c>
+      <c r="E60" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="5">
+        <v>42</v>
+      </c>
+      <c r="J60" s="5">
+        <v>718</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>61</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>135254878</v>
+      </c>
+      <c r="E61" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="5">
+        <v>42</v>
+      </c>
+      <c r="J61" s="5">
+        <v>718</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5">
+        <v>61</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>135254909</v>
+      </c>
+      <c r="E62" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="5">
+        <v>42</v>
+      </c>
+      <c r="J62" s="5">
+        <v>718</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>61</v>
+      </c>
+      <c r="O62" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>135256340</v>
+      </c>
+      <c r="E63" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="5">
+        <v>42</v>
+      </c>
+      <c r="J63" s="5">
+        <v>718</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>61</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>135257386</v>
+      </c>
+      <c r="E64" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="5">
+        <v>42</v>
+      </c>
+      <c r="J64" s="5">
+        <v>718</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>61</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>135257529</v>
+      </c>
+      <c r="E65" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="5">
+        <v>42</v>
+      </c>
+      <c r="J65" s="5">
+        <v>718</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <v>61</v>
+      </c>
+      <c r="O65" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>135257759</v>
+      </c>
+      <c r="E66" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="5">
+        <v>42</v>
+      </c>
+      <c r="J66" s="5">
+        <v>718</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>61</v>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>135257771</v>
+      </c>
+      <c r="E67" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="5">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>718</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
+        <v>61</v>
+      </c>
+      <c r="O67" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>135262680</v>
+      </c>
+      <c r="E68" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="5">
+        <v>42</v>
+      </c>
+      <c r="J68" s="5">
+        <v>718</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>61</v>
+      </c>
+      <c r="O68" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>135262975</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="5">
+        <v>42</v>
+      </c>
+      <c r="J69" s="5">
+        <v>718</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>61</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>135263685</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>718</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1466,31 +2672,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EmissaoFielDepositario.xlsx
+++ b/Treinamento/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6C685B-A495-4949-AD9B-B870BCE29E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F24C87-C9AC-4405-80F4-CF2AB1B57957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="22">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -94,7 +94,7 @@
     <t>5/11/2025</t>
   </si>
   <si>
-    <t>31/10/2025</t>
+    <t>6/11/2025</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
@@ -582,22 +582,22 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>135207192</v>
+        <v>135227431</v>
       </c>
       <c r="E2" s="5">
         <v>601</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" s="5">
         <v>42</v>
       </c>
       <c r="J2" s="5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -613,16 +613,16 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>135207425</v>
+        <v>135227433</v>
       </c>
       <c r="E3" s="5">
         <v>601</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3" s="5">
         <v>42</v>
@@ -644,16 +644,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>135212006</v>
+        <v>135231451</v>
       </c>
       <c r="E4" s="5">
         <v>601</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>42</v>
@@ -675,16 +675,16 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>135216909</v>
+        <v>135238269</v>
       </c>
       <c r="E5" s="5">
         <v>601</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="5">
         <v>42</v>
@@ -706,16 +706,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>135208851</v>
+        <v>135239076</v>
       </c>
       <c r="E6" s="5">
         <v>601</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>135212751</v>
+        <v>135242886</v>
       </c>
       <c r="E7" s="5">
         <v>601</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I7" s="5">
         <v>42</v>
@@ -768,16 +768,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>135214800</v>
+        <v>135244606</v>
       </c>
       <c r="E8" s="5">
         <v>601</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I8" s="5">
         <v>42</v>
@@ -799,16 +799,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>135222454</v>
+        <v>135236151</v>
       </c>
       <c r="E9" s="5">
         <v>601</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I9" s="5">
         <v>42</v>
@@ -830,22 +830,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>123058958</v>
+        <v>135241324</v>
       </c>
       <c r="E10" s="5">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="5">
         <v>42</v>
       </c>
       <c r="J10" s="5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>130298854</v>
+        <v>135207849</v>
       </c>
       <c r="E11" s="5">
         <v>1211</v>
@@ -870,13 +870,13 @@
         <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
         <v>42</v>
       </c>
       <c r="J11" s="5">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>130637043</v>
+        <v>135215109</v>
       </c>
       <c r="E12" s="5">
         <v>1211</v>
@@ -901,13 +901,13 @@
         <v>19</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I12" s="5">
         <v>42</v>
       </c>
       <c r="J12" s="5">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>130691637</v>
+        <v>135224231</v>
       </c>
       <c r="E13" s="5">
         <v>1211</v>
@@ -932,13 +932,13 @@
         <v>19</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5">
         <v>42</v>
       </c>
       <c r="J13" s="5">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -954,16 +954,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>130917673</v>
+        <v>123058958</v>
       </c>
       <c r="E14" s="5">
         <v>1211</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="5">
         <v>42</v>
@@ -985,13 +985,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>131181344</v>
+        <v>130545153</v>
       </c>
       <c r="E15" s="5">
         <v>1211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>18</v>
@@ -1016,13 +1016,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>131485072</v>
+        <v>130747958</v>
       </c>
       <c r="E16" s="5">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>18</v>
@@ -1047,16 +1047,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>132104464</v>
+        <v>130927788</v>
       </c>
       <c r="E17" s="5">
         <v>1211</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="5">
         <v>42</v>
@@ -1078,16 +1078,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>132242374</v>
+        <v>131102858</v>
       </c>
       <c r="E18" s="5">
         <v>1211</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I18" s="5">
         <v>42</v>
@@ -1109,13 +1109,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>132322487</v>
+        <v>131277654</v>
       </c>
       <c r="E19" s="5">
         <v>1211</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>18</v>
@@ -1140,16 +1140,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>132620051</v>
+        <v>131541567</v>
       </c>
       <c r="E20" s="5">
         <v>1211</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I20" s="5">
         <v>42</v>
@@ -1171,16 +1171,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>132786812</v>
+        <v>131689118</v>
       </c>
       <c r="E21" s="5">
         <v>1211</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I21" s="5">
         <v>42</v>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>132859110</v>
+        <v>131785098</v>
       </c>
       <c r="E22" s="5">
         <v>1211</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>18</v>
@@ -1233,16 +1233,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>133351628</v>
+        <v>131890122</v>
       </c>
       <c r="E23" s="5">
         <v>1211</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I23" s="5">
         <v>42</v>
@@ -1264,13 +1264,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>133686201</v>
+        <v>131962172</v>
       </c>
       <c r="E24" s="5">
         <v>1211</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>18</v>
@@ -1295,13 +1295,13 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>133695981</v>
+        <v>132099832</v>
       </c>
       <c r="E25" s="5">
         <v>1211</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>18</v>
@@ -1326,16 +1326,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>133959327</v>
+        <v>132425551</v>
       </c>
       <c r="E26" s="5">
         <v>1211</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I26" s="5">
         <v>42</v>
@@ -1357,13 +1357,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>133966020</v>
+        <v>132484220</v>
       </c>
       <c r="E27" s="5">
         <v>1211</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>18</v>
@@ -1388,16 +1388,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>134010928</v>
+        <v>132890930</v>
       </c>
       <c r="E28" s="5">
         <v>1211</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I28" s="5">
         <v>42</v>
@@ -1419,13 +1419,13 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>134107654</v>
+        <v>132920213</v>
       </c>
       <c r="E29" s="5">
         <v>1211</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>18</v>
@@ -1450,13 +1450,13 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>134224614</v>
+        <v>133091083</v>
       </c>
       <c r="E30" s="5">
         <v>1211</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>18</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>134437598</v>
+        <v>133142799</v>
       </c>
       <c r="E31" s="5">
         <v>1211</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>18</v>
@@ -1512,16 +1512,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>134722457</v>
+        <v>133247561</v>
       </c>
       <c r="E32" s="5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I32" s="5">
         <v>42</v>
@@ -1543,16 +1543,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>134908836</v>
+        <v>133373628</v>
       </c>
       <c r="E33" s="5">
         <v>1211</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I33" s="5">
         <v>42</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>135192496</v>
+        <v>133388898</v>
       </c>
       <c r="E34" s="5">
         <v>1211</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I34" s="5">
         <v>42</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>130298854</v>
+        <v>133397205</v>
       </c>
       <c r="E35" s="5">
         <v>1211</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>20</v>
@@ -1636,13 +1636,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>130637043</v>
+        <v>133532336</v>
       </c>
       <c r="E36" s="5">
         <v>1211</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>18</v>
@@ -1665,13 +1665,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>130917673</v>
+        <v>133565590</v>
       </c>
       <c r="E37" s="5">
         <v>1211</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>18</v>
@@ -1694,13 +1694,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>131181344</v>
+        <v>133947663</v>
       </c>
       <c r="E38" s="5">
         <v>1211</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>18</v>
@@ -1723,16 +1723,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>132242374</v>
+        <v>133962813</v>
       </c>
       <c r="E39" s="5">
         <v>1211</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I39" s="5">
         <v>42</v>
@@ -1752,13 +1752,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>132322487</v>
+        <v>134114490</v>
       </c>
       <c r="E40" s="5">
         <v>1211</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>18</v>
@@ -1781,16 +1781,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>132786812</v>
+        <v>134151915</v>
       </c>
       <c r="E41" s="5">
         <v>1211</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I41" s="5">
         <v>42</v>
@@ -1810,13 +1810,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>132859110</v>
+        <v>134662867</v>
       </c>
       <c r="E42" s="5">
         <v>1211</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>18</v>
@@ -1839,13 +1839,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>133686201</v>
+        <v>134668798</v>
       </c>
       <c r="E43" s="5">
         <v>1211</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>18</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>133966020</v>
+        <v>134720112</v>
       </c>
       <c r="E44" s="5">
         <v>1211</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>18</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>134010928</v>
+        <v>134929266</v>
       </c>
       <c r="E45" s="5">
         <v>1211</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I45" s="5">
         <v>42</v>
@@ -1926,13 +1926,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>134107654</v>
+        <v>135025325</v>
       </c>
       <c r="E46" s="5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>18</v>
@@ -1955,16 +1955,16 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>135192496</v>
+        <v>135037383</v>
       </c>
       <c r="E47" s="5">
         <v>1211</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I47" s="5">
         <v>42</v>
@@ -1984,22 +1984,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>135193982</v>
+        <v>135053062</v>
       </c>
       <c r="E48" s="5">
         <v>1211</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I48" s="5">
         <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -2013,22 +2013,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>135248139</v>
+        <v>135062069</v>
       </c>
       <c r="E49" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I49" s="5">
         <v>42</v>
       </c>
       <c r="J49" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -2042,22 +2042,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>135249587</v>
+        <v>135211843</v>
       </c>
       <c r="E50" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I50" s="5">
         <v>42</v>
       </c>
       <c r="J50" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>135249661</v>
+        <v>135222029</v>
       </c>
       <c r="E51" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I51" s="5">
         <v>42</v>
       </c>
       <c r="J51" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -2100,22 +2100,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>135249921</v>
+        <v>135222870</v>
       </c>
       <c r="E52" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I52" s="5">
         <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -2129,22 +2129,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>135250911</v>
+        <v>135238653</v>
       </c>
       <c r="E53" s="5">
         <v>2013</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I53" s="5">
         <v>42</v>
       </c>
       <c r="J53" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -2158,22 +2158,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>135251121</v>
+        <v>130545153</v>
       </c>
       <c r="E54" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I54" s="5">
         <v>42</v>
       </c>
       <c r="J54" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>135252177</v>
+        <v>130927788</v>
       </c>
       <c r="E55" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I55" s="5">
         <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -2216,22 +2216,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>135252379</v>
+        <v>131277654</v>
       </c>
       <c r="E56" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I56" s="5">
         <v>42</v>
       </c>
       <c r="J56" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>135252492</v>
+        <v>131541567</v>
       </c>
       <c r="E57" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I57" s="5">
         <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -2274,22 +2274,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>135252704</v>
+        <v>131785098</v>
       </c>
       <c r="E58" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I58" s="5">
         <v>42</v>
       </c>
       <c r="J58" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -2303,22 +2303,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>135253514</v>
+        <v>132484220</v>
       </c>
       <c r="E59" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I59" s="5">
         <v>42</v>
       </c>
       <c r="J59" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -2332,22 +2332,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>135253903</v>
+        <v>132920213</v>
       </c>
       <c r="E60" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I60" s="5">
         <v>42</v>
       </c>
       <c r="J60" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K60" s="5">
         <v>0</v>
@@ -2361,22 +2361,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>135254878</v>
+        <v>133142799</v>
       </c>
       <c r="E61" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I61" s="5">
         <v>42</v>
       </c>
       <c r="J61" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K61" s="5">
         <v>0</v>
@@ -2390,13 +2390,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>135254909</v>
+        <v>133373628</v>
       </c>
       <c r="E62" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>20</v>
@@ -2405,7 +2405,7 @@
         <v>42</v>
       </c>
       <c r="J62" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K62" s="5">
         <v>0</v>
@@ -2419,13 +2419,13 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>135256340</v>
+        <v>133397205</v>
       </c>
       <c r="E63" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>20</v>
@@ -2434,7 +2434,7 @@
         <v>42</v>
       </c>
       <c r="J63" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K63" s="5">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>135257386</v>
+        <v>133532336</v>
       </c>
       <c r="E64" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I64" s="5">
         <v>42</v>
       </c>
       <c r="J64" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K64" s="5">
         <v>0</v>
@@ -2477,22 +2477,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>135257529</v>
+        <v>133947663</v>
       </c>
       <c r="E65" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I65" s="5">
         <v>42</v>
       </c>
       <c r="J65" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K65" s="5">
         <v>0</v>
@@ -2506,22 +2506,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>135257759</v>
+        <v>133962813</v>
       </c>
       <c r="E66" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I66" s="5">
         <v>42</v>
       </c>
       <c r="J66" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -2535,22 +2535,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>135257771</v>
+        <v>134114490</v>
       </c>
       <c r="E67" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I67" s="5">
         <v>42</v>
       </c>
       <c r="J67" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K67" s="5">
         <v>0</v>
@@ -2564,22 +2564,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>135262680</v>
+        <v>134929266</v>
       </c>
       <c r="E68" s="5">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I68" s="5">
         <v>42</v>
       </c>
       <c r="J68" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K68" s="5">
         <v>0</v>
@@ -2593,22 +2593,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>135262975</v>
+        <v>135025325</v>
       </c>
       <c r="E69" s="5">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I69" s="5">
         <v>42</v>
       </c>
       <c r="J69" s="5">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
@@ -2622,30 +2622,610 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>135263685</v>
+        <v>135211843</v>
       </c>
       <c r="E70" s="5">
+        <v>1212</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" s="5">
+        <v>42</v>
+      </c>
+      <c r="J70" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>61</v>
+      </c>
+      <c r="O70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>135222870</v>
+      </c>
+      <c r="E71" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="5">
+        <v>42</v>
+      </c>
+      <c r="J71" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5">
+        <v>61</v>
+      </c>
+      <c r="O71" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>135238653</v>
+      </c>
+      <c r="E72" s="5">
         <v>2013</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F72" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="5">
+        <v>42</v>
+      </c>
+      <c r="J72" s="5">
+        <v>8001</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61</v>
+      </c>
+      <c r="O72" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>135232468</v>
+      </c>
+      <c r="E73" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I70" s="5">
-        <v>42</v>
-      </c>
-      <c r="J70" s="5">
+      <c r="I73" s="5">
+        <v>42</v>
+      </c>
+      <c r="J73" s="5">
+        <v>715</v>
+      </c>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <v>61</v>
+      </c>
+      <c r="O73" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>135244785</v>
+      </c>
+      <c r="E74" s="5">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="5">
+        <v>42</v>
+      </c>
+      <c r="J74" s="5">
+        <v>715</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5">
+        <v>61</v>
+      </c>
+      <c r="O74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>135268413</v>
+      </c>
+      <c r="E75" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="5">
+        <v>42</v>
+      </c>
+      <c r="J75" s="5">
         <v>718</v>
       </c>
-      <c r="K70" s="5">
-        <v>0</v>
-      </c>
-      <c r="L70" s="5">
-        <v>61</v>
-      </c>
-      <c r="O70" s="5" t="s">
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5">
+        <v>61</v>
+      </c>
+      <c r="O75" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>135268495</v>
+      </c>
+      <c r="E76" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="5">
+        <v>42</v>
+      </c>
+      <c r="J76" s="5">
+        <v>718</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5">
+        <v>61</v>
+      </c>
+      <c r="O76" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>135268734</v>
+      </c>
+      <c r="E77" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="5">
+        <v>42</v>
+      </c>
+      <c r="J77" s="5">
+        <v>718</v>
+      </c>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5">
+        <v>61</v>
+      </c>
+      <c r="O77" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>135270108</v>
+      </c>
+      <c r="E78" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="5">
+        <v>42</v>
+      </c>
+      <c r="J78" s="5">
+        <v>718</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5">
+        <v>61</v>
+      </c>
+      <c r="O78" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>135272373</v>
+      </c>
+      <c r="E79" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="5">
+        <v>42</v>
+      </c>
+      <c r="J79" s="5">
+        <v>718</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5">
+        <v>61</v>
+      </c>
+      <c r="O79" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>135273499</v>
+      </c>
+      <c r="E80" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="5">
+        <v>42</v>
+      </c>
+      <c r="J80" s="5">
+        <v>718</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>61</v>
+      </c>
+      <c r="O80" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>135274007</v>
+      </c>
+      <c r="E81" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81" s="5">
+        <v>42</v>
+      </c>
+      <c r="J81" s="5">
+        <v>718</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>61</v>
+      </c>
+      <c r="O81" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>135275358</v>
+      </c>
+      <c r="E82" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I82" s="5">
+        <v>42</v>
+      </c>
+      <c r="J82" s="5">
+        <v>718</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5">
+        <v>61</v>
+      </c>
+      <c r="O82" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>135277257</v>
+      </c>
+      <c r="E83" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" s="5">
+        <v>42</v>
+      </c>
+      <c r="J83" s="5">
+        <v>718</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5">
+        <v>61</v>
+      </c>
+      <c r="O83" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>135277974</v>
+      </c>
+      <c r="E84" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84" s="5">
+        <v>42</v>
+      </c>
+      <c r="J84" s="5">
+        <v>718</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5">
+        <v>61</v>
+      </c>
+      <c r="O84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>135279125</v>
+      </c>
+      <c r="E85" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="5">
+        <v>42</v>
+      </c>
+      <c r="J85" s="5">
+        <v>718</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5">
+        <v>61</v>
+      </c>
+      <c r="O85" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>135279227</v>
+      </c>
+      <c r="E86" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="5">
+        <v>42</v>
+      </c>
+      <c r="J86" s="5">
+        <v>718</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5">
+        <v>61</v>
+      </c>
+      <c r="O86" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>135282510</v>
+      </c>
+      <c r="E87" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" s="5">
+        <v>42</v>
+      </c>
+      <c r="J87" s="5">
+        <v>718</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5">
+        <v>61</v>
+      </c>
+      <c r="O87" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>135285033</v>
+      </c>
+      <c r="E88" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="5">
+        <v>42</v>
+      </c>
+      <c r="J88" s="5">
+        <v>718</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5">
+        <v>61</v>
+      </c>
+      <c r="O88" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>135285169</v>
+      </c>
+      <c r="E89" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="5">
+        <v>42</v>
+      